--- a/content/generated/script.generated.xlsx
+++ b/content/generated/script.generated.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-03 00:05:24</t>
+          <t>2026-04-03 00:45:55</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>assets/portraits/judge.png</t>
+          <t>assets/portraits/judge.jpeg</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>assets/portraits/prosecutor.png</t>
+          <t>assets/portraits/prosecutor.jpeg</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>assets/portraits/judge.png</t>
+          <t>assets/portraits/judge.jpeg</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>assets/portraits/prosecutor.png</t>
+          <t>assets/portraits/prosecutor.jpeg</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>assets/portraits/judge.png</t>
+          <t>assets/portraits/judge.jpeg</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>assets/portraits/lawyer.png</t>
+          <t>assets/portraits/lawyer.jpeg</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>assets/portraits/judge.png</t>
+          <t>assets/portraits/judge.jpeg</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>assets/portraits/judge.png</t>
+          <t>assets/portraits/judge.jpeg</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>assets/portraits/manager.png</t>
+          <t>assets/portraits/manager.jpeg</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>assets/portraits/manager.png</t>
+          <t>assets/portraits/manager.jpeg</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>assets/portraits/waitress_generic.png</t>
+          <t>assets/portraits/waitress_generic.jpeg</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>assets/portraits/policeman.png</t>
+          <t>assets/portraits/policeman.jpeg</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>assets/portraits/elder_slum.png</t>
+          <t>assets/portraits/elder_slum.jpeg</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>assets/portraits/elder_slum.png</t>
+          <t>assets/portraits/elder_slum.jpeg</t>
         </is>
       </c>
     </row>
@@ -7199,7 +7199,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>assets/portraits/elder_slum.png</t>
+          <t>assets/portraits/elder_slum.jpeg</t>
         </is>
       </c>
     </row>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>assets/portraits/elder_slum.png</t>
+          <t>assets/portraits/elder_slum.jpeg</t>
         </is>
       </c>
     </row>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>assets/portraits/elder_slum.png</t>
+          <t>assets/portraits/elder_slum.jpeg</t>
         </is>
       </c>
     </row>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>assets/portraits/songgeum.png</t>
+          <t>assets/portraits/songgeum.jpeg</t>
         </is>
       </c>
     </row>

--- a/content/generated/script.generated.xlsx
+++ b/content/generated/script.generated.xlsx
@@ -16,6 +16,8 @@
     <sheet name="EvidenceTable" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="CharacterTable" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="CharacterEmotionTable" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="QuestionTable" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="StateDescriptorTable" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-03 13:43:56</t>
+          <t>2026-04-05 22:28:10</t>
         </is>
       </c>
     </row>
@@ -480,7 +482,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SceneTable, DialogTable, ChoiceTable, BranchTable, EvidenceTable, CharacterTable, CharacterEmotionTable</t>
+          <t>SceneTable, DialogTable, ChoiceTable, BranchTable, EvidenceTable, CharacterTable, CharacterEmotionTable, QuestionTable, StateDescriptorTable</t>
         </is>
       </c>
     </row>
@@ -492,6 +494,516 @@
       </c>
       <c r="B6" t="n">
         <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>QuestionID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SortOrder</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>VisibleRuleID</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>StateRuleID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>QIpangyuCall</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>이판규는 누구에게 불려갔는가</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>광기처럼 보이는 말들이 실제로는 사건의 중심을 향한 반응일 수 있다.</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Witness</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>QR_IpangyuSeen</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>QS_IpangyuCall</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QSonggeumMissing</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>송금은 왜 사라졌는가</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>송금이 자발적으로 사라진 것인지, 의식의 일부로 지워진 것인지가 핵심이다.</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>QR_SonggeumOpen</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>QS_SonggeumMissing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QRitualLead</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>낙원의 의식은 누가 주도했는가</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>무녀, 악보, 기록, 기사 사이를 연결해 의식의 실제 주체를 좁혀야 한다.</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ritual</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>QR_RitualOpen</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>QS_RitualLead</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DescriptorID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TargetFlagID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>MinValue</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>MaxValue</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SD_Investigation_0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>InvestigationProgress</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>초기</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>아직 증언과 단서가 충분히 엮이지 않은 상태입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SD_Investigation_1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>InvestigationProgress</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>사건의 외곽선을 따라가며 주요 흔적을 모으는 단계입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SD_Investigation_2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>InvestigationProgress</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>접근</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>단서가 서로 이어지기 시작했고 질문의 결이 또렷해졌습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD_Investigation_4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>InvestigationProgress</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>99</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>심층</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>표면을 지나 사건의 구조와 의식을 함께 추적하는 단계입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD_Resonance_0</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>안정</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>아직은 현실 감각이 우세한 상태입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SD_Resonance_1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>전조</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>조사 과정 곳곳에서 공명의 낌새가 드러납니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SD_Resonance_2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>심화</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>위험을 감수한 만큼 비현실의 결이 짙어졌습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SD_Resonance_3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>99</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>침식</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>현실과 공명의 경계가 크게 흔들리고 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SD_Trust_0</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SongsoonTrust</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>섣부른 추궁은 관계를 닫아버릴 가능성이 큽니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SD_Trust_1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SongsoonTrust</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>동행</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>경계는 남아 있지만 함께 움직일 정도의 틈은 생겼습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SD_Trust_2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SongsoonTrust</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>99</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>신뢰</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>송순이 등을 돌리지 않고 같은 방향을 보고 있습니다.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -505,7 +1017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,6 +1100,26 @@
       </c>
       <c r="B8" t="n">
         <v>29</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QuestionTable</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>StateDescriptorTable</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -601,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -640,6 +1172,16 @@
           <t>Effect</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>GoalKicker</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>GoalText</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -785,6 +1327,16 @@
           <t>ch2_well</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>조사 목표</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>카페 낙원에서 먼저 붙잡을 단서를 가려내고, 송순이 숨기는 결을 읽어낸다.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1029,6 +1581,16 @@
           <t>ch4a_library</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>조사 목표</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>사라진 언니의 방에서 무엇이 지워졌고 무엇이 남았는지, 제한된 기회 안에 가려낸다.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2122,6 +2684,16 @@
       </c>
       <c r="G50" t="n">
         <v>4</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>결단 목표</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>이 방에서 무엇을 사람으로 남길지 결정한다. 망설일 시간은 길지 않다.</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -18900,7 +19472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18932,6 +19504,21 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>Image</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>CategoryID</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>CategoryTitle</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>CategoryHint</t>
         </is>
       </c>
     </row>
@@ -19181,7 +19768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19205,6 +19792,21 @@
           <t>DefaultImagePath</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>RoleText</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>NotebookSummary1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>NotebookSummary2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19244,6 +19846,21 @@
           <t>assets/portraits/editor.jpeg</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>기록의 문지기</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>무엇이 기사로 남고 무엇이 묻히는지 결정하는 편집장.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>바깥에 흔적을 남길지 말지의 축과 연결된다.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19288,6 +19905,21 @@
           <t>assets/portraits/haesim.jpeg</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>의식의 중심</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>공명과 의식의 중심축에 선 인물.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>신념인지 광기인지 분간하기 어려운 확신을 가진다.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19310,6 +19942,21 @@
           <t>assets/portraits/pan_crazy.png</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>문턱의 죄수</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>광기와 교리 사이를 오가며 사건의 단어를 흘리는 인물.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>헛소리처럼 들리지만 사건의 방향을 먼저 암시한다.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19398,6 +20045,21 @@
           <t>assets/portraits/kum_fixed.png</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>생존자</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>낙원에서 벌어진 일을 견디고 살아남은 여급.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>압박보다 보호에 가까운 태도에서 더 많은 진실이 새어 나온다.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -19464,6 +20126,21 @@
           <t>assets/portraits/songgeum.jpeg</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>실종자</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>사건의 핵심에서 사라진 여급.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>사람들이 입을 다무는 이유가 이 인물과 맞물려 있다.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -19486,6 +20163,21 @@
           <t>assets/portraits/songsoon.jpeg</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>증언자</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>낙원 안쪽 사정을 알고 있지만 쉽게 입을 열지 않는다.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>신뢰를 얻을수록 더 깊은 증언에 접근할 수 있다.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -19528,6 +20220,21 @@
       <c r="D16" t="inlineStr">
         <is>
           <t>assets/portraits/yuu.jpeg</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>기록자</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>법정에서 시작된 실종 사건을 끝까지 물고 늘어지는 기자.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>기록과 은폐의 경계에서 사건을 붙들고 있다.</t>
         </is>
       </c>
     </row>

--- a/content/generated/script.generated.xlsx
+++ b/content/generated/script.generated.xlsx
@@ -18,6 +18,7 @@
     <sheet name="CharacterEmotionTable" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="QuestionTable" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="StateDescriptorTable" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="RuleTable" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,7 +447,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-05 22:28:10</t>
+          <t>2026-04-05 22:55:10</t>
         </is>
       </c>
     </row>
@@ -482,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SceneTable, DialogTable, ChoiceTable, BranchTable, EvidenceTable, CharacterTable, CharacterEmotionTable, QuestionTable, StateDescriptorTable</t>
+          <t>SceneTable, DialogTable, ChoiceTable, BranchTable, EvidenceTable, CharacterTable, CharacterEmotionTable, QuestionTable, StateDescriptorTable, RuleTable</t>
         </is>
       </c>
     </row>
@@ -1011,13 +1012,507 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>RuleRowID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>RuleID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>RuleKind</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FactType</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>FactKey</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ResultValue</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RR_QIpangyuSeen_01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>QR_IpangyuSeen</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Visible</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>RevealedCharacter</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Ipangyu</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Equals</t>
+        </is>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RR_QRitualOpen_01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>QR_RitualOpen</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Visible</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FlagValue</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ReadRitualScore</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gte</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RR_QRitualOpen_02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>QR_RitualOpen</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Visible</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>RevealedCharacter</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Haesim</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Equals</t>
+        </is>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RR_QRitualOpen_03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>QR_RitualOpen</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Visible</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SceneProgressIndex</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gte</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>31</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RR_QSonggeumOpen_01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>QR_SonggeumOpen</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Visible</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HasEvidence</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>EvDiary</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Equals</t>
+        </is>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RR_QSonggeumOpen_02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>QR_SonggeumOpen</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Visible</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HasEvidence</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>EvOldArticles</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Equals</t>
+        </is>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RR_QSonggeumOpen_03</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>QR_SonggeumOpen</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Visible</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SceneProgressIndex</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gte</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>24</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RR_QSonggeumOpen_04</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>QR_SonggeumOpen</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Visible</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RevealedCharacter</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Songgeum</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Equals</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RR_QIpangyuState_01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>QS_IpangyuCall</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FlagValue</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gte</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>공명 전조 확인</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RR_QRitualState_01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>QS_RitualLead</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FlagValue</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ReadRitualScore</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gte</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>의식 구조 접근</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RR_QSonggeumState_01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>QS_SonggeumMissing</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HasEvidence</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>EvDiary</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Equals</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>단서 확보</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1119,6 +1614,16 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RuleTable</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>11</v>
       </c>
     </row>
@@ -19551,6 +20056,21 @@
           <t>assets/ev/bluecloth.jpeg</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>trace</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>현장 물증</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>현장에서 직접 붙잡은 흔적</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19581,6 +20101,21 @@
           <t>assets/items/note.png</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>기록과 기사</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>남겨진 문장과 호출의 흔적</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19611,6 +20146,21 @@
           <t>assets/items/hanbok.png</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ritual</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>의례와 공명</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>문, 무녀, 감응과 연결된 흔적</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19641,6 +20191,21 @@
           <t>assets/items/diary.png</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>기록과 기사</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>지워졌거나 남겨진 문장들</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19671,6 +20236,21 @@
           <t>assets/items/mask.png</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ritual</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>의례와 공명</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>문, 무녀, 감응과 연결된 흔적</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19701,6 +20281,21 @@
           <t>assets/items/scores.png</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ritual</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>의례와 공명</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>문, 무녀, 감응과 연결된 흔적</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19731,6 +20326,21 @@
           <t>assets/items/records.png</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>기록과 기사</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>지워졌거나 남겨진 문장들</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19754,6 +20364,21 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>'그릇은 셋. 둘은 쓰였고 하나가 남았다.' 마지막 무녀가 아직 남아 있다는 증거.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ritual</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>의례와 공명</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>문, 무녀, 감응과 연결된 흔적</t>
         </is>
       </c>
     </row>
@@ -19824,6 +20449,21 @@
           <t>Neutral</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>문턱의 인도자</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>의식이 가장 깊어지는 지점에서 모습을 드러내는 인물.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>사람을 데려가는 쪽인지, 이미 건너간 쪽인지 끝내 분간하기 어렵다.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/content/generated/script.generated.xlsx
+++ b/content/generated/script.generated.xlsx
@@ -447,7 +447,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-05 22:55:10</t>
+          <t>2026-04-06 00:13:27</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,6 +547,61 @@
           <t>StateRuleID</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>RelatedEvidenceIDs</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>SolutionEvidenceID</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>SolutionEvidenceIDs</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>SolutionMode</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SolvedFlagID</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ResolvedDetail</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>SuccessToast</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>FailureToast</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>RewardFlagID</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>RewardValue</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>RewardMode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -582,6 +637,50 @@
           <t>QS_IpangyuCall</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>EvNote, EvBlueCloth, EvRitualNote</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>EvNote</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>QuestionSolved_QIpangyuCall</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>붉은 쪽지는 이판규가 우연히 뛰쳐나간 것이 아니라, 낙원 쪽의 호출에 떠밀려 움직였다는 직접적인 흔적이다. 그의 광기는 불려간 자의 잔향에 가깝다.</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>질문 정리: 이판규를 부른 흔적을 붙들었다.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>아직은 호출의 근거를 바로 묶기 어렵다.</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>InvestigationScore</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -617,6 +716,50 @@
           <t>QS_SonggeumMissing</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>EvDiary, EvBlueHanbok, EvOldArticles</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>EvDiary</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>QuestionSolved_QSonggeumMissing</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>숨겨진 일기장은 송금의 실종이 단순 도피가 아니라, 의례 속 역할로 밀려 들어간 소거였음을 보여준다. 사라짐은 계획된 순서의 일부다.</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>질문 정리: 송금의 실종이 의례와 이어진다는 근거를 확보했다.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>이 단서만으로는 송금의 실종 이유를 단정하기 어렵다.</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ReadRitualScore</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -650,6 +793,59 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>QS_RitualLead</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>EvRitualScore, EvOldArticles, EvRitualNote, EvMask</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>EvRitualNote</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>EvRitualScore, EvRitualNote</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>QuestionSolved_QRitualLead</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>의례실 종이는 낙원의 의식이 우발적 소문이 아니라, 그릇과 순서를 세어가며 밀어붙인 구조적 의례였음을 드러낸다. 누군가 끝까지 판을 쥐고 있었다.</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>질문 정리: 낙원의 의식이 계획된 구조였다는 근거를 붙들었다.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>악보와 의례실 기록이 함께 이어져야 의식의 구조를 단정할 수 있다.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Add</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1375,7 +1571,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RR_QIpangyuState_01</t>
+          <t>RR_QIpangyuState_00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1395,35 +1591,35 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ResonanceLevel</t>
+          <t>QuestionSolved_QIpangyuCall</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gte</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
+          <t>Equals</t>
+        </is>
+      </c>
+      <c r="G10" t="b">
         <v>1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>공명 전조 확인</t>
+          <t>해결됨</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RR_QRitualState_01</t>
+          <t>RR_QIpangyuState_01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>QS_RitualLead</t>
+          <t>QS_IpangyuCall</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1438,7 +1634,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ReadRitualScore</t>
+          <t>ResonanceLevel</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1451,7 +1647,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>의식 구조 접근</t>
+          <t>공명 전조 확인</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1461,12 +1657,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RR_QSonggeumState_01</t>
+          <t>RR_QRitualState_00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>QS_SonggeumMissing</t>
+          <t>QS_RitualLead</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1476,12 +1672,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HasEvidence</t>
+          <t>FlagValue</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>EvDiary</t>
+          <t>QuestionSolved_QRitualLead</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1494,10 +1690,139 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>해결됨</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RR_QRitualState_01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>QS_RitualLead</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FlagValue</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ReadRitualScore</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gte</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>의식 구조 접근</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RR_QSonggeumState_00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>QS_SonggeumMissing</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FlagValue</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>QuestionSolved_QSonggeumMissing</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Equals</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>해결됨</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RR_QSonggeumState_01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>QS_SonggeumMissing</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HasEvidence</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>EvDiary</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Equals</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>단서 확보</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I15" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1624,7 +1949,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/content/generated/script.generated.xlsx
+++ b/content/generated/script.generated.xlsx
@@ -447,7 +447,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-06 00:13:27</t>
+          <t>2026-04-06 00:51:48</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,50 +554,45 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>SolutionEvidenceID</t>
+          <t>SolutionEvidenceIDs</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>SolutionEvidenceIDs</t>
+          <t>SolutionMode</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>SolutionMode</t>
+          <t>SolvedFlagID</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>SolvedFlagID</t>
+          <t>ResolvedDetail</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>ResolvedDetail</t>
+          <t>SuccessToast</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>SuccessToast</t>
+          <t>FailureToast</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>FailureToast</t>
+          <t>RewardFlagID</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>RewardFlagID</t>
+          <t>RewardValue</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
-        <is>
-          <t>RewardValue</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
         <is>
           <t>RewardMode</t>
         </is>
@@ -647,36 +642,35 @@
           <t>EvNote</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>QuestionSolved_QIpangyuCall</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>QuestionSolved_QIpangyuCall</t>
+          <t>붉은 쪽지는 이판규가 우연히 뛰쳐나간 것이 아니라, 낙원 쪽의 호출에 떠밀려 움직였다는 직접적인 흔적이다. 그의 광기는 불려간 자의 잔향에 가깝다.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>붉은 쪽지는 이판규가 우연히 뛰쳐나간 것이 아니라, 낙원 쪽의 호출에 떠밀려 움직였다는 직접적인 흔적이다. 그의 광기는 불려간 자의 잔향에 가깝다.</t>
+          <t>질문 정리: 이판규를 부른 흔적을 붙들었다.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>질문 정리: 이판규를 부른 흔적을 붙들었다.</t>
+          <t>아직은 호출의 근거를 바로 묶기 어렵다.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>아직은 호출의 근거를 바로 묶기 어렵다.</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
           <t>InvestigationScore</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Add</t>
         </is>
@@ -726,36 +720,35 @@
           <t>EvDiary</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>QuestionSolved_QSonggeumMissing</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>QuestionSolved_QSonggeumMissing</t>
+          <t>숨겨진 일기장은 송금의 실종이 단순 도피가 아니라, 의례 속 역할로 밀려 들어간 소거였음을 보여준다. 사라짐은 계획된 순서의 일부다.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>숨겨진 일기장은 송금의 실종이 단순 도피가 아니라, 의례 속 역할로 밀려 들어간 소거였음을 보여준다. 사라짐은 계획된 순서의 일부다.</t>
+          <t>질문 정리: 송금의 실종이 의례와 이어진다는 근거를 확보했다.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>질문 정리: 송금의 실종이 의례와 이어진다는 근거를 확보했다.</t>
+          <t>이 단서만으로는 송금의 실종 이유를 단정하기 어렵다.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>이 단서만으로는 송금의 실종 이유를 단정하기 어렵다.</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
           <t>ReadRitualScore</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="P3" t="n">
         <v>1</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Add</t>
         </is>
@@ -802,48 +795,43 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>EvRitualNote</t>
+          <t>EvRitualScore, EvRitualNote</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>EvRitualScore, EvRitualNote</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>QuestionSolved_QRitualLead</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>QuestionSolved_QRitualLead</t>
+          <t>의례실 종이는 낙원의 의식이 우발적 소문이 아니라, 그릇과 순서를 세어가며 밀어붙인 구조적 의례였음을 드러낸다. 누군가 끝까지 판을 쥐고 있었다.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>의례실 종이는 낙원의 의식이 우발적 소문이 아니라, 그릇과 순서를 세어가며 밀어붙인 구조적 의례였음을 드러낸다. 누군가 끝까지 판을 쥐고 있었다.</t>
+          <t>질문 정리: 낙원의 의식이 계획된 구조였다는 근거를 붙들었다.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>질문 정리: 낙원의 의식이 계획된 구조였다는 근거를 붙들었다.</t>
+          <t>악보와 의례실 기록이 함께 이어져야 의식의 구조를 단정할 수 있다.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>악보와 의례실 기록이 함께 이어져야 의식의 구조를 단정할 수 있다.</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
           <t>ResonanceLevel</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="P4" t="n">
         <v>1</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Add</t>
         </is>
@@ -1869,7 +1857,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>351</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4">
@@ -1889,7 +1877,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -3567,7 +3555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q352"/>
+  <dimension ref="A1:Q360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16608,21 +16596,60 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>ch6_ending_b</t>
+          <t>ch6_ending_a</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>1</v>
-      </c>
-      <c r="C288" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>유웅룡이 이해심을 향해 달려든다. 짧은 충돌. 이해심이 쓰러지고 의식의 결이 끊긴다. 사람 몸으로 겨우 멈춘 의식은 끝내 아름답지도 장엄하지도 않다. 그저 비싼 대가를 치른 범죄 현장처럼 남는다.</t>
+          <t>그래도 이제는 압니다. 누가 사람을 불러냈고, 누구를 순서 안에 밀어 넣었는지. 이름을 되찾지 못해도, 책임의 결만큼은 흐리지 않겠습니다.</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>thought</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>SolvedQuestionCount</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>[2, 3]</t>
         </is>
       </c>
     </row>
@@ -16633,12 +16660,12 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C289" t="inlineStr"/>
       <c r="L289" t="inlineStr">
         <is>
-          <t>문이 닫힌다. 노래가 멎는다. 송금은 그 자리에 쓰러진다. 숨은 붙어 있다. 하지만 눈을 뜨지 않는다.</t>
+          <t>유웅룡이 이해심을 향해 달려든다. 짧은 충돌. 이해심이 쓰러지고 의식의 결이 끊긴다. 사람 몸으로 겨우 멈춘 의식은 끝내 아름답지도 장엄하지도 않다. 그저 비싼 대가를 치른 범죄 현장처럼 남는다.</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -16654,46 +16681,17 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>3</v>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>유웅룡</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>Tense</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C290" t="inlineStr"/>
       <c r="L290" t="inlineStr">
         <is>
-          <t>(수첩을 꺼낸다. 처음으로 모든 것을 적는다. 이판규, 폐공장, 낙원, 이해심, 청의동자, 그리고 두 사람의 이름. 이번엔 사건보다 이름을 먼저 쓴다.)</t>
+          <t>문이 닫힌다. 노래가 멎는다. 송금은 그 자리에 쓰러진다. 숨은 붙어 있다. 하지만 눈을 뜨지 않는다.</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>thought</t>
-        </is>
-      </c>
-      <c r="N290" t="inlineStr">
-        <is>
-          <t>assets/portraits/yuu.jpeg</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -16704,7 +16702,7 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -16733,7 +16731,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>세상이 안 믿어도 상관없습니다. 적어 두면 적어도 없던 일로는 못 넘깁니다. 이번엔 그 정도라도 해야겠습니다.</t>
+          <t>(수첩을 꺼낸다. 처음으로 모든 것을 적는다. 이판규, 폐공장, 낙원, 이해심, 청의동자, 그리고 두 사람의 이름. 이번엔 사건보다 이름을 먼저 쓴다.)</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -16754,26 +16752,26 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>송순</t>
+          <t>유웅룡</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>Yuu</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Uneasy</t>
+          <t>Tense</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -16783,17 +16781,17 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>기록해줘요. 언니 이름도, 여기서 사라진 사람들 이름도. 누가 지워도 한 번은 남았다고 말할 수 있게.</t>
+          <t>세상이 안 믿어도 상관없습니다. 적어 두면 적어도 없던 일로는 못 넘깁니다. 이번엔 그 정도라도 해야겠습니다.</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>thought</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>assets/portraits/songsoon.jpeg</t>
+          <t>assets/portraits/yuu.jpeg</t>
         </is>
       </c>
     </row>
@@ -16804,26 +16802,26 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>유웅룡</t>
+          <t>송순</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Tense</t>
+          <t>Uneasy</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -16833,27 +16831,17 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>이번엔 사건부터 쓰지 않겠습니다. 이름부터 적고, 누가 그 이름을 지웠는지까지 붙여 둘 겁니다. 그 정도는, 기자란 작자도 해야지요.</t>
+          <t>기록해줘요. 언니 이름도, 여기서 사라진 사람들 이름도. 누가 지워도 한 번은 남았다고 말할 수 있게.</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>assets/portraits/yuu.jpeg</t>
-        </is>
-      </c>
-      <c r="O293" t="inlineStr">
-        <is>
-          <t>ReadRitualScore</t>
-        </is>
-      </c>
-      <c r="P293" t="inlineStr">
-        <is>
-          <t>true</t>
+          <t>assets/portraits/songsoon.jpeg</t>
         </is>
       </c>
     </row>
@@ -16864,7 +16852,7 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -16893,7 +16881,7 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>본 사람도 조금은 문턱에 걸친 채 돌아옵니다. 그러니 더 서둘러 적어야지요. 내 안에서조차 희미해지기 전에.</t>
+          <t>이번엔 사건부터 쓰지 않겠습니다. 이름부터 적고, 누가 그 이름을 지웠는지까지 붙여 둘 겁니다. 그 정도는, 기자란 작자도 해야지요.</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -16908,11 +16896,13 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>ResonanceLevel</t>
-        </is>
-      </c>
-      <c r="P294" t="n">
-        <v>2</v>
+          <t>ReadRitualScore</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="295">
@@ -16922,26 +16912,26 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>송순</t>
+          <t>유웅룡</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>Yuu</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Uneasy</t>
+          <t>Tense</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -16951,69 +16941,145 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>그 수첩엔 언니 이름을 제일 먼저 적어줘요. 그 다음이 누구든, 언니가 맨 앞에 와야 해요.</t>
+          <t>본 사람도 조금은 문턱에 걸친 채 돌아옵니다. 그러니 더 서둘러 적어야지요. 내 안에서조차 희미해지기 전에.</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>thought</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>assets/portraits/songsoon.jpeg</t>
+          <t>assets/portraits/yuu.jpeg</t>
         </is>
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>TrustedSongsoon</t>
-        </is>
-      </c>
-      <c r="P295" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="P295" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>ch6_ending_c</t>
+          <t>ch6_ending_b</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>1</v>
-      </c>
-      <c r="C296" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>송순</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Songsoon</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Uneasy</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>문이 활짝 열린다. 무엇이 나왔는지 보이지 않는다. 공간 전체가 잠시 정지한다. 소리가 없다. 빛이 없다. 보는 쪽이 먼저 멈춘 건지, 세상이 먼저 숨을 죽인 건지도 알 수 없다.</t>
+          <t>그 수첩엔 언니 이름을 제일 먼저 적어줘요. 그 다음이 누구든, 언니가 맨 앞에 와야 해요.</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>assets/portraits/songsoon.jpeg</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>TrustedSongsoon</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>ch6_ending_c</t>
+          <t>ch6_ending_b</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>2</v>
-      </c>
-      <c r="C297" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>다시 현실로 돌아왔을 때 — 이해심도, 송금도, 천용해도 없다. 유웅룡과 송순만 남아 있다.</t>
+          <t>이번 기록엔 빈칸이 덜 남을 겁니다. 불려간 사람과 지워진 사람, 판을 짠 자의 이름까지 서로 이어졌으니, 적어도 누가 무엇을 덮으려 했는지는 똑똑히 남길 수 있습니다.</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>thought</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>SolvedQuestionCount</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>[2, 3]</t>
         </is>
       </c>
     </row>
@@ -17024,46 +17090,17 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>3</v>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>유웅룡</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C298" t="inlineStr"/>
       <c r="L298" t="inlineStr">
         <is>
-          <t>…무엇이 나온 걸까요.</t>
+          <t>문이 활짝 열린다. 무엇이 나왔는지 보이지 않는다. 공간 전체가 잠시 정지한다. 소리가 없다. 빛이 없다. 보는 쪽이 먼저 멈춘 건지, 세상이 먼저 숨을 죽인 건지도 알 수 없다.</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="N298" t="inlineStr">
-        <is>
-          <t>assets/portraits/yuu.jpeg</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -17074,46 +17111,17 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>4</v>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>송순</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>Songsoon</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>Uneasy</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C299" t="inlineStr"/>
       <c r="L299" t="inlineStr">
         <is>
-          <t>(대답하지 않는다)</t>
+          <t>다시 현실로 돌아왔을 때 — 이해심도, 송금도, 천용해도 없다. 유웅룡과 송순만 남아 있다.</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="N299" t="inlineStr">
-        <is>
-          <t>assets/portraits/songsoon.jpeg</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -17124,17 +17132,46 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>5</v>
-      </c>
-      <c r="C300" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>대답 대신, 멀리서 아주 짧은 허밍이 한 번 더 스친다. 둘 다 그 소리를 들었는지조차 확신하지 못한다. 확신하지 못한다는 사실이 오히려 더 오래 남는다.</t>
+          <t>…무엇이 나온 걸까요.</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
         </is>
       </c>
     </row>
@@ -17145,26 +17182,26 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>유웅룡</t>
+          <t>송순</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Tense</t>
+          <t>Uneasy</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -17174,17 +17211,17 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>이걸 보고도, 제가 전처럼 문장을 접어 둘 수 있을까요.</t>
+          <t>(대답하지 않는다)</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>assets/portraits/yuu.jpeg</t>
+          <t>assets/portraits/songsoon.jpeg</t>
         </is>
       </c>
     </row>
@@ -17195,46 +17232,17 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>7</v>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>송순</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>Songsoon</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>Uneasy</t>
-        </is>
-      </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C302" t="inlineStr"/>
       <c r="L302" t="inlineStr">
         <is>
-          <t>…모른 체는 할 수 있어도, 잊을 수는 없을 거예요.</t>
+          <t>대답 대신, 멀리서 아주 짧은 허밍이 한 번 더 스친다. 둘 다 그 소리를 들었는지조차 확신하지 못한다. 확신하지 못한다는 사실이 오히려 더 오래 남는다.</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="N302" t="inlineStr">
-        <is>
-          <t>assets/portraits/songsoon.jpeg</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -17245,26 +17253,47 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>8</v>
-      </c>
-      <c r="C303" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>질문을 끝까지 밀고 간 사람만이 남는 침묵도 있다. 두 사람은 아무 결론도 얻지 못했는데, 그래서 오히려 더 오래 그날 밤에서 벗어나지 못한다.</t>
+          <t>이걸 보고도, 제가 전처럼 문장을 접어 둘 수 있을까요.</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>narration</t>
-        </is>
-      </c>
-      <c r="O303" t="inlineStr">
-        <is>
-          <t>InvestigationScore</t>
-        </is>
-      </c>
-      <c r="P303" t="n">
-        <v>3</v>
+          <t>thought</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
+        </is>
       </c>
     </row>
     <row r="304">
@@ -17274,26 +17303,47 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>9</v>
-      </c>
-      <c r="C304" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>송순</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Songsoon</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Uneasy</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>귓가에 남은 허밍은 오래도록 사라지지 않는다. 들은 자만 알아볼 수 있는 미세한 떨림이, 평범한 밤의 공기 속에서도 가끔 문득 되살아난다.</t>
+          <t>…모른 체는 할 수 있어도, 잊을 수는 없을 거예요.</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>narration</t>
-        </is>
-      </c>
-      <c r="O304" t="inlineStr">
-        <is>
-          <t>ResonanceLevel</t>
-        </is>
-      </c>
-      <c r="P304" t="n">
-        <v>2</v>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>assets/portraits/songsoon.jpeg</t>
+        </is>
       </c>
     </row>
     <row r="305">
@@ -17303,46 +17353,17 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>10</v>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>유웅룡</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>Tense</t>
-        </is>
-      </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C305" t="inlineStr"/>
       <c r="L305" t="inlineStr">
         <is>
-          <t>답을 얻진 못했어도, 질문까지 잃어버리진 않았군요. 아마 그게 오늘 밤 남은 전부겠지.</t>
+          <t>질문을 끝까지 밀고 간 사람만이 남는 침묵도 있다. 두 사람은 아무 결론도 얻지 못했는데, 그래서 오히려 더 오래 그날 밤에서 벗어나지 못한다.</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>thought</t>
-        </is>
-      </c>
-      <c r="N305" t="inlineStr">
-        <is>
-          <t>assets/portraits/yuu.jpeg</t>
+          <t>narration</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
@@ -17357,63 +17378,118 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ch6_epilogue</t>
+          <t>ch6_ending_c</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C306" t="inlineStr"/>
       <c r="L306" t="inlineStr">
         <is>
-          <t>며칠 뒤, 경성. 난향일보에는 짧은 기사 한 토막만 실렸다.</t>
+          <t>귓가에 남은 허밍은 오래도록 사라지지 않는다. 들은 자만 알아볼 수 있는 미세한 떨림이, 평범한 밤의 공기 속에서도 가끔 문득 되살아난다.</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
         <is>
           <t>narration</t>
         </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="P306" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ch6_epilogue</t>
+          <t>ch6_ending_c</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>2</v>
-      </c>
-      <c r="C307" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>"낙원 화재로 인한 건물 일부 소실. 인명 피해 없음."</t>
+          <t>답을 얻진 못했어도, 질문까지 잃어버리진 않았군요. 아마 그게 오늘 밤 남은 전부겠지.</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>narration</t>
-        </is>
+          <t>thought</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>InvestigationScore</t>
+        </is>
+      </c>
+      <c r="P307" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ch6_epilogue</t>
+          <t>ch6_ending_c</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="L308" t="inlineStr">
         <is>
-          <t>유웅룡의 이름은 없다. 편집장이 그 짧은 기사를 내려다보며 담배를 문다. 표정이 없다. 표정이 없다는 사실이 오히려 오래 남는다.</t>
+          <t>붙들었던 질문 대부분을 풀고도 이 밤이 이렇게 끝났다는 사실이 오히려 더 잔인하다. 답을 잃은 것이 아니라, 답을 알았는데도 사람을 다 구하지 못했다는 감각이 오래 남는다.</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
           <t>narration</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>SolvedQuestionCount</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>[2, 3]</t>
         </is>
       </c>
     </row>
@@ -17424,12 +17500,12 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="L309" t="inlineStr">
         <is>
-          <t>기사는 짧고, 도시의 밤은 평소와 다르지 않다. 전차는 달리고, 사람들은 다음 날을 준비한다. 아무 일도 없었던 것처럼.</t>
+          <t>며칠 뒤, 경성. 난향일보에는 짧은 기사 한 토막만 실렸다.</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -17445,12 +17521,12 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C310" t="inlineStr"/>
       <c r="L310" t="inlineStr">
         <is>
-          <t>문은 열렸다. 무엇이 나왔는지는 아무도 모른다. 그리고 아무도 묻지 않는다. 도시는 늘 그래왔듯, 감당 못 할 대답 앞에서 질문부터 접어버린다.</t>
+          <t>"낙원 화재로 인한 건물 일부 소실. 인명 피해 없음."</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -17466,12 +17542,12 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="L311" t="inlineStr">
         <is>
-          <t>묻지 않는다는 건 모른다는 뜻이 아니다. 대답을 감당할 수 없어서 외면하는 쪽에 가깝다.</t>
+          <t>유웅룡의 이름은 없다. 편집장이 그 짧은 기사를 내려다보며 담배를 문다. 표정이 없다. 표정이 없다는 사실이 오히려 오래 남는다.</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -17487,27 +17563,17 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C312" t="inlineStr"/>
       <c r="L312" t="inlineStr">
         <is>
-          <t>그래도 어딘가엔 적힌 이름이 남는다. 누군가가 접지 않고 버틴 문장, 끝내 모른 체하지 않겠다고 버틴 사람 덕분에.</t>
+          <t>기사는 짧고, 도시의 밤은 평소와 다르지 않다. 전차는 달리고, 사람들은 다음 날을 준비한다. 아무 일도 없었던 것처럼.</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
           <t>narration</t>
-        </is>
-      </c>
-      <c r="O312" t="inlineStr">
-        <is>
-          <t>ReadRitualScore</t>
-        </is>
-      </c>
-      <c r="P312" t="inlineStr">
-        <is>
-          <t>true</t>
         </is>
       </c>
     </row>
@@ -17518,12 +17584,12 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="L313" t="inlineStr">
         <is>
-          <t>그리고 어떤 밤은, 끝내 누군가의 말을 믿어 준 일 하나로 모양이 달라지기도 한다. 경성에선 그런 일이 기사보다 드물다.</t>
+          <t>하지만 유웅룡의 수첩 안쪽에는 짧지 않은 이름과 문장들이 남는다. 불려간 자, 지워진 자, 판을 짠 자에 대한 메모는 기사보다 길고, 불에 타지 않은 질문처럼 끝내 접히지 않는다.</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -17533,12 +17599,12 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>TrustedSongsoon</t>
+          <t>SolvedQuestionCount</t>
         </is>
       </c>
       <c r="P313" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>[2, 3]</t>
         </is>
       </c>
     </row>
@@ -17549,26 +17615,18 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C314" t="inlineStr"/>
       <c r="L314" t="inlineStr">
         <is>
-          <t>도시 한복판에서는 아무 일도 없었던 것처럼 전차 종이 울린다. 그러나 어떤 이름들은 한 번 적힌 뒤부터, 비록 신문에 나지 않아도 쉽게 다시 지워지지 않는다.</t>
+          <t>문은 열렸다. 무엇이 나왔는지는 아무도 모른다. 그리고 아무도 묻지 않는다. 도시는 늘 그래왔듯, 감당 못 할 대답 앞에서 질문부터 접어버린다.</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
           <t>narration</t>
         </is>
-      </c>
-      <c r="O314" t="inlineStr">
-        <is>
-          <t>InvestigationScore</t>
-        </is>
-      </c>
-      <c r="P314" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -17578,185 +17636,174 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C315" t="inlineStr"/>
       <c r="L315" t="inlineStr">
         <is>
-          <t>그리고 아주 드문 밤이면, 바람결 어딘가에서 허밍이 짧게 스친다. 들은 사람만 잠깐 걸음을 늦춘다.</t>
+          <t>묻지 않는다는 건 모른다는 뜻이 아니다. 대답을 감당할 수 없어서 외면하는 쪽에 가깝다.</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
         <is>
           <t>narration</t>
         </is>
-      </c>
-      <c r="O315" t="inlineStr">
-        <is>
-          <t>ResonanceLevel</t>
-        </is>
-      </c>
-      <c r="P315" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>ch6_outcome</t>
+          <t>ch6_epilogue</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C316" t="inlineStr"/>
       <c r="L316" t="inlineStr">
         <is>
-          <t>노래와 비명, 주문과 숨소리가 한순간 서로를 덮어쓴다. 의식은 흔들리기 시작하지만, 아직 어느 쪽으로 기울지 정해지지 않았다. 이 방에 남은 것은 힘겨루기가 아니라, 끝내 무엇을 사람으로 남길 것인가의 문제다.</t>
+          <t>그래도 어딘가엔 적힌 이름이 남는다. 누군가가 접지 않고 버틴 문장, 끝내 모른 체하지 않겠다고 버틴 사람 덕분에.</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
         <is>
           <t>narration</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>ReadRitualScore</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>ch6_path_a</t>
+          <t>ch6_epilogue</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>1</v>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>송순</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>Songsoon</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>Uneasy</t>
-        </is>
-      </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C317" t="inlineStr"/>
       <c r="L317" t="inlineStr">
         <is>
-          <t>언니… 들리죠? 나예요. 그 방 앞에서도, 창고에서도… 계속 듣고 있었어요. 이제 모른 척 안 할 거예요.</t>
+          <t>그리고 어떤 밤은, 끝내 누군가의 말을 믿어 준 일 하나로 모양이 달라지기도 한다. 경성에선 그런 일이 기사보다 드물다.</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="N317" t="inlineStr">
-        <is>
-          <t>assets/portraits/songsoon.jpeg</t>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>TrustedSongsoon</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>ch6_path_a</t>
+          <t>ch6_epilogue</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C318" t="inlineStr"/>
       <c r="L318" t="inlineStr">
         <is>
-          <t>송순의 목소리가 허밍과 겹쳐지며 방 안 공기의 결이 미세하게 바뀐다. 처음으로 의식 한가운데 사람 체온이 끼어든다.</t>
+          <t>도시 한복판에서는 아무 일도 없었던 것처럼 전차 종이 울린다. 그러나 어떤 이름들은 한 번 적힌 뒤부터, 비록 신문에 나지 않아도 쉽게 다시 지워지지 않는다.</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
           <t>narration</t>
         </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>InvestigationScore</t>
+        </is>
+      </c>
+      <c r="P318" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>ch6_path_a2</t>
+          <t>ch6_epilogue</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C319" t="inlineStr"/>
       <c r="L319" t="inlineStr">
         <is>
-          <t>송금의 노래가 잠깐 흔들린다. 살아 있는 사람의 목소리가 아니라, 아주 오래된 기억이 잠시 되돌아오는 것처럼. 그러나 돌아오는 건 사람 전체가 아니라, 아직 이름이 남아 있는 한 조각뿐이다.</t>
+          <t>그리고 아주 드문 밤이면, 바람결 어딘가에서 허밍이 짧게 스친다. 들은 사람만 잠깐 걸음을 늦춘다.</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
         <is>
           <t>narration</t>
         </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="P319" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>ch6_path_a2</t>
+          <t>ch6_outcome</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C320" t="inlineStr"/>
       <c r="L320" t="inlineStr">
         <is>
-          <t>송순이 끝내 손을 놓지 않았던 태도와, 무서운 소리를 헛것이라 치워 버리지 않았던 믿음이 마지막 실처럼 남아 의식을 흔든다.</t>
+          <t>노래와 비명, 주문과 숨소리가 한순간 서로를 덮어쓴다. 의식은 흔들리기 시작하지만, 아직 어느 쪽으로 기울지 정해지지 않았다. 이 방에 남은 것은 힘겨루기가 아니라, 끝내 무엇을 사람으로 남길 것인가의 문제다.</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
         <is>
           <t>narration</t>
-        </is>
-      </c>
-      <c r="O320" t="inlineStr">
-        <is>
-          <t>TrustedSongsoon</t>
-        </is>
-      </c>
-      <c r="P320" t="inlineStr">
-        <is>
-          <t>true</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>ch6_path_a2</t>
+          <t>ch6_outcome</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C321" t="inlineStr"/>
       <c r="L321" t="inlineStr">
         <is>
-          <t>문 앞에서부터 얽혀 든 허밍의 결이 이 순간 송순의 목소리와 포개진다. 파멸에 더 가까이 다가섰기에, 되려 무엇을 붙들어야 하는지도 더 선명하게 보인다.</t>
+          <t>질문을 끝까지 붙들어 온 사람만이 보이는 결도 있다. 이판규를 부른 손, 송금을 밀어 넣은 순서, 의식을 떠받친 구조가 한꺼번에 겹치며, 이제는 망설임조차 변명으로 쓰기 어려워진다.</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -17766,17 +17813,19 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>ResonanceLevel</t>
-        </is>
-      </c>
-      <c r="P321" t="n">
-        <v>2</v>
+          <t>SolvedQuestionCount</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>[2, 3]</t>
+        </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>ch6_path_b</t>
+          <t>ch6_path_a</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -17784,22 +17833,22 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>유웅룡</t>
+          <t>송순</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Uneasy</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -17809,7 +17858,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>이게 처음이 아니라는 걸 알고 물러서면, 나도 저 기사 밑줄 긋고 접어 둔 사람들과 다를 게 없지.</t>
+          <t>언니… 들리죠? 나예요. 그 방 앞에서도, 창고에서도… 계속 듣고 있었어요. 이제 모른 척 안 할 거예요.</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
@@ -17819,14 +17868,14 @@
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t>assets/portraits/yuu.jpeg</t>
+          <t>assets/portraits/songsoon.jpeg</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>ch6_path_b</t>
+          <t>ch6_path_a</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -17835,7 +17884,7 @@
       <c r="C323" t="inlineStr"/>
       <c r="L323" t="inlineStr">
         <is>
-          <t>유웅룡은 이해심을 향해 달려가며, 지난 기사들에서 지워진 문장들을 머릿속으로 되짚는다. 덮인 문장이 많을수록, 이번엔 몸으로라도 그 빈칸을 메워야 한다고 느낀다.</t>
+          <t>송순의 목소리가 허밍과 겹쳐지며 방 안 공기의 결이 미세하게 바뀐다. 처음으로 의식 한가운데 사람 체온이 끼어든다.</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -17847,97 +17896,68 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>ch6_path_b</t>
+          <t>ch6_path_a2</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>3</v>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>유웅룡</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>Tense</t>
-        </is>
-      </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C324" t="inlineStr"/>
       <c r="L324" t="inlineStr">
         <is>
-          <t>접힌 기록을 또 하나 만들 바엔, 차라리 여기서 같이 부서지는 편이 낫지.</t>
+          <t>송금의 노래가 잠깐 흔들린다. 살아 있는 사람의 목소리가 아니라, 아주 오래된 기억이 잠시 되돌아오는 것처럼. 그러나 돌아오는 건 사람 전체가 아니라, 아직 이름이 남아 있는 한 조각뿐이다.</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>thought</t>
-        </is>
-      </c>
-      <c r="N324" t="inlineStr">
-        <is>
-          <t>assets/portraits/yuu.jpeg</t>
-        </is>
-      </c>
-      <c r="O324" t="inlineStr">
-        <is>
-          <t>FoundOldArticles</t>
-        </is>
-      </c>
-      <c r="P324" t="inlineStr">
-        <is>
-          <t>true</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>ch6_path_b2</t>
+          <t>ch6_path_a2</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C325" t="inlineStr"/>
       <c r="L325" t="inlineStr">
         <is>
-          <t>연락하지 않은 덕분에 아무도 끼어들지 않는다. 이 선택의 결과는 오롯이 두 사람과 의식의 중심에 남는다. 도움을 부르지 않은 대가이기도 하고, 방해받지 않고 끝까지 본 대가이기도 하다.</t>
+          <t>송순이 끝내 손을 놓지 않았던 태도와, 무서운 소리를 헛것이라 치워 버리지 않았던 믿음이 마지막 실처럼 남아 의식을 흔든다.</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
         <is>
           <t>narration</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>TrustedSongsoon</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>ch6_path_b2</t>
+          <t>ch6_path_a2</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C326" t="inlineStr"/>
       <c r="L326" t="inlineStr">
         <is>
-          <t>유웅룡이 창고에서 끝까지 읽어 낸 악보와, 자료실에서 주워 온 낡은 기사 조각들이 여기서 하나의 문장으로 겹친다. 흩어져 있던 것들이 이제는 적어 남길 수 있는 증거가 된다.</t>
+          <t>문 앞에서부터 얽혀 든 허밍의 결이 이 순간 송순의 목소리와 포개진다. 파멸에 더 가까이 다가섰기에, 되려 무엇을 붙들어야 하는지도 더 선명하게 보인다.</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -17947,28 +17967,26 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t>ReadRitualScore</t>
-        </is>
-      </c>
-      <c r="P326" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="P326" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>ch6_path_b2</t>
+          <t>ch6_path_a2</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C327" t="inlineStr"/>
       <c r="L327" t="inlineStr">
         <is>
-          <t>허밍이 아직 귓가에서 가시지 않는다. 유웅룡은 자신 또한 저 문턱에서 아주 비켜 선 목격자만은 아니게 되었다는 사실을 안다. 그래서 더더욱, 본 자의 이름으로 적어 두어야 한다.</t>
+          <t>붙들어 온 질문 셋 중 둘 이상이 이 순간에서 하나로 묶인다. 누구를 불렀는지, 누구를 밀어 넣었는지, 누가 판을 짰는지까지 알았기에 송순의 부름도 허공에 흩어지지 않는다.</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -17978,163 +17996,180 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>ResonanceLevel</t>
-        </is>
-      </c>
-      <c r="P327" t="n">
-        <v>2</v>
+          <t>SolvedQuestionCount</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>[2, 3]</t>
+        </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>ch6_ritual_scene</t>
+          <t>ch6_path_b</t>
         </is>
       </c>
       <c r="B328" t="n">
         <v>1</v>
       </c>
-      <c r="C328" t="inlineStr"/>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>지하 의례실 깊숙이. 이해심이 제단 앞에 선다. 송금은 청색 한복 차림으로 노래하고 있다. 표정이 없다. 살기 위해 버틴 끝에 생기는 무표정이 아니라, 지나치게 오래 빌려 쓰여 자기 얼굴을 잃어버린 사람의 무표정이다.</t>
+          <t>이게 처음이 아니라는 걸 알고 물러서면, 나도 저 기사 밑줄 긋고 접어 둔 사람들과 다를 게 없지.</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>ch6_ritual_scene</t>
+          <t>ch6_path_b</t>
         </is>
       </c>
       <c r="B329" t="n">
         <v>2</v>
       </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>이해심</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>Haesim</t>
-        </is>
-      </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>Trance</t>
-        </is>
-      </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>Center</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+      <c r="C329" t="inlineStr"/>
       <c r="L329" t="inlineStr">
         <is>
-          <t>어리석은 자들이여. 문이 열리는 날, 경성은 비로소 속을 드러낼 것이다. 곪은 자리는 끝내 누군가 헤집어야 한다. 나는 이제 그 일을 두려워하지 않는다.</t>
+          <t>유웅룡은 이해심을 향해 달려가며, 지난 기사들에서 지워진 문장들을 머릿속으로 되짚는다. 덮인 문장이 많을수록, 이번엔 몸으로라도 그 빈칸을 메워야 한다고 느낀다.</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="N329" t="inlineStr">
-        <is>
-          <t>assets/portraits/haesim.jpeg</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>ch6_ritual_scene</t>
+          <t>ch6_path_b</t>
         </is>
       </c>
       <c r="B330" t="n">
         <v>3</v>
       </c>
-      <c r="C330" t="inlineStr"/>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>이해심의 뒤편 어둠 속엔 흰 천으로 얼굴을 가린 남자의 형체가 희미하게 선다. 가까이 있는데도 사람이라기보다 남의 신앙을 뒤에서 빨아먹는 그늘처럼 보인다. 향냄새 밑에 눌린 비린내가 그쪽에서 더 짙다.</t>
+          <t>접힌 기록을 또 하나 만들 바엔, 차라리 여기서 같이 부서지는 편이 낫지.</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>thought</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>FoundOldArticles</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>ch6_ritual_scene</t>
+          <t>ch6_path_b2</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>4</v>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>천용해</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>Cheonyonghae</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C331" t="inlineStr"/>
       <c r="L331" t="inlineStr">
         <is>
-          <t>교주님, 문은 오래 기다렸습니다. 주저하는 자들 소리까지 들여놓을 까닭은 없지요.</t>
+          <t>연락하지 않은 덕분에 아무도 끼어들지 않는다. 이 선택의 결과는 오롯이 두 사람과 의식의 중심에 남는다. 도움을 부르지 않은 대가이기도 하고, 방해받지 않고 끝까지 본 대가이기도 하다.</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>ch6_ritual_scene</t>
+          <t>ch6_path_b2</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C332" t="inlineStr"/>
       <c r="L332" t="inlineStr">
         <is>
-          <t>그 순간 유웅룡의 귓속에서 문 앞 허밍이 다시 울린다. 방 안 노래와 어긋나지 않는다. 아까 문에 귀를 댄 뒤로, 이 공간은 이미 몸 안쪽까지 파고든 듯하다.</t>
+          <t>유웅룡이 창고에서 끝까지 읽어 낸 악보와, 자료실에서 주워 온 낡은 기사 조각들이 여기서 하나의 문장으로 겹친다. 흩어져 있던 것들이 이제는 적어 남길 수 있는 증거가 된다.</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -18144,110 +18179,72 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t>ResonanceLevel</t>
-        </is>
-      </c>
-      <c r="P332" t="n">
-        <v>2</v>
+          <t>ReadRitualScore</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>ch6_ritual_scene</t>
+          <t>ch6_path_b2</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>6</v>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>송금</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>Songgeum</t>
-        </is>
-      </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>Trance</t>
-        </is>
-      </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>Center</t>
-        </is>
-      </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="C333" t="inlineStr"/>
       <c r="L333" t="inlineStr">
         <is>
-          <t>(표정 없이, 노래를 흥얼거린다) …푸른… 옷을… 입고… 문 앞에… 서서…</t>
+          <t>허밍이 아직 귓가에서 가시지 않는다. 유웅룡은 자신 또한 저 문턱에서 아주 비켜 선 목격자만은 아니게 되었다는 사실을 안다. 그래서 더더욱, 본 자의 이름으로 적어 두어야 한다.</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="N333" t="inlineStr">
-        <is>
-          <t>assets/portraits/songgeum.jpeg</t>
-        </is>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="P333" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>ch6_ritual_scene</t>
+          <t>ch6_path_b2</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>7</v>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>송순</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>Songsoon</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>Uneasy</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C334" t="inlineStr"/>
       <c r="L334" t="inlineStr">
         <is>
-          <t>언니… 언니!</t>
+          <t>질문을 끝까지 밀고 와서야, 기록해야 할 문장의 순서도 달라진다. 이판규와 송금, 의식의 설계자까지 하나의 구조로 꿰어졌기에 이번 기록은 더는 단편 기사로 무너지지 않는다.</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="N334" t="inlineStr">
-        <is>
-          <t>assets/portraits/songsoon.jpeg</t>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>SolvedQuestionCount</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>[2, 3]</t>
         </is>
       </c>
     </row>
@@ -18258,12 +18255,12 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C335" t="inlineStr"/>
       <c r="L335" t="inlineStr">
         <is>
-          <t>이해심의 안대 아래로 피가 번지기 시작한다. 하나는 불빛, 하나는 서릿발. 문이 열리고 있다. 방 안 촛불이 바깥바람 없이도 같은 방향으로 눕고, 벽면의 푸른 흔적이 젖은 살처럼 미세하게 꿈틀거린다.</t>
+          <t>지하 의례실 깊숙이. 이해심이 제단 앞에 선다. 송금은 청색 한복 차림으로 노래하고 있다. 표정이 없다. 살기 위해 버틴 끝에 생기는 무표정이 아니라, 지나치게 오래 빌려 쓰여 자기 얼굴을 잃어버린 사람의 무표정이다.</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
@@ -18279,7 +18276,7 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -18308,7 +18305,7 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>너희는 늦었다. 법도, 기사도, 기도도 아무도 구하지 못했다. 나라를 위한다던 자도, 백성을 입에 올리던 자도 결국 하나도 건지지 못했지. 이제 남은 건 치료가 아니라 절단이다. 잘라내지 않으면 이 도시는 끝내 썩은 피를 제 몸이라 착각한 채 죽는다.</t>
+          <t>어리석은 자들이여. 문이 열리는 날, 경성은 비로소 속을 드러낼 것이다. 곪은 자리는 끝내 누군가 헤집어야 한다. 나는 이제 그 일을 두려워하지 않는다.</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
@@ -18329,46 +18326,17 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>10</v>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>유웅룡</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="C337" t="inlineStr"/>
       <c r="L337" t="inlineStr">
         <is>
-          <t>그걸 정화라 부르지 마십시오. 사람을 셈하고 갈아 넣는 짓에 이름만 고상하게 붙인 학살이잖습니까.</t>
+          <t>이해심의 뒤편 어둠 속엔 흰 천으로 얼굴을 가린 남자의 형체가 희미하게 선다. 가까이 있는데도 사람이라기보다 남의 신앙을 뒤에서 빨아먹는 그늘처럼 보인다. 향냄새 밑에 눌린 비린내가 그쪽에서 더 짙다.</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="N337" t="inlineStr">
-        <is>
-          <t>assets/portraits/yuu.jpeg</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -18379,26 +18347,26 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>이해심</t>
+          <t>천용해</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Haesim</t>
+          <t>Cheonyonghae</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Trance</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -18408,17 +18376,12 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>학살? 우습구나. 이 도시는 애당초 누군가를 갈아 넣어 움직여 왔다. 빈민가 아이도, 여급도, 병든 여자도, 나라 잃은 백성도 다 써 먹히며 사라졌지. 나는 다만 그 화덕을 휘장 뒤에 숨기지 않을 뿐이야. 너희는 덮고, 나는 드러낸다.</t>
+          <t>교주님, 문은 오래 기다렸습니다. 주저하는 자들 소리까지 들여놓을 까닭은 없지요.</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
         <is>
           <t>normal</t>
-        </is>
-      </c>
-      <c r="N338" t="inlineStr">
-        <is>
-          <t>assets/portraits/haesim.jpeg</t>
         </is>
       </c>
     </row>
@@ -18429,47 +18392,26 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>12</v>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>이해심</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>Haesim</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>Trance</t>
-        </is>
-      </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>Center</t>
-        </is>
-      </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C339" t="inlineStr"/>
       <c r="L339" t="inlineStr">
         <is>
-          <t>구원은 온전한 자에게 오지 않는다. 다 망가진 자에게만 문이 열린다. 나는 그걸 누구보다 먼저 배웠다. 황족의 피도, 독립의 꿈도, 여자의 몸도, 병든 폐도 끝내 나를 구하지 못했으니까.</t>
+          <t>그 순간 유웅룡의 귓속에서 문 앞 허밍이 다시 울린다. 방 안 노래와 어긋나지 않는다. 아까 문에 귀를 댄 뒤로, 이 공간은 이미 몸 안쪽까지 파고든 듯하다.</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="N339" t="inlineStr">
-        <is>
-          <t>assets/portraits/haesim.jpeg</t>
-        </is>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="P339" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="340">
@@ -18479,26 +18421,26 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>유웅룡</t>
+          <t>송금</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Songgeum</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Trance</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -18508,7 +18450,7 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>당신 뒤에 선 작자가 누군진 이제 알겠습니다. 구원을 입에 올리며 사람 절망을 긁어 모으는 자들 말입니다. 이름만 청의교일 뿐, 속살은 늘 같은 장삿속이군요.</t>
+          <t>(표정 없이, 노래를 흥얼거린다) …푸른… 옷을… 입고… 문 앞에… 서서…</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
@@ -18518,7 +18460,7 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t>assets/portraits/yuu.jpeg</t>
+          <t>assets/portraits/songgeum.jpeg</t>
         </is>
       </c>
     </row>
@@ -18529,26 +18471,26 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>천용해</t>
+          <t>송순</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Cheonyonghae</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Uneasy</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -18558,12 +18500,17 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>장사라…. 말은 곱게도 하는군. 세상은 늘 제 죄를 그런 말로 덮지. 저들은 다만 제 몫을 냈을 뿐이야.</t>
+          <t>언니… 언니!</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
           <t>normal</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>assets/portraits/songsoon.jpeg</t>
         </is>
       </c>
     </row>
@@ -18574,83 +18521,78 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>15</v>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>송순</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>Songsoon</t>
-        </is>
-      </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>Uneasy</t>
-        </is>
-      </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C342" t="inlineStr"/>
       <c r="L342" t="inlineStr">
         <is>
-          <t>몫이라고 부르지 마. 언니도, 없어졌던 사람들도 누구한테 바칠 몫으로 태어난 적 없어.</t>
+          <t>이해심의 안대 아래로 피가 번지기 시작한다. 하나는 불빛, 하나는 서릿발. 문이 열리고 있다. 방 안 촛불이 바깥바람 없이도 같은 방향으로 눕고, 벽면의 푸른 흔적이 젖은 살처럼 미세하게 꿈틀거린다.</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="N342" t="inlineStr">
-        <is>
-          <t>assets/portraits/songsoon.jpeg</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>ch6_threshold</t>
+          <t>ch6_ritual_scene</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>1</v>
-      </c>
-      <c r="C343" t="inlineStr"/>
-      <c r="K343" t="inlineStr">
-        <is>
-          <t>Flicker</t>
+        <v>9</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>이해심</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Haesim</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Trance</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Center</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>노랫소리를 따라 마지막 문턱을 넘기 직전, 두 사람은 동시에 걸음을 멈춘다. 이제부터는 보고도 모른 척할 수 없다.</t>
+          <t>너희는 늦었다. 법도, 기사도, 기도도 아무도 구하지 못했다. 나라를 위한다던 자도, 백성을 입에 올리던 자도 결국 하나도 건지지 못했지. 이제 남은 건 치료가 아니라 절단이다. 잘라내지 않으면 이 도시는 끝내 썩은 피를 제 몸이라 착각한 채 죽는다.</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>assets/portraits/haesim.jpeg</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>ch6_threshold</t>
+          <t>ch6_ritual_scene</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -18664,7 +18606,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Tense</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -18677,19 +18619,9 @@
           <t>Speaker</t>
         </is>
       </c>
-      <c r="H344" t="inlineStr">
-        <is>
-          <t>SlideRight</t>
-        </is>
-      </c>
-      <c r="J344" t="inlineStr">
-        <is>
-          <t>Tremble</t>
-        </is>
-      </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>지금이라도 돌아가고 싶다면 말해요. 여기서부터는 기사도, 증언도, 정의도 우리를 지켜주지 못할 겁니다.</t>
+          <t>그걸 정화라 부르지 마십시오. 사람을 셈하고 갈아 넣는 짓에 이름만 고상하게 붙인 학살이잖습니까.</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
@@ -18706,30 +18638,30 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>ch6_threshold</t>
+          <t>ch6_ritual_scene</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>송순</t>
+          <t>이해심</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>Haesim</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Afraid</t>
+          <t>Trance</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -18737,19 +18669,9 @@
           <t>Speaker</t>
         </is>
       </c>
-      <c r="H345" t="inlineStr">
-        <is>
-          <t>FadeIn</t>
-        </is>
-      </c>
-      <c r="J345" t="inlineStr">
-        <is>
-          <t>Tremble</t>
-        </is>
-      </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>무서워요. 그런데 돌아가면 더 무서울 것 같아요. 언니를 남겨두고 살아가는 쪽이요.</t>
+          <t>학살? 우습구나. 이 도시는 애당초 누군가를 갈아 넣어 움직여 왔다. 빈민가 아이도, 여급도, 병든 여자도, 나라 잃은 백성도 다 써 먹히며 사라졌지. 나는 다만 그 화덕을 휘장 뒤에 숨기지 않을 뿐이야. 너희는 덮고, 나는 드러낸다.</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
@@ -18759,37 +18681,37 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t>assets/portraits/songsoon.jpeg</t>
+          <t>assets/portraits/haesim.jpeg</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>ch6_threshold</t>
+          <t>ch6_ritual_scene</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>유웅룡</t>
+          <t>이해심</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Haesim</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Trance</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -18799,7 +18721,7 @@
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>그럼 갑시다. 이번엔 끝까지 갑니다.</t>
+          <t>구원은 온전한 자에게 오지 않는다. 다 망가진 자에게만 문이 열린다. 나는 그걸 누구보다 먼저 배웠다. 황족의 피도, 독립의 꿈도, 여자의 몸도, 병든 폐도 끝내 나를 구하지 못했으니까.</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
@@ -18809,18 +18731,18 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t>assets/portraits/yuu.jpeg</t>
+          <t>assets/portraits/haesim.jpeg</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>ch6_threshold</t>
+          <t>ch6_ritual_scene</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -18849,7 +18771,7 @@
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>누가 덮으라 해도, 이번엔 못 접습니다. 자료실에서 본 그 기사도 결국 여기까지 이어져 있었으니까.</t>
+          <t>당신 뒤에 선 작자가 누군진 이제 알겠습니다. 구원을 입에 올리며 사람 절망을 긁어 모으는 자들 말입니다. 이름만 청의교일 뿐, 속살은 늘 같은 장삿속이군요.</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
@@ -18860,41 +18782,31 @@
       <c r="N347" t="inlineStr">
         <is>
           <t>assets/portraits/yuu.jpeg</t>
-        </is>
-      </c>
-      <c r="O347" t="inlineStr">
-        <is>
-          <t>FoundOldArticles</t>
-        </is>
-      </c>
-      <c r="P347" t="inlineStr">
-        <is>
-          <t>true</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>ch6_threshold</t>
+          <t>ch6_ritual_scene</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>유웅룡</t>
+          <t>천용해</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Cheonyonghae</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Tense</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -18909,36 +18821,23 @@
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>그리고… 문 앞에서 들은 소리가 아직 귓속에 남아 있습니다. 저 안이 우릴 먼저 듣고 있다는 걸 알면서도 들어가는 셈이지요.</t>
+          <t>장사라…. 말은 곱게도 하는군. 세상은 늘 제 죄를 그런 말로 덮지. 저들은 다만 제 몫을 냈을 뿐이야.</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>thought</t>
-        </is>
-      </c>
-      <c r="N348" t="inlineStr">
-        <is>
-          <t>assets/portraits/yuu.jpeg</t>
-        </is>
-      </c>
-      <c r="O348" t="inlineStr">
-        <is>
-          <t>ResonanceLevel</t>
-        </is>
-      </c>
-      <c r="P348" t="n">
-        <v>2</v>
+          <t>normal</t>
+        </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>ch6_threshold</t>
+          <t>ch6_ritual_scene</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -18967,7 +18866,7 @@
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>기자님이 내 말을 먼저 믿어 줬으니, 저도 이번엔 망설이지 않을게요. 문이 열리면, 제가 먼저 언니를 부를게요.</t>
+          <t>몫이라고 부르지 마. 언니도, 없어졌던 사람들도 누구한테 바칠 몫으로 태어난 적 없어.</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
@@ -18978,16 +18877,6 @@
       <c r="N349" t="inlineStr">
         <is>
           <t>assets/portraits/songsoon.jpeg</t>
-        </is>
-      </c>
-      <c r="O349" t="inlineStr">
-        <is>
-          <t>TrustedSongsoon</t>
-        </is>
-      </c>
-      <c r="P349" t="inlineStr">
-        <is>
-          <t>true</t>
         </is>
       </c>
     </row>
@@ -18998,55 +18887,23 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>8</v>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>유웅룡</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E350" t="inlineStr">
-        <is>
-          <t>Tense</t>
-        </is>
-      </c>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>Speaker</t>
+        <v>1</v>
+      </c>
+      <c r="C350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Flicker</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>자료실에서 주운 기사도, 방 안에서 읽은 기록도 결국 여기까지 밀려왔군요. 이제 남은 건 외면하지 않는 일뿐입니다.</t>
+          <t>노랫소리를 따라 마지막 문턱을 넘기 직전, 두 사람은 동시에 걸음을 멈춘다. 이제부터는 보고도 모른 척할 수 없다.</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>thought</t>
-        </is>
-      </c>
-      <c r="N350" t="inlineStr">
-        <is>
-          <t>assets/portraits/yuu.jpeg</t>
-        </is>
-      </c>
-      <c r="O350" t="inlineStr">
-        <is>
-          <t>InvestigationScore</t>
-        </is>
-      </c>
-      <c r="P350" t="n">
-        <v>3</v>
+          <t>narration</t>
+        </is>
       </c>
     </row>
     <row r="351">
@@ -19056,27 +18913,56 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>9</v>
-      </c>
-      <c r="C351" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>SlideRight</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>Tremble</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>누구에게도 연락하지 않기로 한 덕에, 두 사람은 도움받을 길도 핑계 댈 길도 없이 같은 공포를 정면으로 마주 선다.</t>
+          <t>지금이라도 돌아가고 싶다면 말해요. 여기서부터는 기사도, 증언도, 정의도 우리를 지켜주지 못할 겁니다.</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>narration</t>
-        </is>
-      </c>
-      <c r="O351" t="inlineStr">
-        <is>
-          <t>CalledEditor</t>
-        </is>
-      </c>
-      <c r="P351" t="inlineStr">
-        <is>
-          <t>false</t>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
         </is>
       </c>
     </row>
@@ -19087,56 +18973,464 @@
         </is>
       </c>
       <c r="B352" t="n">
+        <v>3</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>송순</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Songsoon</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Afraid</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>FadeIn</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>Tremble</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>무서워요. 그런데 돌아가면 더 무서울 것 같아요. 언니를 남겨두고 살아가는 쪽이요.</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>assets/portraits/songsoon.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>ch6_threshold</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>4</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>그럼 갑시다. 이번엔 끝까지 갑니다.</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>ch6_threshold</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>5</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>누가 덮으라 해도, 이번엔 못 접습니다. 자료실에서 본 그 기사도 결국 여기까지 이어져 있었으니까.</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>FoundOldArticles</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>ch6_threshold</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>6</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>그리고… 문 앞에서 들은 소리가 아직 귓속에 남아 있습니다. 저 안이 우릴 먼저 듣고 있다는 걸 알면서도 들어가는 셈이지요.</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>thought</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="P355" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>ch6_threshold</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>7</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>송순</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Songsoon</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Uneasy</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>기자님이 내 말을 먼저 믿어 줬으니, 저도 이번엔 망설이지 않을게요. 문이 열리면, 제가 먼저 언니를 부를게요.</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>assets/portraits/songsoon.jpeg</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>TrustedSongsoon</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>ch6_threshold</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>8</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>자료실에서 주운 기사도, 방 안에서 읽은 기록도 결국 여기까지 밀려왔군요. 이제 남은 건 외면하지 않는 일뿐입니다.</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>thought</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>InvestigationScore</t>
+        </is>
+      </c>
+      <c r="P357" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>ch6_threshold</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>9</v>
+      </c>
+      <c r="C358" t="inlineStr"/>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>누구에게도 연락하지 않기로 한 덕에, 두 사람은 도움받을 길도 핑계 댈 길도 없이 같은 공포를 정면으로 마주 선다.</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>CalledEditor</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>ch6_threshold</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
         <v>10</v>
       </c>
-      <c r="C352" t="inlineStr">
+      <c r="C359" t="inlineStr">
         <is>
           <t>유웅룡</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr">
+      <c r="D359" t="inlineStr">
         <is>
           <t>Yuu</t>
         </is>
       </c>
-      <c r="E352" t="inlineStr">
+      <c r="E359" t="inlineStr">
         <is>
           <t>Tense</t>
         </is>
       </c>
-      <c r="F352" t="inlineStr">
+      <c r="F359" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
-      <c r="L352" t="inlineStr">
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
         <is>
           <t>의례실 바닥에서 주운 종이까지 여기로 이어집니다. 남은 건 문장으로 증명하는 일이 아니라, 저 안에서 실제로 끊어내는 일입니다.</t>
         </is>
       </c>
-      <c r="M352" t="inlineStr">
+      <c r="M359" t="inlineStr">
         <is>
           <t>thought</t>
         </is>
       </c>
-      <c r="N352" t="inlineStr">
+      <c r="N359" t="inlineStr">
         <is>
           <t>assets/portraits/yuu.jpeg</t>
         </is>
       </c>
-      <c r="O352" t="inlineStr">
+      <c r="O359" t="inlineStr">
         <is>
           <t>HasEvidence_EvRitualNote</t>
         </is>
       </c>
-      <c r="P352" t="inlineStr">
+      <c r="P359" t="inlineStr">
         <is>
           <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>ch6_threshold</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>11</v>
+      </c>
+      <c r="C360" t="inlineStr"/>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>병원, 폐공장, 자료실, 의례실에서 붙잡은 질문들이 이제야 한 줄로 선다. 끝내 다 푼 것은 아니어도, 무엇을 끊어야 하는지는 더 이상 흐리지 않다.</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>SolvedQuestionCount</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>[2, 3]</t>
         </is>
       </c>
     </row>
@@ -19944,7 +20238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20082,12 +20376,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TrustedSongsoon</t>
+          <t>SolvedQuestionCount</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>[2, 3]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -20107,11 +20401,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SongsoonTrust</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
+          <t>TrustedSongsoon</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -20134,7 +20430,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -20153,13 +20449,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OkryunPushed</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>SongsoonTrust</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -20178,11 +20472,13 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EndingAScore</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
+          <t>OkryunPushed</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -20196,47 +20492,45 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ch6_path_b</t>
+          <t>ch6_path_a2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FoundOldArticles</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>EndingAScore</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ch6_path_b2</t>
+          <t>ch6_ending_a</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>ch6_path_b</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>FoundOldArticles</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>ch6_path_b2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ReadRitualScore</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ch6_ending_b</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -20251,11 +20545,13 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>InvestigationScore</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>3</v>
+          <t>SolvedQuestionCount</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[2, 3]</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -20263,7 +20559,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -20274,21 +20570,69 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>ReadRitualScore</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ch6_ending_b</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ch6_path_b2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>InvestigationScore</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ch6_ending_b</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ch6_path_b2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>CalledEditor</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>ch6_ending_b</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>3</v>
+      <c r="E16" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/content/generated/script.generated.xlsx
+++ b/content/generated/script.generated.xlsx
@@ -447,7 +447,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-06 00:51:48</t>
+          <t>2026-04-06 01:15:11</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,60 +539,75 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>ResolutionType</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>VisibleRuleID</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>StateRuleID</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>RelatedEvidenceIDs</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>SolutionEvidenceIDs</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>SolutionMode</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ContradictionPrompt</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ContradictionStatement</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>SolvedFlagID</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ResolvedDetail</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>SuccessToast</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>FailureToast</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>RewardFlagID</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>RewardValue</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>RewardMode</t>
         </is>
@@ -622,55 +637,55 @@
           <t>Witness</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>QR_IpangyuSeen</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>QS_IpangyuCall</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>EvNote, EvBlueCloth, EvRitualNote</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>EvNote</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>QuestionSolved_QIpangyuCall</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>붉은 쪽지는 이판규가 우연히 뛰쳐나간 것이 아니라, 낙원 쪽의 호출에 떠밀려 움직였다는 직접적인 흔적이다. 그의 광기는 불려간 자의 잔향에 가깝다.</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>질문 정리: 이판규를 부른 흔적을 붙들었다.</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>아직은 호출의 근거를 바로 묶기 어렵다.</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>InvestigationScore</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Add</t>
         </is>
@@ -679,76 +694,91 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QSonggeumMissing</t>
+          <t>QIpangyuMadness</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>송금은 왜 사라졌는가</t>
+          <t>이판규의 말은 단순한 헛소리였는가</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>송금이 자발적으로 사라진 것인지, 의식의 일부로 지워진 것인지가 핵심이다.</t>
+          <t>법정과 병원에서 흘린 말이 죄를 피하려는 넋두리인지, 실제 사건의 흔적인지 갈라내야 한다.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Witness</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>QR_SonggeumOpen</t>
+          <t>Contradiction</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>QS_SonggeumMissing</t>
+          <t>QR_IpangyuSeen</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>EvDiary, EvBlueHanbok, EvOldArticles</t>
+          <t>QS_IpangyuMadness</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>EvDiary</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>QuestionSolved_QSonggeumMissing</t>
+          <t>EvNote, EvBlueCloth, EvRitualNote</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>EvNote</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>숨겨진 일기장은 송금의 실종이 단순 도피가 아니라, 의례 속 역할로 밀려 들어간 소거였음을 보여준다. 사라짐은 계획된 순서의 일부다.</t>
+          <t>이 진술을 뒤집을 근거를 골라야 한다.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>질문 정리: 송금의 실종이 의례와 이어진다는 근거를 확보했다.</t>
+          <t>이판규는 그저 미쳐 날뛴 거요. 누가 불렀다느니, 문이 열린다느니 하는 말은 전부 죄를 피하려고 지어낸 소리였지.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>이 단서만으로는 송금의 실종 이유를 단정하기 어렵다.</t>
+          <t>QuestionSolved_QIpangyuMadness</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>ReadRitualScore</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
+          <t>붉은 쪽지는 이판규의 발작적 발언이 꾸며낸 말이 아니라, 실제 호출의 흔적과 맞닿아 있었음을 보여준다. 그의 말은 헛소리가 아니라 사건의 반향이었다.</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>모순 판별: 이판규의 말이 단순한 헛소리가 아니었다.</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>이 근거만으로는 이판규의 말을 거짓이라 뒤집을 수 없다.</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>InvestigationScore</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Add</t>
         </is>
@@ -757,81 +787,345 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>QSonggeumMissing</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>송금은 왜 사라졌는가</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>송금이 자발적으로 사라진 것인지, 의식의 일부로 지워진 것인지가 핵심이다.</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>QR_SonggeumOpen</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>QS_SonggeumMissing</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>EvDiary, EvBlueHanbok, EvOldArticles</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>EvDiary</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>QuestionSolved_QSonggeumMissing</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>숨겨진 일기장은 송금의 실종이 단순 도피가 아니라, 의례 속 역할로 밀려 들어간 소거였음을 보여준다. 사라짐은 계획된 순서의 일부다.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>질문 정리: 송금의 실종이 의례와 이어진다는 근거를 확보했다.</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>이 단서만으로는 송금의 실종 이유를 단정하기 어렵다.</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>ReadRitualScore</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QSonggeumRunaway</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>송금은 스스로 달아났는가</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>사람들이 입을 다물수록, 실종은 자발적 도피처럼 포장되기 쉽다. 정말 그랬는지 반박할 근거가 필요하다.</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Contradiction</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>QR_SonggeumOpen</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>QS_SonggeumRunaway</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>EvDiary, EvBlueHanbok, EvOldArticles</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>EvDiary</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>도피로 포장된 설명을 뒤집을 근거를 골라야 한다.</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>송금은 겁이 나서 스스로 달아난 거야. 낙원에 남을 이유가 없었으니, 다들 없어진 뒤에 제 발로 도망친 거지.</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>QuestionSolved_QSonggeumRunaway</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>일기장은 송금이 도망칠 여유조차 없이 의례의 배역으로 밀려 들어갔음을 드러낸다. 이 실종은 도피가 아니라 선택당한 소거였다.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>모순 판별: 송금의 실종이 자발적 도피가 아니었다.</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>이 근거만으로는 송금이 스스로 달아났다는 말을 뒤집기 어렵다.</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>ReadRitualScore</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>QRitualLead</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>낙원의 의식은 누가 주도했는가</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>무녀, 악보, 기록, 기사 사이를 연결해 의식의 실제 주체를 좁혀야 한다.</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D6" t="n">
         <v>30</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Ritual</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>QR_RitualOpen</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>QS_RitualLead</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>EvRitualScore, EvOldArticles, EvRitualNote, EvMask</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>EvRitualScore, EvRitualNote</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>QuestionSolved_QRitualLead</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>의례실 종이는 낙원의 의식이 우발적 소문이 아니라, 그릇과 순서를 세어가며 밀어붙인 구조적 의례였음을 드러낸다. 누군가 끝까지 판을 쥐고 있었다.</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>질문 정리: 낙원의 의식이 계획된 구조였다는 근거를 붙들었다.</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>악보와 의례실 기록이 함께 이어져야 의식의 구조를 단정할 수 있다.</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>ResonanceLevel</t>
         </is>
       </c>
-      <c r="P4" t="n">
+      <c r="S6" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QRitualAccident</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>낙원의 의식은 즉흥적 광신이었는가</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>피와 노래가 뒤섞인 현장은 쉽게 광기라 불린다. 하지만 즉흥적 광신인지, 계산된 구조인지 갈라내야 한다.</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>35</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ritual</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Contradiction</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>QR_RitualOpen</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>QS_RitualAccident</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>EvRitualScore, EvOldArticles, EvRitualNote, EvMask</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>EvRitualNote</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>우발적 광신이라는 설명을 뒤집을 근거를 골라야 한다.</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>그날 벌어진 일은 다들 넋이 나간 채 벌인 우발적 광신이었어. 순서도, 준비도, 누가 판을 쥐었는지도 없었지.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>QuestionSolved_QRitualAccident</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>의례실 종이는 이 모든 일이 우발적 집단 광기가 아니라, 순서와 몫을 세어가며 준비한 구조적 의례였음을 못 박는다. 누군가 처음부터 끝까지 판을 짠 것이다.</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>모순 판별: 낙원의 의식이 우발적 광신이 아니었다.</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>이 근거만으로는 의식이 즉흥적 광신이 아니었다고 단정하기 어렵다.</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>Add</t>
         </is>
@@ -1202,7 +1496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1645,12 +1939,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RR_QRitualState_00</t>
+          <t>RR_QIpangyuMadnessState_00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>QS_RitualLead</t>
+          <t>QS_IpangyuMadness</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1665,7 +1959,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>QuestionSolved_QRitualLead</t>
+          <t>QuestionSolved_QIpangyuMadness</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1688,12 +1982,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RR_QRitualState_01</t>
+          <t>RR_QIpangyuMadnessState_01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>QS_RitualLead</t>
+          <t>QS_IpangyuMadness</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1703,25 +1997,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FlagValue</t>
+          <t>HasEvidence</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ReadRitualScore</t>
+          <t>EvNote</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gte</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
+          <t>Equals</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>의식 구조 접근</t>
+          <t>반박 가능</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1731,12 +2025,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RR_QSonggeumState_00</t>
+          <t>RR_QRitualAccidentState_00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>QS_SonggeumMissing</t>
+          <t>QS_RitualAccident</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1751,7 +2045,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>QuestionSolved_QSonggeumMissing</t>
+          <t>QuestionSolved_QRitualAccident</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1774,12 +2068,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RR_QSonggeumState_01</t>
+          <t>RR_QRitualAccidentState_01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>QS_SonggeumMissing</t>
+          <t>QS_RitualAccident</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1794,7 +2088,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>EvDiary</t>
+          <t>EvRitualNote</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1807,10 +2101,268 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>반박 가능</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>RR_QRitualState_00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>QS_RitualLead</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>FlagValue</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>QuestionSolved_QRitualLead</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Equals</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>해결됨</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>RR_QRitualState_01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>QS_RitualLead</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FlagValue</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ReadRitualScore</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gte</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>의식 구조 접근</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>RR_QSonggeumState_00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>QS_SonggeumMissing</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>FlagValue</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>QuestionSolved_QSonggeumMissing</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Equals</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>해결됨</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>RR_QSonggeumState_01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>QS_SonggeumMissing</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HasEvidence</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>EvDiary</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Equals</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>단서 확보</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I19" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>RR_QSonggeumRunawayState_00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>QS_SonggeumRunaway</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FlagValue</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>QuestionSolved_QSonggeumRunaway</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Equals</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>해결됨</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>RR_QSonggeumRunawayState_01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>QS_SonggeumRunaway</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HasEvidence</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>EvDiary</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Equals</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>반박 가능</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1857,7 +2409,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4">
@@ -1917,7 +2469,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -1937,7 +2489,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -3555,7 +4107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q360"/>
+  <dimension ref="A1:Q365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16236,30 +16788,30 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>ch6_ending_a</t>
+          <t>ch6_choice_c</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>송순</t>
+          <t>유웅룡</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>Yuu</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Uneasy</t>
+          <t>Tense</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -16269,38 +16821,87 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>(창고 벽 앞에서 들었던 그 멜로디로 응답한다. 언니의 노래에 맞서는 허밍)</t>
+          <t>이판규를 미친놈 하나로 접어 두려던 판도 여기서 끝입니다. 불려간 자의 말이 헛소리가 아니었다면, 지금 저 안에 있는 것도 우발이 아니라 누군가의 계산이었겠지요.</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>thought</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>assets/portraits/songsoon.jpeg</t>
+          <t>assets/portraits/yuu.jpeg</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>QuestionSolved_QIpangyuMadness</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ch6_ending_a</t>
+          <t>ch6_choice_c</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>2</v>
-      </c>
-      <c r="C281" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>송순</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Songsoon</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Afraid</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>감응이 흔들린다. 이해심이 비틀거리며 무너진다. 문은 반쯤 열린 채 억지로 닫힌다. 닫히는 마지막 순간까지 허밍은 한 사람의 이름을 놓치지 않으려는 것처럼 떨린다.</t>
+          <t>언니가 도망친 게 아니라 붙들린 거라면, 여기서도 같은 말을 하게 둘 순 없어요. 사라진 사람이 먼저 달아났다고, 또 그렇게 몰아갈 테니까요.</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>assets/portraits/songsoon.jpeg</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>QuestionSolved_QSonggeumRunaway</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
@@ -16311,17 +16912,46 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>3</v>
-      </c>
-      <c r="C282" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>송순</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Songsoon</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Uneasy</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>송금이 천천히 고개를 돌린다. 눈이 텅 비어 있다. 살아있지만, 돌아오지 않았다.</t>
+          <t>(창고 벽 앞에서 들었던 그 멜로디로 응답한다. 언니의 노래에 맞서는 허밍)</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>assets/portraits/songsoon.jpeg</t>
         </is>
       </c>
     </row>
@@ -16332,46 +16962,17 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>4</v>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>송순</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>Songsoon</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>Uneasy</t>
-        </is>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C283" t="inlineStr"/>
       <c r="L283" t="inlineStr">
         <is>
-          <t>(언니를 껴안는다. 언니는 반응이 없다)</t>
+          <t>감응이 흔들린다. 이해심이 비틀거리며 무너진다. 문은 반쯤 열린 채 억지로 닫힌다. 닫히는 마지막 순간까지 허밍은 한 사람의 이름을 놓치지 않으려는 것처럼 떨린다.</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="N283" t="inlineStr">
-        <is>
-          <t>assets/portraits/songsoon.jpeg</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -16382,46 +16983,17 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>5</v>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>유웅룡</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>Tense</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="C284" t="inlineStr"/>
       <c r="L284" t="inlineStr">
         <is>
-          <t>돌아온 게 아니군요. 여기까지 와서도 사람 대신 빈자리만 안고 나오게 될 줄은…. 참으로 지독합니다.</t>
+          <t>송금이 천천히 고개를 돌린다. 눈이 텅 비어 있다. 살아있지만, 돌아오지 않았다.</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>thought</t>
-        </is>
-      </c>
-      <c r="N284" t="inlineStr">
-        <is>
-          <t>assets/portraits/yuu.jpeg</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -16432,7 +17004,7 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -16461,7 +17033,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>그래도 언니 이름이 아주 끊기진 않았어요. 아주 잠깐이라도, 나를 알아본 쪽이 있었어요. 그걸로 끝까지 붙들 거예요.</t>
+          <t>(언니를 껴안는다. 언니는 반응이 없다)</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -16472,16 +17044,6 @@
       <c r="N285" t="inlineStr">
         <is>
           <t>assets/portraits/songsoon.jpeg</t>
-        </is>
-      </c>
-      <c r="O285" t="inlineStr">
-        <is>
-          <t>TrustedSongsoon</t>
-        </is>
-      </c>
-      <c r="P285" t="inlineStr">
-        <is>
-          <t>true</t>
         </is>
       </c>
     </row>
@@ -16492,7 +17054,7 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -16521,7 +17083,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>문턱에서부터 귀에 박힌 저 소리가 아직 남아 있습니다. 저쪽이 우리 안에 남긴 흔적이겠지요. 그러니 더더욱, 오늘 밤을 없던 일로 둘 순 없습니다.</t>
+          <t>돌아온 게 아니군요. 여기까지 와서도 사람 대신 빈자리만 안고 나오게 될 줄은…. 참으로 지독합니다.</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -16533,14 +17095,6 @@
         <is>
           <t>assets/portraits/yuu.jpeg</t>
         </is>
-      </c>
-      <c r="O286" t="inlineStr">
-        <is>
-          <t>ResonanceLevel</t>
-        </is>
-      </c>
-      <c r="P286" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="287">
@@ -16550,7 +17104,7 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -16579,7 +17133,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>데려오지 못해도 붙들 수는 있어요. 언니가 사라진 자리를, 내가 끝까지 놓지 않을 거예요.</t>
+          <t>그래도 언니 이름이 아주 끊기진 않았어요. 아주 잠깐이라도, 나를 알아본 쪽이 있었어요. 그걸로 끝까지 붙들 거예요.</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -16590,6 +17144,16 @@
       <c r="N287" t="inlineStr">
         <is>
           <t>assets/portraits/songsoon.jpeg</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>TrustedSongsoon</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
@@ -16600,7 +17164,7 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -16629,7 +17193,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>그래도 이제는 압니다. 누가 사람을 불러냈고, 누구를 순서 안에 밀어 넣었는지. 이름을 되찾지 못해도, 책임의 결만큼은 흐리지 않겠습니다.</t>
+          <t>문턱에서부터 귀에 박힌 저 소리가 아직 남아 있습니다. 저쪽이 우리 안에 남긴 흔적이겠지요. 그러니 더더욱, 오늘 밤을 없던 일로 둘 순 없습니다.</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -16644,54 +17208,120 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>SolvedQuestionCount</t>
-        </is>
-      </c>
-      <c r="P288" t="inlineStr">
-        <is>
-          <t>[2, 3]</t>
-        </is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="P288" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ch6_ending_b</t>
+          <t>ch6_ending_a</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>1</v>
-      </c>
-      <c r="C289" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>송순</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Songsoon</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Uneasy</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>유웅룡이 이해심을 향해 달려든다. 짧은 충돌. 이해심이 쓰러지고 의식의 결이 끊긴다. 사람 몸으로 겨우 멈춘 의식은 끝내 아름답지도 장엄하지도 않다. 그저 비싼 대가를 치른 범죄 현장처럼 남는다.</t>
+          <t>데려오지 못해도 붙들 수는 있어요. 언니가 사라진 자리를, 내가 끝까지 놓지 않을 거예요.</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>assets/portraits/songsoon.jpeg</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ch6_ending_b</t>
+          <t>ch6_ending_a</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>2</v>
-      </c>
-      <c r="C290" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>문이 닫힌다. 노래가 멎는다. 송금은 그 자리에 쓰러진다. 숨은 붙어 있다. 하지만 눈을 뜨지 않는다.</t>
+          <t>그래도 이제는 압니다. 누가 사람을 불러냈고, 누구를 순서 안에 밀어 넣었는지. 이름을 되찾지 못해도, 책임의 결만큼은 흐리지 않겠습니다.</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>thought</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>SolvedQuestionCount</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>[2, 3]</t>
         </is>
       </c>
     </row>
@@ -16702,46 +17332,17 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>3</v>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>유웅룡</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>Tense</t>
-        </is>
-      </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C291" t="inlineStr"/>
       <c r="L291" t="inlineStr">
         <is>
-          <t>(수첩을 꺼낸다. 처음으로 모든 것을 적는다. 이판규, 폐공장, 낙원, 이해심, 청의동자, 그리고 두 사람의 이름. 이번엔 사건보다 이름을 먼저 쓴다.)</t>
+          <t>유웅룡이 이해심을 향해 달려든다. 짧은 충돌. 이해심이 쓰러지고 의식의 결이 끊긴다. 사람 몸으로 겨우 멈춘 의식은 끝내 아름답지도 장엄하지도 않다. 그저 비싼 대가를 치른 범죄 현장처럼 남는다.</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>thought</t>
-        </is>
-      </c>
-      <c r="N291" t="inlineStr">
-        <is>
-          <t>assets/portraits/yuu.jpeg</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -16752,46 +17353,17 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>4</v>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>유웅룡</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>Tense</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C292" t="inlineStr"/>
       <c r="L292" t="inlineStr">
         <is>
-          <t>세상이 안 믿어도 상관없습니다. 적어 두면 적어도 없던 일로는 못 넘깁니다. 이번엔 그 정도라도 해야겠습니다.</t>
+          <t>문이 닫힌다. 노래가 멎는다. 송금은 그 자리에 쓰러진다. 숨은 붙어 있다. 하지만 눈을 뜨지 않는다.</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>thought</t>
-        </is>
-      </c>
-      <c r="N292" t="inlineStr">
-        <is>
-          <t>assets/portraits/yuu.jpeg</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -16802,26 +17374,26 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>송순</t>
+          <t>유웅룡</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>Yuu</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Uneasy</t>
+          <t>Tense</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -16831,17 +17403,17 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>기록해줘요. 언니 이름도, 여기서 사라진 사람들 이름도. 누가 지워도 한 번은 남았다고 말할 수 있게.</t>
+          <t>(수첩을 꺼낸다. 처음으로 모든 것을 적는다. 이판규, 폐공장, 낙원, 이해심, 청의동자, 그리고 두 사람의 이름. 이번엔 사건보다 이름을 먼저 쓴다.)</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>thought</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>assets/portraits/songsoon.jpeg</t>
+          <t>assets/portraits/yuu.jpeg</t>
         </is>
       </c>
     </row>
@@ -16852,7 +17424,7 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -16881,7 +17453,7 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>이번엔 사건부터 쓰지 않겠습니다. 이름부터 적고, 누가 그 이름을 지웠는지까지 붙여 둘 겁니다. 그 정도는, 기자란 작자도 해야지요.</t>
+          <t>세상이 안 믿어도 상관없습니다. 적어 두면 적어도 없던 일로는 못 넘깁니다. 이번엔 그 정도라도 해야겠습니다.</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -16892,16 +17464,6 @@
       <c r="N294" t="inlineStr">
         <is>
           <t>assets/portraits/yuu.jpeg</t>
-        </is>
-      </c>
-      <c r="O294" t="inlineStr">
-        <is>
-          <t>ReadRitualScore</t>
-        </is>
-      </c>
-      <c r="P294" t="inlineStr">
-        <is>
-          <t>true</t>
         </is>
       </c>
     </row>
@@ -16912,26 +17474,26 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>유웅룡</t>
+          <t>송순</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Tense</t>
+          <t>Uneasy</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -16941,26 +17503,18 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>본 사람도 조금은 문턱에 걸친 채 돌아옵니다. 그러니 더 서둘러 적어야지요. 내 안에서조차 희미해지기 전에.</t>
+          <t>기록해줘요. 언니 이름도, 여기서 사라진 사람들 이름도. 누가 지워도 한 번은 남았다고 말할 수 있게.</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>assets/portraits/yuu.jpeg</t>
-        </is>
-      </c>
-      <c r="O295" t="inlineStr">
-        <is>
-          <t>ResonanceLevel</t>
-        </is>
-      </c>
-      <c r="P295" t="n">
-        <v>2</v>
+          <t>assets/portraits/songsoon.jpeg</t>
+        </is>
       </c>
     </row>
     <row r="296">
@@ -16970,26 +17524,26 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>송순</t>
+          <t>유웅룡</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>Yuu</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Uneasy</t>
+          <t>Tense</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -16999,22 +17553,22 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>그 수첩엔 언니 이름을 제일 먼저 적어줘요. 그 다음이 누구든, 언니가 맨 앞에 와야 해요.</t>
+          <t>이번엔 사건부터 쓰지 않겠습니다. 이름부터 적고, 누가 그 이름을 지웠는지까지 붙여 둘 겁니다. 그 정도는, 기자란 작자도 해야지요.</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>thought</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>assets/portraits/songsoon.jpeg</t>
+          <t>assets/portraits/yuu.jpeg</t>
         </is>
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>TrustedSongsoon</t>
+          <t>ReadRitualScore</t>
         </is>
       </c>
       <c r="P296" t="inlineStr">
@@ -17030,7 +17584,7 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -17059,7 +17613,7 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>이번 기록엔 빈칸이 덜 남을 겁니다. 불려간 사람과 지워진 사람, 판을 짠 자의 이름까지 서로 이어졌으니, 적어도 누가 무엇을 덮으려 했는지는 똑똑히 남길 수 있습니다.</t>
+          <t>본 사람도 조금은 문턱에 걸친 채 돌아옵니다. 그러니 더 서둘러 적어야지요. 내 안에서조차 희미해지기 전에.</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
@@ -17074,54 +17628,130 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>SolvedQuestionCount</t>
-        </is>
-      </c>
-      <c r="P297" t="inlineStr">
-        <is>
-          <t>[2, 3]</t>
-        </is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="P297" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>ch6_ending_c</t>
+          <t>ch6_ending_b</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>1</v>
-      </c>
-      <c r="C298" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>송순</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Songsoon</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Uneasy</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>문이 활짝 열린다. 무엇이 나왔는지 보이지 않는다. 공간 전체가 잠시 정지한다. 소리가 없다. 빛이 없다. 보는 쪽이 먼저 멈춘 건지, 세상이 먼저 숨을 죽인 건지도 알 수 없다.</t>
+          <t>그 수첩엔 언니 이름을 제일 먼저 적어줘요. 그 다음이 누구든, 언니가 맨 앞에 와야 해요.</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>assets/portraits/songsoon.jpeg</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>TrustedSongsoon</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ch6_ending_c</t>
+          <t>ch6_ending_b</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>2</v>
-      </c>
-      <c r="C299" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>다시 현실로 돌아왔을 때 — 이해심도, 송금도, 천용해도 없다. 유웅룡과 송순만 남아 있다.</t>
+          <t>이번 기록엔 빈칸이 덜 남을 겁니다. 불려간 사람과 지워진 사람, 판을 짠 자의 이름까지 서로 이어졌으니, 적어도 누가 무엇을 덮으려 했는지는 똑똑히 남길 수 있습니다.</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>thought</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>SolvedQuestionCount</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>[2, 3]</t>
         </is>
       </c>
     </row>
@@ -17132,46 +17762,17 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>3</v>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>유웅룡</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C300" t="inlineStr"/>
       <c r="L300" t="inlineStr">
         <is>
-          <t>…무엇이 나온 걸까요.</t>
+          <t>문이 활짝 열린다. 무엇이 나왔는지 보이지 않는다. 공간 전체가 잠시 정지한다. 소리가 없다. 빛이 없다. 보는 쪽이 먼저 멈춘 건지, 세상이 먼저 숨을 죽인 건지도 알 수 없다.</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="N300" t="inlineStr">
-        <is>
-          <t>assets/portraits/yuu.jpeg</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -17182,46 +17783,17 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>4</v>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>송순</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>Songsoon</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>Uneasy</t>
-        </is>
-      </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C301" t="inlineStr"/>
       <c r="L301" t="inlineStr">
         <is>
-          <t>(대답하지 않는다)</t>
+          <t>다시 현실로 돌아왔을 때 — 이해심도, 송금도, 천용해도 없다. 유웅룡과 송순만 남아 있다.</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="N301" t="inlineStr">
-        <is>
-          <t>assets/portraits/songsoon.jpeg</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -17232,17 +17804,46 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>5</v>
-      </c>
-      <c r="C302" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>대답 대신, 멀리서 아주 짧은 허밍이 한 번 더 스친다. 둘 다 그 소리를 들었는지조차 확신하지 못한다. 확신하지 못한다는 사실이 오히려 더 오래 남는다.</t>
+          <t>…무엇이 나온 걸까요.</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
         </is>
       </c>
     </row>
@@ -17253,26 +17854,26 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>유웅룡</t>
+          <t>송순</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Tense</t>
+          <t>Uneasy</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -17282,17 +17883,17 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>이걸 보고도, 제가 전처럼 문장을 접어 둘 수 있을까요.</t>
+          <t>(대답하지 않는다)</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>assets/portraits/yuu.jpeg</t>
+          <t>assets/portraits/songsoon.jpeg</t>
         </is>
       </c>
     </row>
@@ -17303,46 +17904,17 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>7</v>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>송순</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>Songsoon</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>Uneasy</t>
-        </is>
-      </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C304" t="inlineStr"/>
       <c r="L304" t="inlineStr">
         <is>
-          <t>…모른 체는 할 수 있어도, 잊을 수는 없을 거예요.</t>
+          <t>대답 대신, 멀리서 아주 짧은 허밍이 한 번 더 스친다. 둘 다 그 소리를 들었는지조차 확신하지 못한다. 확신하지 못한다는 사실이 오히려 더 오래 남는다.</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="N304" t="inlineStr">
-        <is>
-          <t>assets/portraits/songsoon.jpeg</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -17353,26 +17925,47 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>8</v>
-      </c>
-      <c r="C305" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>질문을 끝까지 밀고 간 사람만이 남는 침묵도 있다. 두 사람은 아무 결론도 얻지 못했는데, 그래서 오히려 더 오래 그날 밤에서 벗어나지 못한다.</t>
+          <t>이걸 보고도, 제가 전처럼 문장을 접어 둘 수 있을까요.</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>narration</t>
-        </is>
-      </c>
-      <c r="O305" t="inlineStr">
-        <is>
-          <t>InvestigationScore</t>
-        </is>
-      </c>
-      <c r="P305" t="n">
-        <v>3</v>
+          <t>thought</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
+        </is>
       </c>
     </row>
     <row r="306">
@@ -17382,26 +17975,47 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>9</v>
-      </c>
-      <c r="C306" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>송순</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Songsoon</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Uneasy</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>귓가에 남은 허밍은 오래도록 사라지지 않는다. 들은 자만 알아볼 수 있는 미세한 떨림이, 평범한 밤의 공기 속에서도 가끔 문득 되살아난다.</t>
+          <t>…모른 체는 할 수 있어도, 잊을 수는 없을 거예요.</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>narration</t>
-        </is>
-      </c>
-      <c r="O306" t="inlineStr">
-        <is>
-          <t>ResonanceLevel</t>
-        </is>
-      </c>
-      <c r="P306" t="n">
-        <v>2</v>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>assets/portraits/songsoon.jpeg</t>
+        </is>
       </c>
     </row>
     <row r="307">
@@ -17411,46 +18025,17 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>10</v>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>유웅룡</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>Tense</t>
-        </is>
-      </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C307" t="inlineStr"/>
       <c r="L307" t="inlineStr">
         <is>
-          <t>답을 얻진 못했어도, 질문까지 잃어버리진 않았군요. 아마 그게 오늘 밤 남은 전부겠지.</t>
+          <t>질문을 끝까지 밀고 간 사람만이 남는 침묵도 있다. 두 사람은 아무 결론도 얻지 못했는데, 그래서 오히려 더 오래 그날 밤에서 벗어나지 못한다.</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>thought</t>
-        </is>
-      </c>
-      <c r="N307" t="inlineStr">
-        <is>
-          <t>assets/portraits/yuu.jpeg</t>
+          <t>narration</t>
         </is>
       </c>
       <c r="O307" t="inlineStr">
@@ -17469,12 +18054,12 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="L308" t="inlineStr">
         <is>
-          <t>붙들었던 질문 대부분을 풀고도 이 밤이 이렇게 끝났다는 사실이 오히려 더 잔인하다. 답을 잃은 것이 아니라, 답을 알았는데도 사람을 다 구하지 못했다는 감각이 오래 남는다.</t>
+          <t>귓가에 남은 허밍은 오래도록 사라지지 않는다. 들은 자만 알아볼 수 있는 미세한 떨림이, 평범한 밤의 공기 속에서도 가끔 문득 되살아난다.</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -17484,54 +18069,99 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>SolvedQuestionCount</t>
-        </is>
-      </c>
-      <c r="P308" t="inlineStr">
-        <is>
-          <t>[2, 3]</t>
-        </is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="P308" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ch6_epilogue</t>
+          <t>ch6_ending_c</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>1</v>
-      </c>
-      <c r="C309" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>며칠 뒤, 경성. 난향일보에는 짧은 기사 한 토막만 실렸다.</t>
+          <t>답을 얻진 못했어도, 질문까지 잃어버리진 않았군요. 아마 그게 오늘 밤 남은 전부겠지.</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>narration</t>
-        </is>
+          <t>thought</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>InvestigationScore</t>
+        </is>
+      </c>
+      <c r="P309" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ch6_epilogue</t>
+          <t>ch6_ending_c</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C310" t="inlineStr"/>
       <c r="L310" t="inlineStr">
         <is>
-          <t>"낙원 화재로 인한 건물 일부 소실. 인명 피해 없음."</t>
+          <t>붙들었던 질문 대부분을 풀고도 이 밤이 이렇게 끝났다는 사실이 오히려 더 잔인하다. 답을 잃은 것이 아니라, 답을 알았는데도 사람을 다 구하지 못했다는 감각이 오래 남는다.</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
           <t>narration</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>SolvedQuestionCount</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>[2, 3]</t>
         </is>
       </c>
     </row>
@@ -17542,12 +18172,12 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="L311" t="inlineStr">
         <is>
-          <t>유웅룡의 이름은 없다. 편집장이 그 짧은 기사를 내려다보며 담배를 문다. 표정이 없다. 표정이 없다는 사실이 오히려 오래 남는다.</t>
+          <t>며칠 뒤, 경성. 난향일보에는 짧은 기사 한 토막만 실렸다.</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -17563,12 +18193,12 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C312" t="inlineStr"/>
       <c r="L312" t="inlineStr">
         <is>
-          <t>기사는 짧고, 도시의 밤은 평소와 다르지 않다. 전차는 달리고, 사람들은 다음 날을 준비한다. 아무 일도 없었던 것처럼.</t>
+          <t>"낙원 화재로 인한 건물 일부 소실. 인명 피해 없음."</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -17584,27 +18214,17 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="L313" t="inlineStr">
         <is>
-          <t>하지만 유웅룡의 수첩 안쪽에는 짧지 않은 이름과 문장들이 남는다. 불려간 자, 지워진 자, 판을 짠 자에 대한 메모는 기사보다 길고, 불에 타지 않은 질문처럼 끝내 접히지 않는다.</t>
+          <t>유웅룡의 이름은 없다. 편집장이 그 짧은 기사를 내려다보며 담배를 문다. 표정이 없다. 표정이 없다는 사실이 오히려 오래 남는다.</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
           <t>narration</t>
-        </is>
-      </c>
-      <c r="O313" t="inlineStr">
-        <is>
-          <t>SolvedQuestionCount</t>
-        </is>
-      </c>
-      <c r="P313" t="inlineStr">
-        <is>
-          <t>[2, 3]</t>
         </is>
       </c>
     </row>
@@ -17615,12 +18235,12 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C314" t="inlineStr"/>
       <c r="L314" t="inlineStr">
         <is>
-          <t>문은 열렸다. 무엇이 나왔는지는 아무도 모른다. 그리고 아무도 묻지 않는다. 도시는 늘 그래왔듯, 감당 못 할 대답 앞에서 질문부터 접어버린다.</t>
+          <t>기사는 짧고, 도시의 밤은 평소와 다르지 않다. 전차는 달리고, 사람들은 다음 날을 준비한다. 아무 일도 없었던 것처럼.</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -17636,17 +18256,27 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C315" t="inlineStr"/>
       <c r="L315" t="inlineStr">
         <is>
-          <t>묻지 않는다는 건 모른다는 뜻이 아니다. 대답을 감당할 수 없어서 외면하는 쪽에 가깝다.</t>
+          <t>하지만 유웅룡의 수첩 안쪽에는 짧지 않은 이름과 문장들이 남는다. 불려간 자, 지워진 자, 판을 짠 자에 대한 메모는 기사보다 길고, 불에 타지 않은 질문처럼 끝내 접히지 않는다.</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
         <is>
           <t>narration</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>SolvedQuestionCount</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>[2, 3]</t>
         </is>
       </c>
     </row>
@@ -17657,27 +18287,17 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C316" t="inlineStr"/>
       <c r="L316" t="inlineStr">
         <is>
-          <t>그래도 어딘가엔 적힌 이름이 남는다. 누군가가 접지 않고 버틴 문장, 끝내 모른 체하지 않겠다고 버틴 사람 덕분에.</t>
+          <t>문은 열렸다. 무엇이 나왔는지는 아무도 모른다. 그리고 아무도 묻지 않는다. 도시는 늘 그래왔듯, 감당 못 할 대답 앞에서 질문부터 접어버린다.</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
         <is>
           <t>narration</t>
-        </is>
-      </c>
-      <c r="O316" t="inlineStr">
-        <is>
-          <t>ReadRitualScore</t>
-        </is>
-      </c>
-      <c r="P316" t="inlineStr">
-        <is>
-          <t>true</t>
         </is>
       </c>
     </row>
@@ -17688,27 +18308,17 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C317" t="inlineStr"/>
       <c r="L317" t="inlineStr">
         <is>
-          <t>그리고 어떤 밤은, 끝내 누군가의 말을 믿어 준 일 하나로 모양이 달라지기도 한다. 경성에선 그런 일이 기사보다 드물다.</t>
+          <t>묻지 않는다는 건 모른다는 뜻이 아니다. 대답을 감당할 수 없어서 외면하는 쪽에 가깝다.</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
         <is>
           <t>narration</t>
-        </is>
-      </c>
-      <c r="O317" t="inlineStr">
-        <is>
-          <t>TrustedSongsoon</t>
-        </is>
-      </c>
-      <c r="P317" t="inlineStr">
-        <is>
-          <t>true</t>
         </is>
       </c>
     </row>
@@ -17719,12 +18329,12 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C318" t="inlineStr"/>
       <c r="L318" t="inlineStr">
         <is>
-          <t>도시 한복판에서는 아무 일도 없었던 것처럼 전차 종이 울린다. 그러나 어떤 이름들은 한 번 적힌 뒤부터, 비록 신문에 나지 않아도 쉽게 다시 지워지지 않는다.</t>
+          <t>그래도 어딘가엔 적힌 이름이 남는다. 누군가가 접지 않고 버틴 문장, 끝내 모른 체하지 않겠다고 버틴 사람 덕분에.</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -17734,11 +18344,13 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>InvestigationScore</t>
-        </is>
-      </c>
-      <c r="P318" t="n">
-        <v>3</v>
+          <t>ReadRitualScore</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="319">
@@ -17748,12 +18360,12 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C319" t="inlineStr"/>
       <c r="L319" t="inlineStr">
         <is>
-          <t>그리고 아주 드문 밤이면, 바람결 어딘가에서 허밍이 짧게 스친다. 들은 사람만 잠깐 걸음을 늦춘다.</t>
+          <t>그리고 어떤 밤은, 끝내 누군가의 말을 믿어 준 일 하나로 모양이 달라지기도 한다. 경성에선 그런 일이 기사보다 드물다.</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
@@ -17763,47 +18375,57 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>ResonanceLevel</t>
-        </is>
-      </c>
-      <c r="P319" t="n">
-        <v>2</v>
+          <t>TrustedSongsoon</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>ch6_outcome</t>
+          <t>ch6_epilogue</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C320" t="inlineStr"/>
       <c r="L320" t="inlineStr">
         <is>
-          <t>노래와 비명, 주문과 숨소리가 한순간 서로를 덮어쓴다. 의식은 흔들리기 시작하지만, 아직 어느 쪽으로 기울지 정해지지 않았다. 이 방에 남은 것은 힘겨루기가 아니라, 끝내 무엇을 사람으로 남길 것인가의 문제다.</t>
+          <t>도시 한복판에서는 아무 일도 없었던 것처럼 전차 종이 울린다. 그러나 어떤 이름들은 한 번 적힌 뒤부터, 비록 신문에 나지 않아도 쉽게 다시 지워지지 않는다.</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
         <is>
           <t>narration</t>
         </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>InvestigationScore</t>
+        </is>
+      </c>
+      <c r="P320" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>ch6_outcome</t>
+          <t>ch6_epilogue</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C321" t="inlineStr"/>
       <c r="L321" t="inlineStr">
         <is>
-          <t>질문을 끝까지 붙들어 온 사람만이 보이는 결도 있다. 이판규를 부른 손, 송금을 밀어 넣은 순서, 의식을 떠받친 구조가 한꺼번에 겹치며, 이제는 망설임조차 변명으로 쓰기 어려워진다.</t>
+          <t>그리고 아주 드문 밤이면, 바람결 어딘가에서 허밍이 짧게 스친다. 들은 사람만 잠깐 걸음을 늦춘다.</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -17813,78 +18435,57 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>SolvedQuestionCount</t>
-        </is>
-      </c>
-      <c r="P321" t="inlineStr">
-        <is>
-          <t>[2, 3]</t>
-        </is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="P321" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>ch6_path_a</t>
+          <t>ch6_epilogue</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>1</v>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>송순</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>Songsoon</t>
-        </is>
-      </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>Uneasy</t>
-        </is>
-      </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C322" t="inlineStr"/>
       <c r="L322" t="inlineStr">
         <is>
-          <t>언니… 들리죠? 나예요. 그 방 앞에서도, 창고에서도… 계속 듣고 있었어요. 이제 모른 척 안 할 거예요.</t>
+          <t>수첩 가장자리엔 따로 반박해 둔 문장들도 남는다. 미친 헛소리로 몰린 말, 자발적 도피로 덮인 실종, 우발적 광신으로 흐려진 의식. 적어도 그 거짓말만큼은 더는 도시가 편한 말로 접어 두지 못한다.</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="N322" t="inlineStr">
-        <is>
-          <t>assets/portraits/songsoon.jpeg</t>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>SolvedQuestionCount</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>[4, 5, 6]</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>ch6_path_a</t>
+          <t>ch6_outcome</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C323" t="inlineStr"/>
       <c r="L323" t="inlineStr">
         <is>
-          <t>송순의 목소리가 허밍과 겹쳐지며 방 안 공기의 결이 미세하게 바뀐다. 처음으로 의식 한가운데 사람 체온이 끼어든다.</t>
+          <t>노래와 비명, 주문과 숨소리가 한순간 서로를 덮어쓴다. 의식은 흔들리기 시작하지만, 아직 어느 쪽으로 기울지 정해지지 않았다. 이 방에 남은 것은 힘겨루기가 아니라, 끝내 무엇을 사람으로 남길 것인가의 문제다.</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -17896,82 +18497,103 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>ch6_path_a2</t>
+          <t>ch6_outcome</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C324" t="inlineStr"/>
       <c r="L324" t="inlineStr">
         <is>
-          <t>송금의 노래가 잠깐 흔들린다. 살아 있는 사람의 목소리가 아니라, 아주 오래된 기억이 잠시 되돌아오는 것처럼. 그러나 돌아오는 건 사람 전체가 아니라, 아직 이름이 남아 있는 한 조각뿐이다.</t>
+          <t>질문을 끝까지 붙들어 온 사람만이 보이는 결도 있다. 이판규를 부른 손, 송금을 밀어 넣은 순서, 의식을 떠받친 구조가 한꺼번에 겹치며, 이제는 망설임조차 변명으로 쓰기 어려워진다.</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
         <is>
           <t>narration</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>SolvedQuestionCount</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>[2, 3]</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>ch6_path_a2</t>
+          <t>ch6_path_a</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>2</v>
-      </c>
-      <c r="C325" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>송순</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Songsoon</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Uneasy</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>송순이 끝내 손을 놓지 않았던 태도와, 무서운 소리를 헛것이라 치워 버리지 않았던 믿음이 마지막 실처럼 남아 의식을 흔든다.</t>
+          <t>언니… 들리죠? 나예요. 그 방 앞에서도, 창고에서도… 계속 듣고 있었어요. 이제 모른 척 안 할 거예요.</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>narration</t>
-        </is>
-      </c>
-      <c r="O325" t="inlineStr">
-        <is>
-          <t>TrustedSongsoon</t>
-        </is>
-      </c>
-      <c r="P325" t="inlineStr">
-        <is>
-          <t>true</t>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>assets/portraits/songsoon.jpeg</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>ch6_path_a2</t>
+          <t>ch6_path_a</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C326" t="inlineStr"/>
       <c r="L326" t="inlineStr">
         <is>
-          <t>문 앞에서부터 얽혀 든 허밍의 결이 이 순간 송순의 목소리와 포개진다. 파멸에 더 가까이 다가섰기에, 되려 무엇을 붙들어야 하는지도 더 선명하게 보인다.</t>
+          <t>송순의 목소리가 허밍과 겹쳐지며 방 안 공기의 결이 미세하게 바뀐다. 처음으로 의식 한가운데 사람 체온이 끼어든다.</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
         <is>
           <t>narration</t>
         </is>
-      </c>
-      <c r="O326" t="inlineStr">
-        <is>
-          <t>ResonanceLevel</t>
-        </is>
-      </c>
-      <c r="P326" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="327">
@@ -17981,186 +18603,165 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C327" t="inlineStr"/>
       <c r="L327" t="inlineStr">
         <is>
-          <t>붙들어 온 질문 셋 중 둘 이상이 이 순간에서 하나로 묶인다. 누구를 불렀는지, 누구를 밀어 넣었는지, 누가 판을 짰는지까지 알았기에 송순의 부름도 허공에 흩어지지 않는다.</t>
+          <t>송금의 노래가 잠깐 흔들린다. 살아 있는 사람의 목소리가 아니라, 아주 오래된 기억이 잠시 되돌아오는 것처럼. 그러나 돌아오는 건 사람 전체가 아니라, 아직 이름이 남아 있는 한 조각뿐이다.</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
         <is>
           <t>narration</t>
-        </is>
-      </c>
-      <c r="O327" t="inlineStr">
-        <is>
-          <t>SolvedQuestionCount</t>
-        </is>
-      </c>
-      <c r="P327" t="inlineStr">
-        <is>
-          <t>[2, 3]</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>ch6_path_b</t>
+          <t>ch6_path_a2</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>1</v>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>유웅룡</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C328" t="inlineStr"/>
       <c r="L328" t="inlineStr">
         <is>
-          <t>이게 처음이 아니라는 걸 알고 물러서면, 나도 저 기사 밑줄 긋고 접어 둔 사람들과 다를 게 없지.</t>
+          <t>송순이 끝내 손을 놓지 않았던 태도와, 무서운 소리를 헛것이라 치워 버리지 않았던 믿음이 마지막 실처럼 남아 의식을 흔든다.</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="N328" t="inlineStr">
-        <is>
-          <t>assets/portraits/yuu.jpeg</t>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>TrustedSongsoon</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>ch6_path_b</t>
+          <t>ch6_path_a2</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C329" t="inlineStr"/>
       <c r="L329" t="inlineStr">
         <is>
-          <t>유웅룡은 이해심을 향해 달려가며, 지난 기사들에서 지워진 문장들을 머릿속으로 되짚는다. 덮인 문장이 많을수록, 이번엔 몸으로라도 그 빈칸을 메워야 한다고 느낀다.</t>
+          <t>문 앞에서부터 얽혀 든 허밍의 결이 이 순간 송순의 목소리와 포개진다. 파멸에 더 가까이 다가섰기에, 되려 무엇을 붙들어야 하는지도 더 선명하게 보인다.</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
         <is>
           <t>narration</t>
         </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="P329" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>ch6_path_b</t>
+          <t>ch6_path_a2</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>3</v>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>유웅룡</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>Tense</t>
-        </is>
-      </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C330" t="inlineStr"/>
       <c r="L330" t="inlineStr">
         <is>
-          <t>접힌 기록을 또 하나 만들 바엔, 차라리 여기서 같이 부서지는 편이 낫지.</t>
+          <t>붙들어 온 질문 셋 중 둘 이상이 이 순간에서 하나로 묶인다. 누구를 불렀는지, 누구를 밀어 넣었는지, 누가 판을 짰는지까지 알았기에 송순의 부름도 허공에 흩어지지 않는다.</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>thought</t>
-        </is>
-      </c>
-      <c r="N330" t="inlineStr">
-        <is>
-          <t>assets/portraits/yuu.jpeg</t>
+          <t>narration</t>
         </is>
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t>FoundOldArticles</t>
+          <t>SolvedQuestionCount</t>
         </is>
       </c>
       <c r="P330" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>[2, 3]</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>ch6_path_b2</t>
+          <t>ch6_path_b</t>
         </is>
       </c>
       <c r="B331" t="n">
         <v>1</v>
       </c>
-      <c r="C331" t="inlineStr"/>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>연락하지 않은 덕분에 아무도 끼어들지 않는다. 이 선택의 결과는 오롯이 두 사람과 의식의 중심에 남는다. 도움을 부르지 않은 대가이기도 하고, 방해받지 않고 끝까지 본 대가이기도 하다.</t>
+          <t>이게 처음이 아니라는 걸 알고 물러서면, 나도 저 기사 밑줄 긋고 접어 둔 사람들과 다를 게 없지.</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>ch6_path_b2</t>
+          <t>ch6_path_b</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -18169,235 +18770,289 @@
       <c r="C332" t="inlineStr"/>
       <c r="L332" t="inlineStr">
         <is>
-          <t>유웅룡이 창고에서 끝까지 읽어 낸 악보와, 자료실에서 주워 온 낡은 기사 조각들이 여기서 하나의 문장으로 겹친다. 흩어져 있던 것들이 이제는 적어 남길 수 있는 증거가 된다.</t>
+          <t>유웅룡은 이해심을 향해 달려가며, 지난 기사들에서 지워진 문장들을 머릿속으로 되짚는다. 덮인 문장이 많을수록, 이번엔 몸으로라도 그 빈칸을 메워야 한다고 느낀다.</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
         <is>
           <t>narration</t>
-        </is>
-      </c>
-      <c r="O332" t="inlineStr">
-        <is>
-          <t>ReadRitualScore</t>
-        </is>
-      </c>
-      <c r="P332" t="inlineStr">
-        <is>
-          <t>true</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>ch6_path_b2</t>
+          <t>ch6_path_b</t>
         </is>
       </c>
       <c r="B333" t="n">
         <v>3</v>
       </c>
-      <c r="C333" t="inlineStr"/>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>허밍이 아직 귓가에서 가시지 않는다. 유웅룡은 자신 또한 저 문턱에서 아주 비켜 선 목격자만은 아니게 되었다는 사실을 안다. 그래서 더더욱, 본 자의 이름으로 적어 두어야 한다.</t>
+          <t>접힌 기록을 또 하나 만들 바엔, 차라리 여기서 같이 부서지는 편이 낫지.</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>thought</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
         </is>
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>ResonanceLevel</t>
-        </is>
-      </c>
-      <c r="P333" t="n">
-        <v>2</v>
+          <t>FoundOldArticles</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>ch6_path_b2</t>
+          <t>ch6_path_b</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>4</v>
-      </c>
-      <c r="C334" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>질문을 끝까지 밀고 와서야, 기록해야 할 문장의 순서도 달라진다. 이판규와 송금, 의식의 설계자까지 하나의 구조로 꿰어졌기에 이번 기록은 더는 단편 기사로 무너지지 않는다.</t>
+          <t>이판규를 미친놈 하나로 접어 두려던 판도 여기서 끝입니다. 불려간 자의 말이 헛소리가 아니었다면, 지금 저 안의 일 역시 우발이 아니라 누군가의 계산이겠지요.</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>thought</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
         </is>
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>SolvedQuestionCount</t>
+          <t>QuestionSolved_QIpangyuMadness</t>
         </is>
       </c>
       <c r="P334" t="inlineStr">
         <is>
-          <t>[2, 3]</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>ch6_ritual_scene</t>
+          <t>ch6_path_b</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>1</v>
-      </c>
-      <c r="C335" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>송순</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Songsoon</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Afraid</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>지하 의례실 깊숙이. 이해심이 제단 앞에 선다. 송금은 청색 한복 차림으로 노래하고 있다. 표정이 없다. 살기 위해 버틴 끝에 생기는 무표정이 아니라, 지나치게 오래 빌려 쓰여 자기 얼굴을 잃어버린 사람의 무표정이다.</t>
+          <t>언니가 달아난 게 아니라 붙들린 거라면, 여기서도 같은 말로 덮이게 둘 순 없어요. 사라진 사람이 먼저 도망쳤다고, 또 그렇게 몰아갈 테니까요.</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>assets/portraits/songsoon.jpeg</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>QuestionSolved_QSonggeumRunaway</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>ch6_ritual_scene</t>
+          <t>ch6_path_b2</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>2</v>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>이해심</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>Haesim</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>Trance</t>
-        </is>
-      </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>Center</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C336" t="inlineStr"/>
       <c r="L336" t="inlineStr">
         <is>
-          <t>어리석은 자들이여. 문이 열리는 날, 경성은 비로소 속을 드러낼 것이다. 곪은 자리는 끝내 누군가 헤집어야 한다. 나는 이제 그 일을 두려워하지 않는다.</t>
+          <t>연락하지 않은 덕분에 아무도 끼어들지 않는다. 이 선택의 결과는 오롯이 두 사람과 의식의 중심에 남는다. 도움을 부르지 않은 대가이기도 하고, 방해받지 않고 끝까지 본 대가이기도 하다.</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="N336" t="inlineStr">
-        <is>
-          <t>assets/portraits/haesim.jpeg</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>ch6_ritual_scene</t>
+          <t>ch6_path_b2</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C337" t="inlineStr"/>
       <c r="L337" t="inlineStr">
         <is>
-          <t>이해심의 뒤편 어둠 속엔 흰 천으로 얼굴을 가린 남자의 형체가 희미하게 선다. 가까이 있는데도 사람이라기보다 남의 신앙을 뒤에서 빨아먹는 그늘처럼 보인다. 향냄새 밑에 눌린 비린내가 그쪽에서 더 짙다.</t>
+          <t>유웅룡이 창고에서 끝까지 읽어 낸 악보와, 자료실에서 주워 온 낡은 기사 조각들이 여기서 하나의 문장으로 겹친다. 흩어져 있던 것들이 이제는 적어 남길 수 있는 증거가 된다.</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
         <is>
           <t>narration</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>ReadRitualScore</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>ch6_ritual_scene</t>
+          <t>ch6_path_b2</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>4</v>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>천용해</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>Cheonyonghae</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="C338" t="inlineStr"/>
       <c r="L338" t="inlineStr">
         <is>
-          <t>교주님, 문은 오래 기다렸습니다. 주저하는 자들 소리까지 들여놓을 까닭은 없지요.</t>
+          <t>허밍이 아직 귓가에서 가시지 않는다. 유웅룡은 자신 또한 저 문턱에서 아주 비켜 선 목격자만은 아니게 되었다는 사실을 안다. 그래서 더더욱, 본 자의 이름으로 적어 두어야 한다.</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="P338" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>ch6_ritual_scene</t>
+          <t>ch6_path_b2</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C339" t="inlineStr"/>
       <c r="L339" t="inlineStr">
         <is>
-          <t>그 순간 유웅룡의 귓속에서 문 앞 허밍이 다시 울린다. 방 안 노래와 어긋나지 않는다. 아까 문에 귀를 댄 뒤로, 이 공간은 이미 몸 안쪽까지 파고든 듯하다.</t>
+          <t>질문을 끝까지 밀고 와서야, 기록해야 할 문장의 순서도 달라진다. 이판규와 송금, 의식의 설계자까지 하나의 구조로 꿰어졌기에 이번 기록은 더는 단편 기사로 무너지지 않는다.</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
@@ -18407,11 +19062,13 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>ResonanceLevel</t>
-        </is>
-      </c>
-      <c r="P339" t="n">
-        <v>2</v>
+          <t>SolvedQuestionCount</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>[2, 3]</t>
+        </is>
       </c>
     </row>
     <row r="340">
@@ -18421,46 +19078,17 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>6</v>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>송금</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>Songgeum</t>
-        </is>
-      </c>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>Trance</t>
-        </is>
-      </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>Center</t>
-        </is>
-      </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C340" t="inlineStr"/>
       <c r="L340" t="inlineStr">
         <is>
-          <t>(표정 없이, 노래를 흥얼거린다) …푸른… 옷을… 입고… 문 앞에… 서서…</t>
+          <t>지하 의례실 깊숙이. 이해심이 제단 앞에 선다. 송금은 청색 한복 차림으로 노래하고 있다. 표정이 없다. 살기 위해 버틴 끝에 생기는 무표정이 아니라, 지나치게 오래 빌려 쓰여 자기 얼굴을 잃어버린 사람의 무표정이다.</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="N340" t="inlineStr">
-        <is>
-          <t>assets/portraits/songgeum.jpeg</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -18471,26 +19099,26 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>송순</t>
+          <t>이해심</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>Haesim</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Uneasy</t>
+          <t>Trance</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -18500,7 +19128,7 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>언니… 언니!</t>
+          <t>어리석은 자들이여. 문이 열리는 날, 경성은 비로소 속을 드러낼 것이다. 곪은 자리는 끝내 누군가 헤집어야 한다. 나는 이제 그 일을 두려워하지 않는다.</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
@@ -18510,7 +19138,7 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t>assets/portraits/songsoon.jpeg</t>
+          <t>assets/portraits/haesim.jpeg</t>
         </is>
       </c>
     </row>
@@ -18521,12 +19149,12 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C342" t="inlineStr"/>
       <c r="L342" t="inlineStr">
         <is>
-          <t>이해심의 안대 아래로 피가 번지기 시작한다. 하나는 불빛, 하나는 서릿발. 문이 열리고 있다. 방 안 촛불이 바깥바람 없이도 같은 방향으로 눕고, 벽면의 푸른 흔적이 젖은 살처럼 미세하게 꿈틀거린다.</t>
+          <t>이해심의 뒤편 어둠 속엔 흰 천으로 얼굴을 가린 남자의 형체가 희미하게 선다. 가까이 있는데도 사람이라기보다 남의 신앙을 뒤에서 빨아먹는 그늘처럼 보인다. 향냄새 밑에 눌린 비린내가 그쪽에서 더 짙다.</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
@@ -18542,26 +19170,26 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>이해심</t>
+          <t>천용해</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Haesim</t>
+          <t>Cheonyonghae</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Trance</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -18571,17 +19199,12 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>너희는 늦었다. 법도, 기사도, 기도도 아무도 구하지 못했다. 나라를 위한다던 자도, 백성을 입에 올리던 자도 결국 하나도 건지지 못했지. 이제 남은 건 치료가 아니라 절단이다. 잘라내지 않으면 이 도시는 끝내 썩은 피를 제 몸이라 착각한 채 죽는다.</t>
+          <t>교주님, 문은 오래 기다렸습니다. 주저하는 자들 소리까지 들여놓을 까닭은 없지요.</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
         <is>
           <t>normal</t>
-        </is>
-      </c>
-      <c r="N343" t="inlineStr">
-        <is>
-          <t>assets/portraits/haesim.jpeg</t>
         </is>
       </c>
     </row>
@@ -18592,47 +19215,26 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>10</v>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>유웅룡</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C344" t="inlineStr"/>
       <c r="L344" t="inlineStr">
         <is>
-          <t>그걸 정화라 부르지 마십시오. 사람을 셈하고 갈아 넣는 짓에 이름만 고상하게 붙인 학살이잖습니까.</t>
+          <t>그 순간 유웅룡의 귓속에서 문 앞 허밍이 다시 울린다. 방 안 노래와 어긋나지 않는다. 아까 문에 귀를 댄 뒤로, 이 공간은 이미 몸 안쪽까지 파고든 듯하다.</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="N344" t="inlineStr">
-        <is>
-          <t>assets/portraits/yuu.jpeg</t>
-        </is>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="P344" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="345">
@@ -18642,16 +19244,16 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>이해심</t>
+          <t>송금</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Haesim</t>
+          <t>Songgeum</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -18671,7 +19273,7 @@
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>학살? 우습구나. 이 도시는 애당초 누군가를 갈아 넣어 움직여 왔다. 빈민가 아이도, 여급도, 병든 여자도, 나라 잃은 백성도 다 써 먹히며 사라졌지. 나는 다만 그 화덕을 휘장 뒤에 숨기지 않을 뿐이야. 너희는 덮고, 나는 드러낸다.</t>
+          <t>(표정 없이, 노래를 흥얼거린다) …푸른… 옷을… 입고… 문 앞에… 서서…</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
@@ -18681,7 +19283,7 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t>assets/portraits/haesim.jpeg</t>
+          <t>assets/portraits/songgeum.jpeg</t>
         </is>
       </c>
     </row>
@@ -18692,26 +19294,26 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>이해심</t>
+          <t>송순</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Haesim</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Trance</t>
+          <t>Uneasy</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -18721,7 +19323,7 @@
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>구원은 온전한 자에게 오지 않는다. 다 망가진 자에게만 문이 열린다. 나는 그걸 누구보다 먼저 배웠다. 황족의 피도, 독립의 꿈도, 여자의 몸도, 병든 폐도 끝내 나를 구하지 못했으니까.</t>
+          <t>언니… 언니!</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
@@ -18731,7 +19333,7 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t>assets/portraits/haesim.jpeg</t>
+          <t>assets/portraits/songsoon.jpeg</t>
         </is>
       </c>
     </row>
@@ -18742,46 +19344,17 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>13</v>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>유웅룡</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E347" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C347" t="inlineStr"/>
       <c r="L347" t="inlineStr">
         <is>
-          <t>당신 뒤에 선 작자가 누군진 이제 알겠습니다. 구원을 입에 올리며 사람 절망을 긁어 모으는 자들 말입니다. 이름만 청의교일 뿐, 속살은 늘 같은 장삿속이군요.</t>
+          <t>이해심의 안대 아래로 피가 번지기 시작한다. 하나는 불빛, 하나는 서릿발. 문이 열리고 있다. 방 안 촛불이 바깥바람 없이도 같은 방향으로 눕고, 벽면의 푸른 흔적이 젖은 살처럼 미세하게 꿈틀거린다.</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="N347" t="inlineStr">
-        <is>
-          <t>assets/portraits/yuu.jpeg</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -18792,26 +19365,26 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>천용해</t>
+          <t>이해심</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Cheonyonghae</t>
+          <t>Haesim</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Trance</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -18821,12 +19394,17 @@
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>장사라…. 말은 곱게도 하는군. 세상은 늘 제 죄를 그런 말로 덮지. 저들은 다만 제 몫을 냈을 뿐이야.</t>
+          <t>너희는 늦었다. 법도, 기사도, 기도도 아무도 구하지 못했다. 나라를 위한다던 자도, 백성을 입에 올리던 자도 결국 하나도 건지지 못했지. 이제 남은 건 치료가 아니라 절단이다. 잘라내지 않으면 이 도시는 끝내 썩은 피를 제 몸이라 착각한 채 죽는다.</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
         <is>
           <t>normal</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>assets/portraits/haesim.jpeg</t>
         </is>
       </c>
     </row>
@@ -18837,26 +19415,26 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>송순</t>
+          <t>유웅룡</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>Yuu</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Uneasy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -18866,7 +19444,7 @@
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>몫이라고 부르지 마. 언니도, 없어졌던 사람들도 누구한테 바칠 몫으로 태어난 적 없어.</t>
+          <t>그걸 정화라 부르지 마십시오. 사람을 셈하고 갈아 넣는 짓에 이름만 고상하게 붙인 학살이잖습니까.</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
@@ -18876,63 +19454,87 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t>assets/portraits/songsoon.jpeg</t>
+          <t>assets/portraits/yuu.jpeg</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>ch6_threshold</t>
+          <t>ch6_ritual_scene</t>
         </is>
       </c>
       <c r="B350" t="n">
-        <v>1</v>
-      </c>
-      <c r="C350" t="inlineStr"/>
-      <c r="K350" t="inlineStr">
-        <is>
-          <t>Flicker</t>
+        <v>11</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>이해심</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Haesim</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Trance</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Center</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>노랫소리를 따라 마지막 문턱을 넘기 직전, 두 사람은 동시에 걸음을 멈춘다. 이제부터는 보고도 모른 척할 수 없다.</t>
+          <t>학살? 우습구나. 이 도시는 애당초 누군가를 갈아 넣어 움직여 왔다. 빈민가 아이도, 여급도, 병든 여자도, 나라 잃은 백성도 다 써 먹히며 사라졌지. 나는 다만 그 화덕을 휘장 뒤에 숨기지 않을 뿐이야. 너희는 덮고, 나는 드러낸다.</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>assets/portraits/haesim.jpeg</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>ch6_threshold</t>
+          <t>ch6_ritual_scene</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>유웅룡</t>
+          <t>이해심</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Haesim</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Tense</t>
+          <t>Trance</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
@@ -18940,19 +19542,9 @@
           <t>Speaker</t>
         </is>
       </c>
-      <c r="H351" t="inlineStr">
-        <is>
-          <t>SlideRight</t>
-        </is>
-      </c>
-      <c r="J351" t="inlineStr">
-        <is>
-          <t>Tremble</t>
-        </is>
-      </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>지금이라도 돌아가고 싶다면 말해요. 여기서부터는 기사도, 증언도, 정의도 우리를 지켜주지 못할 겁니다.</t>
+          <t>구원은 온전한 자에게 오지 않는다. 다 망가진 자에게만 문이 열린다. 나는 그걸 누구보다 먼저 배웠다. 황족의 피도, 독립의 꿈도, 여자의 몸도, 병든 폐도 끝내 나를 구하지 못했으니까.</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
@@ -18962,37 +19554,37 @@
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t>assets/portraits/yuu.jpeg</t>
+          <t>assets/portraits/haesim.jpeg</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>ch6_threshold</t>
+          <t>ch6_ritual_scene</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>송순</t>
+          <t>유웅룡</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>Yuu</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Afraid</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
@@ -19000,19 +19592,9 @@
           <t>Speaker</t>
         </is>
       </c>
-      <c r="H352" t="inlineStr">
-        <is>
-          <t>FadeIn</t>
-        </is>
-      </c>
-      <c r="J352" t="inlineStr">
-        <is>
-          <t>Tremble</t>
-        </is>
-      </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>무서워요. 그런데 돌아가면 더 무서울 것 같아요. 언니를 남겨두고 살아가는 쪽이요.</t>
+          <t>당신 뒤에 선 작자가 누군진 이제 알겠습니다. 구원을 입에 올리며 사람 절망을 긁어 모으는 자들 말입니다. 이름만 청의교일 뿐, 속살은 늘 같은 장삿속이군요.</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
@@ -19022,27 +19604,27 @@
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t>assets/portraits/songsoon.jpeg</t>
+          <t>assets/portraits/yuu.jpeg</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>ch6_threshold</t>
+          <t>ch6_ritual_scene</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>유웅룡</t>
+          <t>천용해</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Cheonyonghae</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -19062,47 +19644,42 @@
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>그럼 갑시다. 이번엔 끝까지 갑니다.</t>
+          <t>장사라…. 말은 곱게도 하는군. 세상은 늘 제 죄를 그런 말로 덮지. 저들은 다만 제 몫을 냈을 뿐이야.</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
         <is>
           <t>normal</t>
-        </is>
-      </c>
-      <c r="N353" t="inlineStr">
-        <is>
-          <t>assets/portraits/yuu.jpeg</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>ch6_threshold</t>
+          <t>ch6_ritual_scene</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>유웅룡</t>
+          <t>송순</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Uneasy</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
@@ -19112,7 +19689,7 @@
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>누가 덮으라 해도, 이번엔 못 접습니다. 자료실에서 본 그 기사도 결국 여기까지 이어져 있었으니까.</t>
+          <t>몫이라고 부르지 마. 언니도, 없어졌던 사람들도 누구한테 바칠 몫으로 태어난 적 없어.</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
@@ -19122,17 +19699,7 @@
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>assets/portraits/yuu.jpeg</t>
-        </is>
-      </c>
-      <c r="O354" t="inlineStr">
-        <is>
-          <t>FoundOldArticles</t>
-        </is>
-      </c>
-      <c r="P354" t="inlineStr">
-        <is>
-          <t>true</t>
+          <t>assets/portraits/songsoon.jpeg</t>
         </is>
       </c>
     </row>
@@ -19143,55 +19710,23 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>6</v>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>유웅룡</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E355" t="inlineStr">
-        <is>
-          <t>Tense</t>
-        </is>
-      </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>Speaker</t>
+        <v>1</v>
+      </c>
+      <c r="C355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Flicker</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>그리고… 문 앞에서 들은 소리가 아직 귓속에 남아 있습니다. 저 안이 우릴 먼저 듣고 있다는 걸 알면서도 들어가는 셈이지요.</t>
+          <t>노랫소리를 따라 마지막 문턱을 넘기 직전, 두 사람은 동시에 걸음을 멈춘다. 이제부터는 보고도 모른 척할 수 없다.</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>thought</t>
-        </is>
-      </c>
-      <c r="N355" t="inlineStr">
-        <is>
-          <t>assets/portraits/yuu.jpeg</t>
-        </is>
-      </c>
-      <c r="O355" t="inlineStr">
-        <is>
-          <t>ResonanceLevel</t>
-        </is>
-      </c>
-      <c r="P355" t="n">
-        <v>2</v>
+          <t>narration</t>
+        </is>
       </c>
     </row>
     <row r="356">
@@ -19201,26 +19736,26 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>송순</t>
+          <t>유웅룡</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>Yuu</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Uneasy</t>
+          <t>Tense</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
@@ -19228,9 +19763,19 @@
           <t>Speaker</t>
         </is>
       </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>SlideRight</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>Tremble</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>기자님이 내 말을 먼저 믿어 줬으니, 저도 이번엔 망설이지 않을게요. 문이 열리면, 제가 먼저 언니를 부를게요.</t>
+          <t>지금이라도 돌아가고 싶다면 말해요. 여기서부터는 기사도, 증언도, 정의도 우리를 지켜주지 못할 겁니다.</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
@@ -19240,17 +19785,7 @@
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t>assets/portraits/songsoon.jpeg</t>
-        </is>
-      </c>
-      <c r="O356" t="inlineStr">
-        <is>
-          <t>TrustedSongsoon</t>
-        </is>
-      </c>
-      <c r="P356" t="inlineStr">
-        <is>
-          <t>true</t>
+          <t>assets/portraits/yuu.jpeg</t>
         </is>
       </c>
     </row>
@@ -19261,26 +19796,26 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>유웅룡</t>
+          <t>송순</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Tense</t>
+          <t>Afraid</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
@@ -19288,28 +19823,30 @@
           <t>Speaker</t>
         </is>
       </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>FadeIn</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>Tremble</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>자료실에서 주운 기사도, 방 안에서 읽은 기록도 결국 여기까지 밀려왔군요. 이제 남은 건 외면하지 않는 일뿐입니다.</t>
+          <t>무서워요. 그런데 돌아가면 더 무서울 것 같아요. 언니를 남겨두고 살아가는 쪽이요.</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
         <is>
-          <t>assets/portraits/yuu.jpeg</t>
-        </is>
-      </c>
-      <c r="O357" t="inlineStr">
-        <is>
-          <t>InvestigationScore</t>
-        </is>
-      </c>
-      <c r="P357" t="n">
-        <v>3</v>
+          <t>assets/portraits/songsoon.jpeg</t>
+        </is>
       </c>
     </row>
     <row r="358">
@@ -19319,27 +19856,46 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>9</v>
-      </c>
-      <c r="C358" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>누구에게도 연락하지 않기로 한 덕에, 두 사람은 도움받을 길도 핑계 댈 길도 없이 같은 공포를 정면으로 마주 선다.</t>
+          <t>그럼 갑시다. 이번엔 끝까지 갑니다.</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>narration</t>
-        </is>
-      </c>
-      <c r="O358" t="inlineStr">
-        <is>
-          <t>CalledEditor</t>
-        </is>
-      </c>
-      <c r="P358" t="inlineStr">
-        <is>
-          <t>false</t>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
         </is>
       </c>
     </row>
@@ -19350,7 +19906,7 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
@@ -19364,7 +19920,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Tense</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -19379,12 +19935,12 @@
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>의례실 바닥에서 주운 종이까지 여기로 이어집니다. 남은 건 문장으로 증명하는 일이 아니라, 저 안에서 실제로 끊어내는 일입니다.</t>
+          <t>누가 덮으라 해도, 이번엔 못 접습니다. 자료실에서 본 그 기사도 결국 여기까지 이어져 있었으니까.</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -19394,7 +19950,7 @@
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t>HasEvidence_EvRitualNote</t>
+          <t>FoundOldArticles</t>
         </is>
       </c>
       <c r="P359" t="inlineStr">
@@ -19410,25 +19966,292 @@
         </is>
       </c>
       <c r="B360" t="n">
+        <v>6</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>그리고… 문 앞에서 들은 소리가 아직 귓속에 남아 있습니다. 저 안이 우릴 먼저 듣고 있다는 걸 알면서도 들어가는 셈이지요.</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>thought</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="P360" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>ch6_threshold</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>7</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>송순</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Songsoon</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Uneasy</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>기자님이 내 말을 먼저 믿어 줬으니, 저도 이번엔 망설이지 않을게요. 문이 열리면, 제가 먼저 언니를 부를게요.</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>assets/portraits/songsoon.jpeg</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>TrustedSongsoon</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>ch6_threshold</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>8</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>자료실에서 주운 기사도, 방 안에서 읽은 기록도 결국 여기까지 밀려왔군요. 이제 남은 건 외면하지 않는 일뿐입니다.</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>thought</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>InvestigationScore</t>
+        </is>
+      </c>
+      <c r="P362" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>ch6_threshold</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>9</v>
+      </c>
+      <c r="C363" t="inlineStr"/>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>누구에게도 연락하지 않기로 한 덕에, 두 사람은 도움받을 길도 핑계 댈 길도 없이 같은 공포를 정면으로 마주 선다.</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>CalledEditor</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>ch6_threshold</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>10</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>유웅룡</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>의례실 바닥에서 주운 종이까지 여기로 이어집니다. 남은 건 문장으로 증명하는 일이 아니라, 저 안에서 실제로 끊어내는 일입니다.</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>thought</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>assets/portraits/yuu.jpeg</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>HasEvidence_EvRitualNote</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>ch6_threshold</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
         <v>11</v>
       </c>
-      <c r="C360" t="inlineStr"/>
-      <c r="L360" t="inlineStr">
+      <c r="C365" t="inlineStr"/>
+      <c r="L365" t="inlineStr">
         <is>
           <t>병원, 폐공장, 자료실, 의례실에서 붙잡은 질문들이 이제야 한 줄로 선다. 끝내 다 푼 것은 아니어도, 무엇을 끊어야 하는지는 더 이상 흐리지 않다.</t>
         </is>
       </c>
-      <c r="M360" t="inlineStr">
+      <c r="M365" t="inlineStr">
         <is>
           <t>narration</t>
         </is>
       </c>
-      <c r="O360" t="inlineStr">
+      <c r="O365" t="inlineStr">
         <is>
           <t>SolvedQuestionCount</t>
         </is>
       </c>
-      <c r="P360" t="inlineStr">
+      <c r="P365" t="inlineStr">
         <is>
           <t>[2, 3]</t>
         </is>

--- a/content/generated/script.generated.xlsx
+++ b/content/generated/script.generated.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-06 06:08:46</t>
+          <t>2026-04-06 06:42:27</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
@@ -3791,7 +3791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3829,22 +3829,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cond_Branch_ExposedArchive_01</t>
+          <t>Cond_Backroom_EditorRel0_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CG_Branch_ExposedArchivePattern</t>
+          <t>CG_Backroom_EditorRel0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>StateValue</t>
+          <t>Trust</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ExposedArchivePattern</t>
+          <t>Editor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3852,63 +3852,59 @@
           <t>Equal</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="F2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cond_Branch_ExposedTruth_01</t>
+          <t>Cond_Backroom_EditorRel1_01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CG_Branch_ExposedTruthAtRitual</t>
+          <t>CG_Backroom_EditorRel1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>StateValue</t>
+          <t>Trust</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ExposedTruthAtRitual</t>
+          <t>Editor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cond_Branch_FinalChoice_A</t>
+          <t>Cond_Backroom_FoundOldArticles_01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CG_Branch_FinalChoice_A</t>
+          <t>CG_Backroom_FoundOldArticles</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>StateValue</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FinalChoice</t>
+          <t>Ch4ALibraryTakeArticles|Ch4ALibraryExposeArchive</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3918,29 +3914,29 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cond_Branch_FinalChoice_B</t>
+          <t>Cond_Branch_CalledEditorFalse_01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CG_Branch_FinalChoice_B</t>
+          <t>CG_Branch_CalledEditorFalse</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>StateValue</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FinalChoice</t>
+          <t>Ch5PathNoContact</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3950,19 +3946,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cond_Branch_FinalChoice_C</t>
+          <t>Cond_Branch_EndingAScore2_01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CG_Branch_FinalChoice_C</t>
+          <t>CG_Branch_EndingAScore2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3972,39 +3968,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FinalChoice</t>
+          <t>EndingAScore</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cond_Branch_FoundOldArticles_01</t>
+          <t>Cond_Branch_ExposedArchive_01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CG_Branch_FoundOldArticles</t>
+          <t>CG_Branch_ExposedArchivePattern</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>StateValue</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FoundOldArticles</t>
+          <t>Ch4ALibraryExposeArchive</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4021,22 +4015,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cond_Branch_MatchedPattern_01</t>
+          <t>Cond_Branch_ExposedTruth_01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CG_Branch_MatchedPattern</t>
+          <t>CG_Branch_ExposedTruthAtRitual</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>StateValue</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MatchedRitualPattern</t>
+          <t>Ch6FinalExpose</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4053,22 +4047,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cond_Branch_SolvedMid_01</t>
+          <t>Cond_Branch_FinalChoice_A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CG_Branch_SolvedMid</t>
+          <t>CG_Branch_FinalChoice_A</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>StateValue</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SolvedQuestionCount</t>
+          <t>Ch6FinalAnswer</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4078,29 +4072,29 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[2, 3]</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cond_Branch_TouchedRoomWall_01</t>
+          <t>Cond_Branch_FinalChoice_B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CG_Branch_TouchedRoomWall</t>
+          <t>CG_Branch_FinalChoice_B</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>StateValue</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>TouchedRoomWall</t>
+          <t>Ch6FinalBlock|Ch6FinalExpose</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4117,22 +4111,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cond_Library_BlueHanbok_01</t>
+          <t>Cond_Branch_FinalChoice_C</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CG_Library_BlueHanbok</t>
+          <t>CG_Branch_FinalChoice_C</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EvBlueHanbok</t>
+          <t>Ch6FinalHesitate</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4149,22 +4143,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cond_Library_Diary_01</t>
+          <t>Cond_Branch_FoundOldArticles_01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CG_Library_Diary</t>
+          <t>CG_Branch_FoundOldArticles</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EvDiary</t>
+          <t>Ch4ALibraryTakeArticles|Ch4ALibraryExposeArchive</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -4181,12 +4175,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cond_Library_Investigation_01</t>
+          <t>Cond_Branch_Investigation3_01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CG_Library_Investigation2</t>
+          <t>CG_Branch_Investigation3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4205,18 +4199,18 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cond_Library_RunawaySolved_01</t>
+          <t>Cond_Branch_MatchedPattern_01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CG_Library_QSonggeumRunaway</t>
+          <t>CG_Branch_MatchedPattern</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4226,7 +4220,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>QuestionSolved_QSonggeumRunaway</t>
+          <t>MatchedRitualPattern</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -4243,12 +4237,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cond_Outcome_QMadness_01</t>
+          <t>Cond_Branch_OkryunPushed_01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CG_Outcome_QMadness</t>
+          <t>CG_Branch_OkryunPushed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4258,7 +4252,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>QuestionSolved_QIpangyuMadness</t>
+          <t>OkryunPushed</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4275,12 +4269,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cond_Outcome_QRunaway_01</t>
+          <t>Cond_Branch_ReadRitual_01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CG_Outcome_QRunaway</t>
+          <t>CG_Branch_ReadRitual</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4290,7 +4284,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>QuestionSolved_QSonggeumRunaway</t>
+          <t>ReadRitualScore</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4307,12 +4301,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cond_Outcome_SolvedMid_01</t>
+          <t>Cond_Branch_SolvedMid_01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CG_Outcome_SolvedMid</t>
+          <t>CG_Branch_SolvedMid</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4339,86 +4333,82 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cond_RitualRoom_OldArticles_01</t>
+          <t>Cond_Branch_SongsoonTrust1_01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CG_RitualRoom_OldArticles</t>
+          <t>CG_Branch_SongsoonTrust1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>Trust</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EvOldArticles</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cond_RitualRoom_AccidentSolved_01</t>
+          <t>Cond_Branch_SongsoonTrust2_01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CG_RitualRoom_QRitualAccident</t>
+          <t>CG_Branch_SongsoonTrust2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>StateValue</t>
+          <t>Trust</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>QuestionSolved_QRitualAccident</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cond_RitualRoom_RitualScore_01</t>
+          <t>Cond_Branch_TouchedRoomWall_01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CG_RitualRoom_RitualScore</t>
+          <t>CG_Branch_TouchedRoomWall</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>StateValue</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EvRitualScore</t>
+          <t>TouchedRoomWall</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4435,52 +4425,54 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cond_RitualScene_Resonance_01</t>
+          <t>Cond_Cafe_Info2_01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CG_RitualScene_Resonance2</t>
+          <t>CG_Cafe_Info2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ResonanceLevel</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ResonanceLevel</t>
+          <t>Ch2HospitalAskDoor</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>2</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cond_RitualScene_SolvedHigh_01</t>
+          <t>Cond_Descent_CalledEditorTrue_01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CG_RitualScene_SolvedHigh</t>
+          <t>CG_Descent_CalledEditorTrue</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>StateValue</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SolvedQuestionCount</t>
+          <t>Ch5PathContactEditor</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4490,61 +4482,59 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[4, 5, 6]</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cond_Room4_ReadRitual_01</t>
+          <t>Cond_Descent_SongsoonTrust1_01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CG_Room4_ReadRitual</t>
+          <t>CG_Descent_SongsoonTrust1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>StateValue</t>
+          <t>Trust</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ReadRitualScore</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cond_Room4_TrustedSongsoon_01</t>
+          <t>Cond_Hospital_Info2_01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CG_Room4_TrustedSongsoon</t>
+          <t>CG_Hospital_Info2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>StateValue</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TrustedSongsoon</t>
+          <t>Ch2HospitalAskDoor</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4561,22 +4551,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cond_Threshold_CalledEditorFalse_01</t>
+          <t>Cond_Library_BlueHanbok_01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CG_Threshold_CalledEditorFalse</t>
+          <t>CG_Library_BlueHanbok</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>StateValue</t>
+          <t>EvidenceOwned</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CalledEditor</t>
+          <t>EvBlueHanbok</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4586,29 +4576,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cond_Threshold_FoundOldArticles_01</t>
+          <t>Cond_Library_Diary_01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CG_Threshold_FoundOldArticles</t>
+          <t>CG_Library_Diary</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>StateValue</t>
+          <t>EvidenceOwned</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FoundOldArticles</t>
+          <t>EvDiary</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4625,12 +4615,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cond_Threshold_Investigation_01</t>
+          <t>Cond_Library_Investigation_01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CG_Threshold_Investigation3</t>
+          <t>CG_Library_Investigation2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4649,58 +4639,60 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cond_Threshold_Resonance_01</t>
+          <t>Cond_Library_RunawaySolved_01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CG_Threshold_Resonance2</t>
+          <t>CG_Library_QSonggeumRunaway</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ResonanceLevel</t>
+          <t>StateValue</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ResonanceLevel</t>
+          <t>QuestionSolved_QSonggeumRunaway</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>2</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cond_Threshold_RitualNote_01</t>
+          <t>Cond_Outcome_QMadness_01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CG_Threshold_RitualNote</t>
+          <t>CG_Outcome_QMadness</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>StateValue</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EvRitualNote</t>
+          <t>QuestionSolved_QIpangyuMadness</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4717,12 +4709,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cond_Threshold_SolvedMid_01</t>
+          <t>Cond_Outcome_QRunaway_01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CG_Threshold_SolvedMid</t>
+          <t>CG_Outcome_QRunaway</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4732,7 +4724,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SolvedQuestionCount</t>
+          <t>QuestionSolved_QSonggeumRunaway</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4742,37 +4734,511 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[2, 3]</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Cond_Outcome_SolvedMid_01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CG_Outcome_SolvedMid</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>StateValue</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SolvedQuestionCount</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>[2, 3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Cond_RitualRoom_OldArticles_01</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CG_RitualRoom_OldArticles</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EvidenceOwned</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>EvOldArticles</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Cond_RitualRoom_AccidentSolved_01</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CG_RitualRoom_QRitualAccident</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>StateValue</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>QuestionSolved_QRitualAccident</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Cond_RitualRoom_QRitualAccident_01</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CG_RitualRoom_QRitualAccident</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>StateValue</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>QuestionSolved_QRitualAccident</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Cond_RitualRoom_RitualScore_01</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CG_RitualRoom_RitualScore</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EvidenceOwned</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>EvRitualScore</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Cond_RitualScene_Resonance_01</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CG_RitualScene_Resonance2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Cond_RitualScene_SolvedHigh_01</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CG_RitualScene_SolvedHigh</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>StateValue</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SolvedQuestionCount</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>[4, 5, 6]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Cond_Room4_ReadRitual_01</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CG_Room4_ReadRitual</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>StateValue</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ReadRitualScore</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Cond_Room4_TrustedSongsoon_01</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CG_Room4_TrustedSongsoon</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>StateValue</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TrustedSongsoon</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Cond_Threshold_CalledEditorFalse_01</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CG_Threshold_CalledEditorFalse</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ChoiceSelected</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Ch5PathNoContact</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Cond_Threshold_FoundOldArticles_01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CG_Threshold_FoundOldArticles</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ChoiceSelected</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Ch4ALibraryTakeArticles|Ch4ALibraryExposeArchive</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Cond_Threshold_Investigation_01</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CG_Threshold_Investigation3</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>InvestigationScore</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>InvestigationScore</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Cond_Threshold_Resonance_01</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CG_Threshold_Resonance2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Cond_Threshold_RitualNote_01</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CG_Threshold_RitualNote</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>EvidenceOwned</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>EvRitualNote</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Cond_Threshold_SolvedMid_01</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CG_Threshold_SolvedMid</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>StateValue</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SolvedQuestionCount</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>[2, 3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>Cond_Threshold_TrustedSongsoon_01</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>CG_Threshold_TrustedSongsoon</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>StateValue</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>TrustedSongsoon</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Equal</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>true</t>
         </is>
@@ -9552,6 +10018,11 @@
           <t>narration</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>CG_Hospital_Info2</t>
+        </is>
+      </c>
       <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
@@ -9845,6 +10316,11 @@
           <t>thought</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>CG_Hospital_Info2</t>
+        </is>
+      </c>
       <c r="Q76" t="inlineStr">
         <is>
           <t>유웅룡</t>
@@ -10815,6 +11291,11 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>CG_Room4_TrustedSongsoon</t>
+        </is>
+      </c>
       <c r="Q98" t="inlineStr">
         <is>
           <t>송순</t>
@@ -10886,6 +11367,11 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>CG_Room4_TrustedSongsoon</t>
+        </is>
+      </c>
       <c r="Q100" t="inlineStr">
         <is>
           <t>송순</t>
@@ -11528,6 +12014,11 @@
           <t>thought</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>CG_Room4_ReadRitual</t>
+        </is>
+      </c>
       <c r="Q114" t="inlineStr">
         <is>
           <t>유웅룡</t>
@@ -11578,6 +12069,11 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>CG_Room4_TrustedSongsoon</t>
+        </is>
+      </c>
       <c r="Q115" t="inlineStr">
         <is>
           <t>송순</t>
@@ -13840,6 +14336,11 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>CG_Backroom_EditorRel1</t>
+        </is>
+      </c>
       <c r="Q166" t="inlineStr">
         <is>
           <t>편집장</t>
@@ -13890,6 +14391,11 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>CG_Backroom_EditorRel0</t>
+        </is>
+      </c>
       <c r="Q167" t="inlineStr">
         <is>
           <t>편집장</t>
@@ -13990,6 +14496,11 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>CG_Backroom_FoundOldArticles</t>
+        </is>
+      </c>
       <c r="Q169" t="inlineStr">
         <is>
           <t>유웅룡</t>
@@ -14040,6 +14551,11 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>CG_Backroom_FoundOldArticles</t>
+        </is>
+      </c>
       <c r="Q170" t="inlineStr">
         <is>
           <t>편집장</t>
@@ -16443,6 +16959,11 @@
           <t>thought</t>
         </is>
       </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>CG_Room4_ReadRitual</t>
+        </is>
+      </c>
       <c r="Q222" t="inlineStr">
         <is>
           <t>유웅룡</t>
@@ -16614,6 +17135,11 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>CG_Threshold_TrustedSongsoon</t>
+        </is>
+      </c>
       <c r="Q226" t="inlineStr">
         <is>
           <t>송순</t>
@@ -16927,6 +17453,11 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>CG_Room4_ReadRitual</t>
+        </is>
+      </c>
       <c r="Q234" t="inlineStr">
         <is>
           <t>유웅룡</t>
@@ -16977,6 +17508,11 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>CG_Threshold_TrustedSongsoon</t>
+        </is>
+      </c>
       <c r="Q235" t="inlineStr">
         <is>
           <t>송순</t>
@@ -17027,6 +17563,11 @@
           <t>thought</t>
         </is>
       </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>CG_Descent_CalledEditorTrue</t>
+        </is>
+      </c>
       <c r="Q236" t="inlineStr">
         <is>
           <t>유웅룡</t>
@@ -17634,6 +18175,11 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>CG_Descent_SongsoonTrust1</t>
+        </is>
+      </c>
       <c r="Q249" t="inlineStr">
         <is>
           <t>송순</t>
@@ -18055,6 +18601,11 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>CG_Threshold_TrustedSongsoon</t>
+        </is>
+      </c>
       <c r="Q258" t="inlineStr">
         <is>
           <t>유웅룡</t>
@@ -18105,6 +18656,11 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>CG_Threshold_Investigation3</t>
+        </is>
+      </c>
       <c r="Q259" t="inlineStr">
         <is>
           <t>유웅룡</t>
@@ -18504,6 +19060,11 @@
           <t>narration</t>
         </is>
       </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>CG_Threshold_Resonance2</t>
+        </is>
+      </c>
       <c r="Q269" t="inlineStr"/>
     </row>
     <row r="270">
@@ -18615,6 +19176,11 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>CG_Threshold_TrustedSongsoon</t>
+        </is>
+      </c>
       <c r="Q271" t="inlineStr">
         <is>
           <t>송순</t>
@@ -18650,6 +19216,11 @@
           <t>narration</t>
         </is>
       </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>CG_Descent_CalledEditorTrue</t>
+        </is>
+      </c>
       <c r="Q272" t="inlineStr"/>
     </row>
     <row r="273">
@@ -19155,6 +19726,11 @@
           <t>thought</t>
         </is>
       </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>CG_Outcome_QMadness</t>
+        </is>
+      </c>
       <c r="Q284" t="inlineStr">
         <is>
           <t>유웅룡</t>
@@ -19205,6 +19781,11 @@
           <t>normal</t>
         </is>
       </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>CG_Outcome_QRunaway</t>
+        </is>
+      </c>
       <c r="Q285" t="inlineStr">
         <is>
           <t>송순</t>
@@ -20978,6 +21559,11 @@
           <t>narration</t>
         </is>
       </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>CG_Threshold_TrustedSongsoon</t>
+        </is>
+      </c>
       <c r="Q335" t="inlineStr"/>
     </row>
     <row r="336">
@@ -20999,6 +21585,11 @@
           <t>narration</t>
         </is>
       </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>CG_Threshold_Resonance2</t>
+        </is>
+      </c>
       <c r="Q336" t="inlineStr"/>
     </row>
     <row r="337">
@@ -21020,6 +21611,11 @@
           <t>narration</t>
         </is>
       </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>CG_Branch_SolvedMid</t>
+        </is>
+      </c>
       <c r="Q337" t="inlineStr"/>
     </row>
     <row r="338">
@@ -21039,6 +21635,11 @@
       <c r="M338" t="inlineStr">
         <is>
           <t>narration</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>CG_Branch_MatchedPattern</t>
         </is>
       </c>
       <c r="Q338" t="inlineStr"/>
@@ -22760,6 +23361,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ch1NewsroomObedient</t>
+        </is>
+      </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
@@ -22768,31 +23374,36 @@
           <t>세간의 입에 오를 만한 글로 꾸며 보지요.</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Scene</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ch1_newsroom_obedient</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Editor</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>ch1_newsroom</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>EditorRel</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>ch1_newsroom_obedient</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>choice_obedient_react</t>
-        </is>
-      </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ch1NewsroomDefiant</t>
+        </is>
+      </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
@@ -22801,27 +23412,19 @@
           <t>신문감은 되겠지만, 이대로 덮을 마음은 없습니다.</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Scene</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ch1_newsroom_defiant</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>ch1_newsroom</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>EditorRel</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>ch1_newsroom_defiant</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>choice_defiant_react</t>
         </is>
       </c>
     </row>
@@ -22839,6 +23442,16 @@
           <t>점장에게 더 캐묻는다</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dialog</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>inv_mgr</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>ch2_cafe</t>
@@ -22852,11 +23465,6 @@
       <c r="N4" t="inlineStr">
         <is>
           <t>true</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>inv_mgr</t>
         </is>
       </c>
     </row>
@@ -22874,6 +23482,16 @@
           <t>지나치는 여급의 반응을 확인한다</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dialog</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>inv_wtrs</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>ch2_cafe</t>
@@ -22887,11 +23505,6 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>true</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>inv_wtrs</t>
         </is>
       </c>
     </row>
@@ -22909,6 +23522,16 @@
           <t>구석에 앉은 여자를 살핀다</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dialog</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>inv_obs</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>ch2_cafe</t>
@@ -22924,13 +23547,13 @@
           <t>true</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>inv_obs</t>
-        </is>
-      </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ch2HospitalAskRoot</t>
+        </is>
+      </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
@@ -22939,31 +23562,28 @@
           <t>그 망상의 근원부터 기어이 묻고 늘어진다.</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Scene</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ch2_hospital_a</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>ch2_hospital</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>InfoLevel</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>ch2_hospital_a</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>ask_root_react</t>
-        </is>
-      </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ch2HospitalAskDoor</t>
+        </is>
+      </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
@@ -22972,27 +23592,19 @@
           <t>그가 벌벌 떠는 '문'의 정체부터 확인한다.</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Scene</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ch2_hospital_b</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>ch2_hospital</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>InfoLevel</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>2</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>ch2_hospital_b</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>ask_door_react</t>
         </is>
       </c>
     </row>
@@ -23010,6 +23622,16 @@
           <t>위험을 감수하고 벽의 문양에 직접 손을 댄다.</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dialog</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>room4_touch</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>ch3_room4</t>
@@ -23023,11 +23645,6 @@
       <c r="N9" t="n">
         <v>2</v>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>room4_touch</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
@@ -23043,6 +23660,16 @@
           <t>공포보다 기록을 우선하고 일기장의 다음 장을 더 읽는다.</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dialog</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>room4_record</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>ch3_room4</t>
@@ -23056,11 +23683,6 @@
       <c r="N10" t="inlineStr">
         <is>
           <t>true</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>room4_record</t>
         </is>
       </c>
     </row>
@@ -23078,6 +23700,16 @@
           <t>증거보다 먼저 송순에게 혼자 떠맡지 말자고 말한다.</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dialog</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>room4_comfort</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>ch3_room4</t>
@@ -23091,11 +23723,6 @@
       <c r="N11" t="inlineStr">
         <is>
           <t>true</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>room4_comfort</t>
         </is>
       </c>
     </row>
@@ -23108,6 +23735,16 @@
           <t>관자놀이가 깨질 듯해도 악보를 끝까지 읽어 낸다.</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Scene</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ch3_score_read</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>ch3_warehouse</t>
@@ -23121,16 +23758,6 @@
       <c r="N12" t="inlineStr">
         <is>
           <t>true</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>ch3_score_read</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>score_read_react</t>
         </is>
       </c>
     </row>
@@ -23143,6 +23770,16 @@
           <t>악보보다 송순 씨의 귀와 숨결을 먼저 믿는다.</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Scene</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ch3_score_trust</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>ch3_warehouse</t>
@@ -23158,18 +23795,13 @@
           <t>true</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>ch3_score_trust</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>score_trust_react</t>
-        </is>
-      </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ch4ALibraryTakeArticles</t>
+        </is>
+      </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
@@ -23178,29 +23810,19 @@
           <t>기사 뭉치를 챙긴다.</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Scene</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ch4a_articles_take</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>ch4a_library</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>FoundOldArticles</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>ch4a_articles_take</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>articles_take_react</t>
         </is>
       </c>
     </row>
@@ -23213,6 +23835,16 @@
           <t>핵심 문장만 수첩에 적고 넘어간다.</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Scene</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ch4a_articles_note</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>ch4a_library</t>
@@ -23226,18 +23858,13 @@
       <c r="N15" t="n">
         <v>3</v>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>ch4a_articles_note</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>articles_note_react</t>
-        </is>
-      </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ch4ALibraryExposeArchive</t>
+        </is>
+      </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
@@ -23251,29 +23878,19 @@
           <t>CG_Library_QSonggeumRunaway</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Scene</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ch4a_articles_expose</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>ch4a_library</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>FoundOldArticles</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>ch4a_articles_expose</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>articles_expose_react</t>
         </is>
       </c>
     </row>
@@ -23286,6 +23903,16 @@
           <t>알겠어요. 더는 억지로 묻지 않을게요.</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Scene</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ch4b_cafe_hold</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>ch4b_cafe</t>
@@ -23298,16 +23925,6 @@
       </c>
       <c r="N17" t="n">
         <v>2</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>ch4b_cafe_hold</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>hold_react</t>
-        </is>
       </c>
     </row>
     <row r="18">
@@ -23319,6 +23936,16 @@
           <t>조금만 더 말해줘요. 여기서 멈출 순 없어요.</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Scene</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ch4b_cafe_press</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>ch4b_cafe</t>
@@ -23332,16 +23959,6 @@
       <c r="N18" t="inlineStr">
         <is>
           <t>true</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>ch4b_cafe_press</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>press_react</t>
         </is>
       </c>
     </row>
@@ -23354,6 +23971,16 @@
           <t>허밍의 결을 끝까지 듣고, 문 안쪽 호흡을 짚어 본다.</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Scene</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ch5_guarded_door_listen</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>ch5_guarded_door</t>
@@ -23366,16 +23993,6 @@
       </c>
       <c r="N19" t="n">
         <v>2</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>ch5_guarded_door_listen</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>door_listen_react</t>
-        </is>
       </c>
     </row>
     <row r="20">
@@ -23387,6 +24004,16 @@
           <t>송순과 숨을 고른 뒤, 함께 문을 민다.</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Scene</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ch5_guarded_door_steady</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>ch5_guarded_door</t>
@@ -23400,18 +24027,13 @@
       <c r="N20" t="n">
         <v>2</v>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>ch5_guarded_door_steady</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>door_steady_react</t>
-        </is>
-      </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ch5PathContactEditor</t>
+        </is>
+      </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
@@ -23420,33 +24042,28 @@
           <t>편집장에게 연락한다.</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Scene</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ch5_contact_editor</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>ch5_ritual_path</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>CalledEditor</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>ch5_contact_editor</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>contact_editor_react</t>
-        </is>
-      </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ch5PathNoContact</t>
+        </is>
+      </c>
       <c r="C22" t="n">
         <v>2</v>
       </c>
@@ -23455,33 +24072,28 @@
           <t>말하지 않는다. 둘만 간다.</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Scene</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ch5_no_contact</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>ch5_ritual_path</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>CalledEditor</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>ch5_no_contact</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>no_contact_react</t>
-        </is>
-      </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ch6FinalAnswer</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>ChoiceGroup_RitualFinal</t>
@@ -23495,28 +24107,28 @@
           <t>송순이 언니의 노래에 응답한다.</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Dialog</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ritual_answer</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>ch6_ritual_scene</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>FinalChoice</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>ritual_answer</t>
-        </is>
-      </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ch6FinalBlock</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>ChoiceGroup_RitualFinal</t>
@@ -23530,28 +24142,28 @@
           <t>유웅룡이 이해심을 막으러 달려간다.</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dialog</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ritual_block</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>ch6_ritual_scene</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>FinalChoice</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>ritual_block</t>
-        </is>
-      </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ch6FinalHesitate</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>ChoiceGroup_RitualFinal</t>
@@ -23565,28 +24177,28 @@
           <t>아무것도 하지 않고 지켜본다.</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Dialog</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ritual_hesitate</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>ch6_ritual_scene</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>FinalChoice</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>ritual_hesitate</t>
-        </is>
-      </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ch6FinalExpose</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>ChoiceGroup_RitualFinal</t>
@@ -23605,24 +24217,19 @@
           <t>CG_RitualScene_SolvedHigh</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dialog</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ritual_expose</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>ch6_ritual_scene</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>FinalChoice</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>ritual_expose</t>
         </is>
       </c>
     </row>
@@ -23841,19 +24448,14 @@
       <c r="C8" t="n">
         <v>3</v>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CG_Threshold_TrustedSongsoon</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>ch6_ending_a</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>TrustedSongsoon</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>true</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -23871,18 +24473,15 @@
       <c r="C9" t="n">
         <v>4</v>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CG_Branch_SongsoonTrust2</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>ch6_ending_a</t>
         </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SongsoonTrust</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -23899,18 +24498,15 @@
       <c r="C10" t="n">
         <v>5</v>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CG_Branch_SongsoonTrust1</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>ch6_ending_a</t>
         </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SongsoonTrust</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -23927,19 +24523,14 @@
       <c r="C11" t="n">
         <v>6</v>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CG_Branch_OkryunPushed</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>ch6_ending_a</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>OkryunPushed</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>true</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -23957,18 +24548,15 @@
       <c r="C12" t="n">
         <v>7</v>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CG_Branch_EndingAScore2</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>ch6_ending_a</t>
         </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>EndingAScore</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -24085,19 +24673,14 @@
       <c r="C17" t="n">
         <v>4</v>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CG_Branch_ReadRitual</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>ch6_ending_b</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ReadRitualScore</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>true</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -24115,18 +24698,15 @@
       <c r="C18" t="n">
         <v>5</v>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CG_Branch_Investigation3</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>ch6_ending_b</t>
         </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>InvestigationScore</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>3</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -24143,19 +24723,14 @@
       <c r="C19" t="n">
         <v>6</v>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CG_Branch_CalledEditorFalse</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>ch6_ending_b</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>CalledEditor</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>false</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">

--- a/content/generated/script.generated.xlsx
+++ b/content/generated/script.generated.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-06 06:42:27</t>
+          <t>2026-04-06 06:59:44</t>
         </is>
       </c>
     </row>
@@ -3963,21 +3963,23 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>StateValue</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EndingAScore</t>
+          <t>Ch4BCafeHold</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -4215,12 +4217,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>StateValue</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MatchedRitualPattern</t>
+          <t>Ch5RitualPresentMask</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -4247,12 +4249,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>StateValue</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OkryunPushed</t>
+          <t>Ch4BCafePress</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4279,7 +4281,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>StateValue</t>
+          <t>ReadRitualScore</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4343,12 +4345,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Trust</t>
+          <t>SongsoonTrust</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>SongsoonTrust</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4373,12 +4375,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Trust</t>
+          <t>SongsoonTrust</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>SongsoonTrust</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4499,12 +4501,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Trust</t>
+          <t>SongsoonTrust</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>SongsoonTrust</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4973,7 +4975,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>StateValue</t>
+          <t>ReadRitualScore</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5005,12 +5007,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>StateValue</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>TrustedSongsoon</t>
+          <t>Ch3WarehouseTrustSongsoon|Ch3Room4ComfortSongsoon</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5225,12 +5227,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>StateValue</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>TrustedSongsoon</t>
+          <t>Ch3WarehouseTrustSongsoon|Ch3Room4ComfortSongsoon</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -23336,17 +23338,17 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>StateType</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>StateValue</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>SceneID</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>FlagKey</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>FlagValue</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
@@ -23392,7 +23394,7 @@
       <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>ch1_newsroom</t>
         </is>
@@ -23422,13 +23424,18 @@
           <t>ch1_newsroom_defiant</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>ch1_newsroom</t>
         </is>
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ch2CafeAskManager</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>ChoiceGroup_CafeInvestigation</t>
@@ -23452,23 +23459,18 @@
           <t>inv_mgr</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>ch2_cafe</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>CafeInv_Mgr</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ch2CafeAskWaitress</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>ChoiceGroup_CafeInvestigation</t>
@@ -23492,23 +23494,18 @@
           <t>inv_wtrs</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>ch2_cafe</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>CafeInv_Wtrs</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ch2CafeAskObserver</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>ChoiceGroup_CafeInvestigation</t>
@@ -23532,19 +23529,9 @@
           <t>inv_obs</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>ch2_cafe</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>CafeInv_Obs</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>true</t>
         </is>
       </c>
     </row>
@@ -23572,7 +23559,7 @@
           <t>ch2_hospital_a</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>ch2_hospital</t>
         </is>
@@ -23602,13 +23589,18 @@
           <t>ch2_hospital_b</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>ch2_hospital</t>
         </is>
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ch3Room4TouchWall</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>ChoiceGroup_Room4Investigation</t>
@@ -23634,19 +23626,24 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>ch3_room4</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>ResonanceLevel</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ch3Room4ReadRecord</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>ChoiceGroup_Room4Investigation</t>
@@ -23672,21 +23669,24 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>ReadRitualScore</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>ch3_room4</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>ReadRitualScore</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ch3Room4ComfortSongsoon</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>ChoiceGroup_Room4Investigation</t>
@@ -23710,23 +23710,18 @@
           <t>room4_comfort</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>ch3_room4</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>TrustedSongsoon</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ch3WarehouseReadRitual</t>
+        </is>
+      </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
@@ -23747,21 +23742,24 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t>ReadRitualScore</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t>ch3_warehouse</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>ReadRitualScore</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ch3WarehouseTrustSongsoon</t>
+        </is>
+      </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
@@ -23780,19 +23778,9 @@
           <t>ch3_score_trust</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>ch3_warehouse</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>TrustedSongsoon</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>true</t>
         </is>
       </c>
     </row>
@@ -23820,13 +23808,18 @@
           <t>ch4a_articles_take</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>ch4a_library</t>
         </is>
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ch4ALibraryNoteArticles</t>
+        </is>
+      </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
@@ -23847,16 +23840,16 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t>InvestigationScore</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>3</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>ch4a_library</t>
         </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>InvestigationScore</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -23888,13 +23881,18 @@
           <t>ch4a_articles_expose</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>ch4a_library</t>
         </is>
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ch4BCafeHold</t>
+        </is>
+      </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
@@ -23913,21 +23911,18 @@
           <t>ch4b_cafe_hold</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>ch4b_cafe</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>EndingAScore</t>
-        </is>
-      </c>
-      <c r="N17" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ch4BCafePress</t>
+        </is>
+      </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
@@ -23946,23 +23941,18 @@
           <t>ch4b_cafe_press</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>ch4b_cafe</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>OkryunPushed</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ch5GuardedDoorListen</t>
+        </is>
+      </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
@@ -23983,19 +23973,24 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
+          <t>ResonanceLevel</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
           <t>ch5_guarded_door</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>ResonanceLevel</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ch5GuardedDoorSteady</t>
+        </is>
+      </c>
       <c r="C20" t="n">
         <v>2</v>
       </c>
@@ -24016,16 +24011,16 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t>SongsoonTrust</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
           <t>ch5_guarded_door</t>
         </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>SongsoonTrust</t>
-        </is>
-      </c>
-      <c r="N20" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -24052,7 +24047,7 @@
           <t>ch5_contact_editor</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>ch5_ritual_path</t>
         </is>
@@ -24082,7 +24077,7 @@
           <t>ch5_no_contact</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>ch5_ritual_path</t>
         </is>
@@ -24117,7 +24112,7 @@
           <t>ritual_answer</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>ch6_ritual_scene</t>
         </is>
@@ -24152,7 +24147,7 @@
           <t>ritual_block</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>ch6_ritual_scene</t>
         </is>
@@ -24187,7 +24182,7 @@
           <t>ritual_hesitate</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>ch6_ritual_scene</t>
         </is>
@@ -24227,7 +24222,7 @@
           <t>ritual_expose</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>ch6_ritual_scene</t>
         </is>

--- a/content/generated/script.generated.xlsx
+++ b/content/generated/script.generated.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-06 06:59:44</t>
+          <t>2026-04-06 07:15:44</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
@@ -5257,7 +5257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5311,11 +5311,6 @@
           <t>EvidencePromptHint</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>NextScene</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5341,11 +5336,6 @@
           <t>assets/sfx/ambient.mp3</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>ch1_newsroom</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5396,11 +5386,6 @@
           <t>assets/sfx/newsroom.mp3</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>ch2_hospital</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5426,11 +5411,6 @@
           <t>assets/sfx/newsroom.mp3</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>ch2_hospital</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5466,11 +5446,6 @@
           <t>카페 낙원에서 먼저 붙잡을 단서를 가려내고, 송순이 숨기는 결을 읽어낸다.</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>ch2_well</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5496,11 +5471,6 @@
           <t>assets/sfx/creepy.mp3</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>ch2_cafe</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5554,11 +5524,6 @@
       <c r="F9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>ch2_hospital_end</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5587,11 +5552,6 @@
       <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>ch2_hospital_end</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5620,11 +5580,6 @@
       <c r="F11" t="n">
         <v>3</v>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>ch2_factory</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5650,11 +5605,6 @@
           <t>assets/sfx/jazz_dark.mp3</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>ch3_warehouse</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5680,11 +5630,6 @@
           <t>assets/sfx/sad.mp3</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>ch3_room4</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5720,11 +5665,6 @@
           <t>사라진 언니의 방에서 무엇이 지워졌고 무엇이 남았는지, 제한된 기회 안에 가려낸다.</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>ch4a_library</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5750,11 +5690,6 @@
           <t>assets/sfx/sad.mp3</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>ch4a_library</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5780,11 +5715,6 @@
           <t>assets/sfx/sad.mp3</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>ch4a_library</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5813,11 +5743,6 @@
       <c r="F17" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>ch4a_library</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5843,11 +5768,6 @@
           <t>assets/sfx/mystery.mp3</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>ch3_hallway</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5873,11 +5793,6 @@
           <t>assets/sfx/mystery.mp3</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>ch3_hallway</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5903,11 +5818,6 @@
           <t>assets/sfx/tense.mp3</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>ch3_hallway</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5933,11 +5843,6 @@
           <t>assets/sfx/mystery.mp3</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>ch4a_slum</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5963,11 +5868,6 @@
           <t>assets/sfx/mystery.mp3</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>ch4a_slum</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5993,11 +5893,6 @@
           <t>assets/sfx/mystery.mp3</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>ch4a_slum</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6023,11 +5918,6 @@
           <t>assets/sfx/newsroom.mp3</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>ch4b_cafe</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6063,11 +5953,6 @@
           <t>자료실 기사 위에 지금 가진 단서를 직접 겹쳐 보며, 무엇이 같은 손에 의해 지워졌는지 확인한다.</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>ch4a_slum</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6093,11 +5978,6 @@
           <t>assets/sfx/gloomy.mp3</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>ch4a_editor_room</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6123,11 +6003,6 @@
           <t>assets/sfx/sad.mp3</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>ch5_ritual_path</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6178,11 +6053,6 @@
           <t>assets/sfx/jazz_dark.mp3</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>ch4b_backroom</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6208,11 +6078,6 @@
           <t>assets/sfx/jazz_dark.mp3</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>ch4b_backroom</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6238,11 +6103,6 @@
           <t>assets/sfx/creepy_2.mp3</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>ch5_descent</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6271,11 +6131,6 @@
       <c r="F32" t="n">
         <v>3</v>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>ch5_guarded_door</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6301,11 +6156,6 @@
           <t>assets/sfx/creepy_2.mp3</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>ch5_ritual_room</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6334,11 +6184,6 @@
       <c r="F34" t="n">
         <v>2</v>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>ch5_ritual_room</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6364,11 +6209,6 @@
           <t>assets/sfx/creepy_2.mp3</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>ch5_ritual_room</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6394,11 +6234,6 @@
           <t>assets/sfx/creepy_2.mp3</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>ch5_descent</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6427,11 +6262,6 @@
       <c r="F37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>ch5_descent</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6470,11 +6300,6 @@
           <t>의례실에서 붙든 구조와 단서를 지금 이 자리의 흔적에 겹쳐, 무엇이 반복되고 있는지 더 분명하게 확인한다.</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>ch6_threshold</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6500,11 +6325,6 @@
           <t>assets/sfx/ritual_climax.mp3</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>ch6_outcome</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6530,11 +6350,6 @@
           <t>assets/sfx/ritual_climax.mp3</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>ch6_outcome</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6560,11 +6375,6 @@
           <t>assets/sfx/ritual_climax.mp3</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>ch6_outcome</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6590,11 +6400,6 @@
           <t>assets/sfx/ending.mp3</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>ch6_epilogue</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6620,11 +6425,6 @@
           <t>assets/sfx/ending.mp3</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>ch6_epilogue</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6653,11 +6453,6 @@
       <c r="F44" t="n">
         <v>2</v>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>ch6_epilogue</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6711,11 +6506,6 @@
       <c r="F46" t="n">
         <v>2</v>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>ch6_ending_c</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6741,11 +6531,6 @@
           <t>assets/sfx/ritual_climax.mp3</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>ch6_ending_c</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6771,11 +6556,6 @@
           <t>assets/sfx/ending.mp3</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>ch6_ending_c</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6801,11 +6581,6 @@
           <t>assets/sfx/ritual_climax.mp3</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>ch6_ending_c</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6831,11 +6606,6 @@
           <t>assets/sfx/ending.mp3</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>ch6_ending_c</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6874,11 +6644,6 @@
           <t>이 방에서 무엇을 사람으로 남길지 결정한다. 망설일 시간은 길지 않다.</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>ch6_outcome</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6902,11 +6667,6 @@
       <c r="E52" t="inlineStr">
         <is>
           <t>assets/sfx/ritual.mp3</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>ch6_ritual_scene</t>
         </is>
       </c>
     </row>
@@ -23277,7 +23037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23349,16 +23109,6 @@
       <c r="N1" t="inlineStr">
         <is>
           <t>SceneID</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>NextScene</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>NextDialogue</t>
         </is>
       </c>
     </row>
@@ -24239,7 +23989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24268,469 +24018,1304 @@
           <t>NextSceneID</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>FlagKey</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>FlagValue</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>NextScene</t>
-        </is>
-      </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Br_ch1_court_Default</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ch6_outcome</t>
+          <t>ch1_court</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CG_Branch_FinalChoice_A</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ch6_path_a</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>ch6_path_a</t>
+          <t>ch1_newsroom</t>
         </is>
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Br_ch1_newsroom_defiant_Default</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ch6_outcome</t>
+          <t>ch1_newsroom_defiant</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CG_Branch_FinalChoice_B</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ch6_path_b</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>ch6_path_b</t>
+          <t>ch2_hospital</t>
         </is>
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Br_ch1_newsroom_obedient_Default</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ch6_outcome</t>
+          <t>ch1_newsroom_obedient</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CG_Branch_FinalChoice_C</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ch6_ending_c</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>ch6_ending_c</t>
+          <t>ch2_hospital</t>
         </is>
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Br_ch2_cafe_Default</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ch6_path_a</t>
+          <t>ch2_cafe</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CG_Branch_TouchedRoomWall</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ch6_path_a2</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>ch6_path_a2</t>
+          <t>ch2_well</t>
         </is>
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Br_ch2_factory_Default</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ch6_path_a2</t>
+          <t>ch2_factory</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CG_Branch_MatchedPattern</t>
-        </is>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ch6_ending_a</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>ch6_ending_a</t>
+          <t>ch2_cafe</t>
         </is>
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Br_ch2_hospital_a_Default</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ch6_path_a2</t>
+          <t>ch2_hospital_a</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CG_Branch_SolvedMid</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ch6_ending_a</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>ch6_ending_a</t>
+          <t>ch2_hospital_end</t>
         </is>
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Br_ch2_hospital_b_Default</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ch6_path_a2</t>
+          <t>ch2_hospital_b</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CG_Threshold_TrustedSongsoon</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ch6_ending_a</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>ch6_ending_a</t>
+          <t>ch2_hospital_end</t>
         </is>
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Br_ch2_hospital_end_Default</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ch6_path_a2</t>
+          <t>ch2_hospital_end</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CG_Branch_SongsoonTrust2</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ch6_ending_a</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>ch6_ending_a</t>
+          <t>ch2_factory</t>
         </is>
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Br_ch2_well_Default</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ch6_path_a2</t>
+          <t>ch2_well</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CG_Branch_SongsoonTrust1</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ch6_ending_a</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>ch6_ending_a</t>
+          <t>ch3_warehouse</t>
         </is>
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Br_ch3_hallway_Default</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ch6_path_a2</t>
+          <t>ch3_hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CG_Branch_OkryunPushed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ch6_ending_a</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>ch6_ending_a</t>
+          <t>ch3_room4</t>
         </is>
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Br_ch3_room4_Default</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ch6_path_a2</t>
+          <t>ch3_room4</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CG_Branch_EndingAScore2</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ch6_ending_a</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>ch6_ending_a</t>
+          <t>ch4a_library</t>
         </is>
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Br_ch3_room4_comfort_Default</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ch6_path_b</t>
+          <t>ch3_room4_comfort</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CG_Branch_FoundOldArticles</t>
-        </is>
-      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ch6_path_b2</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>ch6_path_b2</t>
+          <t>ch4a_library</t>
         </is>
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Br_ch3_room4_record_Default</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ch6_path_b2</t>
+          <t>ch3_room4_record</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ch4a_library</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Br_ch3_room4_touch_Default</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ch3_room4_touch</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ch4a_library</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Br_ch3_score_read_Default</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ch3_score_read</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ch3_hallway</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Br_ch3_score_trust_Default</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ch3_score_trust</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ch3_hallway</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Br_ch3_warehouse_Default</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ch3_warehouse</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ch3_hallway</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Br_ch4a_articles_expose_Default</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ch4a_articles_expose</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ch4a_slum</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Br_ch4a_articles_note_Default</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ch4a_articles_note</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ch4a_slum</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Br_ch4a_articles_take_Default</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ch4a_articles_take</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ch4a_slum</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Br_ch4a_editor_room_Default</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ch4a_editor_room</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ch4b_cafe</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Br_ch4a_library_Default</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ch4a_library</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ch4a_slum</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Br_ch4a_slum_Default</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ch4a_slum</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ch4a_editor_room</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Br_ch4b_backroom_Default</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ch4b_backroom</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ch5_ritual_path</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Br_ch4b_cafe_hold_Default</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ch4b_cafe_hold</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ch4b_backroom</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Br_ch4b_cafe_press_Default</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ch4b_cafe_press</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ch4b_backroom</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Br_ch5_contact_editor_Default</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ch5_contact_editor</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ch5_descent</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Br_ch5_descent_Default</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ch5_descent</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ch5_guarded_door</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Br_ch5_guarded_door_Default</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ch5_guarded_door</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ch5_ritual_room</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Br_ch5_guarded_door_listen_Default</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ch5_guarded_door_listen</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ch5_ritual_room</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Br_ch5_guarded_door_steady_Default</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ch5_guarded_door_steady</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ch5_ritual_room</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Br_ch5_no_contact_Default</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ch5_no_contact</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ch5_descent</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Br_ch5_ritual_path_Default</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ch5_ritual_path</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ch5_descent</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Br_ch5_ritual_room_Default</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ch5_ritual_room</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ch6_threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Br_ch6_choice_a_Default</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ch6_choice_a</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ch6_outcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Br_ch6_choice_b_Default</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ch6_choice_b</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ch6_outcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Br_ch6_choice_c_Default</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ch6_choice_c</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ch6_outcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Br_ch6_ending_a_Default</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ch6_ending_a</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ch6_epilogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Br_ch6_ending_b_Default</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ch6_ending_b</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ch6_epilogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Br_ch6_ending_c_Default</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ch6_ending_c</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ch6_epilogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ch6_outcome</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CG_Branch_FinalChoice_A</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ch6_path_a</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ch6_outcome</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CG_Branch_FinalChoice_B</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ch6_path_b</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ch6_outcome</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CG_Branch_FinalChoice_C</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ch6_ending_c</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Br_ch6_outcome_Default</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ch6_outcome</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ch6_ending_c</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ch6_path_a</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CG_Branch_TouchedRoomWall</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ch6_path_a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Br_ch6_path_a_Default</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ch6_path_a</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ch6_ending_c</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ch6_path_a2</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CG_Branch_MatchedPattern</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ch6_ending_a</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ch6_path_a2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CG_Branch_SolvedMid</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ch6_ending_a</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ch6_path_a2</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CG_Threshold_TrustedSongsoon</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ch6_ending_a</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ch6_path_a2</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>4</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CG_Branch_SongsoonTrust2</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ch6_ending_a</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ch6_path_a2</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>5</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>CG_Branch_SongsoonTrust1</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ch6_ending_a</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ch6_path_a2</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>6</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CG_Branch_OkryunPushed</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ch6_ending_a</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ch6_path_a2</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>7</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CG_Branch_EndingAScore2</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ch6_ending_a</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Br_ch6_path_a2_Default</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ch6_path_a2</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>8</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ch6_ending_c</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ch6_path_b</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CG_Branch_FoundOldArticles</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ch6_path_b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Br_ch6_path_b_Default</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ch6_path_b</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ch6_ending_c</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ch6_path_b2</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>CG_Branch_ExposedTruthAtRitual</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>ch6_ending_b</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ch6_path_b2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>CG_Branch_ExposedArchivePattern</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
         <is>
           <t>ch6_ending_b</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
+    <row r="60">
+      <c r="B60" t="inlineStr">
         <is>
           <t>ch6_path_b2</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CG_Branch_ExposedArchivePattern</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="C60" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>CG_Branch_SolvedMid</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
         <is>
           <t>ch6_ending_b</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ch6_path_b2</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CG_Branch_ReadRitual</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
         <is>
           <t>ch6_ending_b</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
+    <row r="62">
+      <c r="B62" t="inlineStr">
         <is>
           <t>ch6_path_b2</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>CG_Branch_SolvedMid</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="C62" t="n">
+        <v>5</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CG_Branch_Investigation3</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
         <is>
           <t>ch6_ending_b</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ch6_path_b2</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>6</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CG_Branch_CalledEditorFalse</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
         <is>
           <t>ch6_ending_b</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Br_ch6_path_b2_Default</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>ch6_path_b2</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>CG_Branch_ReadRitual</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ch6_ending_b</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>ch6_ending_b</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ch6_path_b2</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>5</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>CG_Branch_Investigation3</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>ch6_ending_b</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>ch6_ending_b</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ch6_path_b2</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>6</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>CG_Branch_CalledEditorFalse</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>ch6_ending_b</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>ch6_ending_b</t>
+      <c r="C64" t="n">
+        <v>7</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ch6_ending_c</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Br_ch6_ritual_scene_Default</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ch6_ritual_scene</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ch6_outcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Br_ch6_threshold_Default</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ch6_threshold</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ch6_ritual_scene</t>
         </is>
       </c>
     </row>

--- a/content/generated/script.generated.xlsx
+++ b/content/generated/script.generated.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Meta" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ConditionTable" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="GaugeTable" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="GaugeStateTable" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="EffectTable" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="SceneTable" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="DialogTable" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ChoiceGroupTable" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="ChoiceTable" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="BranchTable" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="EvidenceTable" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="EvidenceCategoryTable" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="CharacterTable" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="CharacterEmotionTable" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="InvestigationTable" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="QuestionTable" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="StateDescriptorTable" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ConditionTable" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GaugeTable" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GaugeStateTable" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EffectTable" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SceneTable" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DialogTable" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChoiceGroupTable" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChoiceTable" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BranchTable" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EvidenceTable" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EvidenceCategoryTable" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CharacterTable" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CharacterEmotionTable" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InvestigationTable" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QuestionTable" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StateDescriptorTable" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-13 03:26:04</t>
+          <t>2026-04-14 22:16:12</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -592,7 +592,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ch1NewsroomObedient</t>
+          <t>Ch1CourtPursue</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -600,7 +600,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>세간의 입에 오를 만한 글로 꾸며 보지요.</t>
+          <t>이 판결, 기어이 물고 늘어진다.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -610,19 +610,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ch1_newsroom_obedient</t>
+          <t>ch1_newsroom</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>ch1_newsroom</t>
+          <t>ch1_court</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ch1NewsroomDefiant</t>
+          <t>Ch1CourtComply</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -630,7 +630,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>신문감은 되겠지만, 이대로 덮을 마음은 없습니다.</t>
+          <t>편집장이 원하는 기사를 먼저 써둔다. 그게 실리는 법이다.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -640,24 +640,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ch1_newsroom_defiant</t>
+          <t>ch1_newsroom</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>ch1_newsroom</t>
+          <t>ch1_court</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ch2CafeAskManager</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_CafeInvestigation</t>
+          <t>Ch1NewsroomObedient</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -665,34 +660,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>점장에게 더 캐묻는다</t>
+          <t>세간의 입에 오를 만한 글로 꾸며 보지요.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>inv_mgr</t>
+          <t>ch1_newsroom_obedient</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>ch2_cafe</t>
+          <t>ch1_newsroom</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ch2CafeAskWaitress</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_CafeInvestigation</t>
+          <t>Ch1NewsroomDefiant</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -700,29 +690,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>지나치는 여급의 반응을 확인한다</t>
+          <t>신문감은 되겠지만, 이대로 덮을 마음은 없습니다.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>inv_wtrs</t>
+          <t>ch1_newsroom_defiant</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ch2_cafe</t>
+          <t>ch1_newsroom</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ch2CafeAskObserver</t>
+          <t>Ch2CafeAskManager</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -731,11 +721,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>구석에 앉은 여자를 살핀다</t>
+          <t>점장을 몰아세워 낙원 안쪽 규칙을 흔든다</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -745,7 +735,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>inv_obs</t>
+          <t>inv_mgr</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -757,75 +747,85 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ch2Factory_LookCloser</t>
+          <t>Ch2CafeAskWaitress</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_CafeInvestigation</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>시신의 찢겨진 흉곽 안쪽을 홀린 듯 쳐다본다.</t>
+          <t>여급들의 빚과 눈치를 읽어 낸다</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ch2_factory_shock</t>
+          <t>inv_wtrs</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>ch2_factory</t>
+          <t>ch2_cafe</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ch2HospitalAskRoot</t>
+          <t>Ch2CafeAskObserver</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_CafeInvestigation</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>그 망상의 근원부터 기어이 묻고 늘어진다.</t>
+          <t>구석 손님의 침묵을 정면으로 살핀다</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ch2_hospital_a</t>
+          <t>inv_obs</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>ch2_hospital</t>
+          <t>ch2_cafe</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ch2HospitalAskDoor</t>
+          <t>Ch2Factory_LookCloser</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>그가 벌벌 떠는 '문'의 정체부터 확인한다.</t>
+          <t>시신의 찢겨진 흉곽 안쪽을 홀린 듯 쳐다본다.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -835,104 +835,84 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ch2_hospital_b</t>
+          <t>ch2_factory_shock</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>ch2_hospital</t>
+          <t>ch2_factory</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ch2IpangyuBlueCloth</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_Ipangyu_Confront</t>
+          <t>Ch2HospitalAskRoot</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>푸른 천 조각을 꺼낸다.</t>
+          <t>그 망상의 근원부터 기어이 묻고 늘어진다.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>dlg_ipangyu_reveal</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>EvBlueCloth</t>
+          <t>ch2_hospital_a</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>ch2_ipangyu</t>
+          <t>ch2_hospital</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ch2IpangyuScore</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_Ipangyu_Confront</t>
+          <t>Ch2HospitalAskDoor</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>의식 악보를 내민다.</t>
+          <t>그가 벌벌 떠는 '문'의 정체부터 확인한다.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>dlg_ipangyu_reveal</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>EvRitualScore</t>
+          <t>ch2_hospital_b</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>ch2_ipangyu</t>
+          <t>ch2_hospital</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ch2WellTrustNote</t>
+          <t>Ch2IpangyuBlueCloth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ChoiceGroup_Songsoon_Trust</t>
+          <t>ChoiceGroup_Ipangyu_Confront</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -940,7 +920,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>쪽지를 꺼내 보인다.</t>
+          <t>푸른 천 조각으로 그날 현장에 있었음을 들이민다.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -950,29 +930,29 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>dlg_songsoon_open</t>
+          <t>dlg_ipangyu_reveal</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>EvNote</t>
+          <t>EvBlueCloth</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>ch2_well</t>
+          <t>ch2_ipangyu</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ch2WellTrustCloth</t>
+          <t>Ch2IpangyuScore</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ChoiceGroup_Songsoon_Trust</t>
+          <t>ChoiceGroup_Ipangyu_Confront</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -980,7 +960,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>푸른 천 조각을 내민다.</t>
+          <t>의식 악보를 내밀어 그가 들은 노래를 찌른다.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -990,94 +970,104 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>dlg_songsoon_open</t>
+          <t>dlg_ipangyu_reveal</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>EvBlueCloth</t>
+          <t>EvRitualScore</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>ch2_well</t>
+          <t>ch2_ipangyu</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ch3Room4TouchWall</t>
+          <t>Ch2WellTrustNote</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ChoiceGroup_Room4Investigation</t>
+          <t>ChoiceGroup_Songsoon_Trust</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>위험을 감수하고 벽의 문양에 직접 손을 댄다.</t>
+          <t>쪽지를 꺼내 보인다.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ch3_room4_touch</t>
+          <t>dlg_songsoon_open</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>EvNote</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>ch3_room4</t>
+          <t>ch2_well</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ch3Room4ReadRecord</t>
+          <t>Ch2WellTrustCloth</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ChoiceGroup_Room4Investigation</t>
+          <t>ChoiceGroup_Songsoon_Trust</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>공포보다 기록을 우선하고 일기장의 다음 장을 더 읽는다.</t>
+          <t>푸른 천 조각을 내민다.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ch3_room4_record</t>
+          <t>dlg_songsoon_open</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>EvBlueCloth</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>ch3_room4</t>
+          <t>ch2_well</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ch3Room4ComfortSongsoon</t>
+          <t>Ch3Room4TouchWall</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1086,11 +1076,11 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>증거보다 먼저 송순에게 혼자 떠맡지 말자고 말한다.</t>
+          <t>위험을 감수하고 벽 문양이 남긴 저항 흔적을 짚는다.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1100,7 +1090,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ch3_room4_comfort</t>
+          <t>ch3_room4_touch</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1112,15 +1102,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ch3WarehouseReadRitual</t>
+          <t>Ch3Room4ReadRecord</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_Room4Investigation</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>관자놀이가 깨질 듯해도 악보를 끝까지 읽어 낸다.</t>
+          <t>공포보다 기록을 택하고 일기의 구조를 끝까지 읽는다.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1130,27 +1125,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ch3_score_read</t>
+          <t>ch3_room4_record</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>ch3_warehouse</t>
+          <t>ch3_room4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ch3WarehouseTrustSongsoon</t>
+          <t>Ch3Room4ComfortSongsoon</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_Room4Investigation</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>악보보다 송순 씨의 귀와 숨결을 먼저 믿는다.</t>
+          <t>증거보다 먼저 송순의 무너지는 마음을 붙든다.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1160,67 +1160,57 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ch3_score_trust</t>
+          <t>ch3_room4_comfort</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>ch3_warehouse</t>
+          <t>ch3_room4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ch4AEditorArticles</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_Editor_Confront</t>
+          <t>Ch3WarehouseReadRitual</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1924년 기사 뭉치를 책상에 올려놓는다.</t>
+          <t>관자놀이가 깨질 듯해도 악보를 끝까지 읽어 낸다.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>dlg_editor_reveal</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>EvOldArticles</t>
+          <t>ch3_score_read</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>ch4a_editor_room</t>
+          <t>ch3_warehouse</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ch4ALibraryTakeArticles</t>
+          <t>Ch3WarehouseTrustSongsoon</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>기사 뭉치를 챙긴다.</t>
+          <t>악보보다 송순 씨의 귀와 숨결을 먼저 믿는다.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1230,62 +1220,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ch4a_articles_take</t>
+          <t>ch3_score_trust</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>ch4a_library</t>
+          <t>ch3_warehouse</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ch4ALibraryNoteArticles</t>
+          <t>Ch4AEditorArticles</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_Editor_Confront</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>핵심 문장만 수첩에 적고 넘어간다.</t>
+          <t>1924년 기사 뭉치를 책상에 올려놓는다.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ch4a_articles_note</t>
+          <t>dlg_editor_reveal</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>EvOldArticles</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>ch4a_library</t>
+          <t>ch4a_editor_room</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ch4ALibraryExposeArchive</t>
+          <t>Ch4ALibraryTakeArticles</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>삭제된 문장과 증언을 묶어 편집장의 의도를 먼저 추적한다.</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>CG_Library_QSonggeumRunaway</t>
+          <t>기사 뭉치를 챙긴다.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1295,7 +1290,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ch4a_articles_expose</t>
+          <t>ch4a_articles_take</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1307,35 +1302,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ch4ALibraryEvidenceDiary</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_LibraryEvidence</t>
+          <t>Ch4ALibraryNoteArticles</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>찢어진 일기장을 기사 옆에 펼친다.</t>
+          <t>핵심 문장만 수첩에 적고 넘어간다.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>present_diary</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>EvDiary</t>
+          <t>ch4a_articles_note</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1347,35 +1332,30 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ch4ALibraryEvidenceHanbok</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_LibraryEvidence</t>
+          <t>Ch4ALibraryExposeArchive</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>102</v>
+        <v>3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>청색 한복의 결을 기사 기록과 대조한다.</t>
+          <t>삭제된 문장과 증언을 묶어 편집장의 의도를 먼저 추적한다.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>CG_Library_QSonggeumRunaway</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>present_hanbok</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>EvBlueHanbok</t>
+          <t>ch4a_articles_expose</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1387,95 +1367,105 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ch4BCafeHold</t>
+          <t>Ch4ALibraryEvidenceDiary</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_LibraryEvidence</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>알겠어요. 더는 억지로 묻지 않을게요.</t>
+          <t>찢어진 일기장을 기사 옆에 펼친다.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ch4b_cafe_hold</t>
+          <t>present_diary</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>EvDiary</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>ch4b_cafe</t>
+          <t>ch4a_library</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ch4BCafePress</t>
+          <t>Ch4ALibraryEvidenceHanbok</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_LibraryEvidence</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>조금만 더 말해줘요. 여기서 멈출 순 없어요.</t>
+          <t>청색 한복의 결을 기사 기록과 대조한다.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ch4b_cafe_press</t>
+          <t>present_hanbok</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>EvBlueHanbok</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>ch4b_cafe</t>
+          <t>ch4a_library</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ch4BCafeDiary</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_Okryeon_Confront</t>
+          <t>Ch4BCafeHold</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>송금의 일기장을 꺼내 보인다.</t>
+          <t>알겠어요. 더는 억지로 묻지 않을게요.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>dlg_okryeon_reveal</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>EvDiary</t>
+          <t>ch4b_cafe_hold</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -1487,35 +1477,25 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ch4BCafeHanbok</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_Okryeon_Confront</t>
+          <t>Ch4BCafePress</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>푸른 한복 조각을 내민다.</t>
+          <t>조금만 더 말해줘요. 여기서 멈출 순 없어요.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>dlg_okryeon_reveal</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>EvBlueHanbok</t>
+          <t>ch4b_cafe_press</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -1527,82 +1507,92 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ch5EditorObey</t>
+          <t>Ch4BCafeDiary</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ChoiceGroup_EditorOrder</t>
+          <t>ChoiceGroup_Okryeon_Confront</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>알겠습니다. 여기까지만 하지요.</t>
+          <t>송금의 일기장을 꺼내 보인다.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ch5_descent</t>
+          <t>dlg_okryeon_reveal</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>EvDiary</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>ch5_contact_editor</t>
+          <t>ch4b_cafe</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ch5EditorDefy</t>
+          <t>Ch4BCafeHanbok</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ChoiceGroup_EditorOrder</t>
+          <t>ChoiceGroup_Okryeon_Confront</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>죄송합니다. 여기까지 왔으니 끝냅니다.</t>
+          <t>푸른 한복 조각을 내민다.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ch5_descent</t>
+          <t>dlg_okryeon_reveal</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>EvBlueHanbok</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>ch5_contact_editor</t>
+          <t>ch4b_cafe</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ch5GuardedDoorListen</t>
+          <t>Ch5EditorObey</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ChoiceGroup_GuardedDoor</t>
+          <t>ChoiceGroup_EditorOrder</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1610,7 +1600,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>콧노래의 결을 끝까지 듣고, 문 안쪽 호흡을 짚어 본다.</t>
+          <t>알겠습니다. 여기까지만 하지요.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1620,24 +1610,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ch5_guarded_door_listen</t>
+          <t>ch5_descent</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>ch5_guarded_door</t>
+          <t>ch5_contact_editor</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ch5GuardedDoorSteady</t>
+          <t>Ch5EditorDefy</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ChoiceGroup_GuardedDoor</t>
+          <t>ChoiceGroup_EditorOrder</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1645,7 +1635,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>송순과 숨을 고른 뒤, 함께 문을 민다.</t>
+          <t>죄송합니다. 여기까지 왔으니 끝냅니다.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1655,19 +1645,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ch5_guarded_door_steady</t>
+          <t>ch5_descent</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>ch5_guarded_door</t>
+          <t>ch5_contact_editor</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ch5GuardedDoorObserve</t>
+          <t>Ch5GuardedDoorListen</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1676,11 +1666,11 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>문 틈으로 안을 직접 들여다본다.</t>
+          <t>콧노래의 결을 끝까지 듣고, 문 안쪽 호흡을 짚어 본다.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1690,7 +1680,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ch5_guarded_door_observe</t>
+          <t>ch5_guarded_door_listen</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -1702,77 +1692,82 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ch5IpangyuDealAccept</t>
+          <t>Ch5GuardedDoorSteady</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ChoiceGroup_IpangyuDeal</t>
+          <t>ChoiceGroup_GuardedDoor</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>문구를 따라 한다.</t>
+          <t>송순과 숨을 고른 뒤, 함께 문을 민다.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>dlg_ipangyu_deal_accept</t>
+          <t>ch5_guarded_door_steady</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>ch5_ipangyu_deal</t>
+          <t>ch5_guarded_door</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ch5IpangyuDealRefuse</t>
+          <t>Ch5GuardedDoorObserve</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ChoiceGroup_IpangyuDeal</t>
+          <t>ChoiceGroup_GuardedDoor</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>거절한다.</t>
+          <t>문 틈으로 안의 배치와 위험을 직접 읽어 낸다.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>dlg_ipangyu_deal_refuse</t>
+          <t>ch5_guarded_door_observe</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>ch5_ipangyu_deal</t>
+          <t>ch5_guarded_door</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ch5PathContactEditor</t>
+          <t>Ch5IpangyuDealAccept</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_IpangyuDeal</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1780,29 +1775,34 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편집장에게 연락한다.</t>
+          <t>오염을 감수하고 문구를 따라 해 이름을 받아낸다.</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>ch5_contact_editor</t>
+          <t>dlg_ipangyu_deal_accept</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>ch5_ritual_path</t>
+          <t>ch5_ipangyu_deal</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ch5PathNoContact</t>
+          <t>Ch5IpangyuDealRefuse</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_IpangyuDeal</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1810,109 +1810,89 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>말하지 않는다. 둘만 간다.</t>
+          <t>거래를 끊고 이름 없는 어둠을 감수한다.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ch5_no_contact</t>
+          <t>dlg_ipangyu_deal_refuse</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>ch5_ritual_path</t>
+          <t>ch5_ipangyu_deal</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ch5RitualEvidenceNote</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_RitualEvidence</t>
+          <t>Ch5PathContactEditor</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>의례실 종이를 제단 옆 문장과 맞대 본다.</t>
+          <t>편집장에게 연락한다.</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>present_ritual_note</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>EvRitualNote</t>
+          <t>ch5_contact_editor</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>ch5_ritual_room</t>
+          <t>ch5_ritual_path</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ch5RitualEvidenceScore</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_RitualEvidence</t>
+          <t>Ch5PathNoContact</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>감응 악보를 지금 울리는 노래와 겹쳐 본다.</t>
+          <t>말하지 않는다. 둘만 간다.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>present_ritual_score</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>EvRitualScore</t>
+          <t>ch5_no_contact</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>ch5_ritual_room</t>
+          <t>ch5_ritual_path</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ch5RitualEvidenceMask</t>
+          <t>Ch5RitualEvidenceNote</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1921,16 +1901,11 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>가면의 네 배열을 제단 문양과 대조한다.</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>CG_RitualRoom_QRitualAccident</t>
+          <t>의례실 종이를 제단 옆 문장과 맞대 본다.</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1940,12 +1915,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>present_mask</t>
+          <t>present_ritual_note</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>EvMask</t>
+          <t>EvRitualNote</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -1957,20 +1932,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>article_q1_correct</t>
+          <t>Ch5RitualEvidenceScore</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ChoiceGroup_ArticleQ1</t>
+          <t>ChoiceGroup_RitualEvidence</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>일기장 — 피해자 이름을 직접 특정한다.</t>
+          <t>감응 악보를 지금 울리는 노래와 겹쳐 본다.</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1980,37 +1955,42 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>article_q1_react</t>
+          <t>present_ritual_score</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>EvDiary</t>
+          <t>EvRitualScore</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>ch6_article</t>
+          <t>ch5_ritual_room</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>article_q2_correct</t>
+          <t>Ch5RitualEvidenceMask</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ChoiceGroup_ArticleQ2</t>
+          <t>ChoiceGroup_RitualEvidence</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>의식 악보 — 부적 제작 경위와 감응 방법을 밝힌다.</t>
+          <t>가면의 네 배열을 제단 문양과 대조한다.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>CG_RitualRoom_QRitualAccident</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2020,37 +2000,37 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>article_q2_react</t>
+          <t>present_mask</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>EvRitualScore</t>
+          <t>EvMask</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>ch6_article</t>
+          <t>ch5_ritual_room</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>article_q3_correct</t>
+          <t>article_q1_correct</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ChoiceGroup_ArticleQ3</t>
+          <t>ChoiceGroup_ArticleQ1</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1924년 구 기사 — 구 세력의 계보와 반복된 패턴을 폭로한다.</t>
+          <t>일기장 — 피해자 이름을 직접 특정한다.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2060,12 +2040,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>article_q3_react</t>
+          <t>article_q1_react</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>EvOldArticles</t>
+          <t>EvDiary</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -2077,77 +2057,87 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ch6FinalAnswer</t>
+          <t>article_q2_correct</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ChoiceGroup_RitualFinal</t>
+          <t>ChoiceGroup_ArticleQ2</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>송순이 언니의 노래에 응답한다.</t>
+          <t>의식 악보 — 부적 제작 경위와 감응 방법을 밝힌다.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>ch6_choice_a</t>
+          <t>article_q2_react</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>EvRitualScore</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>ch6_ritual_scene</t>
+          <t>ch6_article</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ch6FinalBlock</t>
+          <t>article_q3_correct</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ChoiceGroup_RitualFinal</t>
+          <t>ChoiceGroup_ArticleQ3</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>유웅룡이 이해심을 막으러 달려간다.</t>
+          <t>1924년 구 기사 — 구 세력의 계보와 반복된 패턴을 폭로한다.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>ch6_choice_b</t>
+          <t>article_q3_react</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>EvOldArticles</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>ch6_ritual_scene</t>
+          <t>ch6_article</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ch6FinalHesitate</t>
+          <t>Ch6FinalAnswer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2156,11 +2146,11 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>아무것도 하지 않고 지켜본다.</t>
+          <t>송순이 언니를 사람의 이름으로 붙들어 세운다.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2170,7 +2160,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>ch6_choice_c</t>
+          <t>ch6_choice_a</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -2182,38 +2172,108 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>Ch6FinalBlock</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_RitualFinal</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>유웅룡이 제단으로 뛰어들어 의식을 몸으로 끊는다.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Scene</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ch6_choice_b</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>ch6_ritual_scene</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ch6FinalHesitate</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_RitualFinal</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>공포에 얼어붙은 채 아무 선택도 하지 못한다.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Scene</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ch6_choice_c</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>ch6_ritual_scene</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>Ch6FinalExpose</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>ChoiceGroup_RitualFinal</t>
         </is>
       </c>
-      <c r="C47" t="n">
+      <c r="C49" t="n">
         <v>4</v>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>지금까지 붙든 질문과 단서를 들이밀며 이해심을 몰아세운다.</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>지금까지 쌓은 질문과 단서를 들이밀어 이해심의 거짓을 폭로한다.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
         <is>
           <t>CG_RitualScene_SolvedHigh</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Dialog</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>ritual_expose</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>ch6_ritual_scene</t>
         </is>
@@ -3739,6 +3799,11 @@
       <c r="C74" t="n">
         <v>1</v>
       </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ch6_ending_b</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3766,7 +3831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3879,62 +3944,62 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EvBlueHanbok</t>
+          <t>EvIpangyuMemo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>청색 비단 한복</t>
+          <t>접견 메모</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>송금의 방에서 발견된 의례용 한복. 소매 안쪽에 바느질 자국과 작은 상처 자국들.</t>
+          <t>이판규가 접견 탁자 틈새에 밀어 넣은 작은 종이 조각. '문은 반드시 열린다. 노래가 준비되면.' 떨리는 손으로 쓰인 글자가 번져 있다.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>assets/items/hanbok.png</t>
+          <t>assets/items/note.png</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ritual</t>
+          <t>record</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ch3_room4</t>
+          <t>ch2_hospital</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EvDiary</t>
+          <t>EvBlueHanbok</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>숨겨진 일기장</t>
+          <t>청색 비단 한복</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>송금의 일기장. '청의의 무녀', '노래가 곧 감응', '문 앞에서 노래를 부를 것'.</t>
+          <t>송금의 방에서 발견된 의례용 한복. 소매 안쪽에 바느질 자국과 작은 상처 자국들.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>assets/items/diary.png</t>
+          <t>assets/items/hanbok.png</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>record</t>
+          <t>ritual</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3943,33 +4008,33 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EvMask</t>
+          <t>EvDiary</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>오징어 가면</t>
+          <t>숨겨진 일기장</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>눈 구멍이 네 개 달린 기괴한 가면. 청의동자의 눈 네 개를 상징한다.</t>
+          <t>송금의 일기장. '청의의 무녀', '노래가 곧 감응', '문 앞에서 노래를 부를 것'.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>assets/items/mask.png</t>
+          <t>assets/items/diary.png</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ritual</t>
+          <t>record</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3978,28 +4043,28 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EvRitualScore</t>
+          <t>EvMask</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>감응 악보</t>
+          <t>오징어 가면</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>주문이 음표 사이에 숨겨진 기묘한 악보. 유웅룡에게만 이명과 고통을 유발한다.</t>
+          <t>눈 구멍이 네 개 달린 기괴한 가면. 청의동자의 눈 네 개를 상징한다.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>assets/items/scores.png</t>
+          <t>assets/items/mask.png</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4009,62 +4074,62 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ch3_warehouse</t>
+          <t>ch3_room4</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EvOldArticles</t>
+          <t>EvRitualScore</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1924년 기사 뭉치</t>
+          <t>감응 악보</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>과거에 발생한 유사 사건의 기록. 편집장이 직접 작성했다. 일부 문장이 삭제되어 있다.</t>
+          <t>주문이 음표 사이에 숨겨진 기묘한 악보. 유웅룡에게만 이명과 고통을 유발한다.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>assets/items/records.png</t>
+          <t>assets/items/scores.png</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>record</t>
+          <t>ritual</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ch4a_library</t>
+          <t>ch3_warehouse</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EvIpangyuName</t>
+          <t>EvOldArticles</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>이판규의 증언</t>
+          <t>1924년 기사 뭉치</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>이판규가 넘겨준 이름. 낙원의 마지막 의식에서 노래한 사람의 이름이 적혀 있다.</t>
+          <t>과거에 발생한 유사 사건의 기록. 편집장이 직접 작성했다. 일부 문장이 삭제되어 있다.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4072,44 +4137,79 @@
           <t>assets/items/records.png</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ch5_ipangyu_deal</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Ch5IpangyuDealAccept</t>
-        </is>
+          <t>ch4a_library</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>EvIpangyuName</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>이판규의 증언</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>이판규가 넘겨준 이름. 낙원의 마지막 의식에서 노래한 사람의 이름이 적혀 있다.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>assets/items/records.png</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ch5_ipangyu_deal</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ch5IpangyuDealAccept</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>EvRitualNote</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>의례실 종이</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>'그릇은 셋. 둘은 쓰였고 하나가 남았다.' 마지막 무녀가 아직 남아 있다는 증거.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>ritual</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>ch5_ritual_room</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="G11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5260,12 +5360,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>낙원에서 무엇을 먼저 볼 것인가</t>
+          <t>낙원에서 먼저 흔들어 볼 결은 무엇인가</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>남은 조사 기회 안에서 현장과 사람의 결 중 무엇을 먼저 붙들지 정하세요.</t>
+          <t>점장의 입, 여급들의 빚, 구석 손님의 침묵 가운데 어디를 먼저 건드릴지 정하세요.</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -5285,12 +5385,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>마지막으로 무엇을 택할 것인가</t>
+          <t>이 방에서 무엇을 사람으로 남길 것인가</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>답할지, 막을지, 머뭇거릴지. 이번 선택은 엔딩의 기울기를 바꿉니다.</t>
+          <t>구해 붙들지, 몸으로 끊을지, 공포에 멈출지, 쌓아 온 질문으로 폭로할지 선택하세요.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -5310,12 +5410,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>방 안의 어떤 흔적을 먼저 붙들 것인가</t>
+          <t>이 방에서 먼저 붙들 진실은 무엇인가</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>벽의 반응, 남겨진 기록, 송순의 마음 가운데 먼저 확인할 결을 고르세요.</t>
+          <t>벽의 흔적, 남겨진 기록, 송순의 흔들림 가운데 어디부터 잡아야 사건의 구조가 드러나는지 고르세요.</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -6438,7 +6538,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -6458,7 +6558,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="8">
@@ -6478,7 +6578,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -6498,7 +6598,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -9404,7 +9504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9487,7 +9587,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>eff_ch1_newsroom_obedient</t>
+          <t>eff_ch1_court_comply</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -9507,7 +9607,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>eff_ch3_room4_read_record</t>
+          <t>eff_ch1_court_pursue</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -9527,27 +9627,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>eff_ch3_room4_touch_wall</t>
+          <t>eff_ch1_newsroom_obedient</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GaugeChange</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Erosion</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>2</v>
+          <t>TrustChange</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Editor</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>eff_ch3_warehouse_read_ritual</t>
+          <t>eff_ch3_room4_read_record</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -9567,7 +9667,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>eff_ch4a_library_note_articles</t>
+          <t>eff_ch3_room4_touch_wall</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -9577,17 +9677,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Credibility</t>
+          <t>Erosion</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>eff_ch5_guarded_door_listen</t>
+          <t>eff_ch3_warehouse_read_ritual</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -9597,37 +9697,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Erosion</t>
+          <t>Credibility</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>eff_ch5_guarded_door_steady</t>
+          <t>eff_ch4a_library_note_articles</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TrustChange</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Songsoon</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>2</v>
+          <t>GaugeChange</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Credibility</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>eff_ch5_observe</t>
+          <t>eff_ch5_guarded_door_listen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -9637,37 +9737,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Credibility</t>
+          <t>Erosion</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>eff_ch5_observe</t>
+          <t>eff_ch5_guarded_door_steady</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GaugeChange</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Erosion</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
+          <t>TrustChange</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Songsoon</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>eff_editor_correct</t>
+          <t>eff_ch5_observe</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -9681,13 +9781,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>eff_editor_defy</t>
+          <t>eff_ch5_observe</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -9697,17 +9797,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Credibility</t>
+          <t>Erosion</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>eff_editor_wrong</t>
+          <t>eff_editor_correct</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -9721,13 +9821,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>eff_ipangyu_correct</t>
+          <t>eff_editor_defy</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -9741,13 +9841,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>eff_ipangyu_correct</t>
+          <t>eff_editor_wrong</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -9757,34 +9857,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Erosion</t>
+          <t>Credibility</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>eff_ipangyu_deal_accept</t>
+          <t>eff_ipangyu_correct</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EvidenceGain</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>EvIpangyuName</t>
-        </is>
+          <t>GaugeChange</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Credibility</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>eff_ipangyu_deal_accept</t>
+          <t>eff_ipangyu_correct</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9804,27 +9907,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>eff_ipangyu_wrong</t>
+          <t>eff_ipangyu_deal_accept</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GaugeChange</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Credibility</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>-1</v>
+          <t>EvidenceGain</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>EvIpangyuName</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>eff_okryeon_diary</t>
+          <t>eff_ipangyu_deal_accept</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9834,7 +9934,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Credibility</t>
+          <t>Erosion</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -9844,7 +9944,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>eff_okryeon_hanbok</t>
+          <t>eff_ipangyu_wrong</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9858,13 +9958,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>eff_okryeon_hanbok</t>
+          <t>eff_okryeon_diary</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9874,7 +9974,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Erosion</t>
+          <t>Credibility</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -9884,7 +9984,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>eff_okryeon_wrong</t>
+          <t>eff_okryeon_hanbok</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -9898,26 +9998,66 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>eff_okryeon_hanbok</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>GaugeChange</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Erosion</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>eff_okryeon_wrong</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GaugeChange</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Credibility</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>eff_songsoon_trust</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>TrustChange</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Songsoon</t>
         </is>
       </c>
-      <c r="G25" t="n">
+      <c r="G27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10118,7 +10258,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>카페 낙원에서 먼저 붙잡을 단서를 가려내고, 송순이 숨기는 결을 읽어낸다.</t>
+          <t>낙원 안에서 누구의 입을 먼저 흔들어야 송금과 낙원의 연결고리가 드러나는지 가려낸다.</t>
         </is>
       </c>
     </row>
@@ -10315,7 +10455,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>이판규가 숨긴 것을 끌어내라. 증거로 그의 입을 열어야 한다.</t>
+          <t>이판규를 압박해 송금과 의식에 닿는 이름을 토하게 만든다. 맞는 증거만이 그의 기억을 흔든다.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -10325,7 +10465,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>그가 아는 것과 연결된 증거만이 그의 말을 움직인다. 무관한 것엔 반응하지 않는다.</t>
+          <t>이판규가 직접 봤거나 들은 것과 이어지는 증거만이 통한다. 맞는 걸 내밀면 그의 미친 말에도 방향이 생긴다.</t>
         </is>
       </c>
     </row>
@@ -10420,7 +10560,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>사라진 언니의 방에서 무엇이 지워졌고 무엇이 남았는지, 제한된 기회 안에 가려낸다.</t>
+          <t>방 안에 남은 흔적 중 무엇이 의식의 구조를 밝히고, 무엇이 송금의 마지막 저항을 보여 주는지 가려낸다.</t>
         </is>
       </c>
     </row>
@@ -10934,6 +11074,16 @@
           <t>assets/sfx/creepy_2.mp3</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>결단 목표</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>문 안의 의식으로 들어가기 전, 두려움에 끌려가지 않고 어떤 태도로 버틸지 결정한다.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -11037,6 +11187,16 @@
           <t>assets/sfx/jazz_dark.mp3</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>결단 목표</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>이판규의 거래를 받아들여 이름을 얻을지, 거절하고 더 어두운 길을 감수할지 결정한다.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -11160,7 +11320,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>기사의 세 항목을 증거로 뒷받침하라. 신용이 쌓여야 기사가 나온다.</t>
+          <t>피해자, 의식, 배후를 각각 입증해 기사 한 장으로 끝까지 몰아붙일 근거를 완성한다.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -11514,7 +11674,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>이 방에서 무엇을 사람으로 남길지 결정한다. 망설일 시간은 길지 않다.</t>
+          <t>송금, 이해심, 그리고 이 방에 쌓인 질문들 사이에서 무엇을 사람 쪽으로 남길지 지금 결정한다.</t>
         </is>
       </c>
     </row>
@@ -11629,7 +11789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S421"/>
+  <dimension ref="A1:S423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13010,7 +13170,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>어서 오십시오. 커피로 하시겠습니까?</t>
+          <t>어서 오십시오. 맥주로 드시겠습니까, 정종으로 드시겠습니까?</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -13090,7 +13250,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>아… 그런 이가 있긴 했지요. 요새는 무대에 세우지 않습니다. 집 안 공기가 좀 달라졌거든요. (잔을 내려놓으며 시선을 피한다)</t>
+          <t>아… 그런 이가 있긴 했지요. 요새는 무대에 올리지 않습니다. 저 아이들 중에 어물쩡 나가려는 것들이 생겨서요. (잔을 내려놓으며 시선을 피한다)</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -14690,7 +14850,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>문틈에서 손이 나와...! 무녀가 다시 노래하면, 이번엔 내 껍데기만 찢기고 진짜 열려 버린단 말—! 끄거오옥...!</t>
+          <t>문틈에서 손이 나와...! 무녀가 다시 노래하면, 이번엔 내 껍데기만 찢기고 문이 기어이 열리고 마는 거야—! 끄거오옥...!</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -14840,7 +15000,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>낙원 외곽 판잣집 골목. 이판규 — 낙원의 오래된 신도이자 교주의 그림자라고 불리는 자가 담벼락에 기대어 서 있다. 처음 보는 얼굴인데 눈빛이 이상하다.</t>
+          <t>낙원 외곽 판잣집 골목. 이판규 — 낙원의 오래된 신도이자 교주의 그림자라고 불리는 자가 담벼락에 기대어 서 있다. 처음 보는 얼굴인데 눈빛이 심상치 않다.</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -15435,7 +15595,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>…처음이에요. 제 말 듣고 그런 식으로 답한 사람. 다들 미쳤다거나, 더럽다거나, 괜히 엮이지 말라고만 했거든요.</t>
+          <t>…처음이에요. 제 말 듣고 그런 식으로 답한 사람. 다들 미쳤다거나, 더럽다거나, 괜히 엮이지 말라고만 했지요.</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -16535,7 +16695,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>…그 말을 기다리고 있었는지도 몰라요. 내가 언니를 못 지켰단 마음이 자꾸 먼저 와서, 뭘 봐도 전부 내 탓처럼 보였거든요.</t>
+          <t>…그 말을 기다리고 있었는지도 몰라요. 내가 언니를 못 지켰단 마음이 자꾸 먼저 와서, 뭘 봐도 전부 내 탓처럼 보였지요.</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -16595,7 +16755,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>그 말 이후 송순의 시선은 죄책감에 붙들리지 않고 방 안 증거들로 다시 옮겨 간다. 서로의 몫을 나눠 든다는 감각이 처음 분명해진다.</t>
+          <t>그 말 이후 송순의 시선은 죄책감에 붙들리지 않고 방 안 증거들로 다시 옮겨 간다. 서로의 몫을 나눠 든다는 감각이 처음 분명해진다. 이제는 언니를 잃은 이유가 아니라, 누가 언니를 가져갔는지 묻는 쪽으로 나아갈 수 있다.</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -16735,7 +16895,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>종이 위 문장을 따라갈수록 방 안의 공포는 도리어 또렷한 순서를 갖추기 시작한다. 유웅룡은 처음으로 이 사건이 괴담이 아니라 설계된 삭제라는 감각을 붙든다.</t>
+          <t>종이 위 문장을 따라갈수록 방 안의 공포는 도리어 또렷한 순서를 갖추기 시작한다. 유웅룡은 처음으로 이 사건이 괴담이 아니라 설계된 삭제라는 감각을 붙든다. 다음엔 그 삭제를 누가 지휘했는지 쫓아야 한다.</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -16835,7 +16995,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>그걸 직접 만지고도 그런 소릴 하세요? 기자님도 참…. 그런데 이제 저도 못 물러가겠어요.</t>
+          <t>그걸 직접 만지고도 그런 소릴 하세요? 기자님도 참…. 그런데 이제 저도 못 물러가겠어요. 언니가 안에서 한 번은 버티려 했다는 거잖아요.</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -17335,7 +17495,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>그래도 와야 했어요. 언니는 인사 한마디 없이 끊겼으니까. 이런 일은 누군가 끝까지 붙들지 않으면, 금세 없던 날로 넘어가 버리잖아요.</t>
+          <t>그래도 와야 했어요. 언니는 인사 한마디 없이 끊겼으니까. 이런 일은 누군가 끝까지 붙들지 않으면, 금세 없던 날로 넘어가 버리니까요.</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -17620,7 +17780,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>무섭죠. 그런데 전… 이상하리만치 귀에 익어요. 예전부터 멀리서 듣던 소리 같아요. 그래서 더 서늘해요.</t>
+          <t>무섭죠. 그런데 전… 기묘하리만치 귀에 익어요. 예전부터 멀리서 듣던 소리 같아요. 그래서 더 서늘해요.</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -19135,7 +19295,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>배고픈 사람들한텐 구원이란 말이 독보다 세지. 밥 한 그릇보다, 내일이 달라질 거라는 말이 더 위험하거든.</t>
+          <t>배고픈 사람들한텐 구원이란 말이 독보다 세지. 밥 한 그릇보다, 내일이 달라질 거라는 말이 더 위험한 것이오.</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -19255,7 +19415,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>그 여잔 천국을 약속하지 않았어. 대신 조선을 구하려면 한 번 몽땅 썩은 살을 도려내야 한다고 했지. 기묘하지? 세상이 지나치게 기울어져 있으면, 구원보다 파멸이 더 공평해 보일 때가 있거든.</t>
+          <t>그 여잔 천국을 약속하지 않았어. 대신 조선을 구하려면 한 번 몽땅 썩은 살을 도려내야 한다고 했지. 기묘하지 않은가. 세상이 지나치게 기울어져 있으면, 구원보다 파멸이 더 공평해 보일 때가 있는 법이오.</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -19815,7 +19975,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>그날 다들 노래를 듣긴 했어요. 그런데 아무도 같은 소릴 들은 것 같지가 않았어요. 누구는 어미 목소리 같다고 했고, 누구는 물 밑에서 누가 웃는 소리 같다 했어요. 그게 제일 무서웠어요.</t>
+          <t>그날 다들 노래를 듣긴 했어요. 그런데 아무도 같은 소릴 들은 것 같지가 않았어요. 누구는 어미 목소리 같다고 했고, 누구는 물 밑에서 누가 웃는 소리 같다 했어요. 그 점이 더욱 소름이 끼쳤어요.</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -23070,7 +23230,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>언니, 그 소리 따라가지 마. 나 봐. 나 아직 여기 있어. 네 이름 아직 여기 남아 있어.</t>
+          <t>언니, 그 소리 따라가지 마. 나 봐. 나 아직 여기 있어. 네 이름 아직 여기 남아 있어. 저 사람들 입에서 지워지기 전에 내가 먼저 부를게.</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -23130,7 +23290,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>이쯤 했으면 충분하잖아. 사람 갈아 넣고도 정화라 부를 셈이면, 그 입부터 막아야지.</t>
+          <t>이쯤이면 충분하겠지. 사람 갈아 넣고도 정화라 부를 셈이면, 이번엔 글이 아니라 몸으로라도 그 입부터 막아야지.</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -23170,7 +23330,7 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>두 사람은 아주 짧은 순간, 아무 쪽도 택하지 못하고 얼어붙는다. 공포는 때로 물러서는 감정보다 먼저 사람 몸을 멈추게 한다.</t>
+          <t>두 사람은 아주 짧은 순간, 아무 쪽도 택하지 못하고 얼어붙는다. 공포는 때로 물러서는 감정보다 먼저 사람 몸을 멈추게 한다. 아무것도 하지 않은 대가가 무엇인지, 바로 다음 순간 몸으로 알게 된다.</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -23360,7 +23520,7 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>감응이 흔들린다. 이해심이 비틀거리며 무너진다. 문은 반쯤 열린 채 억지로 닫힌다. 닫히는 마지막 순간까지 콧노래는 한 사람의 이름을 놓치지 않으려는 것처럼 떨린다.</t>
+          <t>감응이 흔들린다. 이해심이 비틀거리며 무너진다. 문은 반쯤 열린 채 억지로 닫힌다. 닫히는 마지막 순간까지 콧노래는 한 사람의 이름을 놓치지 않으려는 것처럼 떨린다. 누군가를 완전히 데려오진 못해도, 끝내 사람 쪽으로 당겨 두려는 힘만은 남는다.</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -23700,7 +23860,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>유웅룡이 이해심을 향해 달려든다. 짧은 충돌. 이해심이 쓰러지고 의식의 결이 끊긴다. 사람 몸으로 겨우 멈춘 의식은 끝내 아름답지도 장엄하지도 않다. 그저 비싼 대가를 치른 범죄 현장처럼 남는다.</t>
+          <t>유웅룡이 이해심을 향해 달려든다. 짧은 충돌. 이해심이 쓰러지고 의식의 결이 끊긴다. 사람 몸으로 겨우 멈춘 의식은 끝내 아름답지도 장엄하지도 않다. 그저 비싼 대가를 치른 범죄 현장처럼 남는다. 대신 이번엔 누가 무엇을 했는지 적을 문장만은 남았다.</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -24185,7 +24345,7 @@
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>대답 대신, 멀리서 아주 짧은 콧노래가 한 번 더 스친다. 둘 다 그 소리를 들었는지조차 확신하지 못한다. 확신하지 못한다는 사실이 오히려 더 오래 남는다.</t>
+          <t>대답 대신, 멀리서 아주 짧은 콧노래가 한 번 더 스친다. 둘 다 그 소리를 들었는지조차 확신하지 못한다. 확신하지 못한다는 사실이 오히려 더 오래 남는다. 아무것도 택하지 못했던 순간의 공백이, 이후의 모든 밤에 질문처럼 달라붙는다.</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
@@ -24465,7 +24625,7 @@
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>기사는 짧고, 도시의 밤은 평소와 다르지 않다. 전차는 달리고, 사람들은 다음 날을 준비한다. 아무 일도 없었던 것처럼.</t>
+          <t>기사 한 토막으로는 아무것도 끝나지 않는다. 다만 누군가는 사람을 붙들려 했고, 누군가는 몸으로 막으려 했고, 누군가는 끝내 그 밤을 설명하지 못한 채 남았다. 그 차이는 기록보다 오래 사람들 안에 남는다.</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
@@ -24485,17 +24645,12 @@
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>하지만 유웅룡의 수첩 안쪽에는 짧지 않은 이름과 문장들이 남는다. 불려간 자, 지워진 자, 판을 짠 자에 대한 메모는 기사보다 길고, 불에 타지 않은 질문처럼 끝내 접히지 않는다.</t>
+          <t>기사는 짧고, 도시의 밤은 평소와 다르지 않다. 전차는 달리고, 사람들은 다음 날을 준비한다. 아무 일도 없었던 것처럼.</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
         <is>
           <t>narration</t>
-        </is>
-      </c>
-      <c r="N357" t="inlineStr">
-        <is>
-          <t>CG_Branch_SolvedMid</t>
         </is>
       </c>
     </row>
@@ -24510,12 +24665,17 @@
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>문은 열렸다. 무엇이 나왔는지는 아무도 모른다. 그리고 아무도 묻지 않는다. 도시는 늘 그래왔듯, 감당 못 할 대답 앞에서 질문부터 접어버린다.</t>
+          <t>하지만 유웅룡의 수첩 안쪽에는 짧지 않은 이름과 문장들이 남는다. 불려간 자, 지워진 자, 판을 짠 자에 대한 메모는 기사보다 길고, 불에 타지 않은 질문처럼 끝내 접히지 않는다.</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
         <is>
           <t>narration</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>CG_Branch_SolvedMid</t>
         </is>
       </c>
     </row>
@@ -24530,7 +24690,7 @@
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>묻지 않는다는 건 모른다는 뜻이 아니다. 대답을 감당할 수 없어서 외면하는 쪽에 가깝다.</t>
+          <t>문은 열렸다. 무엇이 나왔는지는 아무도 모른다. 그리고 아무도 묻지 않는다. 도시는 늘 그래왔듯, 감당 못 할 대답 앞에서 질문부터 접어버린다.</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
@@ -24550,17 +24710,12 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>그래도 어딘가엔 적힌 이름이 남는다. 누군가가 접지 않고 버틴 문장, 끝내 모른 체하지 않겠다고 버틴 사람 덕분에.</t>
+          <t>묻지 않는다는 건 모른다는 뜻이 아니다. 대답을 감당할 수 없어서 외면하는 쪽에 가깝다.</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
         <is>
           <t>narration</t>
-        </is>
-      </c>
-      <c r="N360" t="inlineStr">
-        <is>
-          <t>CG_Room4_ReadRitual</t>
         </is>
       </c>
     </row>
@@ -24575,7 +24730,7 @@
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>그리고 어떤 밤은, 끝내 누군가의 말을 믿어 준 일 하나로 모양이 달라지기도 한다. 경성에선 그런 일이 기사보다 드물다.</t>
+          <t>그래도 어딘가엔 적힌 이름이 남는다. 누군가가 접지 않고 버틴 문장, 끝내 모른 체하지 않겠다고 버틴 사람 덕분에.</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
@@ -24585,7 +24740,7 @@
       </c>
       <c r="N361" t="inlineStr">
         <is>
-          <t>CG_Threshold_TrustedSongsoon</t>
+          <t>CG_Room4_ReadRitual</t>
         </is>
       </c>
     </row>
@@ -24600,7 +24755,7 @@
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>도시 한복판에서는 아무 일도 없었던 것처럼 전차 종이 울린다. 그러나 어떤 이름들은 한 번 적힌 뒤부터, 비록 신문에 나지 않아도 쉽게 다시 지워지지 않는다.</t>
+          <t>그리고 어떤 밤은, 끝내 누군가의 말을 믿어 준 일 하나로 모양이 달라지기도 한다. 경성에선 그런 일이 기사보다 드물다.</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
@@ -24610,7 +24765,7 @@
       </c>
       <c r="N362" t="inlineStr">
         <is>
-          <t>CG_Threshold_Investigation3</t>
+          <t>CG_Threshold_TrustedSongsoon</t>
         </is>
       </c>
     </row>
@@ -24625,7 +24780,7 @@
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>그리고 아주 드문 밤이면, 바람결 어딘가에서 콧노래가 짧게 스친다. 들은 사람만 잠깐 걸음을 늦춘다.</t>
+          <t>도시 한복판에서는 아무 일도 없었던 것처럼 전차 종이 울린다. 그러나 어떤 이름들은 한 번 적힌 뒤부터, 비록 신문에 나지 않아도 쉽게 다시 지워지지 않는다.</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
@@ -24635,7 +24790,7 @@
       </c>
       <c r="N363" t="inlineStr">
         <is>
-          <t>CG_Threshold_Resonance2</t>
+          <t>CG_Threshold_Investigation3</t>
         </is>
       </c>
     </row>
@@ -24650,7 +24805,7 @@
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>수첩 가장자리엔 따로 반박해 둔 문장들도 남는다. 미친 헛소리로 몰린 말, 자발적 도피로 덮인 실종, 우발적 광신으로 흐려진 의식. 적어도 그 거짓말만큼은 더는 도시가 편한 말로 접어 두지 못한다.</t>
+          <t>그리고 아주 드문 밤이면, 바람결 어딘가에서 콧노래가 짧게 스친다. 들은 사람만 잠깐 걸음을 늦춘다.</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
@@ -24660,7 +24815,7 @@
       </c>
       <c r="N364" t="inlineStr">
         <is>
-          <t>CG_RitualScene_SolvedHigh</t>
+          <t>CG_Threshold_Resonance2</t>
         </is>
       </c>
     </row>
@@ -24675,7 +24830,7 @@
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>자료실에서 이어 붙인 기사와 제단 앞에서 들이민 반박까지 남아 있다면, 그 수첩은 더 이상 메모장이 아니다. 도시에 맞서 끝내 접지 않은 고발문에 가깝다.</t>
+          <t>수첩 가장자리엔 따로 반박해 둔 문장들도 남는다. 미친 헛소리로 몰린 말, 자발적 도피로 덮인 실종, 우발적 광신으로 흐려진 의식. 적어도 그 거짓말만큼은 더는 도시가 편한 말로 접어 두지 못한다.</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
@@ -24685,27 +24840,32 @@
       </c>
       <c r="N365" t="inlineStr">
         <is>
-          <t>CG_Branch_ExposedArchivePattern</t>
+          <t>CG_RitualScene_SolvedHigh</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="B366" t="inlineStr">
         <is>
-          <t>ch6_outcome</t>
+          <t>ch6_epilogue</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>노래와 비명, 주문과 숨소리가 한순간 서로를 덮어쓴다. 의식은 흔들리기 시작하지만, 아직 어느 쪽으로 기울지 정해지지 않았다. 이 방에 남은 것은 힘겨루기가 아니라, 끝내 무엇을 사람으로 남길 것인가의 문제다.</t>
+          <t>자료실에서 이어 붙인 기사와 제단 앞에서 들이민 반박까지 남아 있다면, 그 수첩은 더 이상 메모장이 아니다. 도시에 맞서 끝내 접지 않은 고발문에 가깝다.</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
         <is>
           <t>narration</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>CG_Branch_ExposedArchivePattern</t>
         </is>
       </c>
     </row>
@@ -24716,21 +24876,16 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>질문을 끝까지 붙들어 온 사람만이 보이는 결도 있다. 이판규를 부른 손, 송금을 밀어 넣은 순서, 의식을 떠받친 구조가 한꺼번에 겹치며, 이제는 망설임조차 변명으로 쓰기 어려워진다.</t>
+          <t>노래와 비명, 주문과 숨소리가 한순간 서로를 덮어쓴다. 의식은 흔들리기 시작하지만, 아직 어느 쪽으로 기울지 정해지지 않았다. 이 방에 남은 것은 힘겨루기가 아니라, 끝내 무엇을 사람으로 남길 것인가의 문제다.</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
         <is>
           <t>narration</t>
-        </is>
-      </c>
-      <c r="N367" t="inlineStr">
-        <is>
-          <t>CG_Outcome_SolvedMid</t>
         </is>
       </c>
     </row>
@@ -24741,108 +24896,113 @@
         </is>
       </c>
       <c r="C368" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>더 나아가, 그중 몇몇은 아예 거짓말의 모양으로 남아 있었다. 미친 넋두리, 자발적 도피, 우발적 광신. 여기까지 오며 그 편한 설명들을 하나씩 부순 사람에겐 이제 무엇을 택하든 변명할 자리가 더 좁다.</t>
+          <t>방금 내린 선택은 이미 대가를 만들고 있다. 누군가는 이름을 붙들고, 누군가는 몸을 던졌고, 누군가는 단 한 박자 늦었다. 그 차이가 이제 각기 다른 결말의 속도를 만든다.</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
         <is>
           <t>narration</t>
-        </is>
-      </c>
-      <c r="N368" t="inlineStr">
-        <is>
-          <t>CG_RitualScene_SolvedHigh</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="B369" t="inlineStr">
         <is>
-          <t>ch6_path_a</t>
+          <t>ch6_outcome</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>1</v>
-      </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>Songsoon</t>
-        </is>
-      </c>
-      <c r="E369" t="inlineStr">
-        <is>
-          <t>Uneasy</t>
-        </is>
-      </c>
-      <c r="F369" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="G369" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>언니… 들리죠? 나예요. 그 방 앞에서도, 창고에서도… 계속 듣고 있었어요. 이제 모른 척 안 할 거예요.</t>
+          <t>질문을 끝까지 붙들어 온 사람만이 보이는 결도 있다. 이판규를 부른 손, 송금을 밀어 넣은 순서, 의식을 떠받친 구조가 한꺼번에 겹치며, 이제는 망설임조차 변명으로 쓰기 어려워진다.</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>CG_Outcome_SolvedMid</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="B370" t="inlineStr">
         <is>
-          <t>ch6_path_a</t>
+          <t>ch6_outcome</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>송순의 목소리가 콧노래과 겹쳐지며 방 안 공기의 결이 미세하게 바뀐다. 처음으로 의식 한가운데 사람 체온이 끼어든다.</t>
+          <t>더 나아가, 그중 몇몇은 아예 거짓말의 모양으로 남아 있었다. 미친 넋두리, 자발적 도피, 우발적 광신. 여기까지 오며 그 편한 설명들을 하나씩 부순 사람에겐 이제 무엇을 택하든 변명할 자리가 더 좁다.</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
         <is>
           <t>narration</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>CG_RitualScene_SolvedHigh</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="B371" t="inlineStr">
         <is>
-          <t>ch6_path_a2</t>
+          <t>ch6_path_a</t>
         </is>
       </c>
       <c r="C371" t="n">
         <v>1</v>
       </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Songsoon</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Uneasy</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>송금의 노래가 잠깐 흔들린다. 살아 있는 사람의 목소리가 아니라, 아주 오래된 기억이 잠시 되돌아오는 것처럼. 그러나 돌아오는 건 사람 전체가 아니라, 아직 이름이 남아 있는 한 조각뿐이다.</t>
+          <t>언니… 들리죠? 나예요. 그 방 앞에서도, 창고에서도… 계속 듣고 있었어요. 이제 모른 척 안 할 거예요.</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="B372" t="inlineStr">
         <is>
-          <t>ch6_path_a2</t>
+          <t>ch6_path_a</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -24850,17 +25010,12 @@
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>송순이 끝내 손을 놓지 않았던 태도와, 무서운 소리를 헛것이라 치워 버리지 않았던 믿음이 마지막 실처럼 남아 의식을 흔든다.</t>
+          <t>송순의 목소리가 콧노래과 겹쳐지며 방 안 공기의 결이 미세하게 바뀐다. 처음으로 의식 한가운데 사람 체온이 끼어든다. 구해 내려는 이름 하나가 제단의 질서를 비틀기 시작한다.</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
         <is>
           <t>narration</t>
-        </is>
-      </c>
-      <c r="N372" t="inlineStr">
-        <is>
-          <t>CG_Threshold_TrustedSongsoon</t>
         </is>
       </c>
     </row>
@@ -24871,21 +25026,16 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>문 앞에서부터 얽혀 든 콧노래의 결이 이 순간 송순의 목소리와 포개진다. 파멸에 더 가까이 다가섰기에, 되려 무엇을 붙들어야 하는지도 더 선명하게 보인다.</t>
+          <t>송금의 노래가 잠깐 흔들린다. 살아 있는 사람의 목소리가 아니라, 아주 오래된 기억이 잠시 되돌아오는 것처럼. 그러나 돌아오는 건 사람 전체가 아니라, 아직 이름이 남아 있는 한 조각뿐이다.</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
         <is>
           <t>narration</t>
-        </is>
-      </c>
-      <c r="N373" t="inlineStr">
-        <is>
-          <t>CG_Threshold_Resonance2</t>
         </is>
       </c>
     </row>
@@ -24896,11 +25046,11 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>붙들어 온 질문 셋 중 둘 이상이 이 순간에서 하나로 묶인다. 누구를 불렀는지, 누구를 밀어 넣었는지, 누가 판을 짰는지까지 알았기에 송순의 부름도 허공에 흩어지지 않는다.</t>
+          <t>송순이 끝내 손을 놓지 않았던 태도와, 무서운 소리를 헛것이라 치워 버리지 않았던 믿음이 마지막 실처럼 남아 의식을 흔든다.</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
@@ -24910,7 +25060,7 @@
       </c>
       <c r="N374" t="inlineStr">
         <is>
-          <t>CG_Branch_SolvedMid</t>
+          <t>CG_Threshold_TrustedSongsoon</t>
         </is>
       </c>
     </row>
@@ -24921,11 +25071,11 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>가면의 눈과 제단 문양이 어떻게 맞물렸는지까지 짚고 들어왔기에, 두 사람이 지금 끊어 낸 것이 막연한 공포가 아니라 짜여진 의식의 한 축이었다는 사실이 더 분명하게 남는다.</t>
+          <t>문 앞에서부터 얽혀 든 콧노래의 결이 이 순간 송순의 목소리와 포개진다. 파멸에 더 가까이 다가섰기에, 되려 무엇을 붙들어야 하는지도 더 선명하게 보인다.</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
@@ -24935,67 +25085,57 @@
       </c>
       <c r="N375" t="inlineStr">
         <is>
-          <t>CG_Branch_MatchedPattern</t>
+          <t>CG_Threshold_Resonance2</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="B376" t="inlineStr">
         <is>
-          <t>ch6_path_b</t>
+          <t>ch6_path_a2</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>1</v>
-      </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E376" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F376" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G376" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
+        <v>4</v>
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>이게 처음이 아니라는 걸 알고 물러서면, 나도 저 기사 밑줄 긋고 접어 둔 사람들과 다를 게 없지.</t>
+          <t>붙들어 온 질문 셋 중 둘 이상이 이 순간에서 하나로 묶인다. 누구를 불렀는지, 누구를 밀어 넣었는지, 누가 판을 짰는지까지 알았기에 송순의 부름도 허공에 흩어지지 않는다.</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>CG_Branch_SolvedMid</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="B377" t="inlineStr">
         <is>
-          <t>ch6_path_b</t>
+          <t>ch6_path_a2</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>유웅룡은 이해심을 향해 달려가며, 지난 기사들에서 지워진 문장들을 머릿속으로 되짚는다. 덮인 문장이 많을수록, 이번엔 몸으로라도 그 빈칸을 메워야 한다고 느낀다.</t>
+          <t>가면의 눈과 제단 문양이 어떻게 맞물렸는지까지 짚고 들어왔기에, 두 사람이 지금 끊어 낸 것이 막연한 공포가 아니라 짜여진 의식의 한 축이었다는 사실이 더 분명하게 남는다.</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
         <is>
           <t>narration</t>
+        </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>CG_Branch_MatchedPattern</t>
         </is>
       </c>
     </row>
@@ -25006,7 +25146,7 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25015,7 +25155,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Tense</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
@@ -25030,17 +25170,12 @@
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>접힌 기록을 또 하나 만들 바엔, 차라리 여기서 같이 부서지는 편이 낫지.</t>
+          <t>이게 처음이 아니라는 걸 알고 물러서면, 나도 저 기사 밑줄 긋고 접어 둔 사람들과 다를 게 없지.</t>
         </is>
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>thought</t>
-        </is>
-      </c>
-      <c r="N378" t="inlineStr">
-        <is>
-          <t>CG_Branch_FoundOldArticles</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -25051,41 +25186,16 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>11</v>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>Tense</t>
-        </is>
-      </c>
-      <c r="F379" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G379" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>이판규를 미친놈 하나로 접어 두려던 판도 여기서 끝입니다. 불려간 자의 말이 헛소리가 아니었다면, 지금 저 안의 일 역시 우발이 아니라 누군가의 계산이겠지요.</t>
+          <t>유웅룡은 이해심을 향해 달려가며, 지난 기사들에서 지워진 문장들을 머릿속으로 되짚는다. 덮인 문장이 많을수록, 이번엔 몸으로라도 그 빈칸을 메워야 한다고 느낀다. 기록자의 결단이 처음으로 육탄이 된다.</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>thought</t>
-        </is>
-      </c>
-      <c r="N379" t="inlineStr">
-        <is>
-          <t>CG_Outcome_QMadness</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -25096,21 +25206,21 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>Yuu</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Afraid</t>
+          <t>Tense</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
@@ -25120,62 +25230,107 @@
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>언니가 달아난 게 아니라 붙들린 거라면, 여기서도 같은 말로 덮이게 둘 순 없어요. 사라진 사람이 먼저 도망쳤다고, 또 그렇게 몰아갈 테니까요.</t>
+          <t>접힌 기록을 또 하나 만들 바엔, 차라리 여기서 같이 부서지는 편이 낫지.</t>
         </is>
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>thought</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
         <is>
-          <t>CG_Outcome_QRunaway</t>
+          <t>CG_Branch_FoundOldArticles</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="B381" t="inlineStr">
         <is>
-          <t>ch6_path_b2</t>
+          <t>ch6_path_b</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>연락하지 않은 덕분에 아무도 끼어들지 않는다. 이 선택의 결과는 오롯이 두 사람과 의식의 중심에 남는다. 도움을 부르지 않은 대가이기도 하고, 방해받지 않고 끝까지 본 대가이기도 하다.</t>
+          <t>이판규를 미친놈 하나로 접어 두려던 판도 여기서 끝입니다. 불려간 자의 말이 헛소리가 아니었다면, 지금 저 안의 일 역시 우발이 아니라 누군가의 계산이겠지요.</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>thought</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>CG_Outcome_QMadness</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="B382" t="inlineStr">
         <is>
-          <t>ch6_path_b2</t>
+          <t>ch6_path_b</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Songsoon</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Afraid</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>유웅룡이 창고에서 끝까지 읽어 낸 악보와, 자료실에서 주워 온 낡은 기사 조각들이 여기서 하나의 문장으로 겹친다. 흩어져 있던 것들이 이제는 적어 남길 수 있는 증거가 된다.</t>
+          <t>언니가 달아난 게 아니라 붙들린 거라면, 여기서도 같은 말로 덮이게 둘 순 없어요. 사라진 사람이 먼저 도망쳤다고, 또 그렇게 몰아갈 테니까요.</t>
         </is>
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
         <is>
-          <t>CG_Room4_ReadRitual</t>
+          <t>CG_Outcome_QRunaway</t>
         </is>
       </c>
     </row>
@@ -25186,21 +25341,16 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>콧노래가 아직 귓가에서 가시지 않는다. 유웅룡은 자신 또한 저 문턱에서 아주 비켜 선 목격자만은 아니게 되었다는 사실을 안다. 그래서 더더욱, 본 자의 이름으로 적어 두어야 한다.</t>
+          <t>연락하지 않은 덕분에 아무도 끼어들지 않는다. 이 선택의 결과는 오롯이 두 사람과 의식의 중심에 남는다. 도움을 부르지 않은 대가이기도 하고, 방해받지 않고 끝까지 본 대가이기도 하다.</t>
         </is>
       </c>
       <c r="M383" t="inlineStr">
         <is>
           <t>narration</t>
-        </is>
-      </c>
-      <c r="N383" t="inlineStr">
-        <is>
-          <t>CG_Threshold_Resonance2</t>
         </is>
       </c>
     </row>
@@ -25211,11 +25361,11 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>질문을 끝까지 밀고 와서야, 기록해야 할 문장의 순서도 달라진다. 이판규와 송금, 의식의 설계자까지 하나의 구조로 꿰어졌기에 이번 기록은 더는 단편 기사로 무너지지 않는다.</t>
+          <t>유웅룡이 창고에서 끝까지 읽어 낸 악보와, 자료실에서 주워 온 낡은 기사 조각들이 여기서 하나의 문장으로 겹친다. 흩어져 있던 것들이 이제는 적어 남길 수 있는 증거가 된다.</t>
         </is>
       </c>
       <c r="M384" t="inlineStr">
@@ -25225,7 +25375,7 @@
       </c>
       <c r="N384" t="inlineStr">
         <is>
-          <t>CG_Branch_SolvedMid</t>
+          <t>CG_Room4_ReadRitual</t>
         </is>
       </c>
     </row>
@@ -25236,11 +25386,11 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>자료실에서 이어 붙인 문장과 제단 앞에서 들이민 반박까지 겹치자, 남길 기록은 추측보다 고발문에 가까워진다. 누가 어떤 거짓말로 사람을 밀어 넣었는지까지 적을 자리가 생긴다.</t>
+          <t>콧노래가 아직 귓가에서 가시지 않는다. 유웅룡은 자신 또한 저 문턱에서 아주 비켜 선 목격자만은 아니게 되었다는 사실을 안다. 그래서 더더욱, 본 자의 이름으로 적어 두어야 한다.</t>
         </is>
       </c>
       <c r="M385" t="inlineStr">
@@ -25250,7 +25400,7 @@
       </c>
       <c r="N385" t="inlineStr">
         <is>
-          <t>CG_Branch_ExposedArchivePattern</t>
+          <t>CG_Threshold_Resonance2</t>
         </is>
       </c>
     </row>
@@ -25261,11 +25411,11 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>마지막 제단 앞에서 거짓말의 모양을 직접 들이민 탓에, 이제는 우발이었다는 말로도 이 밤을 봉합하기 어렵다. 남길 문장 자체가 한층 더 날카로워진다.</t>
+          <t>질문을 끝까지 밀고 와서야, 기록해야 할 문장의 순서도 달라진다. 이판규와 송금, 의식의 설계자까지 하나의 구조로 꿰어졌기에 이번 기록은 더는 단편 기사로 무너지지 않는다.</t>
         </is>
       </c>
       <c r="M386" t="inlineStr">
@@ -25275,67 +25425,57 @@
       </c>
       <c r="N386" t="inlineStr">
         <is>
-          <t>CG_Branch_ExposedTruthAtRitual</t>
+          <t>CG_Branch_SolvedMid</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="B387" t="inlineStr">
         <is>
-          <t>ch6_ritual_scene</t>
+          <t>ch6_path_b2</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>지하 의례실 깊숙이. 이해심이 제단 앞에 선다. 송금은 청색 한복 차림으로 노래하고 있다. 표정이 없다. 살기 위해 버틴 끝에 생기는 무표정이 아니라, 지나치게 오래 빌려 쓰여 자기 얼굴을 잃어버린 사람의 무표정이다.</t>
+          <t>자료실에서 이어 붙인 문장과 제단 앞에서 들이민 반박까지 겹치자, 남길 기록은 추측보다 고발문에 가까워진다. 누가 어떤 거짓말로 사람을 밀어 넣었는지까지 적을 자리가 생긴다.</t>
         </is>
       </c>
       <c r="M387" t="inlineStr">
         <is>
           <t>narration</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>CG_Branch_ExposedArchivePattern</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="B388" t="inlineStr">
         <is>
-          <t>ch6_ritual_scene</t>
+          <t>ch6_path_b2</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>2</v>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>Haesim</t>
-        </is>
-      </c>
-      <c r="E388" t="inlineStr">
-        <is>
-          <t>Trance</t>
-        </is>
-      </c>
-      <c r="F388" t="inlineStr">
-        <is>
-          <t>Center</t>
-        </is>
-      </c>
-      <c r="G388" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
+        <v>6</v>
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>어리석은 자들이여. 문이 열리는 날, 경성은 비로소 속을 드러낼 것이다. 곪은 자리는 끝내 누군가 헤집어야 한다. 나는 이제 그 일을 두려워하지 않는다.</t>
+          <t>마지막 제단 앞에서 거짓말의 모양을 직접 들이민 탓에, 이제는 우발이었다는 말로도 이 밤을 봉합하기 어렵다. 남길 문장 자체가 한층 더 날카로워진다.</t>
         </is>
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>CG_Branch_ExposedTruthAtRitual</t>
         </is>
       </c>
     </row>
@@ -25346,11 +25486,11 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>이해심의 뒤편 어둠 속엔 흰 천으로 얼굴을 가린 남자의 형체가 희미하게 선다. 가까이 있는데도 사람이라기보다 남의 신앙을 뒤에서 빨아먹는 그늘처럼 보인다. 향냄새 밑에 눌린 비린내가 그쪽에서 더 짙다.</t>
+          <t>지하 의례실 깊숙이. 이해심이 제단 앞에 선다. 송금은 청색 한복 차림으로 노래하고 있다. 표정이 없다. 살기 위해 버틴 끝에 생기는 무표정이 아니라, 지나치게 오래 빌려 쓰여 자기 얼굴을 잃어버린 사람의 무표정이다.</t>
         </is>
       </c>
       <c r="M389" t="inlineStr">
@@ -25366,21 +25506,21 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Cheonyonghae</t>
+          <t>Haesim</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Trance</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
@@ -25390,7 +25530,7 @@
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>교주님, 문은 오래 기다렸습니다. 주저하는 자들 소리까지 들여놓을 까닭은 없지요.</t>
+          <t>어리석은 자들이여. 문이 열리는 날, 경성은 비로소 속을 드러낼 것이다. 곪은 자리는 끝내 누군가 헤집어야 한다. 나는 이제 그 일을 두려워하지 않는다.</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
@@ -25406,21 +25546,16 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>그 순간 유웅룡의 귓속에서 문 앞 콧노래가 다시 울린다. 방 안 노래와 어긋나지 않는다. 아까 문에 귀를 댄 뒤로, 이 공간은 이미 몸 안쪽까지 파고든 듯하다.</t>
+          <t>이해심의 뒤편 어둠 속엔 흰 천으로 얼굴을 가린 남자의 형체가 희미하게 선다. 가까이 있는데도 사람이라기보다 남의 신앙을 뒤에서 빨아먹는 그늘처럼 보인다. 향냄새 밑에 눌린 비린내가 그쪽에서 더 짙다.</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
         <is>
           <t>narration</t>
-        </is>
-      </c>
-      <c r="N391" t="inlineStr">
-        <is>
-          <t>CG_RitualScene_Resonance2</t>
         </is>
       </c>
     </row>
@@ -25431,21 +25566,21 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Songgeum</t>
+          <t>Cheonyonghae</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Trance</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
@@ -25455,7 +25590,7 @@
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>(표정 없이, 노래를 흥얼거린다) …푸른… 옷을… 입고… 문 앞에… 서서…</t>
+          <t>교주님, 문은 오래 기다렸습니다. 주저하는 자들 소리까지 들여놓을 까닭은 없지요.</t>
         </is>
       </c>
       <c r="M392" t="inlineStr">
@@ -25471,36 +25606,21 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>7</v>
-      </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>Songsoon</t>
-        </is>
-      </c>
-      <c r="E393" t="inlineStr">
-        <is>
-          <t>Uneasy</t>
-        </is>
-      </c>
-      <c r="F393" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="G393" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
+        <v>5</v>
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>언니… 언니!</t>
+          <t>그 순간 유웅룡의 귓속에서 문 앞 콧노래가 다시 울린다. 방 안 노래와 어긋나지 않는다. 아까 문에 귀를 댄 뒤로, 이 공간은 이미 몸 안쪽까지 파고든 듯하다.</t>
         </is>
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>CG_RitualScene_Resonance2</t>
         </is>
       </c>
     </row>
@@ -25511,16 +25631,36 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Songgeum</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Trance</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Center</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>이해심의 안대 아래로 피가 번지기 시작한다. 하나는 불빛, 하나는 서릿발. 문이 열리고 있다. 방 안 촛불이 바깥바람 없이도 같은 방향으로 눕고, 벽면의 푸른 흔적이 젖은 살처럼 미세하게 꿈틀거린다.</t>
+          <t>(표정 없이, 노래를 흥얼거린다) …푸른… 옷을… 입고… 문 앞에… 서서…</t>
         </is>
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -25531,21 +25671,21 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Haesim</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Trance</t>
+          <t>Uneasy</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
@@ -25555,7 +25695,7 @@
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>너희는 늦었다. 법도, 기사도, 기도도 아무도 구하지 못했다. 나라를 위한다던 자도, 백성을 입에 올리던 자도 결국 하나도 건지지 못했지. 이제 남은 건 치료가 아니라 절단이다. 잘라내지 않으면 이 도시는 끝내 썩은 피를 제 몸이라 착각한 채 죽는다.</t>
+          <t>언니… 언니!</t>
         </is>
       </c>
       <c r="M395" t="inlineStr">
@@ -25571,36 +25711,16 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>10</v>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E396" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F396" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G396" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>그걸 정화라 부르지 마십시오. 사람을 셈하고 갈아 넣는 짓에 이름만 고상하게 붙인 학살이잖습니까.</t>
+          <t>이해심의 안대 아래로 피가 번지기 시작한다. 하나는 불빛, 하나는 서릿발. 문이 열리고 있다. 방 안 촛불이 바깥바람 없이도 같은 방향으로 눕고, 벽면의 푸른 흔적이 젖은 살처럼 미세하게 꿈틀거린다.</t>
         </is>
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -25611,7 +25731,7 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25635,7 +25755,7 @@
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>학살? 우습구나. 이 도시는 애당초 누군가를 갈아 넣어 움직여 왔다. 빈민가 아이도, 여급도, 병든 여자도, 나라 잃은 백성도 다 써 먹히며 사라졌지. 나는 다만 그 화덕을 휘장 뒤에 숨기지 않을 뿐이야. 너희는 덮고, 나는 드러낸다.</t>
+          <t>너희는 늦었다. 법도, 기사도, 기도도 아무도 구하지 못했다. 나라를 위한다던 자도, 백성을 입에 올리던 자도 결국 하나도 건지지 못했지. 이제 남은 건 치료가 아니라 절단이다. 잘라내지 않으면 이 도시는 끝내 썩은 피를 제 몸이라 착각한 채 죽는다.</t>
         </is>
       </c>
       <c r="M397" t="inlineStr">
@@ -25651,21 +25771,21 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Haesim</t>
+          <t>Yuu</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Trance</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
@@ -25675,7 +25795,7 @@
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>구원은 온전한 자에게 오지 않는다. 다 망가진 자에게만 문이 열린다. 나는 그걸 누구보다 먼저 배웠다. 황족의 피도, 독립의 꿈도, 여자의 몸도, 병든 폐도 끝내 나를 구하지 못했으니까.</t>
+          <t>그걸 정화라 부르지 마십시오. 사람을 셈하고 갈아 넣는 짓에 이름만 고상하게 붙인 학살이잖습니까.</t>
         </is>
       </c>
       <c r="M398" t="inlineStr">
@@ -25691,21 +25811,21 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Haesim</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Trance</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
@@ -25715,7 +25835,7 @@
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>당신 뒤에 선 작자가 누군진 이제 알겠습니다. 구원을 입에 올리며 사람 절망을 긁어 모으는 자들 말입니다. 이름만 청의교일 뿐, 속살은 늘 같은 장삿속이군요.</t>
+          <t>학살? 우습구나. 이 도시는 애당초 누군가를 갈아 넣어 움직여 왔다. 빈민가 아이도, 여급도, 병든 여자도, 나라 잃은 백성도 다 써 먹히며 사라졌지. 나는 다만 그 화덕을 휘장 뒤에 숨기지 않을 뿐이야. 너희는 덮고, 나는 드러낸다.</t>
         </is>
       </c>
       <c r="M399" t="inlineStr">
@@ -25731,21 +25851,21 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Cheonyonghae</t>
+          <t>Haesim</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Trance</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
@@ -25755,7 +25875,7 @@
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>장사라…. 말은 곱게도 하는군. 세상은 늘 제 죄를 그런 말로 덮지. 저들은 다만 제 몫을 냈을 뿐이야.</t>
+          <t>구원은 온전한 자에게 오지 않는다. 다 망가진 자에게만 문이 열린다. 나는 그걸 누구보다 먼저 배웠다. 황족의 피도, 독립의 꿈도, 여자의 몸도, 병든 폐도 끝내 나를 구하지 못했으니까.</t>
         </is>
       </c>
       <c r="M400" t="inlineStr">
@@ -25771,21 +25891,21 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>Yuu</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Uneasy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
@@ -25795,7 +25915,7 @@
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>몫이라고 부르지 마. 언니도, 없어졌던 사람들도 누구한테 바칠 몫으로 태어난 적 없어.</t>
+          <t>당신 뒤에 선 작자가 누군진 이제 알겠습니다. 구원을 입에 올리며 사람 절망을 긁어 모으는 자들 말입니다. 이름만 청의교일 뿐, 속살은 늘 같은 장삿속이군요.</t>
         </is>
       </c>
       <c r="M401" t="inlineStr">
@@ -25807,50 +25927,65 @@
     <row r="402">
       <c r="B402" t="inlineStr">
         <is>
-          <t>ch6_threshold</t>
+          <t>ch6_ritual_scene</t>
         </is>
       </c>
       <c r="C402" t="n">
-        <v>1</v>
-      </c>
-      <c r="K402" t="inlineStr">
-        <is>
-          <t>Flicker</t>
+        <v>14</v>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Cheonyonghae</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>노랫소리를 따라 마지막 문턱을 넘기 직전, 두 사람은 동시에 걸음을 멈춘다. 이제부터는 보고도 모른 척할 수 없다.</t>
+          <t>장사라…. 말은 곱게도 하는군. 세상은 늘 제 죄를 그런 말로 덮지. 저들은 다만 제 몫을 냈을 뿐이야.</t>
         </is>
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="B403" t="inlineStr">
         <is>
-          <t>ch6_threshold</t>
+          <t>ch6_ritual_scene</t>
         </is>
       </c>
       <c r="C403" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Tense</t>
+          <t>Uneasy</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
@@ -25858,19 +25993,9 @@
           <t>Speaker</t>
         </is>
       </c>
-      <c r="H403" t="inlineStr">
-        <is>
-          <t>SlideRight</t>
-        </is>
-      </c>
-      <c r="J403" t="inlineStr">
-        <is>
-          <t>Tremble</t>
-        </is>
-      </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>지금이라도 돌아가고 싶다면 말해요. 여기서부터는 기사도, 증언도, 정의도 우리를 지켜주지 못할 겁니다.</t>
+          <t>몫이라고 부르지 마. 언니도, 없어졌던 사람들도 누구한테 바칠 몫으로 태어난 적 없어.</t>
         </is>
       </c>
       <c r="M403" t="inlineStr">
@@ -25886,46 +26011,21 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>3</v>
-      </c>
-      <c r="D404" t="inlineStr">
-        <is>
-          <t>Songsoon</t>
-        </is>
-      </c>
-      <c r="E404" t="inlineStr">
-        <is>
-          <t>Afraid</t>
-        </is>
-      </c>
-      <c r="F404" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="G404" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
-      <c r="H404" t="inlineStr">
-        <is>
-          <t>FadeIn</t>
-        </is>
-      </c>
-      <c r="J404" t="inlineStr">
-        <is>
-          <t>Tremble</t>
+        <v>1</v>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Flicker</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>무서워요. 그런데 돌아가면 더 무서울 것 같아요. 언니를 남겨두고 살아가는 쪽이요.</t>
+          <t>노랫소리를 따라 마지막 문턱을 넘기 직전, 두 사람은 동시에 걸음을 멈춘다. 이제부터는 보고도 모른 척할 수 없다.</t>
         </is>
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -25936,7 +26036,7 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25945,7 +26045,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Tense</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
@@ -25958,9 +26058,19 @@
           <t>Speaker</t>
         </is>
       </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>SlideRight</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>Tremble</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>그럼 갑시다. 이번엔 끝까지 갑니다.</t>
+          <t>지금이라도 돌아가고 싶다면 말해요. 여기서부터는 기사도, 증언도, 정의도 우리를 지켜주지 못할 겁니다.</t>
         </is>
       </c>
       <c r="M405" t="inlineStr">
@@ -25976,21 +26086,21 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Afraid</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
@@ -25998,19 +26108,24 @@
           <t>Speaker</t>
         </is>
       </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>FadeIn</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>Tremble</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>누가 덮으라 해도, 이번엔 못 접습니다. 자료실에서 본 그 기사도 결국 여기까지 이어져 있었으니까.</t>
+          <t>무서워요. 그런데 돌아가면 더 무서울 것 같아요. 언니를 남겨두고 살아가는 쪽이요.</t>
         </is>
       </c>
       <c r="M406" t="inlineStr">
         <is>
           <t>normal</t>
-        </is>
-      </c>
-      <c r="N406" t="inlineStr">
-        <is>
-          <t>CG_Threshold_FoundOldArticles</t>
         </is>
       </c>
     </row>
@@ -26021,7 +26136,7 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26030,7 +26145,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Tense</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
@@ -26045,17 +26160,12 @@
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>그리고… 문 앞에서 들은 소리가 아직 귓속에 남아 있습니다. 저 안이 우릴 먼저 듣고 있다는 걸 알면서도 들어가는 셈이지요.</t>
+          <t>그럼 갑시다. 이번엔 끝까지 갑니다.</t>
         </is>
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>thought</t>
-        </is>
-      </c>
-      <c r="N407" t="inlineStr">
-        <is>
-          <t>CG_Threshold_Resonance2</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -26066,21 +26176,21 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>Yuu</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Uneasy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
@@ -26090,7 +26200,7 @@
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>기자님이 내 말을 먼저 믿어 줬으니, 저도 이번엔 망설이지 않을게요. 문이 열리면, 제가 먼저 언니를 부를게요.</t>
+          <t>누가 덮으라 해도, 이번엔 못 접습니다. 자료실에서 본 그 기사도 결국 여기까지 이어져 있었으니까.</t>
         </is>
       </c>
       <c r="M408" t="inlineStr">
@@ -26100,7 +26210,7 @@
       </c>
       <c r="N408" t="inlineStr">
         <is>
-          <t>CG_Threshold_TrustedSongsoon</t>
+          <t>CG_Threshold_FoundOldArticles</t>
         </is>
       </c>
     </row>
@@ -26111,7 +26221,7 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26135,7 +26245,7 @@
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>자료실에서 주운 기사도, 방 안에서 읽은 기록도 결국 여기까지 밀려왔군요. 이제 남은 건 외면하지 않는 일뿐입니다.</t>
+          <t>그리고… 문 앞에서 들은 소리가 아직 귓속에 남아 있습니다. 저 안이 우릴 먼저 듣고 있다는 걸 알면서도 들어가는 셈이지요.</t>
         </is>
       </c>
       <c r="M409" t="inlineStr">
@@ -26145,7 +26255,7 @@
       </c>
       <c r="N409" t="inlineStr">
         <is>
-          <t>CG_Threshold_Investigation3</t>
+          <t>CG_Threshold_Resonance2</t>
         </is>
       </c>
     </row>
@@ -26156,21 +26266,41 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Songsoon</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Uneasy</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>누구에게도 연락하지 않기로 한 덕에, 두 사람은 도움받을 길도 핑계 댈 길도 없이 같은 공포를 정면으로 마주 선다.</t>
+          <t>기자님이 내 말을 먼저 믿어 줬으니, 저도 이번엔 망설이지 않을게요. 문이 열리면, 제가 먼저 언니를 부를게요.</t>
         </is>
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
         <is>
-          <t>CG_Threshold_CalledEditorFalse</t>
+          <t>CG_Threshold_TrustedSongsoon</t>
         </is>
       </c>
     </row>
@@ -26181,7 +26311,7 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26205,7 +26335,7 @@
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>의례실 바닥에서 주운 종이까지 여기로 이어집니다. 남은 건 문장으로 증명하는 일이 아니라, 저 안에서 실제로 끊어내는 일입니다.</t>
+          <t>자료실에서 주운 기사도, 방 안에서 읽은 기록도 결국 여기까지 밀려왔군요. 이제 남은 건 외면하지 않는 일뿐입니다.</t>
         </is>
       </c>
       <c r="M411" t="inlineStr">
@@ -26215,7 +26345,7 @@
       </c>
       <c r="N411" t="inlineStr">
         <is>
-          <t>CG_Threshold_RitualNote</t>
+          <t>CG_Threshold_Investigation3</t>
         </is>
       </c>
     </row>
@@ -26226,11 +26356,11 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>병원, 폐공장, 자료실, 의례실에서 붙잡은 질문들이 이제야 한 줄로 선다. 끝내 다 푼 것은 아니어도, 무엇을 끊어야 하는지는 더 이상 흐리지 않다.</t>
+          <t>누구에게도 연락하지 않기로 한 덕에, 두 사람은 도움받을 길도 핑계 댈 길도 없이 같은 공포를 정면으로 마주 선다.</t>
         </is>
       </c>
       <c r="M412" t="inlineStr">
@@ -26240,67 +26370,77 @@
       </c>
       <c r="N412" t="inlineStr">
         <is>
-          <t>CG_Threshold_SolvedMid</t>
+          <t>CG_Threshold_CalledEditorFalse</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="B413" t="inlineStr">
         <is>
-          <t>scene_ending_erosion</t>
+          <t>ch6_threshold</t>
         </is>
       </c>
       <c r="C413" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>낙원 안쪽 깊은 방에서 의식이 끝났다. 불꽃은 꺼졌지만 공기는 아직 뜨겁고, 유웅룡은 그 자리에 무릎을 꿇고 있었다.</t>
+          <t>의례실 바닥에서 주운 종이까지 여기로 이어집니다. 남은 건 문장으로 증명하는 일이 아니라, 저 안에서 실제로 끊어내는 일입니다.</t>
         </is>
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>thought</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>CG_Threshold_RitualNote</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="B414" t="inlineStr">
         <is>
-          <t>scene_ending_erosion</t>
+          <t>ch6_threshold</t>
         </is>
       </c>
       <c r="C414" t="n">
-        <v>2</v>
-      </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E414" t="inlineStr">
-        <is>
-          <t>Tense</t>
-        </is>
-      </c>
-      <c r="F414" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G414" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
+        <v>11</v>
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>나는 더 이상 기록하지 않기로 한다. 이 사람들 곁에 남는 것이 내가 고른 길이다. 증거도, 기사도, 신용도 필요 없다.</t>
+          <t>병원, 폐공장, 자료실, 의례실에서 붙잡은 질문들이 이제야 한 줄로 선다. 끝내 다 푼 것은 아니어도, 무엇을 끊어야 하는지는 더 이상 흐리지 않다.</t>
         </is>
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>CG_Threshold_SolvedMid</t>
         </is>
       </c>
     </row>
@@ -26311,11 +26451,11 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>기자 유웅룡은 그날 밤 사라졌다. 경성 어딘가에서 그를 봤다는 말이 돌았지만, 아무도 확인하지 않았다. 기사는 끝내 쓰이지 않았다.</t>
+          <t>낙원 안쪽 깊은 방에서 의식이 끝났다. 불꽃은 꺼졌지만 공기는 아직 뜨겁고, 유웅룡은 그 자리에 무릎을 꿇고 있었다.</t>
         </is>
       </c>
       <c r="M415" t="inlineStr">
@@ -26331,31 +26471,51 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>낙원은 여전히 그 자리에 있었다. 불빛도, 노래도, 사람들도.</t>
+          <t>나는 더 이상 기록하지 않기로 한다. 이 사람들 곁에 남는 것이 내가 고른 길이다. 증거도, 기사도, 신용도 필요 없다.</t>
         </is>
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>thought</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="B417" t="inlineStr">
         <is>
-          <t>scene_gameover_credibility</t>
+          <t>scene_ending_erosion</t>
         </is>
       </c>
       <c r="C417" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>기록은 남았지만 믿어 줄 사람은 없다. 기자로서의 발언권은 완전히 무너졌다.</t>
+          <t>기자 유웅룡은 그날 밤 사라졌다. 경성 어딘가에서 그를 봤다는 말이 돌았지만, 아무도 확인하지 않았다. 기사는 끝내 쓰이지 않았다.</t>
         </is>
       </c>
       <c r="M417" t="inlineStr">
@@ -26367,40 +26527,20 @@
     <row r="418">
       <c r="B418" t="inlineStr">
         <is>
-          <t>scene_gameover_credibility</t>
+          <t>scene_ending_erosion</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>2</v>
-      </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>Editor</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr">
-        <is>
-          <t>Angry</t>
-        </is>
-      </c>
-      <c r="F418" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="G418" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
+        <v>4</v>
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>평판이 바닥이야. 자네 기사는 더 이상 검토도 못 해. 아무도 이 신문에 실린 걸 믿지 않으니까.</t>
+          <t>낙원은 여전히 그 자리에 있었다. 불빛도, 노래도, 사람들도.</t>
         </is>
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -26411,36 +26551,16 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>3</v>
-      </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E419" t="inlineStr">
-        <is>
-          <t>Tense</t>
-        </is>
-      </c>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G419" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>이렇게 끝날 줄은 몰랐다. 증거보다 신뢰가 먼저라는 걸, 뒤늦게야 깨달았다.</t>
+          <t>기록은 남았지만 믿어 줄 사람은 없다. 기자로서의 발언권은 완전히 무너졌다.</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -26451,34 +26571,114 @@
         </is>
       </c>
       <c r="C420" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Editor</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Angry</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>유웅룡의 이름은 지면에서 사라졌다. 기사는 쓰이지 않았고, 사건은 묻혔다.</t>
+          <t>평판이 바닥이야. 자네 기사는 더 이상 검토도 못 해. 아무도 이 신문에 실린 걸 믿지 않으니까.</t>
         </is>
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="B421" t="inlineStr">
         <is>
+          <t>scene_gameover_credibility</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>3</v>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>이렇게 끝날 줄은 몰랐다. 증거보다 신뢰가 먼저라는 걸, 뒤늦게야 깨달았다.</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>thought</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>scene_gameover_credibility</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>4</v>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>유웅룡의 이름은 지면에서 사라졌다. 기사는 쓰이지 않았고, 사건은 묻혔다.</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>narration</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="B423" t="inlineStr">
+        <is>
           <t>scene_gameover_erosion</t>
         </is>
       </c>
-      <c r="C421" t="n">
+      <c r="C423" t="n">
         <v>1</v>
       </c>
-      <c r="L421" t="inlineStr">
+      <c r="L423" t="inlineStr">
         <is>
           <t>더는 기록과 현실의 경계를 붙들 수 없다. 의식은 끝내 사건 바깥으로 미끄러진다.</t>
         </is>
       </c>
-      <c r="M421" t="inlineStr">
+      <c r="M423" t="inlineStr">
         <is>
           <t>narration</t>
         </is>

--- a/content/generated/script.generated.xlsx
+++ b/content/generated/script.generated.xlsx
@@ -23,7 +23,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CharacterTable" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CharacterEmotionTable" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QuestionTable" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StateDescriptorTable" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QuestionAnswerTable" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StateDescriptorTable" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -452,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-12 21:04:29</t>
+          <t>2026-08-12 22:51:25</t>
         </is>
       </c>
     </row>
@@ -488,7 +489,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ConditionTable, GaugeTable, GaugeStateTable, EffectTable, SceneTable, DialogTable, ChoiceGroupTable, ChoiceTable, BranchTable, EvidenceTable, EvidenceCategoryTable, CharacterTable, CharacterEmotionTable, QuestionTable, StateDescriptorTable</t>
+          <t>ConditionTable, GaugeTable, GaugeStateTable, EffectTable, SceneTable, DialogTable, ChoiceGroupTable, ChoiceTable, BranchTable, EvidenceTable, EvidenceCategoryTable, CharacterTable, CharacterEmotionTable, QuestionTable, QuestionAnswerTable, StateDescriptorTable</t>
         </is>
       </c>
     </row>
@@ -599,7 +600,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>이 판결, 기어이 물고 늘어진다.</t>
+          <t>판결문에서 푸른 천과 이판규의 시선을 따로 기록한다.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -629,7 +630,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편집장이 원하는 기사를 먼저 써둔다. 그게 실리는 법이다.</t>
+          <t>판결문을 먼저 편집국에 넘겨 신문감으로 정리한다.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -7196,6 +7197,1372 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>AnswerID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>QuestionID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>SortOrder</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>AnswerText</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>RequiredEvidenceIDs</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>IsCorrect</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>EffectGroupID</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ResultText</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>NextType</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>NextID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>QArchivePattern_Correct</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>QArchivePattern</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>과거 기사와 빈민가 목격담은 같은 방식의 실종이 기록에서 반복해 지워졌음을 보여 준다.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>EvOldArticles, EvSlumWitness</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>신문의 삭제와 목격자의 공포가 같은 빈자리를 가리킨다. 실종은 개인의 불운이 아니라 반복된 구조였다.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QArchivePattern_Erosion</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>QArchivePattern</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>목격자가 떨었으니, 사라진 사람들은 아직 빈민가 골목에서 이름을 부른다.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>EvSlumWitness</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>eff_question_erosion</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>두려운 증언을 유령의 증거로 바꿨다. 반복을 만든 기록의 손길은 다시 어둠 속으로 숨는다.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QArchivePattern_Credibility</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>QArchivePattern</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>30</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>낡은 기사 몇 장만으로 모든 현재 실종이 같은 범인의 짓이라고 쓴다.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>eff_question_credibility</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>기사만으로는 현재의 실종을 단정할 수 없다. 시간의 간격과 증언의 빈칸을 무시한 기사거리가 된다.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QCallPattern_Correct</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>QCallPattern</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>쪽지의 지시와 푸른 천의 표식은 사람을 낙원으로 몰아넣은 같은 호출의 흔적이다.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>EvNote, EvBlueCloth</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>글로 남은 지시와 몸에 남는 표식이 겹친다. 호출은 우연한 폐기물이 아니라 사람을 움직이는 명령이었다.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QCallPattern_Erosion</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>QCallPattern</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>붉은 쪽지는 읽는 사람마다 제 발로 낙원으로 끌려가게 만든다.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>EvNote</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>eff_question_erosion</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>명령의 흔적을 곧장 저주의 힘으로 바꿨다. 누가 사람을 몰았는지 묻는 질문이 사라진다.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QCallPattern_Credibility</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>QCallPattern</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>푸른 천 하나만으로 공장과 낙원이 같은 명령을 썼다고 발표한다.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>eff_question_credibility</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>표식 하나는 의심의 출발점일 뿐 연결의 증거는 아니다. 서로 다른 장소를 너무 빨리 한 사건으로 묶었다.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QIpangyuCall_Correct</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>QIpangyuCall</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>붉은 쪽지는 낙원 쪽에서 이판규를 직접 불러낸 호출이다.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>EvNote</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>쪽지의 지시가 이판규의 행선지와 맞물린다. 그는 우연히 달아난 것이 아니라 낙원 쪽 호출에 떠밀렸다.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QIpangyuCall_Erosion</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>QIpangyuCall</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>20</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>이판규를 부른 것은 쪽지가 아니라 공장 안에 남은 의식 그 자체다.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>EvRitualNote</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>eff_question_erosion</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>의식의 기척을 너무 쉽게 의지로 읽었다. 기록보다 공포가 먼저 결론을 밀어 넣는다.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QIpangyuCall_Credibility</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>QIpangyuCall</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>30</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>푸른 천은 이판규가 공장 인부에게 불려갔다는 명찰이다.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>eff_question_credibility</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>푸른 천만으로는 누가 누구를 불렀는지 증명할 수 없다. 추측이 기록의 빈칸을 대신했다.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QIpangyuMadness_Correct</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>QIpangyuMadness</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>붉은 쪽지가 남아 있으므로, 이판규의 호출 이야기는 실제 흔적과 맞닿아 있다.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>EvNote</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>발작처럼 흘린 말과 쪽지의 호출이 맞물린다. 그의 말은 죄를 피하려 지어낸 헛소리만은 아니다.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QIpangyuMadness_Erosion</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>QIpangyuMadness</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>이판규는 공장에 남은 노래를 들었기에 이미 의식의 편이 되었다.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>EvRitualNote</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>eff_question_erosion</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>불안한 기척을 곧장 공모의 증거로 바꿨다. 사람의 말이 의식의 소음 속으로 가라앉는다.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QIpangyuMadness_Credibility</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>QIpangyuMadness</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>30</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>푸른 천이 있었으니 이판규의 진술은 전부 사실이다.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>eff_question_credibility</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>천 조각 하나로 진술 전체를 보증할 수는 없다. 반박은 근거가 아니라 성급한 단정이 되었다.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QRitualAccident_Correct</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>QRitualAccident</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>의례실 종이의 순서와 몫은 이 일이 준비된 구조였음을 반박한다.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>EvRitualNote</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>종이에 남은 순서와 숫자는 우발적 광신이라는 설명을 무너뜨린다. 누군가가 사람 수까지 세며 의식을 준비했다.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QRitualAccident_Erosion</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>QRitualAccident</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>가면의 네 눈이 움직였으니 그날의 광기는 저절로 시작됐다.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>EvMask</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>eff_question_erosion</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>섬뜩한 인상을 원인으로 단정했다. 두려움은 계획을 읽는 대신 스스로 움직이는 물건을 만들어 낸다.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QRitualAccident_Credibility</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>QRitualAccident</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>옛 기사에 소란이 적혔으니, 그날은 준비 없는 난동이었다.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>eff_question_credibility</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>기사의 소란이라는 표현만으로 준비 여부를 가를 수 없다. 요약 문장이 현장의 구조를 지웠다.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QRitualErasure_Correct</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>QRitualErasure</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>악보의 노래와 의례실 기록은 사람의 이름을 흐리고 배역으로 바꾸는 정해진 절차다.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>EvRitualScore, EvRitualNote</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>노래의 결과 기록의 순서가 맞물린다. 의식은 사람을 단번에 없애지 않고, 이름부터 의례의 몫으로 바꿨다.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QRitualErasure_Erosion</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>QRitualErasure</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>20</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>악보를 읽는 순간 노래가 내 이름까지 지워 버린다.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>EvRitualScore</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>eff_question_both</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>의식의 위험을 현재의 확정된 운명으로 발표했다. 공포가 기록을 잠식하며, 남길 문장마저 흔들린다.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QRitualErasure_Credibility</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>QRitualErasure</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>의례실 종이 한 장만으로 노래가 모든 사람의 이름을 지웠다고 단정한다.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>eff_question_credibility</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>종이는 절차의 일부를 보여 줄 뿐 노래의 작동 전체를 증명하지 않는다. 한 조각을 결론으로 삼았다.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QRitualLead_Correct</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>QRitualLead</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>감응 악보와 의례실 기록은 누군가가 순서와 사람 수를 세며 의식을 주도했음을 보여 준다.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>EvRitualScore, EvRitualNote</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>악보의 결과 기록의 숫자가 같은 구조를 가리킨다. 낙원의 의식은 우발적 소문이 아니라 누군가 끝까지 쥔 판이었다.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QRitualLead_Erosion</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>QRitualLead</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>20</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>가면의 눈이 나를 바라보았으니, 가면 자체가 의식을 주도했다.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>EvMask</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>eff_question_erosion</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>시선의 감각을 주체의 증거로 삼았다. 사람과 물건의 경계가 흐려질수록 기록은 멀어진다.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>QRitualLead_Credibility</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>QRitualLead</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>30</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>낡은 기사에 이름이 없으니 신문사가 의식을 주도했다.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>eff_question_credibility</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>삭제된 이름은 은폐의 흔적이지 주도자의 서명은 아니다. 빈칸을 범인으로 발표할 수는 없다.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>QRoom4Purpose_Correct</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>QRoom4Purpose</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>청색 한복과 네 눈 가면은 4호실이 사람을 의례의 배역으로 준비시키던 곳임을 보여 준다.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>EvBlueHanbok, EvMask</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>의복과 가면은 장식이 아니라 역할을 갈아 끼우는 도구였다. 4호실은 사람을 의례의 몫으로 준비시키던 자리다.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>QRoom4Purpose_Erosion</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>QRoom4Purpose</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>20</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>일기에 남은 이름이 흐려졌으니 4호실 벽이 사람의 이름을 먹었다.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>EvDiary</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>eff_question_erosion</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>사람을 지운 구조를 방의 괴물로 바꿔 버렸다. 벽보다 그 벽을 사용한 이들이 먼저 사라진다.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>QRoom4Purpose_Credibility</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>QRoom4Purpose</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>30</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>청색 한복 하나가 있으니 4호실은 단순한 분장실이었다.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>eff_question_credibility</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>한 벌의 옷만으로 방의 용도를 줄여 버렸다. 가면과 기록이 가리키는 강제의 구조를 놓쳤다.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>QSonggeumMissing_Correct</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>QSonggeumMissing</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>10</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>송금은 일기에 적힌 대로 의례의 배역으로 밀려 들어가며 사라졌다.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>EvDiary</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>일기는 송금의 실종이 도피가 아니라, 사람을 의례의 몫으로 바꾸는 순서 안에서 벌어진 소거였음을 남긴다.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>QSonggeumMissing_Erosion</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>QSonggeumMissing</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>20</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>청색 한복이 송금의 몸을 삼켜 낙원 안으로 데려갔다.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>EvBlueHanbok</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>eff_question_erosion</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>의복에 남은 기척을 사람의 운명으로 덮어썼다. 남은 기록을 읽기보다 공포가 빈자리를 채운다.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>QSonggeumMissing_Credibility</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>QSonggeumMissing</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>30</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>낡은 기사에 실종이 적혔으니 송금도 같은 날 도망쳤다.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>eff_question_credibility</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>기사의 반복은 구조를 암시할 뿐 송금의 행적을 확정하지 않는다. 시대와 사람을 억지로 한 줄에 묶었다.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>QSonggeumRunaway_Correct</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>QSonggeumRunaway</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>10</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>일기는 송금에게 도망칠 틈이 없었고, 의례의 배역으로 정해졌음을 보여 준다.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>EvDiary</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>송금의 실종은 스스로 떠난 도피가 아니다. 선택당한 사람을 지워 버리는 의례의 순서가 그를 밀어 넣었다.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>QSonggeumRunaway_Erosion</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>QSonggeumRunaway</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>20</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>송금은 청색 한복을 입는 순간 자기 이름을 버리고 사라지기로 했다.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>EvBlueHanbok</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>eff_question_erosion</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>옷의 상징을 송금의 자발적 선택으로 바꿔 버렸다. 의식이 강요한 자리에 그의 목소리는 남지 않는다.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>QSonggeumRunaway_Credibility</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>QSonggeumRunaway</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>30</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>옛 기사에도 도망자가 있었으니 송금도 같은 방식으로 달아났다.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>eff_question_credibility</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>과거 기사는 반복을 의심하게 할 뿐, 송금의 선택을 말해 주지 않는다. 비교가 증언을 대신했다.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -7610,7 +8977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7662,7 +9029,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -7768,10 +9135,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>QuestionAnswerTable</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>StateDescriptorTable</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B17" t="n">
         <v>11</v>
       </c>
     </row>
@@ -11195,7 +12572,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>scene_ending_erosion</t>
+          <t>scene_gameover_erosion</t>
         </is>
       </c>
     </row>
@@ -11210,7 +12587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11798,7 +13175,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>eff_r9_document</t>
+          <t>eff_question_both</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -11808,7 +13185,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Credibility</t>
+          <t>Erosion</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -11818,7 +13195,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>eff_r9_follow_sound</t>
+          <t>eff_question_both</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -11828,37 +13205,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Erosion</t>
+          <t>Credibility</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>eff_r9_songsoon_support</t>
+          <t>eff_question_credibility</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TrustChange</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Songsoon</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>1</v>
+          <t>GaugeChange</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Credibility</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>eff_ritual_wrong</t>
+          <t>eff_question_erosion</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -11868,17 +13245,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Credibility</t>
+          <t>Erosion</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>eff_room4_conclusion_wrong</t>
+          <t>eff_r9_document</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -11892,13 +13269,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>eff_room4_note_match</t>
+          <t>eff_r9_follow_sound</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -11908,7 +13285,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Credibility</t>
+          <t>Erosion</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -11918,47 +13295,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>eff_slum_hanbok_press</t>
+          <t>eff_r9_songsoon_support</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GaugeChange</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Erosion</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
+          <t>TrustChange</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Songsoon</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>eff_songsoon_trust</t>
+          <t>eff_ritual_wrong</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TrustChange</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Songsoon</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>1</v>
+          <t>GaugeChange</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Credibility</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>eff_songsoon_wrong</t>
+          <t>eff_room4_conclusion_wrong</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -11978,20 +13355,100 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>eff_room4_note_match</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>GaugeChange</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Credibility</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>eff_slum_hanbok_press</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>GaugeChange</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Erosion</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>eff_songsoon_trust</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TrustChange</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Songsoon</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>eff_songsoon_wrong</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>GaugeChange</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Credibility</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>eff_threshold_erosion_touch</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>GaugeChange</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Erosion</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D43" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12006,7 +13463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12070,6 +13527,16 @@
           <t>InvestigationHint</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ForcedQuestionIDs</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>QuestionMode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12095,6 +13562,17 @@
           <t>assets/sfx/ambient.mp3</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>첫 기록</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>법정에서 지워진 흔적을 어떤 기록으로 남길지 정한다.</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12120,6 +13598,7 @@
           <t>assets/sfx/newsroom.mp3</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12145,6 +13624,7 @@
           <t>assets/sfx/newsroom.mp3</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12190,6 +13670,7 @@
           <t>법정 기록, 누락된 피해 기록, 편집장의 금지선 가운데 두 가지를 확인해 취재의 출발점을 정하세요.</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12215,6 +13696,7 @@
           <t>assets/sfx/newsroom.mp3</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12260,6 +13742,7 @@
           <t>점장의 입, 여급들의 빚, 구석 손님의 침묵 가운데 어디를 먼저 건드릴지 정하세요.</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12285,6 +13768,7 @@
           <t>assets/sfx/creepy.mp3</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12313,6 +13797,16 @@
       <c r="F9" t="n">
         <v>3</v>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>QIpangyuCall</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12338,6 +13832,7 @@
           <t>assets/sfx/tense.mp3</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12366,6 +13861,7 @@
       <c r="F11" t="n">
         <v>1</v>
       </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12394,6 +13890,7 @@
       <c r="F12" t="n">
         <v>1</v>
       </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12422,6 +13919,7 @@
       <c r="F13" t="n">
         <v>3</v>
       </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12457,6 +13955,16 @@
           <t>네가 가진 것이 이 사건과 연결된 증거라는 걸 보여줘야 송순이 입을 연다.</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>QIpangyuMadness, QCallPattern</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12482,6 +13990,7 @@
           <t>assets/sfx/sad.mp3</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12527,6 +14036,7 @@
           <t>벽의 흔적, 남겨진 기록, 송순의 흔들림 가운데 어디부터 잡아야 사건의 구조가 드러나는지 고르세요.</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12562,6 +14072,16 @@
           <t>의식의 계획성과 송금의 실종을 함께 보여 주는 단서를 골라야 한다.</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>QSonggeumMissing, QSonggeumRunaway, QRoom4Purpose</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12587,6 +14107,7 @@
           <t>assets/sfx/mystery.mp3</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12612,6 +14133,7 @@
           <t>assets/sfx/mystery.mp3</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -12637,6 +14159,7 @@
           <t>assets/sfx/tense.mp3</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -12662,6 +14185,7 @@
           <t>assets/sfx/mystery.mp3</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -12687,6 +14211,7 @@
           <t>assets/sfx/mystery.mp3</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -12712,6 +14237,7 @@
           <t>assets/sfx/mystery.mp3</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -12747,6 +14273,7 @@
           <t>그가 직접 연관된 증거를 꺼내야만 그의 입이 열린다. 무관한 것을 내밀면 외면한다.</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -12782,6 +14309,7 @@
           <t>자료실 기사 위에 지금 가진 단서를 직접 겹쳐 보며, 무엇이 같은 손에 의해 지워졌는지 확인한다.</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -12827,6 +14355,16 @@
           <t>여자가 파는 믿음, 뒤에 숨은 사내, 최근에 사라진 이들의 흔적 가운데 어디를 먼저 건드릴지 정하세요.</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>QArchivePattern</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -12862,6 +14400,7 @@
           <t>결근·세탁 기록과 출입 동선을 서로 다른 두 축으로 확인해, 사라짐과 지하 문을 연결한다.</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -12897,6 +14436,7 @@
           <t>옥련이 알고 있는 것과 연결된 단서만이 그녀의 입을 더 열게 한다.</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -12922,6 +14462,7 @@
           <t>assets/sfx/jazz_dark.mp3</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -12947,6 +14488,7 @@
           <t>assets/sfx/jazz_dark.mp3</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -12972,6 +14514,7 @@
           <t>assets/sfx/creepy_2.mp3</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -13000,6 +14543,7 @@
       <c r="F32" t="n">
         <v>3</v>
       </c>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -13045,6 +14589,7 @@
           <t>노랫소리, 문 안의 배치, 송순의 호흡 가운데 두 가지를 확인하고 의례실에 들어갈 준비를 하세요.</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -13070,6 +14615,7 @@
           <t>assets/sfx/creepy_2.mp3</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -13105,6 +14651,7 @@
           <t>송금이 자발적 무녀가 아니라 강제로 편입됐음을 확인하고, 이번 밤 끊어야 할 순번을 읽는다.</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -13133,6 +14680,7 @@
       <c r="F36" t="n">
         <v>1</v>
       </c>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -13171,6 +14719,16 @@
           <t>의례실에서 붙든 구조와 단서를 지금 이 자리의 흔적에 겹쳐, 무엇이 반복되고 있는지 더 분명하게 확인한다.</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>QRitualLead, QRitualAccident, QRitualErasure</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -13216,6 +14774,7 @@
           <t>올바른 증거를 고르면 신용이 오른다. 맞지 않는 증거를 내밀면 기사의 신뢰가 흔들린다.</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -13241,6 +14800,7 @@
           <t>assets/sfx/ritual_climax.mp3</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -13266,6 +14826,7 @@
           <t>assets/sfx/ritual_climax.mp3</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -13291,6 +14852,7 @@
           <t>assets/sfx/ritual_climax.mp3</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -13316,6 +14878,7 @@
           <t>assets/sfx/ending.mp3</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -13341,6 +14904,7 @@
           <t>assets/sfx/ending.mp3</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -13369,6 +14933,7 @@
       <c r="F44" t="n">
         <v>2</v>
       </c>
+      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -13394,6 +14959,7 @@
           <t>assets/sfx/ending.mp3</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -13429,6 +14995,7 @@
           <t>폭로로 만든 틈을 어디에 쓸지 고른다. 사람을 붙들거나, 의식을 끊거나, 기록을 남긴다.</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -13457,6 +15024,7 @@
       <c r="F47" t="n">
         <v>2</v>
       </c>
+      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -13482,6 +15050,7 @@
           <t>assets/sfx/ritual_climax.mp3</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -13507,6 +15076,7 @@
           <t>assets/sfx/ending.mp3</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -13532,6 +15102,7 @@
           <t>assets/sfx/ritual_climax.mp3</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -13557,6 +15128,7 @@
           <t>assets/sfx/ending.mp3</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -13595,6 +15167,7 @@
           <t>송금, 이해심, 그리고 이 방에 쌓인 질문들 사이에서 무엇을 사람 쪽으로 남길지 지금 결정한다.</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -13620,6 +15193,7 @@
           <t>assets/sfx/ritual.mp3</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -13645,6 +15219,7 @@
           <t>assets/sfx/ritual_climax.mp3</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -13670,6 +15245,7 @@
           <t>assets/sfx/ending.mp3</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -13695,6 +15271,7 @@
           <t>assets/sfx/ending.mp3</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/content/generated/script.generated.xlsx
+++ b/content/generated/script.generated.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-12 22:51:25</t>
+          <t>2026-08-12 23:05:24</t>
         </is>
       </c>
     </row>

--- a/content/generated/script.generated.xlsx
+++ b/content/generated/script.generated.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-12 23:05:24</t>
+          <t>2026-08-12 23:45:27</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CG_QR_IpangyuSeen_01</t>
+          <t>CG_QR_CheckpointFactoryShock</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CG_QR_IpangyuSeen_01</t>
+          <t>CG_QR_CheckpointWell</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6599,7 +6599,11 @@
           <t>Witness</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CG_QR_CheckpointWell</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6667,7 +6671,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CG_QR_SonggeumOpen_01, CG_QR_SonggeumOpen_02, CG_QR_SonggeumOpen_03, CG_QR_SonggeumOpen_04</t>
+          <t>CG_QR_CheckpointRoom4Conclusion</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6750,7 +6754,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CG_QR_SonggeumOpen_01, CG_QR_SonggeumOpen_02, CG_QR_SonggeumOpen_03, CG_QR_SonggeumOpen_04</t>
+          <t>CG_QR_CheckpointRoom4Conclusion</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -6836,7 +6840,11 @@
           <t>Missing</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>CG_QR_CheckpointRoom4Conclusion</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6904,7 +6912,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CG_QR_RitualOpen_01, CG_QR_RitualOpen_02, CG_QR_RitualOpen_03</t>
+          <t>CG_QR_CheckpointRitualRoom</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -6992,7 +7000,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CG_QR_RitualOpen_01, CG_QR_RitualOpen_02, CG_QR_RitualOpen_03</t>
+          <t>CG_QR_CheckpointRitualRoom</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -7078,7 +7086,11 @@
           <t>Record</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CG_QR_CheckpointSlum</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7144,7 +7156,11 @@
           <t>Ritual</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CG_QR_CheckpointRitualRoom</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7289,7 +7305,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -7335,7 +7351,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -7377,7 +7393,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -7419,7 +7435,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -7465,7 +7481,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -7507,7 +7523,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -7549,7 +7565,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -7595,7 +7611,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -7637,7 +7653,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -7679,7 +7695,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -7725,7 +7741,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -7767,7 +7783,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -7809,7 +7825,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -7855,7 +7871,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -7897,7 +7913,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -7939,7 +7955,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -7985,7 +8001,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -8027,7 +8043,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -8069,7 +8085,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -8115,7 +8131,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -8157,7 +8173,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -8199,7 +8215,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -8245,7 +8261,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -8287,7 +8303,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -8329,7 +8345,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -8375,7 +8391,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -8417,7 +8433,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -8459,7 +8475,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -8505,7 +8521,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -8547,7 +8563,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -8999,7 +9015,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3">
@@ -9163,7 +9179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10859,22 +10875,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cond_RR_QIpangyuSeen_01</t>
+          <t>Cond_QR_CheckpointFactoryShock_01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CG_QR_IpangyuSeen_01</t>
+          <t>CG_QR_CheckpointFactoryShock</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>RevealedCharacter</t>
+          <t>SceneVisited</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Ipangyu</t>
+          <t>ch2_factory_shock</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -10891,52 +10907,54 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cond_RR_QRitualOpen_01</t>
+          <t>Cond_QR_CheckpointRitualRoom_01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CG_QR_RitualOpen_01</t>
+          <t>CG_QR_CheckpointRitualRoom</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>SceneVisited</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ReadRitualScore</t>
+          <t>ch5_ritual_room</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>1</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cond_RR_QRitualOpen_02</t>
+          <t>Cond_QR_CheckpointRoom4Conclusion_01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CG_QR_RitualOpen_02</t>
+          <t>CG_QR_CheckpointRoom4Conclusion</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>RevealedCharacter</t>
+          <t>SceneVisited</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Haesim</t>
+          <t>ch3_room4_conclusion</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -10953,47 +10971,54 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cond_RR_QRitualOpen_03</t>
+          <t>Cond_QR_CheckpointSlum_01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CG_QR_RitualOpen_03</t>
+          <t>CG_QR_CheckpointSlum</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SceneProgressIndex</t>
+          <t>SceneVisited</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ch4a_slum</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>31</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cond_RR_QSonggeumOpen_01</t>
+          <t>Cond_QR_CheckpointWell_01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CG_QR_SonggeumOpen_01</t>
+          <t>CG_QR_CheckpointWell</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>SceneVisited</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EvDiary</t>
+          <t>ch2_well</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -11010,22 +11035,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cond_RR_QSonggeumOpen_02</t>
+          <t>Cond_RR_QIpangyuSeen_01</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CG_QR_SonggeumOpen_02</t>
+          <t>CG_QR_IpangyuSeen_01</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>RevealedCharacter</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>EvOldArticles</t>
+          <t>Ipangyu</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -11042,17 +11067,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cond_RR_QSonggeumOpen_03</t>
+          <t>Cond_RR_QRitualOpen_01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CG_QR_SonggeumOpen_03</t>
+          <t>CG_QR_RitualOpen_01</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SceneProgressIndex</t>
+          <t>GaugeValue</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ReadRitualScore</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -11061,18 +11091,18 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cond_RR_QSonggeumOpen_04</t>
+          <t>Cond_RR_QRitualOpen_02</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CG_QR_SonggeumOpen_04</t>
+          <t>CG_QR_RitualOpen_02</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -11082,7 +11112,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Songgeum</t>
+          <t>Haesim</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -11099,84 +11129,79 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cond_RR_QIpangyuState_00</t>
+          <t>Cond_RR_QRitualOpen_03</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CG_QS_IpangyuCall_01</t>
+          <t>CG_QR_RitualOpen_03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>QuestionSolved</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>QuestionSolved_QIpangyuCall</t>
+          <t>SceneProgressIndex</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cond_RR_QIpangyuState_01</t>
+          <t>Cond_RR_QSonggeumOpen_01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CG_QS_IpangyuCall_02</t>
+          <t>CG_QR_SonggeumOpen_01</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>EvidenceOwned</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Erosion</t>
+          <t>EvDiary</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>1</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cond_RR_QIpangyuMadnessState_00</t>
+          <t>Cond_RR_QSonggeumOpen_02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CG_QS_IpangyuMadness_01</t>
+          <t>CG_QR_SonggeumOpen_02</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>QuestionSolved</t>
+          <t>EvidenceOwned</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>QuestionSolved_QIpangyuMadness</t>
+          <t>EvOldArticles</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -11193,54 +11218,47 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cond_RR_QIpangyuMadnessState_01</t>
+          <t>Cond_RR_QSonggeumOpen_03</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CG_QS_IpangyuMadness_02</t>
+          <t>CG_QR_SonggeumOpen_03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>EvNote</t>
+          <t>SceneProgressIndex</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cond_RR_QRitualAccidentState_00</t>
+          <t>Cond_RR_QSonggeumOpen_04</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CG_QS_RitualAccident_01</t>
+          <t>CG_QR_SonggeumOpen_04</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>QuestionSolved</t>
+          <t>RevealedCharacter</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>QuestionSolved_QRitualAccident</t>
+          <t>Songgeum</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -11257,22 +11275,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cond_RR_QRitualAccidentState_01</t>
+          <t>Cond_RR_QIpangyuState_00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CG_QS_RitualAccident_02</t>
+          <t>CG_QS_IpangyuCall_01</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>QuestionSolved</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EvRitualNote</t>
+          <t>QuestionSolved_QIpangyuCall</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -11289,84 +11307,84 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cond_RR_QRitualState_00</t>
+          <t>Cond_RR_QIpangyuState_01</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CG_QS_RitualLead_01</t>
+          <t>CG_QS_IpangyuCall_02</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>QuestionSolved</t>
+          <t>GaugeValue</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>QuestionSolved_QRitualLead</t>
+          <t>Erosion</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cond_RR_QRitualState_01</t>
+          <t>Cond_RR_QIpangyuMadnessState_00</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CG_QS_RitualLead_02</t>
+          <t>CG_QS_IpangyuMadness_01</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>QuestionSolved</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ReadRitualScore</t>
+          <t>QuestionSolved_QIpangyuMadness</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>1</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cond_RR_QSonggeumState_00</t>
+          <t>Cond_RR_QIpangyuMadnessState_01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CG_QS_SonggeumMissing_01</t>
+          <t>CG_QS_IpangyuMadness_02</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>QuestionSolved</t>
+          <t>EvidenceOwned</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>QuestionSolved_QSonggeumMissing</t>
+          <t>EvNote</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -11383,22 +11401,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cond_RR_QSonggeumState_01</t>
+          <t>Cond_RR_QRitualAccidentState_00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CG_QS_SonggeumMissing_02</t>
+          <t>CG_QS_RitualAccident_01</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>QuestionSolved</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>EvDiary</t>
+          <t>QuestionSolved_QRitualAccident</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -11415,22 +11433,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cond_RR_QSonggeumRunawayState_00</t>
+          <t>Cond_RR_QRitualAccidentState_01</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CG_QS_SonggeumRunaway_01</t>
+          <t>CG_QS_RitualAccident_02</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>QuestionSolved</t>
+          <t>EvidenceOwned</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>QuestionSolved_QSonggeumRunaway</t>
+          <t>EvRitualNote</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -11447,22 +11465,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cond_RR_QSonggeumRunawayState_01</t>
+          <t>Cond_RR_QRitualState_00</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CG_QS_SonggeumRunaway_02</t>
+          <t>CG_QS_RitualLead_01</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>QuestionSolved</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>EvDiary</t>
+          <t>QuestionSolved_QRitualLead</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -11479,44 +11497,42 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cond_RitualRoom_OldArticles_01</t>
+          <t>Cond_RR_QRitualState_01</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CG_RitualRoom_OldArticles</t>
+          <t>CG_QS_RitualLead_02</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>GaugeValue</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>EvOldArticles</t>
+          <t>ReadRitualScore</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cond_RitualRoom_AccidentSolved_01</t>
+          <t>Cond_RR_QSonggeumState_00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CG_RitualRoom_QRitualAccident</t>
+          <t>CG_QS_SonggeumMissing_01</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -11526,7 +11542,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>QuestionSolved_QRitualAccident</t>
+          <t>QuestionSolved_QSonggeumMissing</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -11543,22 +11559,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cond_RitualRoom_QRitualAccident_01</t>
+          <t>Cond_RR_QSonggeumState_01</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CG_RitualRoom_QRitualAccident</t>
+          <t>CG_QS_SonggeumMissing_02</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>QuestionSolved</t>
+          <t>EvidenceOwned</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>QuestionSolved_QRitualAccident</t>
+          <t>EvDiary</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -11575,22 +11591,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cond_RitualRoom_RitualScore_01</t>
+          <t>Cond_RR_QSonggeumRunawayState_00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CG_RitualRoom_RitualScore</t>
+          <t>CG_QS_SonggeumRunaway_01</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>QuestionSolved</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EvRitualScore</t>
+          <t>QuestionSolved_QSonggeumRunaway</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -11607,102 +11623,108 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cond_RitualScene_Resonance_01</t>
+          <t>Cond_RR_QSonggeumRunawayState_01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CG_RitualScene_Resonance2</t>
+          <t>CG_QS_SonggeumRunaway_02</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>EvidenceOwned</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Erosion</t>
+          <t>EvDiary</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>2</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cond_RitualScene_SolvedHigh_01</t>
+          <t>Cond_RitualRoom_OldArticles_01</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CG_RitualScene_SolvedHigh</t>
+          <t>CG_RitualRoom_OldArticles</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>EvidenceOwned</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SolvedQuestionCount</t>
+          <t>EvOldArticles</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>7</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cond_Ritual_Erosion6_01</t>
+          <t>Cond_RitualRoom_AccidentSolved_01</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CG_Ritual_Erosion6</t>
+          <t>CG_RitualRoom_QRitualAccident</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>QuestionSolved</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Erosion</t>
+          <t>QuestionSolved_QRitualAccident</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>6</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cond_Ritual_QRoom4Purpose_01</t>
+          <t>Cond_RitualRoom_QRitualAccident_01</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CG_Ritual_QRoom4Purpose</t>
+          <t>CG_RitualRoom_QRitualAccident</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -11712,7 +11734,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>QuestionSolved_QRoom4Purpose</t>
+          <t>QuestionSolved_QRitualAccident</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -11729,12 +11751,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cond_Room4_HasNote_01</t>
+          <t>Cond_RitualRoom_RitualScore_01</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CG_Room4_HasNote</t>
+          <t>CG_RitualRoom_RitualScore</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -11744,7 +11766,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>EvNote</t>
+          <t>EvRitualScore</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -11761,12 +11783,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cond_Room4_ReadRitual_01</t>
+          <t>Cond_RitualScene_Resonance_01</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CG_Room4_ReadRitual</t>
+          <t>CG_RitualScene_Resonance2</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -11776,7 +11798,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ReadRitualScore</t>
+          <t>Erosion</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -11785,92 +11807,88 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cond_Room4_TrustedSongsoon_01</t>
+          <t>Cond_RitualScene_SolvedHigh_01</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CG_Room4_TrustedSongsoon</t>
+          <t>CG_RitualScene_SolvedHigh</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ChoiceSelected</t>
+          <t>GaugeValue</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Ch3WarehouseTrustSongsoon|Ch3Room4ComfortSongsoon</t>
+          <t>SolvedQuestionCount</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cond_Slum_HasHanbok_01</t>
+          <t>Cond_Ritual_Erosion6_01</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CG_Slum_HasHanbok</t>
+          <t>CG_Ritual_Erosion6</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>GaugeValue</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>EvBlueHanbok</t>
+          <t>Erosion</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cond_Threshold_CalledEditorFalse_01</t>
+          <t>Cond_Ritual_QRoom4Purpose_01</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CG_Threshold_CalledEditorFalse</t>
+          <t>CG_Ritual_QRoom4Purpose</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ChoiceSelected</t>
+          <t>QuestionSolved</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Ch5PathNoContact</t>
+          <t>QuestionSolved_QRoom4Purpose</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -11887,42 +11905,44 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cond_Threshold_Credibility7_01</t>
+          <t>Cond_Room4_HasNote_01</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CG_Threshold_Credibility7</t>
+          <t>CG_Room4_HasNote</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>EvidenceOwned</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Credibility</t>
+          <t>EvNote</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
-        <v>7</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cond_Threshold_Erosion6_01</t>
+          <t>Cond_Room4_ReadRitual_01</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CG_Threshold_Erosion6</t>
+          <t>CG_Room4_ReadRitual</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -11932,7 +11952,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Erosion</t>
+          <t>ReadRitualScore</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -11941,18 +11961,18 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cond_Threshold_FoundOldArticles_01</t>
+          <t>Cond_Room4_TrustedSongsoon_01</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CG_Threshold_FoundOldArticles</t>
+          <t>CG_Room4_TrustedSongsoon</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -11962,7 +11982,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Ch4ALibraryTakeArticles|Ch4ALibraryExposeArchive</t>
+          <t>Ch3WarehouseTrustSongsoon|Ch3Room4ComfortSongsoon</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -11979,104 +11999,106 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cond_Threshold_Investigation_01</t>
+          <t>Cond_Slum_HasHanbok_01</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CG_Threshold_Investigation3</t>
+          <t>CG_Slum_HasHanbok</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>EvidenceOwned</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Credibility</t>
+          <t>EvBlueHanbok</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F91" t="n">
-        <v>3</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cond_Threshold_Resonance_01</t>
+          <t>Cond_Threshold_CalledEditorFalse_01</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CG_Threshold_Resonance2</t>
+          <t>CG_Threshold_CalledEditorFalse</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Erosion</t>
+          <t>Ch5PathNoContact</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F92" t="n">
-        <v>2</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cond_Threshold_RitualNote_01</t>
+          <t>Cond_Threshold_Credibility7_01</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CG_Threshold_RitualNote</t>
+          <t>CG_Threshold_Credibility7</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>GaugeValue</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>EvRitualNote</t>
+          <t>Credibility</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cond_Threshold_SolvedMid_01</t>
+          <t>Cond_Threshold_Erosion6_01</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CG_Threshold_SolvedMid</t>
+          <t>CG_Threshold_Erosion6</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -12086,47 +12108,201 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SolvedQuestionCount</t>
+          <t>Erosion</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>[4, 5, 6]</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>Cond_Threshold_FoundOldArticles_01</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>CG_Threshold_FoundOldArticles</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ChoiceSelected</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Ch4ALibraryTakeArticles|Ch4ALibraryExposeArchive</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Cond_Threshold_Investigation_01</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>CG_Threshold_Investigation3</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>GaugeValue</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Credibility</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Cond_Threshold_Resonance_01</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>CG_Threshold_Resonance2</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>GaugeValue</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Erosion</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Cond_Threshold_RitualNote_01</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>CG_Threshold_RitualNote</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>EvidenceOwned</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>EvRitualNote</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Cond_Threshold_SolvedMid_01</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CG_Threshold_SolvedMid</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>GaugeValue</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>SolvedQuestionCount</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>[4, 5, 6]</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
           <t>Cond_Threshold_TrustedSongsoon_01</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>CG_Threshold_TrustedSongsoon</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>ChoiceSelected</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>Ch3WarehouseTrustSongsoon|Ch3Room4ComfortSongsoon</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>Equal</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>true</t>
         </is>

--- a/content/generated/script.generated.xlsx
+++ b/content/generated/script.generated.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-12 23:45:27</t>
+          <t>2026-08-19 08:54:08</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>신문감은 되겠지만, 이대로 덮을 마음은 없습니다.</t>
+          <t>신문감이야 되겠지만, 사람 둘 지운 자리에 괴담만 얹을 마음은 없습니다.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -16456,7 +16456,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>덮으라는 말은 들었습니다. 그래도 묻힌 문장까지 눈감아 줄 생각은 없습니다. 읽히는 기사와 남겨야 할 기록은 따로 갈 겁니다.</t>
+          <t>괴담으로 감싸라는 말은 들었습니다. 그래도 사람 지운 자리까지 눈감아 줄 생각은 없습니다. 읽히는 기사와 남겨야 할 기록은 따로 갈 겁니다.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">

--- a/content/generated/script.generated.xlsx
+++ b/content/generated/script.generated.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-19 22:15:52</t>
+          <t>2026-08-20 12:49:51</t>
         </is>
       </c>
     </row>
@@ -465,7 +465,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>G:\GSD\game\data\game_data.js</t>
+          <t>G:\GSD\game\data\game_data.js + G:\GSD\game\data\chapters/*.js</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N76"/>
+  <dimension ref="A1:N79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1002,7 +1002,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ch2Factory_LookCloser</t>
+          <t>Ch2FactoryCheckFootprint</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_FactoryInvestigation</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1010,17 +1015,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>시신의 찢겨진 흉곽 안쪽을 홀린 듯 쳐다본다.</t>
+          <t>진흙에 남은 자국을 자세히 살핀다.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ch2_factory_shock</t>
+          <t>factory_footprint</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1032,75 +1037,90 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ch2FactoryShockDocument</t>
+          <t>Ch2FactoryCheckStain</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_FactoryInvestigation</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>시신과 쪽지를 분리해 기록하고 낙원으로 향한다.</t>
+          <t>천장 철골의 푸른 얼룩을 살핀다.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ch2_cafe</t>
+          <t>factory_stain</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>ch2_factory_shock</t>
+          <t>ch2_factory</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ch2FactoryShockFollowSong</t>
+          <t>Ch2FactoryAskPoliceman</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_FactoryInvestigation</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>환청의 방향을 따라 서둘러 낙원으로 향한다.</t>
+          <t>경찰에게 다른 목격 사항이 있는지 캐묻는다.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ch2_cafe</t>
+          <t>factory_policeman</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>ch2_factory_shock</t>
+          <t>ch2_factory</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ch2HospitalAskRoot</t>
+          <t>Ch2Factory_LookCloser</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_FactoryInvestigation</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>그 망상의 근원부터 기어이 묻고 늘어진다.</t>
+          <t>시신의 찢겨진 흉곽 안쪽을 홀린 듯 쳐다본다.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1110,27 +1130,27 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ch2_hospital_a</t>
+          <t>ch2_factory_shock</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>ch2_hospital</t>
+          <t>ch2_factory</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ch2HospitalAskDoor</t>
+          <t>Ch2FactoryShockDocument</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>그가 벌벌 떠는 '문'의 정체부터 확인한다.</t>
+          <t>시신과 쪽지를 분리해 기록하고 낙원으로 향한다.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1140,27 +1160,27 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ch2_hospital_b</t>
+          <t>ch2_cafe</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>ch2_hospital</t>
+          <t>ch2_factory_shock</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ch2EscapeDocument</t>
+          <t>Ch2FactoryShockFollowSong</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>탈주 경로와 목격을 수첩에 남긴 뒤 현장으로 향한다.</t>
+          <t>환청의 방향을 따라 서둘러 낙원으로 향한다.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1170,27 +1190,27 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ch2_factory</t>
+          <t>ch2_cafe</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>ch2_hospital_end</t>
+          <t>ch2_factory_shock</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ch2EscapePursue</t>
+          <t>Ch2HospitalAskRoot</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>사라진 이판규가 끌려간 방향을 끝까지 쫓는다.</t>
+          <t>그 망상의 근원부터 기어이 묻고 늘어진다.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1200,204 +1220,194 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ch2_factory</t>
+          <t>ch2_hospital_a</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>ch2_hospital_end</t>
+          <t>ch2_hospital</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ch2WellTrustNote</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_Songsoon_Trust</t>
+          <t>Ch2HospitalAskDoor</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>쪽지를 꺼내 보인다.</t>
+          <t>그가 벌벌 떠는 '문'의 정체부터 확인한다.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>dlg_songsoon_open</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>EvNote</t>
+          <t>ch2_hospital_b</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>ch2_well</t>
+          <t>ch2_hospital</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ch2WellTrustCloth</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_Songsoon_Trust</t>
+          <t>Ch2EscapeDocument</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>푸른 천 조각을 내민다.</t>
+          <t>탈주 경로와 목격을 수첩에 남긴 뒤 현장으로 향한다.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>dlg_songsoon_open</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>EvBlueCloth</t>
+          <t>ch2_factory</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>ch2_well</t>
+          <t>ch2_hospital_end</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ch3HallwayHoldHand</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_HallwayBonus</t>
+          <t>Ch2EscapePursue</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>문을 밀기 전, 먼저 송순의 손을 마주 잡는다.</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>CG_Room4_TrustedSongsoon</t>
+          <t>사라진 이판규가 끌려간 방향을 끝까지 쫓는다.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>hallway_hold_hand_react</t>
+          <t>ch2_factory</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>ch3_hallway</t>
+          <t>ch2_hospital_end</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ch3HallwayPromiseRecord</t>
+          <t>Ch2WellTrustNote</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_Songsoon_Trust</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>송순에게 이 방에서 본 일을 함께 기록하겠다고 약속한다.</t>
+          <t>쪽지를 꺼내 보인다.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ch3_room4</t>
+          <t>dlg_songsoon_open</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>EvNote</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>ch3_hallway</t>
+          <t>ch2_well</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ch3HallwayDocumentMarks</t>
+          <t>Ch2WellTrustCloth</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_Songsoon_Trust</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>102</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>문 앞 긁힌 자국을 수첩에 옮겨 적는다.</t>
+          <t>푸른 천 조각을 내민다.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ch3_room4</t>
+          <t>dlg_songsoon_open</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>EvBlueCloth</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>ch3_hallway</t>
+          <t>ch2_well</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ch3Room4TouchWall</t>
+          <t>Ch3HallwayHoldHand</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ChoiceGroup_Room4Investigation</t>
+          <t>ChoiceGroup_HallwayBonus</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1405,7 +1415,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>위험을 감수하고 벽 문양이 남긴 저항 흔적을 짚는다.</t>
+          <t>문을 밀기 전, 먼저 송순의 손을 마주 잡는다.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CG_Room4_TrustedSongsoon</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1415,24 +1430,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>room4_touch</t>
+          <t>hallway_hold_hand_react</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>ch3_room4</t>
+          <t>ch3_hallway</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ch3Room4ReadRecord</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_Room4Investigation</t>
+          <t>Ch3HallwayPromiseRecord</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1440,34 +1450,29 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>공포보다 기록을 택하고 일기의 구조를 끝까지 읽는다.</t>
+          <t>송순에게 이 방에서 본 일을 함께 기록하겠다고 약속한다.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>room4_record</t>
+          <t>ch3_room4</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>ch3_room4</t>
+          <t>ch3_hallway</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ch3Room4ComfortSongsoon</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_Room4Investigation</t>
+          <t>Ch3HallwayDocumentMarks</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1475,29 +1480,29 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>증거보다 먼저 송순의 무너지는 마음을 붙든다.</t>
+          <t>문 앞 긁힌 자국을 수첩에 옮겨 적는다.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>room4_comfort</t>
+          <t>ch3_room4</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>ch3_room4</t>
+          <t>ch3_hallway</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ch3Room4CompareNote</t>
+          <t>Ch3Room4TouchWall</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1506,16 +1511,11 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>쥐고 있던 붉은 쪽지를 방 안 흔적과 나란히 맞대 본다.</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>CG_Room4_HasNote</t>
+          <t>위험을 감수하고 벽 문양이 남긴 저항 흔적을 짚는다.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>room4_note</t>
+          <t>room4_touch</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -1537,85 +1537,95 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ch3WarehouseReadRitual</t>
+          <t>Ch3Room4ReadRecord</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_Room4Investigation</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>관자놀이가 깨질 듯해도 악보를 끝까지 읽어 낸다.</t>
+          <t>공포보다 기록을 택하고 일기의 구조를 끝까지 읽는다.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ch3_score_read</t>
+          <t>room4_record</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>ch3_warehouse</t>
+          <t>ch3_room4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ch3WarehouseTrustSongsoon</t>
+          <t>Ch3Room4ComfortSongsoon</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_Room4Investigation</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>악보보다 송순 씨의 귀와 숨결을 먼저 믿는다.</t>
+          <t>증거보다 먼저 송순의 무너지는 마음을 붙든다.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ch3_score_trust</t>
+          <t>room4_comfort</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>ch3_warehouse</t>
+          <t>ch3_room4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ch4AEditorRecallArchive</t>
+          <t>Ch3Room4CompareNote</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ChoiceGroup_EditorRoomBonus</t>
+          <t>ChoiceGroup_Room4Investigation</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>삭제된 문장을 이었던 방식 그대로, 편집장의 말도 끝까지 받아 적는다.</t>
+          <t>쥐고 있던 붉은 쪽지를 방 안 흔적과 나란히 맞대 본다.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CG_Branch_ExposedArchivePattern</t>
+          <t>CG_Room4_HasNote</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1625,67 +1635,57 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>editor_room_archive_react</t>
+          <t>room4_note</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>ch4a_editor_room</t>
+          <t>ch3_room4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ch4AEditorArticles</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_Editor_Confront</t>
+          <t>Ch3WarehouseReadRitual</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1924년 기사 뭉치를 책상에 올려놓는다.</t>
+          <t>관자놀이가 깨질 듯해도 악보를 끝까지 읽어 낸다.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>dlg_editor_reveal</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>EvOldArticles</t>
+          <t>ch3_score_read</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>ch4a_editor_room</t>
+          <t>ch3_warehouse</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ch4ALibraryTakeArticles</t>
+          <t>Ch3WarehouseTrustSongsoon</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>기사 뭉치를 챙긴다.</t>
+          <t>악보보다 송순 씨의 귀와 숨결을 먼저 믿는다.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1695,112 +1695,117 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>ch4a_articles_take</t>
+          <t>ch3_score_trust</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>ch4a_library</t>
+          <t>ch3_warehouse</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ch4ALibraryNoteArticles</t>
+          <t>Ch4AEditorRecallArchive</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_EditorRoomBonus</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>핵심 문장만 수첩에 적고 넘어간다.</t>
+          <t>삭제된 문장을 이었던 방식 그대로, 편집장의 말도 끝까지 받아 적는다.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>CG_Branch_ExposedArchivePattern</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ch4a_articles_note</t>
+          <t>editor_room_archive_react</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>ch4a_library</t>
+          <t>ch4a_editor_room</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ch4ALibraryExposeArchive</t>
+          <t>Ch4AEditorArticles</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_Editor_Confront</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>삭제된 문장과 증언을 묶어 편집장의 의도를 먼저 추적한다.</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>CG_Library_QSonggeumRunaway</t>
+          <t>1924년 기사 뭉치를 책상에 올려놓는다.</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>ch4a_articles_expose</t>
+          <t>dlg_editor_reveal</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>EvOldArticles</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>ch4a_library</t>
+          <t>ch4a_editor_room</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ch4ALibraryEvidenceDiary</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_LibraryEvidence</t>
+          <t>Ch4ALibraryTakeArticles</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>숨겨진 일기장을 기사 옆에 펼친다.</t>
+          <t>기사 뭉치를 챙긴다.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>present_diary</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>EvDiary</t>
+          <t>ch4a_articles_take</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -1812,35 +1817,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ch4ALibraryEvidenceHanbok</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_LibraryEvidence</t>
+          <t>Ch4ALibraryNoteArticles</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>청색 한복의 결을 기사 기록과 대조한다.</t>
+          <t>핵심 문장만 수첩에 적고 넘어간다.</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>present_hanbok</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>EvBlueHanbok</t>
+          <t>ch4a_articles_note</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -1852,55 +1847,55 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ch4aSlumAskBelief</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_SlumInvestigation</t>
+          <t>Ch4ALibraryExposeArchive</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>그 여자가 사람들에게 무얼 판다는 건지 캐묻는다</t>
+          <t>삭제된 문장과 증언을 묶어 편집장의 의도를 먼저 추적한다.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>CG_Library_QSonggeumRunaway</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>inv_belief</t>
+          <t>ch4a_articles_expose</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>ch4a_slum</t>
+          <t>ch4a_library</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ch4aSlumAskMasked</t>
+          <t>Ch4ALibraryEvidenceDiary</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ChoiceGroup_SlumInvestigation</t>
+          <t>ChoiceGroup_LibraryEvidence</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>뒤에 있다는 얼굴 가린 사내를 캐묻는다</t>
+          <t>숨겨진 일기장을 기사 옆에 펼친다.</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1910,32 +1905,37 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>inv_masked</t>
+          <t>present_diary</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>EvDiary</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>ch4a_slum</t>
+          <t>ch4a_library</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ch4aSlumAskMissing</t>
+          <t>Ch4ALibraryEvidenceHanbok</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ChoiceGroup_SlumInvestigation</t>
+          <t>ChoiceGroup_LibraryEvidence</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>102</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>이 골목에서 최근에 사라진 여자가 있었는지 캐묻는다</t>
+          <t>청색 한복의 결을 기사 기록과 대조한다.</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1945,19 +1945,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>inv_missing</t>
+          <t>present_hanbok</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>EvBlueHanbok</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>ch4a_slum</t>
+          <t>ch4a_library</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ch4aSlumAskHanbok</t>
+          <t>Ch4aSlumAskBelief</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1966,16 +1971,11 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>청색 한복을 꺼내 보이며 이 옷이 어디서 나온 건지 캐묻는다</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>CG_Slum_HasHanbok</t>
+          <t>그 여자가 사람들에게 무얼 판다는 건지 캐묻는다</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>inv_hanbok</t>
+          <t>inv_belief</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -1997,20 +1997,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ch4bBackroomCheckAbsence</t>
+          <t>Ch4aSlumAskMasked</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ChoiceGroup_BackroomInvestigation</t>
+          <t>ChoiceGroup_SlumInvestigation</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>결근표와 빈 객실 장부를 대조해, 누가 어떤 날 사라졌는지 확인한다.</t>
+          <t>뒤에 있다는 얼굴 가린 사내를 캐묻는다</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2020,32 +2020,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>backroom_absence</t>
+          <t>inv_masked</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>ch4b_backroom</t>
+          <t>ch4a_slum</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ch4bBackroomTraceLaundry</t>
+          <t>Ch4aSlumAskMissing</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ChoiceGroup_BackroomInvestigation</t>
+          <t>ChoiceGroup_SlumInvestigation</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>세탁 자루와 무대 뒤 출입 흔적을 따라, 지하로 이어진 동선을 확인한다.</t>
+          <t>이 골목에서 최근에 사라진 여자가 있었는지 캐묻는다</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2055,142 +2055,147 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>backroom_route</t>
+          <t>inv_missing</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>ch4b_backroom</t>
+          <t>ch4a_slum</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ch4BCafeHold</t>
+          <t>Ch4aSlumAskHanbok</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_SlumInvestigation</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>알겠어요. 더는 억지로 묻지 않을게요.</t>
+          <t>청색 한복을 꺼내 보이며 이 옷이 어디서 나온 건지 캐묻는다</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>CG_Slum_HasHanbok</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>ch4b_cafe_hold</t>
+          <t>inv_hanbok</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>ch4b_cafe</t>
+          <t>ch4a_slum</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ch4BCafePress</t>
+          <t>Ch4bBackroomCheckAbsence</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_BackroomInvestigation</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>조금만 더 말해줘요. 여기서 멈출 순 없어요.</t>
+          <t>결근표와 빈 객실 장부를 대조해, 누가 어떤 날 사라졌는지 확인한다.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>ch4b_cafe_press</t>
+          <t>backroom_absence</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>ch4b_cafe</t>
+          <t>ch4b_backroom</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ch4BCafeErosionPress</t>
+          <t>Ch4bBackroomTraceLaundry</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_BackroomInvestigation</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>이유 모를 확신에 이끌려, 그 소리가 들리는 쪽을 그대로 좇는다.</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>CG_Cafe4b_Erosion2</t>
+          <t>세탁 자루와 무대 뒤 출입 흔적을 따라, 지하로 이어진 동선을 확인한다.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>ch4b_cafe_press</t>
+          <t>backroom_route</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>ch4b_cafe</t>
+          <t>ch4b_backroom</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ch4BCafeDiary</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_Okryeon_Confront</t>
+          <t>Ch4BCafeHold</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>송금의 일기장을 꺼내 보인다.</t>
+          <t>알겠어요. 더는 억지로 묻지 않을게요.</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>dlg_okryeon_reveal</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>EvDiary</t>
+          <t>ch4b_cafe_hold</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -2202,35 +2207,25 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ch4BCafeHanbok</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_Okryeon_Confront</t>
+          <t>Ch4BCafePress</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>푸른 한복 조각을 내민다.</t>
+          <t>조금만 더 말해줘요. 여기서 멈출 순 없어요.</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>dlg_okryeon_reveal</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>EvBlueHanbok</t>
+          <t>ch4b_cafe_press</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -2242,20 +2237,20 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ch5EditorObey</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_EditorOrder</t>
+          <t>Ch4BCafeErosionPress</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>…알겠습니다. 무리는 하지 않겠습니다.</t>
+          <t>이유 모를 확신에 이끌려, 그 소리가 들리는 쪽을 그대로 좇는다.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>CG_Cafe4b_Erosion2</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2265,72 +2260,72 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>ch5_descent</t>
+          <t>ch4b_cafe_press</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>ch5_contact_editor</t>
+          <t>ch4b_cafe</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ch5EditorDefy</t>
+          <t>Ch4BCafeDiary</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ChoiceGroup_EditorOrder</t>
+          <t>ChoiceGroup_Okryeon_Confront</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>죄송합니다. 여기까지 왔으니 끝을 봐야겠습니다.</t>
+          <t>송금의 일기장을 꺼내 보인다.</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>ch5_descent</t>
+          <t>dlg_okryeon_reveal</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>EvDiary</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>ch5_contact_editor</t>
+          <t>ch4b_cafe</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ch5DescentSelfReliant</t>
+          <t>Ch4BCafeHanbok</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ChoiceGroup_Descent</t>
+          <t>ChoiceGroup_Okryeon_Confront</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편집장 도움 없이 왔다는 사실을 되새기며 스스로 다잡는다.</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>CG_Branch_CalledEditorFalse</t>
+          <t>푸른 한복 조각을 내민다.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2340,27 +2335,37 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>descent_self_reliant_react</t>
+          <t>dlg_okryeon_reveal</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>EvBlueHanbok</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>ch5_descent</t>
+          <t>ch4b_cafe</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ch5DescentSignal</t>
+          <t>Ch5EditorObey</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_EditorOrder</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>송순과 멈출 신호를 정하고 계단을 내려간다.</t>
+          <t>…알겠습니다. 무리는 하지 않겠습니다.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2370,27 +2375,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>ch5_guarded_door</t>
+          <t>ch5_descent</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>ch5_descent</t>
+          <t>ch5_contact_editor</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ch5DescentFollowSong</t>
+          <t>Ch5EditorDefy</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_EditorOrder</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>콧노래의 박자를 기억하며 소리가 나는 쪽으로 간다.</t>
+          <t>죄송합니다. 여기까지 왔으니 끝을 봐야겠습니다.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2400,24 +2410,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>ch5_guarded_door</t>
+          <t>ch5_descent</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>ch5_descent</t>
+          <t>ch5_contact_editor</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ch5GuardedDoorListen</t>
+          <t>Ch5DescentSelfReliant</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ChoiceGroup_GuardedDoorInvestigation</t>
+          <t>ChoiceGroup_Descent</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -2425,7 +2435,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>콧노래의 결을 끝까지 듣고, 문 안쪽 호흡을 짚어 본다.</t>
+          <t>편집장 도움 없이 왔다는 사실을 되새기며 스스로 다잡는다.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>CG_Branch_CalledEditorFalse</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2435,24 +2450,19 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>door_listen</t>
+          <t>descent_self_reliant_react</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>ch5_guarded_door</t>
+          <t>ch5_descent</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ch5GuardedDoorSteady</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_GuardedDoorInvestigation</t>
+          <t>Ch5DescentSignal</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -2460,34 +2470,29 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>송순과 숨을 고른 뒤, 함께 문을 민다.</t>
+          <t>송순과 멈출 신호를 정하고 계단을 내려간다.</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>door_steady</t>
+          <t>ch5_guarded_door</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>ch5_guarded_door</t>
+          <t>ch5_descent</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ch5GuardedDoorObserve</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_GuardedDoorInvestigation</t>
+          <t>Ch5DescentFollowSong</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -2495,29 +2500,29 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>문 틈으로 안의 배치와 위험을 직접 읽어 낸다.</t>
+          <t>콧노래의 박자를 기억하며 소리가 나는 쪽으로 간다.</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>door_observe</t>
+          <t>ch5_guarded_door</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>ch5_guarded_door</t>
+          <t>ch5_descent</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ch5GuardedDoorReadScore</t>
+          <t>Ch5GuardedDoorListen</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2526,16 +2531,11 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>감응 악보를 펼쳐 지금 흘러나오는 노래의 순서와 맞춰 본다.</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>CG_GuardedDoor_HasScore</t>
+          <t>콧노래의 결을 끝까지 듣고, 문 안쪽 호흡을 짚어 본다.</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>guarded_door_score_react</t>
+          <t>door_listen</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -2557,20 +2557,20 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ch5ParticipantLedgerRead</t>
+          <t>Ch5GuardedDoorSteady</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ChoiceGroup_ParticipantLedger</t>
+          <t>ChoiceGroup_GuardedDoorInvestigation</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>일기와 공연 순서표를 명부에 겹쳐 강제 편입과 기본 순번을 확인한다.</t>
+          <t>송순과 숨을 고른 뒤, 함께 문을 민다.</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2580,37 +2580,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>ledger_read</t>
+          <t>door_steady</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>ch5_participant_ledger</t>
+          <t>ch5_guarded_door</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ch5ParticipantLedgerReveal</t>
+          <t>Ch5GuardedDoorObserve</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ChoiceGroup_ParticipantLedger</t>
+          <t>ChoiceGroup_GuardedDoorInvestigation</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>염료를 닦아 숨긴 순번까지 드러내고 의식 교란의 틈을 읽는다.</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>CG_ParticipantLedger_Erosion3</t>
+          <t>문 틈으로 안의 배치와 위험을 직접 읽어 낸다.</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2620,92 +2615,112 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>ledger_reveal</t>
+          <t>door_observe</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>ch5_participant_ledger</t>
+          <t>ch5_guarded_door</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ch5PathContactEditor</t>
+          <t>Ch5GuardedDoorReadScore</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_GuardedDoorInvestigation</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편집장에게 연락한다.</t>
+          <t>감응 악보를 펼쳐 지금 흘러나오는 노래의 순서와 맞춰 본다.</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>CG_GuardedDoor_HasScore</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>ch5_contact_editor</t>
+          <t>guarded_door_score_react</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>ch5_ritual_path</t>
+          <t>ch5_guarded_door</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Ch5PathNoContact</t>
+          <t>Ch5ParticipantLedgerRead</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_ParticipantLedger</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>말하지 않는다. 둘만 간다.</t>
+          <t>일기와 공연 순서표를 명부에 겹쳐 강제 편입과 기본 순번을 확인한다.</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ch5_no_contact</t>
+          <t>ledger_read</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>ch5_ritual_path</t>
+          <t>ch5_participant_ledger</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ch5RitualEvidenceNote</t>
+          <t>Ch5ParticipantLedgerReveal</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ChoiceGroup_RitualEvidence</t>
+          <t>ChoiceGroup_ParticipantLedger</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>의례실 종이를 제단 앞 문장과 맞대 본다.</t>
+          <t>염료를 닦아 숨긴 순번까지 드러내고 의식 교란의 틈을 읽는다.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>CG_ParticipantLedger_Erosion3</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2715,127 +2730,92 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>present_ritual_note</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>EvRitualNote</t>
+          <t>ledger_reveal</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>ch5_ritual_room</t>
+          <t>ch5_participant_ledger</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ch5RitualEvidenceScore</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_RitualEvidence</t>
+          <t>Ch5PathContactEditor</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>감응 악보를 지금 울리는 노래와 겹쳐 본다.</t>
+          <t>편집장에게 연락한다.</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>present_ritual_score</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>EvRitualScore</t>
+          <t>ch5_contact_editor</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>ch5_ritual_room</t>
+          <t>ch5_ritual_path</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ch5RitualEvidenceMask</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>ChoiceGroup_RitualEvidence</t>
+          <t>Ch5PathNoContact</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>103</v>
+        <v>2</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>가면의 눈 배열을 제단 문양과 대조한다.</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>CG_RitualRoom_QRitualAccident</t>
+          <t>말하지 않는다. 둘만 간다.</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>present_mask</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>EvMask</t>
+          <t>ch5_no_contact</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>ch5_ritual_room</t>
+          <t>ch5_ritual_path</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ch6ArticleRecallCafePress</t>
+          <t>Ch5RitualEvidenceNote</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ChoiceGroup_ArticleBonus</t>
+          <t>ChoiceGroup_RitualEvidence</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>카페에서 옥련을 더 밀어붙였던 그 밤을 떠올리며 문장을 고쳐 쓴다.</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>CG_Branch_EndingAScore2</t>
+          <t>의례실 종이를 제단 앞 문장과 맞대 본다.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2845,32 +2825,37 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>article_cafe_press_react</t>
+          <t>present_ritual_note</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>EvRitualNote</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>ch6_article</t>
+          <t>ch5_ritual_room</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>article_q1_correct</t>
+          <t>Ch5RitualEvidenceScore</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ChoiceGroup_ArticleQ1</t>
+          <t>ChoiceGroup_RitualEvidence</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>일기장 — 피해자 이름을 직접 특정한다.</t>
+          <t>감응 악보를 지금 울리는 노래와 겹쳐 본다.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2880,37 +2865,42 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>article_q1_react</t>
+          <t>present_ritual_score</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>EvDiary</t>
+          <t>EvRitualScore</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>ch6_article</t>
+          <t>ch5_ritual_room</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>article_q2_correct</t>
+          <t>Ch5RitualEvidenceMask</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ChoiceGroup_ArticleQ2</t>
+          <t>ChoiceGroup_RitualEvidence</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>의식 악보 — 노래로 사람을 묶어 둔 감응의 방법을 밝힌다.</t>
+          <t>가면의 눈 배열을 제단 문양과 대조한다.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>CG_RitualRoom_QRitualAccident</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2920,37 +2910,42 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>article_q2_react</t>
+          <t>present_mask</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>EvRitualScore</t>
+          <t>EvMask</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>ch6_article</t>
+          <t>ch5_ritual_room</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>article_q3_correct</t>
+          <t>Ch6ArticleRecallCafePress</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ChoiceGroup_ArticleQ3</t>
+          <t>ChoiceGroup_ArticleBonus</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>103</v>
+        <v>1</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1924년 기사 뭉치 — 과거에도 반복된 실종의 계보를 폭로한다.</t>
+          <t>카페에서 옥련을 더 밀어붙였던 그 밤을 떠올리며 문장을 고쳐 쓴다.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>CG_Branch_EndingAScore2</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2960,12 +2955,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>article_q3_react</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>EvOldArticles</t>
+          <t>article_cafe_press_react</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -2977,112 +2967,127 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ch6FinalAnswer</t>
+          <t>article_q1_correct</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ChoiceGroup_RitualFinal</t>
+          <t>ChoiceGroup_ArticleQ1</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>송순이 언니를 사람의 이름으로 붙들어 세운다.</t>
+          <t>일기장 — 피해자 이름을 직접 특정한다.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ch6_choice_a</t>
+          <t>article_q1_react</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>EvDiary</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>ch6_final_decision</t>
+          <t>ch6_article</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ch6FinalBlock</t>
+          <t>article_q2_correct</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ChoiceGroup_RitualFinal</t>
+          <t>ChoiceGroup_ArticleQ2</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>유웅룡이 명부의 순번과 악보를 따라 제단을 끊는다.</t>
+          <t>의식 악보 — 노래로 사람을 묶어 둔 감응의 방법을 밝힌다.</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>ch6_choice_b</t>
+          <t>article_q2_react</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>EvRitualScore</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>ch6_final_decision</t>
+          <t>ch6_article</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ch6FinalRecord</t>
+          <t>article_q3_correct</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ChoiceGroup_RitualFinal</t>
+          <t>ChoiceGroup_ArticleQ3</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>기사와 목격, 명부를 남겨 반복된 구조를 드러낸다.</t>
+          <t>1924년 기사 뭉치 — 과거에도 반복된 실종의 계보를 폭로한다.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Scene</t>
+          <t>Dialog</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ch6_choice_b</t>
+          <t>article_q3_react</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>EvOldArticles</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>ch6_final_decision</t>
+          <t>ch6_article</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ch6FinalExpose</t>
+          <t>Ch6FinalAnswer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3095,34 +3100,29 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>지금까지 쌓은 질문과 단서를 들이밀어 이해심의 거짓을 폭로한다.</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>CG_Proof_All</t>
+          <t>송순이 언니를 사람의 이름으로 붙들어 세운다.</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>ritual_expose</t>
+          <t>ch6_choice_a</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>ch6_ritual_scene</t>
+          <t>ch6_final_decision</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ch6FinalHesitate</t>
+          <t>Ch6FinalBlock</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>증명을 끝내지 못한 채 공포에 얼어붙는다.</t>
+          <t>유웅룡이 명부의 순번과 악보를 따라 제단을 끊는다.</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3145,90 +3145,200 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>ch6_choice_c</t>
+          <t>ch6_choice_b</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>ch6_ritual_scene</t>
+          <t>ch6_final_decision</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Ch6ThresholdErosionTouch</t>
+          <t>Ch6FinalRecord</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ChoiceGroup_Threshold</t>
+          <t>ChoiceGroup_RitualFinal</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>이미 물든 감각으로, 문에 먼저 손을 얹는다.</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>CG_Threshold_Erosion6</t>
+          <t>기사와 목격, 명부를 남겨 반복된 구조를 드러낸다.</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dialog</t>
+          <t>Scene</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>threshold_erosion_react</t>
+          <t>ch6_choice_b</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>ch6_threshold</t>
+          <t>ch6_final_decision</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>Ch6FinalExpose</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_RitualFinal</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>지금까지 쌓은 질문과 단서를 들이밀어 이해심의 거짓을 폭로한다.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>CG_Proof_All</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Dialog</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>ritual_expose</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>ch6_ritual_scene</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Ch6FinalHesitate</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_RitualFinal</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>2</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>증명을 끝내지 못한 채 공포에 얼어붙는다.</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Scene</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>ch6_choice_c</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>ch6_ritual_scene</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Ch6ThresholdErosionTouch</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ChoiceGroup_Threshold</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>이미 물든 감각으로, 문에 먼저 손을 얹는다.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>CG_Threshold_Erosion6</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Dialog</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>threshold_erosion_react</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>ch6_threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>Ch6ThresholdCredibilityResolve</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>ChoiceGroup_Threshold</t>
         </is>
       </c>
-      <c r="C76" t="n">
+      <c r="C79" t="n">
         <v>2</v>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>그동안 지켜 낸 기자로서의 신뢰를 되새기며 두려움을 억누른다.</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>CG_Threshold_Credibility7</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Dialog</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>threshold_credibility_react</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>ch6_threshold</t>
         </is>
@@ -9055,7 +9165,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -9065,7 +9175,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -14084,6 +14194,16 @@
           <t>assets/sfx/creepy.mp3</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>폐공장 현장을 살펴라</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>시신에 다가가기 전에, 남은 흔적과 목격담부터 확인할 수 있습니다.</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -16059,6 +16179,16 @@
       <c r="C11" t="n">
         <v>10</v>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ScreenShake</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>assets/sfx/gavel_strike.mp3</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>판결봉이 차갑게 울리고, 방청석의 조선인들은 억눌린 숨만 삼킨다. 항의보다 먼저 체념이 퍼진다. 이 법정에선 억울함조차 순서를 기다려야 한다.</t>
@@ -16199,6 +16329,16 @@
           <t>Speaker</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>FlashDark</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>assets/sfx/whisper_dissonant.mp3</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>(눈이 마주친 순간, 뱃속 내장이 통째로 얼어붙는 듯했다. 텅 빈 동공 너머로 축축하고 기괴한 심연이 아가리를 벌리고 있었다. 단순한 미치광이의 눈깔이 아니다. 저건… 다른 무언가가 사람 가죽을 뒤덮고 쳐다보는 꼴이다.)</t>
@@ -16419,6 +16559,11 @@
           <t>Speaker</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ScreenShake</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>(파리 떼가 꼬인 시체 사진이 박힌 조서를 손바닥으로 내리찍으며) 빈민가 조선인 핏덩이들 두어 놈 뒈진 게 대수야? 독자년놈들은 쉰내 나는 죽음 따위보다, 살갗이 벗겨지는 기괴한 피비린내를 원한다고. 사람 속을 파먹는 진짜배기 괴담 말이야!</t>
@@ -16539,6 +16684,11 @@
           <t>Speaker</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>BloodSmear</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>(짓이겨진 아이의 시체 사진 위로 시뻘건 담뱃재가 툭툭 떨어진다. 애새끼들 숨통 끊어진 연유보다, 지면에 바를 저렴한 흑백 잉크값이 더 비싸게 먹히는 구렁창. 역겨운 피냄새가 나지만, 내 밥줄도 이 구렁창 아가리에서 나온다.)</t>
@@ -17164,6 +17314,11 @@
       <c r="C42" t="n">
         <v>3</v>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Flicker</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>시신 주변 진흙엔 사람 발도 짐승 발도 아닌 자국이 짓이겨져 있다. 발가락이 없고 뒤꿈치만 깊다. 천장 철골 아래엔 푸른 얼룩이 금속을 갉아먹은 듯 번져 있다.</t>
@@ -17855,6 +18010,11 @@
           <t>ShakeHard</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>RitualGlow</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr">
         <is>
           <t>청의의 감응을 잇는 분께… (갑자기 주문처럼) 감응이여, 감응이여, 숭성하옵시며—</t>
@@ -17940,6 +18100,11 @@
           <t>ShakeLight</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>BlueTrace</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr">
         <is>
           <t>종교가 아냐… 감응이지. 참된 감응. 그 애들은 열쇠였어. 허나 둘 다 틀렸어. 문은 한 치도 벌어지지 않았는데 노래만 자꾸 들렸어… 문 저편에서 누가 젖은 숨을 들이마시는 것처럼.</t>
@@ -18700,6 +18865,11 @@
           <t>ScreenShake</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>assets/sfx/wet_crack.mp3</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr">
         <is>
           <t>(갑자기 허리를 기괴하게 접으며 구토하듯 제 목을 쥐어뜯는다) 잘못했어요... 다시는 안 그럴게요...!</t>
@@ -18765,6 +18935,11 @@
           <t>Flash</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>assets/sfx/bone_snap.mp3</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr">
         <is>
           <t>(기괴한 뼈 파열음) 이판규가 짐승처럼 네 발로 접혀 교도관의 면상을 짓밟고 뛰어오른다.</t>
@@ -18830,6 +19005,11 @@
           <t>ScreenShake</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>assets/sfx/door_slam.mp3</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr">
         <is>
           <t>병원 복도 끝 쇠문이 굉음과 함께 뜯길 듯 부딪친다.</t>
@@ -19155,6 +19335,11 @@
       <c r="C99" t="n">
         <v>3</v>
       </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Flicker</t>
+        </is>
+      </c>
       <c r="N99" t="inlineStr">
         <is>
           <t>잠긴 문 앞에 서자, 아주 짧은 콧노래가 복도 끝에서 흘렀다가 사라진다. 이번엔 방 안이 아니라 복도 자체가 따라 부른 것처럼 들린다.</t>
@@ -19605,6 +19790,11 @@
           <t>Speaker</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Flash</t>
+        </is>
+      </c>
       <c r="N111" t="inlineStr">
         <is>
           <t>…이건 뭐예요? (가면을 보며) 눈이 네 개나 있어요. 무섭게 생겼어요.</t>
@@ -19905,6 +20095,11 @@
       <c r="C119" t="n">
         <v>13</v>
       </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>RitualGlow</t>
+        </is>
+      </c>
       <c r="N119" t="inlineStr">
         <is>
           <t>방 안 어딘가에서 다시 짧은 콧노래가 스친다. 이번엔 송순의 손끝이 멈추지 않는다. 대신 벽지 아래, 누군가 손톱으로 긁어 남긴 듯한 문양이 처음으로 눈에 들어온다.</t>
@@ -20100,6 +20295,11 @@
       <c r="C124" t="n">
         <v>2</v>
       </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Flash</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr">
         <is>
           <t>유웅룡은 눈을 찌르는 통증을 참고 악보 끝까지 시선을 밀어 넣는다. 음표 아래 숨은 글씨가 뒤늦게 한 줄로 이어진다. '문이 열리면 먼저 이름이 벗겨진다.'</t>
@@ -20560,6 +20760,11 @@
           <t>BlueTrace</t>
         </is>
       </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>assets/ev/score.jpeg</t>
+        </is>
+      </c>
       <c r="N137" t="inlineStr">
         <is>
           <t>흩어진 악보들 사이, 유독 한 장만 젖은 비단처럼 번들거린다. 푸른 잉크로 덧씌운 음표가 빛을 받지 않아도 희미하게 떠오른다.</t>
@@ -20610,6 +20815,16 @@
           <t>BlueTrace</t>
         </is>
       </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>assets/ev/score.jpeg</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>assets/sfx/whisper_dissonant.mp3</t>
+        </is>
+      </c>
       <c r="N138" t="inlineStr">
         <is>
           <t>…기묘하군… 왜 이러지. 내가 글자를 읽는 게 아니라, 글자가 내 속을 먼저 더듬는 것 같아…</t>
@@ -20660,6 +20875,11 @@
           <t>Flicker</t>
         </is>
       </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>assets/ev/score.jpeg</t>
+        </is>
+      </c>
       <c r="N139" t="inlineStr">
         <is>
           <t>기자님. (그의 손을 붙잡는다) 숨부터 고르세요. 천천히요. 여기, 제가 있어요.</t>
@@ -20700,6 +20920,11 @@
           <t>Speaker</t>
         </is>
       </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>assets/ev/score.jpeg</t>
+        </is>
+      </c>
       <c r="N140" t="inlineStr">
         <is>
           <t>(악보를 들여다본다) 이 노래… 음표 사이에 아주 작은 글씨가 있어요. '청의의 감응을 숭성하옵시며…'</t>
@@ -20740,6 +20965,11 @@
           <t>Speaker</t>
         </is>
       </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>assets/ev/score.jpeg</t>
+        </is>
+      </c>
       <c r="N141" t="inlineStr">
         <is>
           <t>이건 노래가 아니에요. 불러서 듣게 하는 게 아니라, 부르면 무언가가 대답하게 만드는 주문이에요.</t>
@@ -20780,6 +21010,7 @@
           <t>Speaker</t>
         </is>
       </c>
+      <c r="L142" t="inlineStr"/>
       <c r="N142" t="inlineStr">
         <is>
           <t>송순 씨는… 괜찮습니까? 난 종이 한 장 붙든 것뿐인데 속이 뒤집히는데.</t>
@@ -23885,6 +24116,11 @@
       <c r="C224" t="n">
         <v>5</v>
       </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Flicker</t>
+        </is>
+      </c>
       <c r="N224" t="inlineStr">
         <is>
           <t>계단 벽면엔 손톱으로 긁은 듯한 자국과 말라붙은 푸른 얼룩이 이어진다. 누군가 위로 올라오려다 실패한 흔적처럼 보인다.</t>
@@ -24005,6 +24241,11 @@
           <t>Speaker</t>
         </is>
       </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>BlueTrace</t>
+        </is>
+      </c>
       <c r="N227" t="inlineStr">
         <is>
           <t>귓속에서 아까부터 낮은 웅웅거림이 떠나질 않는다. 계단이 아니라 머릿속에서 나는 소리 같기도 하다.</t>
@@ -24095,6 +24336,11 @@
       <c r="C230" t="n">
         <v>1</v>
       </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Flicker</t>
+        </is>
+      </c>
       <c r="N230" t="inlineStr">
         <is>
           <t>계단 끝엔 나무도 쇠도 아닌 재질의 문이 서 있다. 젖은 살갗처럼 미세하게 꿈틀거리며, 가까이 갈수록 사람 체온을 거꾸로 빨아들이는 것처럼 서늘하다.</t>
@@ -24195,6 +24441,11 @@
       <c r="C233" t="n">
         <v>4</v>
       </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>BlueTrace</t>
+        </is>
+      </c>
       <c r="N233" t="inlineStr">
         <is>
           <t>문 틈 사이로 흘러나오는 노랫소리는 이제 분명히 사람 목소리다. 그러나 감정이 빠져 있다. 사람이 부르는데 사람 것 같지 않고, 누군가 그 목소리를 안쪽에서 빌려 쓰는 것처럼 들린다.</t>
@@ -24235,6 +24486,11 @@
           <t>Speaker</t>
         </is>
       </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>FlashDark</t>
+        </is>
+      </c>
       <c r="N234" t="inlineStr">
         <is>
           <t>언니 목소리예요. 맞는데… 그 안에 언니가 없는 것 같아요.</t>
@@ -25375,6 +25631,11 @@
           <t>BloodSmear</t>
         </is>
       </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>assets/ev/bluecloth.jpeg</t>
+        </is>
+      </c>
       <c r="N264" t="inlineStr">
         <is>
           <t>제단 주변엔 크기 다른 파란 천 조각이 흩어져 있다. 아이 옷에서 뜯어낸 듯한 자국, 여급 옷감에서 잘라 낸 듯한 비단 결, 마른 피가 스민 매듭이 한데 뒤엉켜 있다.</t>
@@ -25400,6 +25661,16 @@
           <t>BloodSmear</t>
         </is>
       </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>assets/ev/bluecloth.jpeg</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>assets/sfx/sting_horror.mp3</t>
+        </is>
+      </c>
       <c r="N265" t="inlineStr">
         <is>
           <t>제단 기둥 너머 검은 얼룩 하나가 순간 사람 형상처럼 일그러진다. 폐공장에서 본 이판규의 꺾인 목과 비슷한 윤곽이 스쳤다가, 촛농과 그을음이 엉긴 얼룩으로 다시 흩어진다. 시체가 다시 여기 있을 리는 없다. 다만 그 죽음이 이 방 안에 아직 눌어붙어 있는 것처럼 보인다.</t>
@@ -25445,6 +25716,7 @@
           <t>Tremble</t>
         </is>
       </c>
+      <c r="L266" t="inlineStr"/>
       <c r="N266" t="inlineStr">
         <is>
           <t>이상해요. 지금 여긴 우리뿐인데… 누가 아직 벽 안쪽에서 숨을 고르고 있는 것 같아요.</t>
@@ -25470,6 +25742,11 @@
           <t>RitualGlow</t>
         </is>
       </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>assets/sfx/ritual_chant.mp3</t>
+        </is>
+      </c>
       <c r="N267" t="inlineStr">
         <is>
           <t>그때, 더 깊은 곳에서 여성의 노랫소리가 흘러나온다. 표정 없는, 감정 없는 노래. 기도를 흉내 내지만 기원은 없고, 위로를 흉내 내지만 사람 숨을 더 얇게 만드는 소리다.</t>
@@ -26575,6 +26852,11 @@
       <c r="C298" t="n">
         <v>2</v>
       </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>ScreenShake</t>
+        </is>
+      </c>
       <c r="N298" t="inlineStr">
         <is>
           <t>감응이 흔들린다. 이해심이 비틀거리며 무너진다. 문은 반쯤 열린 채 억지로 닫힌다. 닫히는 마지막 순간까지 콧노래는 한 사람의 이름을 놓치지 않으려는 것처럼 떨린다. 누군가를 완전히 데려오진 못해도, 끝내 사람 쪽으로 당겨 두려는 힘만은 남는다.</t>
@@ -26595,6 +26877,11 @@
       <c r="C299" t="n">
         <v>3</v>
       </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>FlashDark</t>
+        </is>
+      </c>
       <c r="N299" t="inlineStr">
         <is>
           <t>송금이 천천히 고개를 돌린다. 눈이 텅 비어 있다. 살아있지만, 돌아오지 않았다.</t>
@@ -26960,6 +27247,11 @@
       <c r="C309" t="n">
         <v>2</v>
       </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Fade</t>
+        </is>
+      </c>
       <c r="N309" t="inlineStr">
         <is>
           <t>문이 닫힌다. 노래가 멎는다. 송금은 그 자리에 쓰러진다. 숨은 붙어 있다. 하지만 눈을 뜨지 않는다.</t>
@@ -27305,6 +27597,11 @@
       <c r="C318" t="n">
         <v>1</v>
       </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>FlashDark</t>
+        </is>
+      </c>
       <c r="N318" t="inlineStr">
         <is>
           <t>문이 활짝 열린다. 무엇이 나왔는지 보이지 않는다. 공간 전체가 잠시 정지한다. 소리가 없다. 빛이 없다. 보는 쪽이 먼저 멈춘 건지, 세상이 먼저 숨을 죽인 건지도 알 수 없다.</t>
@@ -27425,6 +27722,11 @@
       <c r="C322" t="n">
         <v>5</v>
       </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>BlueTrace</t>
+        </is>
+      </c>
       <c r="N322" t="inlineStr">
         <is>
           <t>대답 대신, 멀리서 아주 짧은 콧노래가 한 번 더 스친다. 둘 다 그 소리를 들었는지조차 확신하지 못한다. 확신하지 못한다는 사실이 오히려 더 오래 남는다. 아무것도 택하지 못했던 순간의 공백이, 이후의 모든 밤에 질문처럼 달라붙는다.</t>
@@ -28590,6 +28892,11 @@
       <c r="C366" t="n">
         <v>1</v>
       </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>assets/ev/hanbok.jpeg</t>
+        </is>
+      </c>
       <c r="N366" t="inlineStr">
         <is>
           <t>지하 의례실 깊숙이. 이해심이 제단 앞에 선다. 송금은 청색 한복 차림으로 노래하고 있다. 표정이 없다. 살기 위해 버틴 끝에 생기는 무표정이 아니라, 지나치게 오래 빌려 쓰여 자기 얼굴을 잃어버린 사람의 무표정이다.</t>
@@ -28630,6 +28937,11 @@
           <t>Speaker</t>
         </is>
       </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>assets/ev/hanbok.jpeg</t>
+        </is>
+      </c>
       <c r="N367" t="inlineStr">
         <is>
           <t>어리석은 자들이여. 문이 열리는 날, 경성은 비로소 속을 드러낼 것이다. 곪은 자리는 끝내 누군가 헤집어야 한다. 나는 이제 그 일을 두려워하지 않는다.</t>
@@ -28650,6 +28962,12 @@
       <c r="C368" t="n">
         <v>3</v>
       </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Flicker</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr"/>
       <c r="N368" t="inlineStr">
         <is>
           <t>이해심의 뒤편 어둠 속엔 흰 천으로 얼굴을 가린 남자의 형체가 희미하게 선다. 가까이 있는데도 사람이라기보다 남의 신앙을 뒤에서 빨아먹는 그늘처럼 보인다. 향냄새 밑에 눌린 비린내가 그쪽에서 더 짙다.</t>
@@ -28710,6 +29028,11 @@
       <c r="C370" t="n">
         <v>5</v>
       </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>BlueTrace</t>
+        </is>
+      </c>
       <c r="N370" t="inlineStr">
         <is>
           <t>그 순간 유웅룡의 귓속에서 문 앞 콧노래가 다시 울린다. 방 안 노래와 어긋나지 않는다. 아까 문에 귀를 댄 뒤로, 이 공간은 이미 몸 안쪽까지 파고든 듯하다.</t>
@@ -28755,6 +29078,16 @@
           <t>Speaker</t>
         </is>
       </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>RitualGlow</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>assets/sfx/ritual_chant.mp3</t>
+        </is>
+      </c>
       <c r="N371" t="inlineStr">
         <is>
           <t>(표정 없이, 노래를 흥얼거린다) …푸른… 옷을… 입고… 문 앞에… 서서…</t>
@@ -28815,6 +29148,16 @@
       <c r="C373" t="n">
         <v>8</v>
       </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>FlashDark</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>assets/sfx/heartbeat_low.mp3</t>
+        </is>
+      </c>
       <c r="N373" t="inlineStr">
         <is>
           <t>이해심의 안대 아래로 피가 번지기 시작한다. 하나는 불빛, 하나는 서릿발. 문이 열리고 있다. 방 안 촛불이 바깥바람 없이도 같은 방향으로 눕고, 벽면의 푸른 흔적이 젖은 살처럼 미세하게 꿈틀거린다.</t>
@@ -29093,6 +29436,11 @@
       <c r="G380" t="inlineStr">
         <is>
           <t>Speaker</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>ScreenShake</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -29852,7 +30200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30075,57 +30423,57 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ChoiceGroup_GuardedDoor</t>
+          <t>ChoiceGroup_FactoryInvestigation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Investigation</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ChoiceGroup_GuardedDoorInvestigation</t>
+          <t>ChoiceGroup_GuardedDoor</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Investigation</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ChoiceGroup_HallwayBonus</t>
+          <t>ChoiceGroup_GuardedDoorInvestigation</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Investigation</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ChoiceGroup_LibraryEvidence</t>
+          <t>ChoiceGroup_HallwayBonus</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Evidence</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -30135,42 +30483,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ChoiceGroup_NewsroomInvestigation</t>
+          <t>ChoiceGroup_LibraryEvidence</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Investigation</t>
+          <t>Evidence</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ChoiceGroup_Okryeon_Confront</t>
+          <t>ChoiceGroup_NewsroomInvestigation</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Evidence</t>
+          <t>Investigation</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ChoiceGroup_ParticipantLedger</t>
+          <t>ChoiceGroup_Okryeon_Confront</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Evidence</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -30180,12 +30528,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ChoiceGroup_RitualEvidence</t>
+          <t>ChoiceGroup_ParticipantLedger</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Evidence</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -30195,12 +30543,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ChoiceGroup_RitualFinal</t>
+          <t>ChoiceGroup_RitualEvidence</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Evidence</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -30210,12 +30558,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ChoiceGroup_Room4Conclusion</t>
+          <t>ChoiceGroup_RitualFinal</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Evidence</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -30225,22 +30573,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ChoiceGroup_Room4Investigation</t>
+          <t>ChoiceGroup_Room4Conclusion</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Investigation</t>
+          <t>Evidence</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ChoiceGroup_SlumInvestigation</t>
+          <t>ChoiceGroup_Room4Investigation</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -30255,30 +30603,45 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ChoiceGroup_Songsoon_Trust</t>
+          <t>ChoiceGroup_SlumInvestigation</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Evidence</t>
+          <t>Investigation</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>ChoiceGroup_Songsoon_Trust</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>ChoiceGroup_Threshold</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D29" t="n">
         <v>1</v>
       </c>
     </row>

--- a/content/generated/script.generated.xlsx
+++ b/content/generated/script.generated.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-20 12:49:51</t>
+          <t>2026-08-21 09:34:28</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>ch6_choice_b</t>
+          <t>ch6_choice_record</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -3355,7 +3355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4108,32 +4108,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Br_ch6_epilogue_ErosionHigh</t>
+          <t>Br_ch6_choice_record_Default</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ch6_epilogue</t>
+          <t>ch6_choice_record</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>1</v>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>CG_Erosion_High</t>
-        </is>
-      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>scene_ending_erosion</t>
+          <t>ch6_outcome</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Br_ch6_epilogue_EndingB</t>
+          <t>Br_ch6_epilogue_ErosionHigh</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4142,23 +4137,23 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CG_Epilogue_EndingB</t>
+          <t>CG_Erosion_High</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ch6_ending_b</t>
+          <t>scene_ending_erosion</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Br_ch6_epilogue_EndingA</t>
+          <t>Br_ch6_epilogue_EndingB</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4167,56 +4162,61 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CG_Epilogue_EndingA</t>
+          <t>CG_Epilogue_EndingB</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ch6_ending_a</t>
+          <t>ch6_ending_b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Br_ch6_epilogue_EndingA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ch6_epilogue</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CG_Epilogue_EndingA</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ch6_ending_a</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Br_ch6_epilogue_Default</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>ch6_epilogue</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="C42" t="n">
         <v>4</v>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>ch6_ending_c</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>ch6_outcome</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>CG_Branch_FinalChoice_A</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>ch6_path_a</t>
         </is>
       </c>
     </row>
@@ -4227,16 +4227,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CG_Branch_FinalChoice_B</t>
+          <t>CG_Branch_FinalChoice_A</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ch6_path_b</t>
+          <t>ch6_path_a</t>
         </is>
       </c>
     </row>
@@ -4247,72 +4247,72 @@
         </is>
       </c>
       <c r="C44" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CG_Branch_FinalChoice_B</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ch6_path_b</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ch6_outcome</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
         <v>3</v>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>CG_Branch_FinalChoice_C</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>ch6_ending_c</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Br_ch6_outcome_Default</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>ch6_outcome</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>4</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CG_Branch_FinalChoice_Record</t>
+        </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ch6_ending_c</t>
+          <t>ch6_path_record</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
-          <t>ch6_path_a</t>
+          <t>ch6_outcome</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CG_Branch_TouchedRoomWall</t>
+          <t>CG_Branch_FinalChoice_C</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ch6_path_a2</t>
+          <t>ch6_ending_c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Br_ch6_path_a_Default</t>
+          <t>Br_ch6_outcome_Default</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ch6_path_a</t>
+          <t>ch6_outcome</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>ch6_path_a2</t>
+          <t>ch6_path_a</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4331,32 +4331,32 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CG_Branch_MatchedPattern</t>
+          <t>CG_Branch_TouchedRoomWall</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ch6_ending_a</t>
+          <t>ch6_path_a2</t>
         </is>
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Br_ch6_path_a_Default</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ch6_path_a2</t>
+          <t>ch6_path_a</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>2</v>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>CG_Branch_SolvedMid</t>
-        </is>
-      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ch6_ending_a</t>
+          <t>ch6_ending_c_answer</t>
         </is>
       </c>
     </row>
@@ -4367,11 +4367,11 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CG_Threshold_TrustedSongsoon</t>
+          <t>CG_Branch_MatchedPattern</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4387,11 +4387,11 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CG_Branch_SongsoonTrust2</t>
+          <t>CG_Branch_SolvedMid</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4407,11 +4407,11 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CG_Branch_SongsoonTrust1</t>
+          <t>CG_Threshold_TrustedSongsoon</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4427,11 +4427,11 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CG_Branch_OkryunPushed</t>
+          <t>CG_Branch_SongsoonTrust2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4447,11 +4447,11 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CG_Branch_EndingAScore2</t>
+          <t>CG_Branch_SongsoonTrust1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4461,58 +4461,58 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Br_ch6_path_a2_Default</t>
-        </is>
-      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>ch6_path_a2</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>CG_Branch_OkryunPushed</t>
+        </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ch6_ending_c</t>
+          <t>ch6_ending_a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="inlineStr">
         <is>
-          <t>ch6_path_b</t>
+          <t>ch6_path_a2</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CG_Branch_FoundOldArticles</t>
+          <t>CG_Branch_EndingAScore2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ch6_path_b2</t>
+          <t>ch6_ending_a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Br_ch6_path_b_Default</t>
+          <t>Br_ch6_path_a2_Default</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ch6_path_b</t>
+          <t>ch6_path_a2</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
     <row r="58">
       <c r="B58" t="inlineStr">
         <is>
-          <t>ch6_path_b2</t>
+          <t>ch6_path_b</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CG_Branch_ExposedTruthAtRitual</t>
+          <t>CG_Branch_FoundOldArticles</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ch6_ending_b</t>
+          <t>ch6_path_b2</t>
         </is>
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Br_ch6_path_b_Default</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ch6_path_b2</t>
+          <t>ch6_path_b</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>2</v>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>CG_Branch_ExposedArchivePattern</t>
-        </is>
-      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ch6_ending_b</t>
+          <t>ch6_ending_c_block</t>
         </is>
       </c>
     </row>
@@ -4567,11 +4567,11 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CG_Branch_SolvedMid</t>
+          <t>CG_Branch_ExposedTruthAtRitual</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4587,11 +4587,11 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CG_Branch_ReadRitual</t>
+          <t>CG_Branch_ExposedArchivePattern</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4607,11 +4607,11 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CG_Branch_Investigation3</t>
+          <t>CG_Branch_SolvedMid</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4627,93 +4627,88 @@
         </is>
       </c>
       <c r="C63" t="n">
+        <v>4</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CG_Branch_ReadRitual</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ch6_ending_b</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ch6_path_b2</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>5</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CG_Branch_Investigation3</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ch6_ending_b</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ch6_path_b2</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
         <v>6</v>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>CG_Branch_CalledEditorFalse</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>ch6_ending_b</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Br_ch6_path_b2_Default</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>ch6_path_b2</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>7</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>ch6_ending_c</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Br_ch6_ritual_scene_Expose</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>ch6_ritual_scene</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>CG_Branch_ExposedTruthAtRitual</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>ch6_final_decision</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Br_ch6_ritual_scene_Default</t>
+          <t>Br_ch6_path_b2_Default</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ch6_ritual_scene</t>
+          <t>ch6_path_b2</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ch6_article</t>
+          <t>ch6_ending_c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Br_ch6_threshold_ErosionMax</t>
+          <t>Br_ch6_path_record_Complete</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ch6_threshold</t>
+          <t>ch6_path_record</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -4721,74 +4716,165 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>CG_Erosion_Max</t>
+          <t>CG_Branch_FinalRecordComplete</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>scene_gameover_erosion</t>
+          <t>ch6_ending_b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Br_ch6_threshold_CredibilityZero</t>
+          <t>Br_ch6_path_record_Default</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ch6_threshold</t>
+          <t>ch6_path_record</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>2</v>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>CG_Credibility_Zero</t>
-        </is>
-      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>scene_gameover_credibility</t>
+          <t>ch6_ending_c_record</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Br_ch6_threshold_Default</t>
+          <t>Br_ch6_ritual_scene_Expose</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ch6_threshold</t>
+          <t>ch6_ritual_scene</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CG_Branch_ExposedTruthAtRitual</t>
+        </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ch6_ritual_scene</t>
+          <t>ch6_final_decision</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>Br_ch6_ritual_scene_Default</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ch6_ritual_scene</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ch6_article</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Br_ch6_threshold_ErosionMax</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ch6_threshold</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>CG_Erosion_Max</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>scene_gameover_erosion</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Br_ch6_threshold_CredibilityZero</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ch6_threshold</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>2</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>CG_Credibility_Zero</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>scene_gameover_credibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Br_ch6_threshold_Default</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ch6_threshold</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>3</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ch6_ritual_scene</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>Br_gameover_credibility_End</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>scene_gameover_credibility</t>
         </is>
       </c>
-      <c r="C70" t="n">
+      <c r="C74" t="n">
         <v>1</v>
       </c>
+      <c r="E74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4801,7 +4887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4949,59 +5035,62 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EvBlueHanbok</t>
+          <t>EvIpangyuStatement</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>청색 비단 한복</t>
+          <t>이판규의 탈주 전 진술</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>송금의 방에서 발견된 의례용 한복. 소매 안쪽에 바느질 자국과 작은 상처 자국들.</t>
+          <t>이판규는 누군가의 호출과 문이 열리는 순간을 반복해 말했다. 공포에 질린 말투와 구체적인 순서는 단순한 횡설수설로 치부하기 어렵다.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>assets/ev/hanbok.jpeg</t>
+          <t>assets/items/note.png</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ritual</t>
+          <t>testimony</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ch3_room4</t>
-        </is>
+          <t>ch2_hospital_end</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EvDiary</t>
+          <t>EvBlueHanbok</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>숨겨진 일기장</t>
+          <t>청색 비단 한복</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>송금의 일기장. '청의의 무녀', '노래가 곧 감응', '문 앞에서 노래를 부를 것'.</t>
+          <t>송금의 방에서 발견된 의례용 한복. 소매 안쪽에 바느질 자국과 작은 상처 자국들.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>assets/ev/diary.jpeg</t>
+          <t>assets/ev/hanbok.jpeg</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>record</t>
+          <t>ritual</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5009,61 +5098,66 @@
           <t>ch3_room4</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>2</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EvMask</t>
+          <t>EvDiary</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>네 눈 가면</t>
+          <t>숨겨진 일기장</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>눈 구멍이 네 개 달린 기괴한 가면. 청의동자의 눈 네 개를 상징한다.</t>
+          <t>송금의 일기장. '청의의 무녀', '노래가 곧 감응', '문 앞에서 노래를 부를 것'.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>assets/ev/mask.jpeg</t>
+          <t>assets/ev/diary.jpeg</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ritual</t>
+          <t>record</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>ch3_room4</t>
         </is>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EvRitualScore</t>
+          <t>EvMask</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>감응 악보</t>
+          <t>네 눈 가면</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>주문이 음표 사이에 숨겨진 기묘한 악보. 유웅룡에게만 이명과 고통을 유발한다.</t>
+          <t>눈 구멍이 네 개 달린 기괴한 가면. 청의동자의 눈 네 개를 상징한다.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>assets/ev/score.jpeg</t>
+          <t>assets/ev/mask.jpeg</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5073,62 +5167,64 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ch3_warehouse</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
+          <t>ch3_room4</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EvOldArticles</t>
+          <t>EvRitualScore</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1924년 기사 뭉치</t>
+          <t>감응 악보</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>과거에 발생한 유사 사건의 기록. 편집장이 직접 작성했다. 일부 문장이 삭제되어 있다.</t>
+          <t>주문이 음표 사이에 숨겨진 기묘한 악보. 유웅룡에게만 이명과 고통을 유발한다.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>assets/ev/note.jpeg</t>
+          <t>assets/ev/score.jpeg</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>record</t>
+          <t>ritual</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ch4a_library</t>
+          <t>ch3_warehouse</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EvSlumWitness</t>
+          <t>EvOldArticles</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>얼굴 가린 사내의 목격담</t>
+          <t>1924년 기사 뭉치</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>노인이 전한 흰 천으로 얼굴을 가린 사내, 천용해에 대한 소문. 낙원 의식을 주도한 손이 하나 더 있었다는 증거다.</t>
+          <t>과거에 발생한 유사 사건의 기록. 편집장이 직접 작성했다. 일부 문장이 삭제되어 있다.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5138,34 +5234,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>trace</t>
+          <t>record</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ch4a_slum</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Ch4aSlumAskMasked</t>
-        </is>
+          <t>ch4a_library</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EvBasementRoute</t>
+          <t>EvSlumWitness</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>세탁 수레의 지하 출입 흔적</t>
+          <t>얼굴 가린 사내의 목격담</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>푸른 염료가 묻은 세탁 자루와 바퀴 자국. 결근 처리된 여급들이 무대 뒤 가림막 아래 지하 출입구로 옮겨졌음을 보여 준다.</t>
+          <t>노인이 전한 흰 천으로 얼굴을 가린 사내, 천용해에 대한 소문. 낙원 의식을 주도한 손이 하나 더 있었다는 증거다.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5175,32 +5269,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>record</t>
+          <t>trace</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ch4b_backroom</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
+          <t>ch4a_slum</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ch4aSlumAskMasked</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EvParticipantLedger</t>
+          <t>EvBasementRoute</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>염료 묻은 참여자 명부</t>
+          <t>세탁 수레의 지하 출입 흔적</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>의식에 편입된 사람과 배역·순번이 적힌 명부. 송금은 자원자가 아니라 강제로 배정된 편입자로 기록되어 있다.</t>
+          <t>푸른 염료가 묻은 세탁 자루와 바퀴 자국. 결근 처리된 여급들이 무대 뒤 가림막 아래 지하 출입구로 옮겨졌음을 보여 준다.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5210,47 +5306,82 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ritual</t>
+          <t>record</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ch5_participant_ledger</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Ch5ParticipantLedgerRead</t>
-        </is>
+          <t>ch4b_backroom</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>EvParticipantLedger</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>염료 묻은 참여자 명부</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>의식에 편입된 사람과 배역·순번이 적힌 명부. 송금은 자원자가 아니라 강제로 배정된 편입자로 기록되어 있다.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>assets/ev/note.jpeg</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ritual</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ch5_participant_ledger</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ch5ParticipantLedgerRead</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>EvRitualNote</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>의례실 종이</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>'그릇은 셋. 둘은 쓰였고 하나가 남았다.' 마지막 무녀가 아직 남아 있다는 증거.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>'곪은 것은 도려내야 한다. 그릇은 셋, 둘은 쓰였고 하나가 남았다.' 이해심의 정화 논리와 마지막 무녀의 자리를 함께 적어 둔 기록.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>ritual</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>ch5_ritual_room</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="G14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6613,12 +6744,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>EvNote, EvBlueCloth, EvRitualNote</t>
+          <t>EvNote, EvBlueCloth, EvIpangyuStatement, EvRitualNote</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>EvNote</t>
+          <t>EvNote, EvIpangyuStatement</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>All</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -6638,7 +6774,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>붉은 쪽지는 이판규의 발작적 발언이 꾸며낸 말이 아니라, 실제 호출의 흔적과 맞닿아 있었음을 보여준다. 그의 말은 헛소리가 아니라 사건의 반향이었다.</t>
+          <t>붉은 쪽지의 호출과 탈주 직전 진술이 맞물린다. 이판규는 의식의 말을 제 언어로 되뇌고 있었던 셈이다.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -6859,7 +6995,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>EvDiary</t>
+          <t>EvDiary, EvBlueHanbok</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>All</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -6879,7 +7020,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>일기장은 송금이 도망칠 여유조차 없이 의례의 배역으로 밀려 들어갔음을 드러낸다. 이 실종은 도피가 아니라 선택당한 소거였다.</t>
+          <t>일기와 청색 한복은 송금이 도망친 것이 아니라, 의례가 요구한 배역으로 입혀지고 밀려 들어갔음을 함께 보여 준다. 이 실종은 도피가 아니라 강요된 소거였다.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -7764,12 +7905,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>붉은 쪽지가 남아 있으므로, 이판규의 호출 이야기는 실제 흔적과 맞닿아 있다.</t>
+          <t>붉은 쪽지의 호출과 탈주 직전 진술이 맞물리므로, 이판규의 말은 실제 의식의 반향이다.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>EvNote</t>
+          <t>EvNote, EvIpangyuStatement</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -7780,7 +7921,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>발작처럼 흘린 말과 쪽지의 호출이 맞물린다. 그의 말은 죄를 피하려 지어낸 헛소리만은 아니다.</t>
+          <t>쪽지가 가리킨 호출과 탈주 직전의 말이 맞물린다. 이판규는 의식의 말을 제 언어로 되뇌고 있었던 셈이다.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -7811,7 +7952,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>EvRitualNote</t>
+          <t>EvIpangyuStatement</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -8544,12 +8685,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>일기는 송금에게 도망칠 틈이 없었고, 의례의 배역으로 정해졌음을 보여 준다.</t>
+          <t>일기와 청색 한복은 송금이 의례의 배역으로 입혀진 채 끌려갔음을 보여 준다.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>EvDiary</t>
+          <t>EvDiary, EvBlueHanbok</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -8560,7 +8701,7 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>송금의 실종은 스스로 떠난 도피가 아니다. 선택당한 사람을 지워 버리는 의례의 순서가 그를 밀어 넣었다.</t>
+          <t>일기의 증언과 한복의 용도가 겹친다. 송금의 실종은 스스로 떠난 도피가 아니라, 배역으로 입혀진 뒤 밀려난 결과다.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -9105,7 +9246,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3">
@@ -9145,7 +9286,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -9155,7 +9296,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -9185,7 +9326,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -9195,7 +9336,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -9269,7 +9410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9702,7 +9843,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ch6FinalBlock|Ch6FinalRecord</t>
+          <t>Ch6FinalBlock</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -9751,12 +9892,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cond_Branch_FoundOldArticles_01</t>
+          <t>Cond_Branch_FinalChoice_Record</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CG_Branch_FoundOldArticles</t>
+          <t>CG_Branch_FinalChoice_Record</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -9766,7 +9907,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ch4ALibraryTakeArticles|Ch4ALibraryExposeArchive</t>
+          <t>Ch6FinalRecord</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -9783,42 +9924,44 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cond_Branch_Investigation3_01</t>
+          <t>Cond_Branch_FinalRecordComplete</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CG_Branch_Investigation3</t>
+          <t>CG_Branch_FinalRecordComplete</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>QuestionSolved</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Credibility</t>
+          <t>QuestionSolved_QArchivePattern</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>3</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cond_Branch_MatchedPattern_01</t>
+          <t>Cond_Branch_FoundOldArticles_01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CG_Branch_MatchedPattern</t>
+          <t>CG_Branch_FoundOldArticles</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -9828,7 +9971,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ch5RitualPresentMask</t>
+          <t>Ch4ALibraryTakeArticles|Ch4ALibraryExposeArchive</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -9845,84 +9988,84 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cond_Branch_OkryunPushed_01</t>
+          <t>Cond_Branch_Investigation3_01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CG_Branch_OkryunPushed</t>
+          <t>CG_Branch_Investigation3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ChoiceSelected</t>
+          <t>GaugeValue</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ch4BCafePress</t>
+          <t>Credibility</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cond_Branch_ReadRitual_01</t>
+          <t>Cond_Branch_MatchedPattern_01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CG_Branch_ReadRitual</t>
+          <t>CG_Branch_MatchedPattern</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ReadRitualScore</t>
+          <t>Ch5RitualPresentMask</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cond_Branch_SolvedMid_01</t>
+          <t>Cond_Branch_OkryunPushed_01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CG_Branch_SolvedMid</t>
+          <t>CG_Branch_OkryunPushed</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SolvedQuestionCount</t>
+          <t>Ch4BCafePress</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9932,29 +10075,29 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[4, 5, 6]</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cond_Branch_SongsoonTrust1_01</t>
+          <t>Cond_Branch_ReadRitual_01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CG_Branch_SongsoonTrust1</t>
+          <t>CG_Branch_ReadRitual</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Trust</t>
+          <t>GaugeValue</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>ReadRitualScore</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9969,84 +10112,84 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cond_Branch_SongsoonTrust2_01</t>
+          <t>Cond_Branch_SolvedMid_01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CG_Branch_SongsoonTrust2</t>
+          <t>CG_Branch_SolvedMid</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Trust</t>
+          <t>GaugeValue</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>SolvedQuestionCount</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>2</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>[4, 5, 6]</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cond_Branch_TouchedRoomWall_01</t>
+          <t>Cond_Branch_SongsoonTrust1_01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CG_Branch_TouchedRoomWall</t>
+          <t>CG_Branch_SongsoonTrust1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ChoiceSelected</t>
+          <t>Trust</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ch3Room4TouchWall</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cond_Cafe4b_Erosion2_01</t>
+          <t>Cond_Branch_SongsoonTrust2_01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CG_Cafe4b_Erosion2</t>
+          <t>CG_Branch_SongsoonTrust2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>Trust</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Erosion</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10061,12 +10204,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cond_Cafe_Info2_01</t>
+          <t>Cond_Branch_TouchedRoomWall_01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CG_Cafe_Info2</t>
+          <t>CG_Branch_TouchedRoomWall</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -10076,7 +10219,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ch2HospitalAskDoor</t>
+          <t>Ch3Room4TouchWall</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -10093,44 +10236,42 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cond_Ch2Well_ShowedCloth_01</t>
+          <t>Cond_Cafe4b_Erosion2_01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CG_Ch2Well_ShowedCloth</t>
+          <t>CG_Cafe4b_Erosion2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ChoiceSelected</t>
+          <t>GaugeValue</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ch2WellTrustCloth</t>
+          <t>Erosion</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cond_Ch2Well_ShowedNote_01</t>
+          <t>Cond_Cafe_Info2_01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CG_Ch2Well_ShowedNote</t>
+          <t>CG_Cafe_Info2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -10140,7 +10281,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ch2WellTrustNote</t>
+          <t>Ch2HospitalAskDoor</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -10157,42 +10298,44 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cond_Credibility_Zero_01</t>
+          <t>Cond_Ch2Well_ShowedCloth_01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CG_Credibility_Zero</t>
+          <t>CG_Ch2Well_ShowedCloth</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Credibility</t>
+          <t>Ch2WellTrustCloth</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LessEqual</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cond_Descent_CalledEditorTrue_01</t>
+          <t>Cond_Ch2Well_ShowedNote_01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CG_Descent_CalledEditorTrue</t>
+          <t>CG_Ch2Well_ShowedNote</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -10202,7 +10345,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ch5PathContactEditor</t>
+          <t>Ch2WellTrustNote</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -10219,12 +10362,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cond_Descent_Erosion3_01</t>
+          <t>Cond_Credibility_Zero_01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CG_Descent_Erosion3</t>
+          <t>CG_Credibility_Zero</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -10234,57 +10377,59 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Erosion</t>
+          <t>Credibility</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
+          <t>LessEqual</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cond_Descent_SongsoonTrust1_01</t>
+          <t>Cond_Descent_CalledEditorTrue_01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CG_Descent_SongsoonTrust1</t>
+          <t>CG_Descent_CalledEditorTrue</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Trust</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>Ch5PathContactEditor</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>1</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cond_EndingB_ErodedRecord_01</t>
+          <t>Cond_Descent_Erosion3_01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CG_EndingB_ErodedRecord</t>
+          <t>CG_Descent_Erosion3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -10303,28 +10448,28 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cond_EndingB_ErodedRecord_02</t>
+          <t>Cond_Descent_SongsoonTrust1_01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CG_EndingB_ErodedRecord</t>
+          <t>CG_Descent_SongsoonTrust1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>Trust</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Credibility</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -10333,18 +10478,18 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cond_Epilogue_EndingA_01</t>
+          <t>Cond_EndingB_ErodedRecord_01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CG_Epilogue_EndingA</t>
+          <t>CG_EndingB_ErodedRecord</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -10354,7 +10499,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SolvedQuestionCount</t>
+          <t>Erosion</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -10363,18 +10508,18 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cond_Epilogue_EndingA_02</t>
+          <t>Cond_EndingB_ErodedRecord_02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CG_Epilogue_EndingA</t>
+          <t>CG_EndingB_ErodedRecord</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -10399,12 +10544,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cond_Epilogue_EndingB_01</t>
+          <t>Cond_Epilogue_EndingA_01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CG_Epilogue_EndingB</t>
+          <t>CG_Epilogue_EndingA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -10419,24 +10564,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>[4, 5, 6]</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cond_Epilogue_EndingB_02</t>
+          <t>Cond_Epilogue_EndingA_02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CG_Epilogue_EndingB</t>
+          <t>CG_Epilogue_EndingA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -10461,44 +10604,44 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cond_Epilogue_NotExposed</t>
+          <t>Cond_Epilogue_EndingB_01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CG_Epilogue_NotExposed</t>
+          <t>CG_Epilogue_EndingB</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ChoiceSelected</t>
+          <t>GaugeValue</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ch6FinalExpose</t>
+          <t>SolvedQuestionCount</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>NotEqual</t>
+          <t>Equal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>[4, 5, 6]</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cond_Erosion_High_01</t>
+          <t>Cond_Epilogue_EndingB_02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CG_Erosion_High</t>
+          <t>CG_Epilogue_EndingB</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -10508,7 +10651,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Erosion</t>
+          <t>Credibility</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -10523,116 +10666,114 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cond_Erosion_Max_01</t>
+          <t>Cond_Epilogue_NotExposed</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CG_Erosion_Max</t>
+          <t>CG_Epilogue_NotExposed</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Erosion</t>
+          <t>Ch6FinalExpose</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>10</v>
+          <t>NotEqual</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cond_FinalChoice_BlockOnly</t>
+          <t>Cond_Erosion_High_01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CG_FinalChoice_BlockOnly</t>
+          <t>CG_Erosion_High</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ChoiceSelected</t>
+          <t>GaugeValue</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ch6FinalBlock</t>
+          <t>Erosion</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cond_FinalChoice_RecordOnly</t>
+          <t>Cond_Erosion_Max_01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CG_FinalChoice_RecordOnly</t>
+          <t>CG_Erosion_Max</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ChoiceSelected</t>
+          <t>GaugeValue</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ch6FinalRecord</t>
+          <t>Erosion</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cond_GuardedDoor_HasScore_01</t>
+          <t>Cond_FinalChoice_BlockOnly</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CG_GuardedDoor_HasScore</t>
+          <t>CG_FinalChoice_BlockOnly</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EvRitualScore</t>
+          <t>Ch6FinalBlock</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -10649,22 +10790,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cond_Hospital_Info2_01</t>
+          <t>Cond_GuardedDoor_HasScore_01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CG_Hospital_Info2</t>
+          <t>CG_GuardedDoor_HasScore</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ChoiceSelected</t>
+          <t>EvidenceOwned</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ch2HospitalAskDoor</t>
+          <t>EvRitualScore</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -10681,22 +10822,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cond_Library_BlueHanbok_01</t>
+          <t>Cond_Hospital_Info2_01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CG_Library_BlueHanbok</t>
+          <t>CG_Hospital_Info2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EvBlueHanbok</t>
+          <t>Ch2HospitalAskDoor</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -10713,12 +10854,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cond_Library_Diary_01</t>
+          <t>Cond_Library_BlueHanbok_01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CG_Library_Diary</t>
+          <t>CG_Library_BlueHanbok</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -10728,7 +10869,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>EvDiary</t>
+          <t>EvBlueHanbok</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -10745,74 +10886,74 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cond_Library_Investigation_01</t>
+          <t>Cond_Library_Diary_01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CG_Library_Investigation2</t>
+          <t>CG_Library_Diary</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>EvidenceOwned</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Credibility</t>
+          <t>EvDiary</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>2</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cond_Library_RunawaySolved_01</t>
+          <t>Cond_Library_Investigation_01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CG_Library_QSonggeumRunaway</t>
+          <t>CG_Library_Investigation2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>QuestionSolved</t>
+          <t>GaugeValue</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>QuestionSolved_QSonggeumRunaway</t>
+          <t>Credibility</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cond_Outcome_QMadness_01</t>
+          <t>Cond_Library_RunawaySolved_01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CG_Outcome_QMadness</t>
+          <t>CG_Library_QSonggeumRunaway</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -10822,7 +10963,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>QuestionSolved_QIpangyuMadness</t>
+          <t>QuestionSolved_QSonggeumRunaway</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -10839,12 +10980,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cond_Outcome_QRunaway_01</t>
+          <t>Cond_Outcome_QMadness_01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CG_Outcome_QRunaway</t>
+          <t>CG_Outcome_QMadness</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -10854,7 +10995,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>QuestionSolved_QSonggeumRunaway</t>
+          <t>QuestionSolved_QIpangyuMadness</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -10871,22 +11012,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cond_Outcome_SolvedMid_01</t>
+          <t>Cond_Outcome_QRunaway_01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CG_Outcome_SolvedMid</t>
+          <t>CG_Outcome_QRunaway</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>QuestionSolved</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SolvedQuestionCount</t>
+          <t>QuestionSolved_QSonggeumRunaway</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -10896,19 +11037,19 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>[4, 5, 6]</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cond_ParticipantLedger_Erosion3_01</t>
+          <t>Cond_Outcome_SolvedMid_01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CG_ParticipantLedger_Erosion3</t>
+          <t>CG_Outcome_SolvedMid</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -10918,54 +11059,54 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Erosion</t>
+          <t>SolvedQuestionCount</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>3</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>[4, 5, 6]</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cond_Proof_All_01</t>
+          <t>Cond_ParticipantLedger_Erosion3_01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CG_Proof_All</t>
+          <t>CG_ParticipantLedger_Erosion3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>QuestionSolved</t>
+          <t>GaugeValue</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>QuestionSolved_QSonggeumMissing|QuestionSolved_QSonggeumRunaway|QuestionSolved_QRoom4Purpose</t>
+          <t>Erosion</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cond_Proof_All_02</t>
+          <t>Cond_Proof_All_01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -10980,7 +11121,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>QuestionSolved_QIpangyuCall|QuestionSolved_QIpangyuMadness|QuestionSolved_QCallPattern|QuestionSolved_QArchivePattern</t>
+          <t>QuestionSolved_QSonggeumMissing|QuestionSolved_QSonggeumRunaway|QuestionSolved_QRoom4Purpose</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -10997,7 +11138,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cond_Proof_All_03</t>
+          <t>Cond_Proof_All_02</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -11012,7 +11153,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>QuestionSolved_QRitualLead|QuestionSolved_QRitualAccident|QuestionSolved_QRitualErasure</t>
+          <t>QuestionSolved_QIpangyuCall|QuestionSolved_QIpangyuMadness|QuestionSolved_QCallPattern|QuestionSolved_QArchivePattern</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -11029,12 +11170,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cond_Proof_Person_01</t>
+          <t>Cond_Proof_All_03</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CG_Proof_Person</t>
+          <t>CG_Proof_All</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -11044,7 +11185,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>QuestionSolved_QSonggeumMissing|QuestionSolved_QSonggeumRunaway|QuestionSolved_QRoom4Purpose</t>
+          <t>QuestionSolved_QRitualLead|QuestionSolved_QRitualAccident|QuestionSolved_QRitualErasure</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -11061,12 +11202,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cond_Proof_Ritual_01</t>
+          <t>Cond_Proof_Person_01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CG_Proof_Ritual</t>
+          <t>CG_Proof_Person</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -11076,7 +11217,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>QuestionSolved_QRitualLead|QuestionSolved_QRitualAccident|QuestionSolved_QRitualErasure</t>
+          <t>QuestionSolved_QSonggeumMissing|QuestionSolved_QSonggeumRunaway|QuestionSolved_QRoom4Purpose</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -11093,12 +11234,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cond_Proof_Structure_01</t>
+          <t>Cond_Proof_Ritual_01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CG_Proof_Structure</t>
+          <t>CG_Proof_Ritual</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -11108,7 +11249,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>QuestionSolved_QIpangyuCall|QuestionSolved_QIpangyuMadness|QuestionSolved_QCallPattern|QuestionSolved_QArchivePattern</t>
+          <t>QuestionSolved_QRitualLead|QuestionSolved_QRitualAccident|QuestionSolved_QRitualErasure</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -11125,22 +11266,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cond_QR_CheckpointFactoryShock_01</t>
+          <t>Cond_Proof_Structure_01</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CG_QR_CheckpointFactoryShock</t>
+          <t>CG_Proof_Structure</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SceneVisited</t>
+          <t>QuestionSolved</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ch2_factory_shock</t>
+          <t>QuestionSolved_QIpangyuCall|QuestionSolved_QIpangyuMadness|QuestionSolved_QCallPattern|QuestionSolved_QArchivePattern</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -11157,12 +11298,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cond_QR_CheckpointRitualRoom_01</t>
+          <t>Cond_QR_CheckpointFactoryShock_01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CG_QR_CheckpointRitualRoom</t>
+          <t>CG_QR_CheckpointFactoryShock</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -11172,7 +11313,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ch5_ritual_room</t>
+          <t>ch2_factory_shock</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -11189,12 +11330,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cond_QR_CheckpointRoom4Conclusion_01</t>
+          <t>Cond_QR_CheckpointRitualRoom_01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CG_QR_CheckpointRoom4Conclusion</t>
+          <t>CG_QR_CheckpointRitualRoom</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -11204,7 +11345,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ch3_room4_conclusion</t>
+          <t>ch5_ritual_room</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -11221,12 +11362,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cond_QR_CheckpointSlum_01</t>
+          <t>Cond_QR_CheckpointRoom4Conclusion_01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CG_QR_CheckpointSlum</t>
+          <t>CG_QR_CheckpointRoom4Conclusion</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -11236,7 +11377,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ch4a_slum</t>
+          <t>ch3_room4_conclusion</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -11253,12 +11394,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cond_QR_CheckpointWell_01</t>
+          <t>Cond_QR_CheckpointSlum_01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CG_QR_CheckpointWell</t>
+          <t>CG_QR_CheckpointSlum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -11268,7 +11409,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ch2_well</t>
+          <t>ch4a_slum</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -11285,22 +11426,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cond_RR_QIpangyuSeen_01</t>
+          <t>Cond_QR_CheckpointWell_01</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CG_QR_IpangyuSeen_01</t>
+          <t>CG_QR_CheckpointWell</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>RevealedCharacter</t>
+          <t>SceneVisited</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Ipangyu</t>
+          <t>ch2_well</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -11317,131 +11458,131 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cond_RR_QRitualOpen_01</t>
+          <t>Cond_RR_QIpangyuSeen_01</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CG_QR_RitualOpen_01</t>
+          <t>CG_QR_IpangyuSeen_01</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>RevealedCharacter</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ReadRitualScore</t>
+          <t>Ipangyu</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>1</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cond_RR_QRitualOpen_02</t>
+          <t>Cond_RR_QRitualOpen_01</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CG_QR_RitualOpen_02</t>
+          <t>CG_QR_RitualOpen_01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>RevealedCharacter</t>
+          <t>GaugeValue</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Haesim</t>
+          <t>ReadRitualScore</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cond_RR_QRitualOpen_03</t>
+          <t>Cond_RR_QRitualOpen_02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CG_QR_RitualOpen_03</t>
+          <t>CG_QR_RitualOpen_02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SceneProgressIndex</t>
+          <t>RevealedCharacter</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Haesim</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>31</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cond_RR_QSonggeumOpen_01</t>
+          <t>Cond_RR_QRitualOpen_03</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CG_QR_SonggeumOpen_01</t>
+          <t>CG_QR_RitualOpen_03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>EvDiary</t>
+          <t>SceneProgressIndex</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cond_RR_QSonggeumOpen_02</t>
+          <t>Cond_RR_QSonggeumOpen_01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CG_QR_SonggeumOpen_02</t>
+          <t>CG_QR_SonggeumOpen_01</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -11451,7 +11592,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>EvOldArticles</t>
+          <t>EvDiary</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -11468,79 +11609,79 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cond_RR_QSonggeumOpen_03</t>
+          <t>Cond_RR_QSonggeumOpen_02</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CG_QR_SonggeumOpen_03</t>
+          <t>CG_QR_SonggeumOpen_02</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SceneProgressIndex</t>
+          <t>EvidenceOwned</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>EvOldArticles</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>24</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cond_RR_QSonggeumOpen_04</t>
+          <t>Cond_RR_QSonggeumOpen_03</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CG_QR_SonggeumOpen_04</t>
+          <t>CG_QR_SonggeumOpen_03</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>RevealedCharacter</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Songgeum</t>
+          <t>SceneProgressIndex</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cond_RR_QIpangyuState_00</t>
+          <t>Cond_RR_QSonggeumOpen_04</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CG_QS_IpangyuCall_01</t>
+          <t>CG_QR_SonggeumOpen_04</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>QuestionSolved</t>
+          <t>RevealedCharacter</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>QuestionSolved_QIpangyuCall</t>
+          <t>Songgeum</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -11557,84 +11698,84 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cond_RR_QIpangyuState_01</t>
+          <t>Cond_RR_QIpangyuState_00</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CG_QS_IpangyuCall_02</t>
+          <t>CG_QS_IpangyuCall_01</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>QuestionSolved</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Erosion</t>
+          <t>QuestionSolved_QIpangyuCall</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>1</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cond_RR_QIpangyuMadnessState_00</t>
+          <t>Cond_RR_QIpangyuState_01</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CG_QS_IpangyuMadness_01</t>
+          <t>CG_QS_IpangyuCall_02</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>QuestionSolved</t>
+          <t>GaugeValue</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>QuestionSolved_QIpangyuMadness</t>
+          <t>Erosion</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cond_RR_QIpangyuMadnessState_01</t>
+          <t>Cond_RR_QIpangyuMadnessState_00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CG_QS_IpangyuMadness_02</t>
+          <t>CG_QS_IpangyuMadness_01</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>QuestionSolved</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>EvNote</t>
+          <t>QuestionSolved_QIpangyuMadness</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -11651,22 +11792,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cond_RR_QRitualAccidentState_00</t>
+          <t>Cond_RR_QIpangyuMadnessState_01</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CG_QS_RitualAccident_01</t>
+          <t>CG_QS_IpangyuMadness_02</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>QuestionSolved</t>
+          <t>EvidenceOwned</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>QuestionSolved_QRitualAccident</t>
+          <t>EvNote</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -11683,22 +11824,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cond_RR_QRitualAccidentState_01</t>
+          <t>Cond_RR_QRitualAccidentState_00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CG_QS_RitualAccident_02</t>
+          <t>CG_QS_RitualAccident_01</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>QuestionSolved</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EvRitualNote</t>
+          <t>QuestionSolved_QRitualAccident</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -11715,22 +11856,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cond_RR_QRitualState_00</t>
+          <t>Cond_RR_QRitualAccidentState_01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CG_QS_RitualLead_01</t>
+          <t>CG_QS_RitualAccident_02</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>QuestionSolved</t>
+          <t>EvidenceOwned</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>QuestionSolved_QRitualLead</t>
+          <t>EvRitualNote</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -11747,84 +11888,84 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cond_RR_QRitualState_01</t>
+          <t>Cond_RR_QRitualState_00</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CG_QS_RitualLead_02</t>
+          <t>CG_QS_RitualLead_01</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>QuestionSolved</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ReadRitualScore</t>
+          <t>QuestionSolved_QRitualLead</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>1</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cond_RR_QSonggeumState_00</t>
+          <t>Cond_RR_QRitualState_01</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CG_QS_SonggeumMissing_01</t>
+          <t>CG_QS_RitualLead_02</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>QuestionSolved</t>
+          <t>GaugeValue</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>QuestionSolved_QSonggeumMissing</t>
+          <t>ReadRitualScore</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cond_RR_QSonggeumState_01</t>
+          <t>Cond_RR_QSonggeumState_00</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CG_QS_SonggeumMissing_02</t>
+          <t>CG_QS_SonggeumMissing_01</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>QuestionSolved</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>EvDiary</t>
+          <t>QuestionSolved_QSonggeumMissing</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -11841,22 +11982,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cond_RR_QSonggeumRunawayState_00</t>
+          <t>Cond_RR_QSonggeumState_01</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CG_QS_SonggeumRunaway_01</t>
+          <t>CG_QS_SonggeumMissing_02</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>QuestionSolved</t>
+          <t>EvidenceOwned</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>QuestionSolved_QSonggeumRunaway</t>
+          <t>EvDiary</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -11873,22 +12014,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cond_RR_QSonggeumRunawayState_01</t>
+          <t>Cond_RR_QSonggeumRunawayState_00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CG_QS_SonggeumRunaway_02</t>
+          <t>CG_QS_SonggeumRunaway_01</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>QuestionSolved</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EvDiary</t>
+          <t>QuestionSolved_QSonggeumRunaway</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -11905,12 +12046,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cond_RitualRoom_OldArticles_01</t>
+          <t>Cond_RR_QSonggeumRunawayState_01</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CG_RitualRoom_OldArticles</t>
+          <t>CG_QS_SonggeumRunaway_02</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -11920,7 +12061,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>EvOldArticles</t>
+          <t>EvDiary</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -11937,22 +12078,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cond_RitualRoom_AccidentSolved_01</t>
+          <t>Cond_RitualRoom_OldArticles_01</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CG_RitualRoom_QRitualAccident</t>
+          <t>CG_RitualRoom_OldArticles</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>QuestionSolved</t>
+          <t>EvidenceOwned</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>QuestionSolved_QRitualAccident</t>
+          <t>EvOldArticles</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -11969,7 +12110,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cond_RitualRoom_QRitualAccident_01</t>
+          <t>Cond_RitualRoom_AccidentSolved_01</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -12001,22 +12142,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cond_RitualRoom_RitualScore_01</t>
+          <t>Cond_RitualRoom_QRitualAccident_01</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CG_RitualRoom_RitualScore</t>
+          <t>CG_RitualRoom_QRitualAccident</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>QuestionSolved</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>EvRitualScore</t>
+          <t>QuestionSolved_QRitualAccident</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -12033,42 +12174,44 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cond_RitualScene_Resonance_01</t>
+          <t>Cond_RitualRoom_RitualScore_01</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CG_RitualScene_Resonance2</t>
+          <t>CG_RitualRoom_RitualScore</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>EvidenceOwned</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Erosion</t>
+          <t>EvRitualScore</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>2</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cond_RitualScene_SolvedHigh_01</t>
+          <t>Cond_RitualScene_Resonance_01</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CG_RitualScene_SolvedHigh</t>
+          <t>CG_RitualScene_Resonance2</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -12078,7 +12221,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SolvedQuestionCount</t>
+          <t>Erosion</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -12087,18 +12230,18 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cond_Ritual_Erosion6_01</t>
+          <t>Cond_RitualScene_SolvedHigh_01</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CG_Ritual_Erosion6</t>
+          <t>CG_RitualScene_SolvedHigh</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -12108,7 +12251,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Erosion</t>
+          <t>SolvedQuestionCount</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -12117,60 +12260,58 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cond_Ritual_QRoom4Purpose_01</t>
+          <t>Cond_Ritual_Erosion6_01</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CG_Ritual_QRoom4Purpose</t>
+          <t>CG_Ritual_Erosion6</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>QuestionSolved</t>
+          <t>GaugeValue</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>QuestionSolved_QRoom4Purpose</t>
+          <t>Erosion</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cond_Room4_HasNote_01</t>
+          <t>Cond_Ritual_QRoom4Purpose_01</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CG_Room4_HasNote</t>
+          <t>CG_Ritual_QRoom4Purpose</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>QuestionSolved</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>EvNote</t>
+          <t>QuestionSolved_QRoom4Purpose</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -12187,84 +12328,84 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cond_Room4_ReadRitual_01</t>
+          <t>Cond_Room4_HasNote_01</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CG_Room4_ReadRitual</t>
+          <t>CG_Room4_HasNote</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>EvidenceOwned</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ReadRitualScore</t>
+          <t>EvNote</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F94" t="n">
-        <v>1</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cond_Room4_TrustedSongsoon_01</t>
+          <t>Cond_Room4_ReadRitual_01</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CG_Room4_TrustedSongsoon</t>
+          <t>CG_Room4_ReadRitual</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ChoiceSelected</t>
+          <t>GaugeValue</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Ch3WarehouseTrustSongsoon|Ch3Room4ComfortSongsoon</t>
+          <t>ReadRitualScore</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Cond_Slum_HasHanbok_01</t>
+          <t>Cond_Room4_TrustedSongsoon_01</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CG_Slum_HasHanbok</t>
+          <t>CG_Room4_TrustedSongsoon</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>EvBlueHanbok</t>
+          <t>Ch3WarehouseTrustSongsoon|Ch3Room4ComfortSongsoon</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -12281,22 +12422,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Cond_Threshold_CalledEditorFalse_01</t>
+          <t>Cond_Slum_HasHanbok_01</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CG_Threshold_CalledEditorFalse</t>
+          <t>CG_Slum_HasHanbok</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ChoiceSelected</t>
+          <t>EvidenceOwned</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Ch5PathNoContact</t>
+          <t>EvBlueHanbok</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -12313,42 +12454,44 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Cond_Threshold_Credibility7_01</t>
+          <t>Cond_Threshold_CalledEditorFalse_01</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CG_Threshold_Credibility7</t>
+          <t>CG_Threshold_CalledEditorFalse</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Credibility</t>
+          <t>Ch5PathNoContact</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F98" t="n">
-        <v>7</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Cond_Threshold_Erosion6_01</t>
+          <t>Cond_Threshold_Credibility7_01</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CG_Threshold_Erosion6</t>
+          <t>CG_Threshold_Credibility7</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -12358,7 +12501,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Erosion</t>
+          <t>Credibility</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -12367,80 +12510,80 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Cond_Threshold_FoundOldArticles_01</t>
+          <t>Cond_Threshold_Erosion6_01</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CG_Threshold_FoundOldArticles</t>
+          <t>CG_Threshold_Erosion6</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ChoiceSelected</t>
+          <t>GaugeValue</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Ch4ALibraryTakeArticles|Ch4ALibraryExposeArchive</t>
+          <t>Erosion</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Cond_Threshold_Investigation_01</t>
+          <t>Cond_Threshold_FoundOldArticles_01</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CG_Threshold_Investigation3</t>
+          <t>CG_Threshold_FoundOldArticles</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>ChoiceSelected</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Credibility</t>
+          <t>Ch4ALibraryTakeArticles|Ch4ALibraryExposeArchive</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>GreaterEqual</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
-        <v>3</v>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Cond_Threshold_Resonance_01</t>
+          <t>Cond_Threshold_Investigation_01</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CG_Threshold_Resonance2</t>
+          <t>CG_Threshold_Investigation3</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -12450,7 +12593,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Erosion</t>
+          <t>Credibility</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -12459,60 +12602,58 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cond_Threshold_RitualNote_01</t>
+          <t>Cond_Threshold_Resonance_01</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CG_Threshold_RitualNote</t>
+          <t>CG_Threshold_Resonance2</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>EvidenceOwned</t>
+          <t>GaugeValue</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>EvRitualNote</t>
+          <t>Erosion</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Equal</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Cond_Threshold_SolvedMid_01</t>
+          <t>Cond_Threshold_RitualNote_01</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CG_Threshold_SolvedMid</t>
+          <t>CG_Threshold_RitualNote</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>GaugeValue</t>
+          <t>EvidenceOwned</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>SolvedQuestionCount</t>
+          <t>EvRitualNote</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -12522,37 +12663,69 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>[4, 5, 6]</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>Cond_Threshold_SolvedMid_01</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CG_Threshold_SolvedMid</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>GaugeValue</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>SolvedQuestionCount</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Equal</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>[4, 5, 6]</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
           <t>Cond_Threshold_TrustedSongsoon_01</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>CG_Threshold_TrustedSongsoon</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>ChoiceSelected</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>Ch3WarehouseTrustSongsoon|Ch3Room4ComfortSongsoon</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>Equal</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>true</t>
         </is>
@@ -13889,7 +14062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15293,7 +15466,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ch6_ending_a</t>
+          <t>ch6_choice_record</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -15301,7 +15474,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>엔딩 A — 돌아오지 않은 언니</t>
+          <t>남기는 쪽</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -15311,7 +15484,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>assets/sfx/ending.mp3</t>
+          <t>assets/sfx/ritual_climax.mp3</t>
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
@@ -15319,7 +15492,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ch6_ending_b</t>
+          <t>ch6_ending_a</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -15327,7 +15500,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>엔딩 B — 기록된 것들</t>
+          <t>엔딩 A — 돌아오지 않은 언니</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -15345,7 +15518,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ch6_ending_c</t>
+          <t>ch6_ending_b</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -15353,7 +15526,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>엔딩 C — 문 너머</t>
+          <t>엔딩 B — 기록된 것들</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -15365,16 +15538,13 @@
         <is>
           <t>assets/sfx/ending.mp3</t>
         </is>
-      </c>
-      <c r="F44" t="n">
-        <v>2</v>
       </c>
       <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ch6_epilogue</t>
+          <t>ch6_ending_c</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -15382,25 +15552,28 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>에필로그</t>
+          <t>엔딩 C — 문 너머</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>assets/bg/newsroom.jpeg</t>
+          <t>assets/bg/ritual_room.jpg</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>assets/sfx/ending.mp3</t>
         </is>
+      </c>
+      <c r="F45" t="n">
+        <v>2</v>
       </c>
       <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ch6_final_decision</t>
+          <t>ch6_ending_c_answer</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -15408,7 +15581,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>폭로 뒤의 결단</t>
+          <t>엔딩 C — 닿지 못한 대답</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -15418,25 +15591,18 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>assets/sfx/ritual_climax.mp3</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>마지막 결단</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>폭로로 만든 틈을 어디에 쓸지 고른다. 사람을 붙들거나, 의식을 끊거나, 기록을 남긴다.</t>
-        </is>
+          <t>assets/sfx/ending.mp3</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>2</v>
       </c>
       <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ch6_outcome</t>
+          <t>ch6_ending_c_block</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -15444,7 +15610,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>의식의 균열</t>
+          <t>엔딩 C — 끊기지 않은 의식</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -15454,7 +15620,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>assets/sfx/ritual_climax.mp3</t>
+          <t>assets/sfx/ending.mp3</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -15465,7 +15631,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ch6_path_a</t>
+          <t>ch6_ending_c_record</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -15473,7 +15639,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>콧노래의 응답</t>
+          <t>엔딩 C — 빈 기록</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -15483,15 +15649,18 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>assets/sfx/ritual_climax.mp3</t>
-        </is>
+          <t>assets/sfx/ending.mp3</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>2</v>
       </c>
       <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ch6_path_a2</t>
+          <t>ch6_epilogue</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -15499,12 +15668,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>돌아오지 않은 숨</t>
+          <t>에필로그</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>assets/bg/ritual_room.jpg</t>
+          <t>assets/bg/newsroom.jpeg</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -15517,7 +15686,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ch6_path_b</t>
+          <t>ch6_final_decision</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -15525,7 +15694,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>기록자의 선택</t>
+          <t>폭로 뒤의 결단</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -15536,6 +15705,16 @@
       <c r="E50" t="inlineStr">
         <is>
           <t>assets/sfx/ritual_climax.mp3</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>마지막 결단</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>폭로로 만든 틈을 어디에 쓸지 고른다. 사람을 붙들거나, 의식을 끊거나, 기록을 남긴다.</t>
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
@@ -15543,7 +15722,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ch6_path_b2</t>
+          <t>ch6_outcome</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -15551,7 +15730,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>남겨진 기록</t>
+          <t>의식의 균열</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -15561,15 +15740,18 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>assets/sfx/ending.mp3</t>
-        </is>
+          <t>assets/sfx/ritual_climax.mp3</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>2</v>
       </c>
       <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ch6_ritual_scene</t>
+          <t>ch6_path_a</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -15577,7 +15759,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>의식 현장</t>
+          <t>콧노래의 응답</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -15588,19 +15770,6 @@
       <c r="E52" t="inlineStr">
         <is>
           <t>assets/sfx/ritual_climax.mp3</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>4</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>결단 목표</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>송금, 이해심, 그리고 이 방에 쌓인 질문들 사이에서 무엇을 사람 쪽으로 남길지 지금 결정한다.</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
@@ -15608,7 +15777,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ch6_threshold</t>
+          <t>ch6_path_a2</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -15616,7 +15785,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>의식 직전</t>
+          <t>돌아오지 않은 숨</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -15626,7 +15795,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>assets/sfx/ritual.mp3</t>
+          <t>assets/sfx/ending.mp3</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
@@ -15634,7 +15803,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>scene_ending_erosion</t>
+          <t>ch6_path_b</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -15642,7 +15811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>침식의 끝</t>
+          <t>제단을 끊는 쪽</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -15660,20 +15829,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>scene_gameover_credibility</t>
+          <t>ch6_path_b2</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>평판 붕괴 — 게임오버</t>
+          <t>끊긴 순서</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>assets/bg/newsroom.jpeg</t>
+          <t>assets/bg/ritual_room.jpg</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -15686,28 +15855,171 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>ch6_path_record</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>6</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>증인의 문장</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>assets/bg/ritual_room.jpg</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>assets/sfx/ending.mp3</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ch6_ritual_scene</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>6</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>의식 현장</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>assets/bg/ritual_room.jpg</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>assets/sfx/ritual_climax.mp3</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>4</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>결단 목표</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>송금, 이해심, 그리고 이 방에 쌓인 질문들 사이에서 무엇을 사람 쪽으로 남길지 지금 결정한다.</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ch6_threshold</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>6</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>의식 직전</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>assets/bg/ritual_room.jpg</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>assets/sfx/ritual.mp3</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>scene_ending_erosion</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>6</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>침식의 끝</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>assets/bg/ritual_room.jpg</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>assets/sfx/ritual_climax.mp3</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>scene_gameover_credibility</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>평판 붕괴 — 게임오버</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>assets/bg/newsroom.jpeg</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>assets/sfx/ending.mp3</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>scene_gameover_erosion</t>
         </is>
       </c>
-      <c r="B56" t="n">
+      <c r="B61" t="n">
         <v>0</v>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>게임 오버 - 침식</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>assets/bg/factory.jpeg</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>assets/sfx/ending.mp3</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15720,7 +16032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U402"/>
+  <dimension ref="A1:U401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17659,7 +17971,6 @@
           <t>Fade</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>유웅룡은 간신히 억눌린 숨을 내쉬며, 시신이 사후경직으로 악착같이 움켜쥐고 있는 오른손을 억지로 펴낸다.</t>
@@ -21010,7 +21321,6 @@
           <t>Speaker</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr"/>
       <c r="N142" t="inlineStr">
         <is>
           <t>송순 씨는… 괜찮습니까? 난 종이 한 장 붙든 것뿐인데 속이 뒤집히는데.</t>
@@ -22143,7 +22453,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>클리핑 사이사이에는 붉은 연필 자국이 남아 있다. 누군가 의도적으로 문장을 지우고, 남겨야 할 정보만 남긴 흔적이다. 덮은 자의 손길이 오히려 사건의 테두리를 또렷하게 만든다.</t>
+          <t>클리핑 여백에는 붉은 연필 자국과 함께 짧은 문장이 남아 있다. ‘곪은 것은 도려내야 한다.’ 서명처럼 적힌 두 글자, 해심. 지운 이는 흔적을 감췄지만, 누군가는 그 빈자리를 이용해 더 잔인한 결론을 적어 넣었다.</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -23358,7 +23668,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>...그건 모르겠어요. 저는 도망쳤으니까. 뒤를 안 봤어요.</t>
+          <t>...그건 모르겠어요. 저는 도망쳤으니까. 뒤는 안 봤어요. 다만 거울에, 한쪽 눈을 가린 여자가 서 있었어요. 손님들한테는 늘 아픈 사람들을 거둬 준다고 말하던 여자요.</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -25716,7 +26026,6 @@
           <t>Tremble</t>
         </is>
       </c>
-      <c r="L266" t="inlineStr"/>
       <c r="N266" t="inlineStr">
         <is>
           <t>이상해요. 지금 여긴 우리뿐인데… 누가 아직 벽 안쪽에서 숨을 고르고 있는 것 같아요.</t>
@@ -26079,7 +26388,7 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>창고에서 챙긴 악보와 같은 결입니다. 소리를 읽는 법만 알면, 이 의식이 사람 발을 어디로 모는지도 보입니다.</t>
+          <t>악보가 사람을 부르는 순서를 적어 두었다면, 제단의 기록은 그 순서가 누구에게 쓰였는지를 세고 있습니다.</t>
         </is>
       </c>
       <c r="O275" t="inlineStr">
@@ -26124,7 +26433,7 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>자료실에서 본 낡은 기사 뭉치가 괜한 옛이야기가 아니었군요. 지워진 문장과 남겨진 제단이 같은 손 아래 놓여 있습니다.</t>
+          <t>자료실 여백에 남은 ‘해심’이라는 이름도 여기까지 이어집니다. 오래된 기사는 접혔고, 그 빈자리에 의식이 자랐습니다.</t>
         </is>
       </c>
       <c r="O276" t="inlineStr">
@@ -26169,7 +26478,7 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>이걸 우발적 광신쯤으로 넘기긴 어렵습니다. 종이에 적힌 순서와 남은 몫이 전부 맞아떨어져요. 저들은 처음부터 사람 수까지 세며 판을 굴렸습니다.</t>
+          <t>이건 우발적인 광신이 아닙니다. 누군가 사람 수와 순서를 세며, 빠진 자리를 다음 사람으로 메워 왔어요.</t>
         </is>
       </c>
       <c r="O277" t="inlineStr">
@@ -26214,7 +26523,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>4호실의 옷과 가면까지 떠올리면, 이곳은 사람을 무작정 해친 자리가 아니다. 이름과 얼굴을 벗겨 의식의 배역으로 갈아 끼우던 자리다.</t>
+          <t>4호실의 옷과 가면은 그 계산의 준비물이었군요. 사람을 없애는 게 아니라, 다른 몫으로 바꾸기 위해.</t>
         </is>
       </c>
       <c r="O278" t="inlineStr">
@@ -26572,54 +26881,29 @@
       <c r="C290" t="n">
         <v>2</v>
       </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>기록으로 남기려 했는데, 이 틈은 말보다 몸이 먼저 메워야 한다. 일단 막아 두면, 그다음에 남길 수 있으니까.</t>
+          <t>유웅룡이 제단 쪽으로 몸을 던진다. 글로는 늦는 순간이 있다. 이번만큼은 몸이 문장보다 먼저 나간다.</t>
         </is>
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="P290" t="inlineStr">
-        <is>
-          <t>CG_FinalChoice_RecordOnly</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="B291" t="inlineStr">
         <is>
-          <t>ch6_choice_b</t>
+          <t>ch6_choice_c</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>유웅룡이 제단 쪽으로 몸을 던진다. 글로는 늦는 순간이 있다. 이번만큼은 몸이 문장보다 먼저 나간다.</t>
+          <t>두 사람은 아주 짧은 순간, 아무 쪽도 택하지 못하고 얼어붙는다. 공포는 때로 물러서는 감정보다 먼저 사람 몸을 멈추게 한다. 아무것도 하지 않은 대가가 무엇인지, 바로 다음 순간 몸으로 알게 된다.</t>
         </is>
       </c>
       <c r="O291" t="inlineStr">
@@ -26635,16 +26919,36 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>두 사람은 아주 짧은 순간, 아무 쪽도 택하지 못하고 얼어붙는다. 공포는 때로 물러서는 감정보다 먼저 사람 몸을 멈추게 한다. 아무것도 하지 않은 대가가 무엇인지, 바로 다음 순간 몸으로 알게 된다.</t>
+          <t>…빌어먹을, 한 박자 늦었군.</t>
         </is>
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>thought</t>
         </is>
       </c>
     </row>
@@ -26655,7 +26959,7 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26679,12 +26983,17 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>…빌어먹을, 한 박자 늦었군.</t>
+          <t>이판규를 미친놈 하나로 접어 두려던 판도 여기서 끝입니다. 불려간 자의 말이 헛소리가 아니었다면, 지금 저 안에 있는 것도 우발이 아니라 누군가의 계산이었겠지요.</t>
         </is>
       </c>
       <c r="O293" t="inlineStr">
         <is>
           <t>thought</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>CG_Outcome_QMadness</t>
         </is>
       </c>
     </row>
@@ -26695,21 +27004,21 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Tense</t>
+          <t>Afraid</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -26719,87 +27028,77 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>이판규를 미친놈 하나로 접어 두려던 판도 여기서 끝입니다. 불려간 자의 말이 헛소리가 아니었다면, 지금 저 안에 있는 것도 우발이 아니라 누군가의 계산이었겠지요.</t>
+          <t>언니가 도망친 게 아니라 붙들린 거라면, 여기서도 같은 말을 하게 둘 순 없어요. 사라진 사람이 먼저 달아났다고, 또 그렇게 몰아갈 테니까요.</t>
         </is>
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
         <is>
-          <t>CG_Outcome_QMadness</t>
+          <t>CG_Outcome_QRunaway</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="B295" t="inlineStr">
         <is>
-          <t>ch6_choice_c</t>
+          <t>ch6_choice_record</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>8</v>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>Songsoon</t>
-        </is>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>Afraid</t>
-        </is>
-      </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>언니가 도망친 게 아니라 붙들린 거라면, 여기서도 같은 말을 하게 둘 순 없어요. 사라진 사람이 먼저 달아났다고, 또 그렇게 몰아갈 테니까요.</t>
+          <t>유웅룡은 제단 앞의 명부를 움켜쥐고, 젖은 종이가 찢어지기 전에 이름과 순번을 수첩으로 옮긴다. 이 순간을 멈추지 못하더라도, 누가 누구를 어디로 밀어 넣었는지는 사라지게 두지 않는다.</t>
         </is>
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="P295" t="inlineStr">
-        <is>
-          <t>CG_Outcome_QRunaway</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="B296" t="inlineStr">
         <is>
-          <t>ch6_ending_a</t>
+          <t>ch6_choice_record</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>기사가 짧은 화재 소식으로 지면에 실리고도, 그날 밤 의식 현장의 장면은 여전히 몸이 먼저 기억한다. 며칠이 지나도 그 순간만은 지워지지 않는다.</t>
+          <t>송순 씨, 목소리를 놓치지 마요. 난 여기 적겠습니다. 누가 살아서 나가든, 이 방이 없던 일은 못 되게.</t>
         </is>
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>narration</t>
-        </is>
-      </c>
-      <c r="P296" t="inlineStr">
-        <is>
-          <t>CG_Epilogue_NotExposed</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -26810,36 +27109,21 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>1</v>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>Songsoon</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>Uneasy</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>(창고 벽 앞에서 들었던 그 멜로디로 응답한다. 언니의 노래에 맞서는 콧노래)</t>
+          <t>기사가 짧은 화재 소식으로 지면에 실리고도, 그날 밤 의식 현장의 장면은 여전히 몸이 먼저 기억한다. 며칠이 지나도 그 순간만은 지워지지 않는다.</t>
         </is>
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>CG_Epilogue_NotExposed</t>
         </is>
       </c>
     </row>
@@ -26850,21 +27134,36 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>2</v>
-      </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t>ScreenShake</t>
+        <v>1</v>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Songsoon</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Uneasy</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>감응이 흔들린다. 이해심이 비틀거리며 무너진다. 문은 반쯤 열린 채 억지로 닫힌다. 닫히는 마지막 순간까지 콧노래는 한 사람의 이름을 놓치지 않으려는 것처럼 떨린다. 누군가를 완전히 데려오진 못해도, 끝내 사람 쪽으로 당겨 두려는 힘만은 남는다.</t>
+          <t>(창고 벽 앞에서 들었던 그 멜로디로 응답한다. 언니의 노래에 맞서는 콧노래)</t>
         </is>
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -26875,16 +27174,16 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>FlashDark</t>
+          <t>ScreenShake</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>송금이 천천히 고개를 돌린다. 눈이 텅 비어 있다. 살아있지만, 돌아오지 않았다.</t>
+          <t>감응이 흔들린다. 이해심이 비틀거리며 무너진다. 문은 반쯤 열린 채 억지로 닫힌다. 닫히는 마지막 순간까지 콧노래는 한 사람의 이름을 놓치지 않으려는 것처럼 떨린다. 누군가를 완전히 데려오진 못해도, 끝내 사람 쪽으로 당겨 두려는 힘만은 남는다.</t>
         </is>
       </c>
       <c r="O299" t="inlineStr">
@@ -26900,36 +27199,21 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>4</v>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>Songsoon</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>Uneasy</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>Speaker</t>
+        <v>3</v>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>FlashDark</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>(언니를 껴안는다. 언니는 반응이 없다)</t>
+          <t>송금이 천천히 고개를 돌린다. 눈이 텅 비어 있다. 살아있지만, 돌아오지 않았다.</t>
         </is>
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -26940,21 +27224,21 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Tense</t>
+          <t>Uneasy</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -26964,12 +27248,12 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>돌아온 게 아니군요. 여기까지 와서도 사람 대신 빈자리만 안고 나오게 될 줄은…. 참으로 지독합니다.</t>
+          <t>(언니를 껴안는다. 언니는 반응이 없다)</t>
         </is>
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -26980,21 +27264,21 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>Yuu</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Uneasy</t>
+          <t>Tense</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -27004,17 +27288,12 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>그래도 언니 이름이 아주 끊기진 않았어요. 아주 잠깐이라도, 나를 알아본 쪽이 있었어요. 그걸로 끝까지 붙들 거예요.</t>
+          <t>돌아온 게 아니군요. 여기까지 와서도 사람 대신 빈자리만 안고 나오게 될 줄은…. 참으로 지독합니다.</t>
         </is>
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="P302" t="inlineStr">
-        <is>
-          <t>CG_Threshold_TrustedSongsoon</t>
+          <t>thought</t>
         </is>
       </c>
     </row>
@@ -27025,21 +27304,21 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Tense</t>
+          <t>Uneasy</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -27049,17 +27328,17 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>문턱에서부터 귀에 박힌 저 소리가 아직 남아 있습니다. 저쪽이 우리 안에 남긴 흔적이겠지요. 그러니 더더욱, 오늘 밤을 없던 일로 둘 순 없습니다.</t>
+          <t>그래도 언니 이름이 아주 끊기진 않았어요. 아주 잠깐이라도, 나를 알아본 쪽이 있었어요. 그걸로 끝까지 붙들 거예요.</t>
         </is>
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="P303" t="inlineStr">
         <is>
-          <t>CG_Threshold_Resonance2</t>
+          <t>CG_Threshold_TrustedSongsoon</t>
         </is>
       </c>
     </row>
@@ -27070,21 +27349,21 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>Yuu</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Uneasy</t>
+          <t>Tense</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -27094,12 +27373,17 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>데려오지 못해도 붙들 수는 있어요. 언니가 사라진 자리를, 내가 끝까지 놓지 않을 거예요.</t>
+          <t>문턱에서부터 귀에 박힌 저 소리가 아직 남아 있습니다. 저쪽이 우리 안에 남긴 흔적이겠지요. 그러니 더더욱, 오늘 밤을 없던 일로 둘 순 없습니다.</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>thought</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>CG_Threshold_Resonance2</t>
         </is>
       </c>
     </row>
@@ -27110,21 +27394,21 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Tense</t>
+          <t>Uneasy</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -27134,17 +27418,12 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>그래도 이제는 압니다. 누가 사람을 불러냈고, 누구를 순서 안에 밀어 넣었는지. 이름을 되찾지 못해도, 책임의 결만큼은 흐리지 않겠습니다.</t>
+          <t>데려오지 못해도 붙들 수는 있어요. 언니가 사라진 자리를, 내가 끝까지 놓지 않을 거예요.</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>thought</t>
-        </is>
-      </c>
-      <c r="P305" t="inlineStr">
-        <is>
-          <t>CG_Branch_SolvedMid</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -27155,7 +27434,7 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -27179,7 +27458,7 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>적어도 이 의식이 어떻게 짜였는지는 이제 분명합니다. 오늘 밤을 막연한 재앙 하나로 넘기진 않겠습니다. 누가 판을 깔았는지도 함께 남길 겁니다.</t>
+          <t>그래도 이제는 압니다. 누가 사람을 불러냈고, 누구를 순서 안에 밀어 넣었는지. 이름을 되찾지 못해도, 책임의 결만큼은 흐리지 않겠습니다.</t>
         </is>
       </c>
       <c r="O306" t="inlineStr">
@@ -27189,32 +27468,52 @@
       </c>
       <c r="P306" t="inlineStr">
         <is>
-          <t>CG_Branch_MatchedPattern</t>
+          <t>CG_Branch_SolvedMid</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="B307" t="inlineStr">
         <is>
-          <t>ch6_ending_b</t>
+          <t>ch6_ending_a</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>기사가 짧은 화재 소식으로 지면에 실리고도, 그날 밤 벌어진 일은 따로 적어 두지 않고는 넘길 수 없었다. 유웅룡은 그 순간을 다시 떠올린다.</t>
+          <t>적어도 이 의식이 어떻게 짜였는지는 이제 분명합니다. 오늘 밤을 막연한 재앙 하나로 넘기진 않겠습니다. 누가 판을 깔았는지도 함께 남길 겁니다.</t>
         </is>
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>thought</t>
         </is>
       </c>
       <c r="P307" t="inlineStr">
         <is>
-          <t>CG_Epilogue_NotExposed</t>
+          <t>CG_Branch_MatchedPattern</t>
         </is>
       </c>
     </row>
@@ -27225,16 +27524,21 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>유웅룡이 이해심을 향해 달려든다. 짧은 충돌. 이해심이 쓰러지고 의식의 결이 끊긴다. 사람 몸으로 겨우 멈춘 의식은 끝내 아름답지도 장엄하지도 않다. 그저 비싼 대가를 치른 범죄 현장처럼 남는다. 대신 이번엔 누가 무엇을 했는지 적을 문장만은 남았다.</t>
+          <t>기사가 짧은 화재 소식으로 지면에 실리고도, 그날 밤 벌어진 일은 따로 적어 두지 않고는 넘길 수 없었다. 유웅룡은 그 순간을 다시 떠올린다.</t>
         </is>
       </c>
       <c r="O308" t="inlineStr">
         <is>
           <t>narration</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>CG_Epilogue_NotExposed</t>
         </is>
       </c>
     </row>
@@ -27245,16 +27549,11 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>2</v>
-      </c>
-      <c r="K309" t="inlineStr">
-        <is>
-          <t>Fade</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>문이 닫힌다. 노래가 멎는다. 송금은 그 자리에 쓰러진다. 숨은 붙어 있다. 하지만 눈을 뜨지 않는다.</t>
+          <t>유웅룡이 이해심을 향해 달려든다. 짧은 충돌. 이해심이 쓰러지고 의식의 결이 끊긴다. 사람 몸으로 겨우 멈춘 의식은 끝내 아름답지도 장엄하지도 않다. 그저 비싼 대가를 치른 범죄 현장처럼 남는다. 대신 이번엔 누가 무엇을 했는지 적을 문장만은 남았다.</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
@@ -27270,36 +27569,21 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>3</v>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>Tense</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>Speaker</t>
+        <v>2</v>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Fade</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>(수첩을 꺼낸다. 처음으로 모든 것을 적는다. 이판규, 폐공장, 낙원, 이해심, 청의동자, 그리고 두 사람의 이름. 이번엔 사건보다 이름을 먼저 쓴다.)</t>
+          <t>문이 닫힌다. 노래가 멎는다. 송금은 그 자리에 쓰러진다. 숨은 붙어 있다. 하지만 눈을 뜨지 않는다.</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -27310,7 +27594,7 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27334,7 +27618,7 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>세상이 안 믿어도 상관없습니다. 적어 두면 적어도 없던 일로는 못 넘깁니다. 이번엔 그 정도라도 해야겠습니다.</t>
+          <t>(수첩을 꺼낸다. 처음으로 모든 것을 적는다. 이판규, 폐공장, 낙원, 이해심, 청의동자, 그리고 두 사람의 이름. 이번엔 사건보다 이름을 먼저 쓴다.)</t>
         </is>
       </c>
       <c r="O311" t="inlineStr">
@@ -27350,21 +27634,21 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>Yuu</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Uneasy</t>
+          <t>Tense</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -27374,12 +27658,12 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>기록해줘요. 언니 이름도, 여기서 사라진 사람들 이름도. 누가 지워도 한 번은 남았다고 말할 수 있게.</t>
+          <t>세상이 안 믿어도 상관없습니다. 적어 두면 적어도 없던 일로는 못 넘깁니다. 이번엔 그 정도라도 해야겠습니다.</t>
         </is>
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>thought</t>
         </is>
       </c>
     </row>
@@ -27390,21 +27674,21 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Tense</t>
+          <t>Uneasy</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -27414,17 +27698,12 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>이번엔 사건부터 쓰지 않겠습니다. 이름부터 적고, 누가 그 이름을 지웠는지까지 붙여 둘 겁니다. 그 정도는, 기자란 작자도 해야지요.</t>
+          <t>기록해줘요. 언니 이름도, 여기서 사라진 사람들 이름도. 누가 지워도 한 번은 남았다고 말할 수 있게.</t>
         </is>
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>thought</t>
-        </is>
-      </c>
-      <c r="P313" t="inlineStr">
-        <is>
-          <t>CG_Room4_ReadRitual</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -27435,7 +27714,7 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -27459,7 +27738,7 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>본 사람도 조금은 문턱에 걸친 채 돌아옵니다. 그러니 더 서둘러 적어야지요. 내 안에서조차 희미해지기 전에.</t>
+          <t>이번엔 사건부터 쓰지 않겠습니다. 이름부터 적고, 누가 그 이름을 지웠는지까지 붙여 둘 겁니다. 그 정도는, 기자란 작자도 해야지요.</t>
         </is>
       </c>
       <c r="O314" t="inlineStr">
@@ -27469,7 +27748,7 @@
       </c>
       <c r="P314" t="inlineStr">
         <is>
-          <t>CG_Threshold_Resonance2</t>
+          <t>CG_Room4_ReadRitual</t>
         </is>
       </c>
     </row>
@@ -27480,21 +27759,21 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>Yuu</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Uneasy</t>
+          <t>Tense</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -27504,17 +27783,17 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>그 수첩엔 언니 이름을 제일 먼저 적어줘요. 그 다음이 누구든, 언니가 맨 앞에 와야 해요.</t>
+          <t>본 사람도 조금은 문턱에 걸친 채 돌아옵니다. 그러니 더 서둘러 적어야지요. 내 안에서조차 희미해지기 전에.</t>
         </is>
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>thought</t>
         </is>
       </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>CG_Threshold_TrustedSongsoon</t>
+          <t>CG_Threshold_Resonance2</t>
         </is>
       </c>
     </row>
@@ -27525,21 +27804,21 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Tense</t>
+          <t>Uneasy</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -27549,17 +27828,17 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>이번 기록엔 빈칸이 덜 남을 겁니다. 불려간 사람과 지워진 사람, 판을 짠 자의 이름까지 서로 이어졌으니, 적어도 누가 무엇을 덮으려 했는지는 똑똑히 남길 수 있습니다.</t>
+          <t>그 수첩엔 언니 이름을 제일 먼저 적어줘요. 그 다음이 누구든, 언니가 맨 앞에 와야 해요.</t>
         </is>
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="P316" t="inlineStr">
         <is>
-          <t>CG_Branch_SolvedMid</t>
+          <t>CG_Threshold_TrustedSongsoon</t>
         </is>
       </c>
     </row>
@@ -27570,46 +27849,66 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>기사는 그 주 목요일 석간에 실렸다. 제목은 없었다. 이름이 먼저였고, 날짜가 그 다음이었다. 사람들은 읽었고, 일부는 오려두었다.</t>
+          <t>이번 기록엔 빈칸이 덜 남을 겁니다. 불려간 사람과 지워진 사람, 판을 짠 자의 이름까지 서로 이어졌으니, 적어도 누가 무엇을 덮으려 했는지는 똑똑히 남길 수 있습니다.</t>
         </is>
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>thought</t>
         </is>
       </c>
       <c r="P317" t="inlineStr">
         <is>
-          <t>CG_EndingB_ErodedRecord</t>
+          <t>CG_Branch_SolvedMid</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="B318" t="inlineStr">
         <is>
-          <t>ch6_ending_c</t>
+          <t>ch6_ending_b</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>1</v>
-      </c>
-      <c r="K318" t="inlineStr">
-        <is>
-          <t>FlashDark</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>문이 활짝 열린다. 무엇이 나왔는지 보이지 않는다. 공간 전체가 잠시 정지한다. 소리가 없다. 빛이 없다. 보는 쪽이 먼저 멈춘 건지, 세상이 먼저 숨을 죽인 건지도 알 수 없다.</t>
+          <t>기사는 그 주 목요일 석간에 실렸다. 제목은 없었다. 이름이 먼저였고, 날짜가 그 다음이었다. 사람들은 읽었고, 일부는 오려두었다.</t>
         </is>
       </c>
       <c r="O318" t="inlineStr">
         <is>
           <t>narration</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>CG_EndingB_ErodedRecord</t>
         </is>
       </c>
     </row>
@@ -27620,11 +27919,16 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>FlashDark</t>
+        </is>
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>다시 현실로 돌아왔을 때 — 이해심도, 송금도, 천용해도 없다. 유웅룡과 송순만 남아 있다.</t>
+          <t>문이 활짝 열린다. 무엇이 나왔는지 보이지 않는다. 공간 전체가 잠시 정지한다. 소리가 없다. 빛이 없다. 보는 쪽이 먼저 멈춘 건지, 세상이 먼저 숨을 죽인 건지도 알 수 없다.</t>
         </is>
       </c>
       <c r="O319" t="inlineStr">
@@ -27640,36 +27944,16 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>3</v>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>…무엇이 나온 걸까요.</t>
+          <t>다시 현실로 돌아왔을 때 — 이해심도, 송금도, 천용해도 없다. 유웅룡과 송순만 남아 있다.</t>
         </is>
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -27680,21 +27964,21 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>Yuu</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Uneasy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -27704,7 +27988,7 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>(대답하지 않는다)</t>
+          <t>…무엇이 나온 걸까요.</t>
         </is>
       </c>
       <c r="O321" t="inlineStr">
@@ -27720,21 +28004,36 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>5</v>
-      </c>
-      <c r="K322" t="inlineStr">
-        <is>
-          <t>BlueTrace</t>
+        <v>4</v>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Songsoon</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Uneasy</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t>대답 대신, 멀리서 아주 짧은 콧노래가 한 번 더 스친다. 둘 다 그 소리를 들었는지조차 확신하지 못한다. 확신하지 못한다는 사실이 오히려 더 오래 남는다. 아무것도 택하지 못했던 순간의 공백이, 이후의 모든 밤에 질문처럼 달라붙는다.</t>
+          <t>(대답하지 않는다)</t>
         </is>
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -27745,36 +28044,21 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>6</v>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>Tense</t>
-        </is>
-      </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>Speaker</t>
+        <v>5</v>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>BlueTrace</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t>이걸 보고도, 제가 전처럼 문장을 접어 둘 수 있을까요.</t>
+          <t>대답 대신, 멀리서 아주 짧은 콧노래가 한 번 더 스친다. 둘 다 그 소리를 들었는지조차 확신하지 못한다. 확신하지 못한다는 사실이 오히려 더 오래 남는다. 아무것도 택하지 못했던 순간의 공백이, 이후의 모든 밤에 질문처럼 달라붙는다.</t>
         </is>
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -27785,21 +28069,21 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>Yuu</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Uneasy</t>
+          <t>Tense</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -27809,12 +28093,12 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t>…모른 체는 할 수 있어도, 잊을 수는 없을 거예요.</t>
+          <t>이걸 보고도, 제가 전처럼 문장을 접어 둘 수 있을까요.</t>
         </is>
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>thought</t>
         </is>
       </c>
     </row>
@@ -27825,21 +28109,36 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Songsoon</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Uneasy</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t>질문을 끝까지 밀고 간 사람만이 남는 침묵도 있다. 두 사람은 아무 결론도 얻지 못했는데, 그래서 오히려 더 오래 그날 밤에서 벗어나지 못한다.</t>
+          <t>…모른 체는 할 수 있어도, 잊을 수는 없을 거예요.</t>
         </is>
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>narration</t>
-        </is>
-      </c>
-      <c r="P325" t="inlineStr">
-        <is>
-          <t>CG_Threshold_Investigation3</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -27875,101 +28174,106 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>10</v>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>Tense</t>
-        </is>
-      </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
+        <v>11</v>
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t>답을 얻진 못했어도, 질문까지 잃어버리진 않았군요. 아마 그게 오늘 밤 남은 전부겠지.</t>
+          <t>붙들었던 질문 대부분을 풀고도 이 밤이 이렇게 끝났다는 사실이 오히려 더 잔인하다. 답을 잃은 것이 아니라, 답을 알았는데도 사람을 다 구하지 못했다는 감각이 오래 남는다.</t>
         </is>
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>narration</t>
         </is>
       </c>
       <c r="P327" t="inlineStr">
         <is>
-          <t>CG_Threshold_Investigation3</t>
+          <t>CG_Branch_SolvedMid</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="B328" t="inlineStr">
         <is>
-          <t>ch6_ending_c</t>
+          <t>ch6_ending_c_answer</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>FlashDark</t>
+        </is>
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t>붙들었던 질문 대부분을 풀고도 이 밤이 이렇게 끝났다는 사실이 오히려 더 잔인하다. 답을 잃은 것이 아니라, 답을 알았는데도 사람을 다 구하지 못했다는 감각이 오래 남는다.</t>
+          <t>대답을 골랐지만, 송금의 노래는 끝내 사람의 목소리로 돌아오지 않는다. 제단은 이름 하나를 더 삼킨 채 고요해진다.</t>
         </is>
       </c>
       <c r="O328" t="inlineStr">
         <is>
           <t>narration</t>
-        </is>
-      </c>
-      <c r="P328" t="inlineStr">
-        <is>
-          <t>CG_Branch_SolvedMid</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="B329" t="inlineStr">
         <is>
-          <t>ch6_epilogue</t>
+          <t>ch6_ending_c_answer</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t>며칠 뒤, 경성. 난향일보에는 짧은 기사 한 토막만 실렸다.</t>
+          <t>그래도 맞는 말을 했다고 생각했는데요.</t>
         </is>
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>thought</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="B330" t="inlineStr">
         <is>
-          <t>ch6_epilogue</t>
+          <t>ch6_ending_c_block</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>FlashDark</t>
+        </is>
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t>"낙원 화재로 인한 건물 일부 소실. 인명 피해 없음."</t>
+          <t>제단을 끊으려 했지만, 오래 준비된 순서는 손 하나로 멎지 않는다. 이해심의 노래가 더 깊은 곳으로 가라앉는다.</t>
         </is>
       </c>
       <c r="O330" t="inlineStr">
@@ -27981,35 +28285,60 @@
     <row r="331">
       <c r="B331" t="inlineStr">
         <is>
-          <t>ch6_epilogue</t>
+          <t>ch6_ending_c_block</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t>유웅룡의 이름은 없다. 편집장이 그 짧은 기사를 내려다보며 담배를 문다. 표정이 없다. 표정이 없다는 사실이 오히려 오래 남는다.</t>
+          <t>이번엔 막으려 했어요. 그런데 무엇을 끊어야 하는지도 늦게 알았습니다.</t>
         </is>
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>thought</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="B332" t="inlineStr">
         <is>
-          <t>ch6_epilogue</t>
+          <t>ch6_ending_c_record</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>BlueTrace</t>
+        </is>
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t>기사 한 토막으로는 아무것도 끝나지 않는다. 다만 누군가는 사람을 붙들려 했고, 누군가는 몸으로 막으려 했고, 누군가는 끝내 그 밤을 설명하지 못한 채 남았다. 그 차이는 기록보다 오래 사람들 안에 남는다.</t>
+          <t>유웅룡은 수첩을 펼치지만, 이름과 사건을 하나로 묶을 마지막 문장이 없다. 기록은 남았으나 누군가를 구할 만큼 단단하지 못하다.</t>
         </is>
       </c>
       <c r="O332" t="inlineStr">
@@ -28021,20 +28350,40 @@
     <row r="333">
       <c r="B333" t="inlineStr">
         <is>
-          <t>ch6_epilogue</t>
+          <t>ch6_ending_c_record</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t>기사는 짧고, 도시의 밤은 평소와 다르지 않다. 전차는 달리고, 사람들은 다음 날을 준비한다. 아무 일도 없었던 것처럼.</t>
+          <t>이름은 적었지만, 누가 왜 사라졌는지는 끝내 증명하지 못했습니다.</t>
         </is>
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>thought</t>
         </is>
       </c>
     </row>
@@ -28045,21 +28394,16 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t>하지만 유웅룡의 수첩 안쪽에는 짧지 않은 이름과 문장들이 남는다. 불려간 자, 지워진 자, 판을 짠 자에 대한 메모는 기사보다 길고, 불에 타지 않은 질문처럼 끝내 접히지 않는다.</t>
+          <t>며칠 뒤, 경성. 난향일보에는 짧은 기사 한 토막만 실렸다.</t>
         </is>
       </c>
       <c r="O334" t="inlineStr">
         <is>
           <t>narration</t>
-        </is>
-      </c>
-      <c r="P334" t="inlineStr">
-        <is>
-          <t>CG_Branch_SolvedMid</t>
         </is>
       </c>
     </row>
@@ -28070,11 +28414,11 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t>그날 밤 문은 분명 흔들렸다. 그 틈으로 무엇이 새어 나왔는지는 아무도 모른다. 그리고 아무도 묻지 않는다. 도시는 늘 그래왔듯, 감당 못 할 대답 앞에서 질문부터 접어버린다.</t>
+          <t>"낙원 화재로 인한 건물 일부 소실. 인명 피해 없음."</t>
         </is>
       </c>
       <c r="O335" t="inlineStr">
@@ -28090,11 +28434,11 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t>묻지 않는다는 건 모른다는 뜻이 아니다. 대답을 감당할 수 없어서 외면하는 쪽에 가깝다.</t>
+          <t>유웅룡의 이름은 없다. 편집장이 그 짧은 기사를 내려다보며 담배를 문다. 표정이 없다. 표정이 없다는 사실이 오히려 오래 남는다.</t>
         </is>
       </c>
       <c r="O336" t="inlineStr">
@@ -28110,21 +28454,16 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t>그래도 어딘가엔 적힌 이름이 남는다. 누군가가 접지 않고 버틴 문장, 끝내 모른 체하지 않겠다고 버틴 사람 덕분에.</t>
+          <t>기사는 짧고, 도시의 밤은 평소와 다르지 않다. 전차는 달리고, 사람들은 다음 날을 준비한다. 아무 일도 없었던 것처럼.</t>
         </is>
       </c>
       <c r="O337" t="inlineStr">
         <is>
           <t>narration</t>
-        </is>
-      </c>
-      <c r="P337" t="inlineStr">
-        <is>
-          <t>CG_Room4_ReadRitual</t>
         </is>
       </c>
     </row>
@@ -28135,11 +28474,11 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t>그리고 어떤 밤은, 끝내 누군가의 말을 믿어 준 일 하나로 모양이 달라지기도 한다. 경성에선 그런 일이 기사보다 드물다.</t>
+          <t>하지만 유웅룡의 수첩 안쪽에는 짧지 않은 이름과 문장들이 남는다. 불려간 자, 지워진 자, 판을 짠 자에 대한 메모는 기사보다 길고, 불에 타지 않은 질문처럼 끝내 접히지 않는다.</t>
         </is>
       </c>
       <c r="O338" t="inlineStr">
@@ -28149,7 +28488,7 @@
       </c>
       <c r="P338" t="inlineStr">
         <is>
-          <t>CG_Threshold_TrustedSongsoon</t>
+          <t>CG_Branch_SolvedMid</t>
         </is>
       </c>
     </row>
@@ -28160,11 +28499,11 @@
         </is>
       </c>
       <c r="C339" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t>도시 한복판에서는 아무 일도 없었던 것처럼 전차 종이 울린다. 그러나 어떤 이름들은 한 번 적힌 뒤부터, 비록 신문에 나지 않아도 쉽게 다시 지워지지 않는다.</t>
+          <t>그래도 어딘가엔 적힌 이름이 남는다. 누군가가 접지 않고 버틴 문장, 끝내 모른 체하지 않겠다고 버틴 사람 덕분에.</t>
         </is>
       </c>
       <c r="O339" t="inlineStr">
@@ -28174,7 +28513,7 @@
       </c>
       <c r="P339" t="inlineStr">
         <is>
-          <t>CG_Threshold_Investigation3</t>
+          <t>CG_Room4_ReadRitual</t>
         </is>
       </c>
     </row>
@@ -28284,7 +28623,7 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t>노래와 비명, 주문과 숨소리가 한순간 서로를 덮어쓴다. 의식은 흔들리기 시작하지만, 아직 어느 쪽으로 기울지 정해지지 않았다. 이 방에 남은 것은 힘겨루기가 아니라, 끝내 무엇을 사람으로 남길 것인가의 문제다.</t>
+          <t>노래와 비명이 맞부딪치며 의식이 흔들린다. 이제 남은 문제는 무엇을 사람으로 남길 것인가다.</t>
         </is>
       </c>
       <c r="O344" t="inlineStr">
@@ -28300,16 +28639,21 @@
         </is>
       </c>
       <c r="C345" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t>방금의 선택은 이미 대가를 만들고 있다. 부른 이름이든, 던진 몸이든, 놓친 한 박자든 — 이 방은 그 차이를 잊지 않고 그대로 되돌려 준다.</t>
+          <t>이판규를 부른 손과 송금을 밀어 넣은 순서, 의식의 구조가 한 문장으로 겹친다. 이제 망설임도 변명이 되기 어렵다.</t>
         </is>
       </c>
       <c r="O345" t="inlineStr">
         <is>
           <t>narration</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>CG_Outcome_SolvedMid</t>
         </is>
       </c>
     </row>
@@ -28320,11 +28664,11 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t>질문을 끝까지 붙들어 온 사람만이 보이는 결도 있다. 이판규를 부른 손, 송금을 밀어 넣은 순서, 의식을 떠받친 구조가 한꺼번에 겹치며, 이제는 망설임조차 변명으로 쓰기 어려워진다.</t>
+          <t>미친 넋두리, 자발적 도피, 우발적 광신. 편한 거짓말을 부순 뒤에는 무엇을 택하든 책임만 남는다.</t>
         </is>
       </c>
       <c r="O346" t="inlineStr">
@@ -28334,32 +28678,47 @@
       </c>
       <c r="P346" t="inlineStr">
         <is>
-          <t>CG_Outcome_SolvedMid</t>
+          <t>CG_RitualScene_SolvedHigh</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="B347" t="inlineStr">
         <is>
-          <t>ch6_outcome</t>
+          <t>ch6_path_a</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Songsoon</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Uneasy</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t>그중 몇몇은 아예 거짓말의 모양으로 남아 있었다. 미친 넋두리, 자발적 도피, 우발적 광신. 여기까지 오며 그 편한 설명들을 하나씩 부순 사람에겐 이제 무엇을 택하든 변명할 자리가 더 좁다.</t>
+          <t>언니… 들리죠? 나예요. 그 방 앞에서도, 창고에서도… 계속 듣고 있었어요. 이제 모른 척 안 할 거예요.</t>
         </is>
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t>narration</t>
-        </is>
-      </c>
-      <c r="P347" t="inlineStr">
-        <is>
-          <t>CG_RitualScene_SolvedHigh</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -28370,51 +28729,31 @@
         </is>
       </c>
       <c r="C348" t="n">
-        <v>1</v>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>Songsoon</t>
-        </is>
-      </c>
-      <c r="E348" t="inlineStr">
-        <is>
-          <t>Uneasy</t>
-        </is>
-      </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t>언니… 들리죠? 나예요. 그 방 앞에서도, 창고에서도… 계속 듣고 있었어요. 이제 모른 척 안 할 거예요.</t>
+          <t>송순의 목소리가 콧노래와 겹쳐지며 방 안 공기의 결이 미세하게 바뀐다. 처음으로 의식 한가운데 사람 체온이 끼어든다. 구해 내려는 이름 하나가 제단의 질서를 비틀기 시작한다.</t>
         </is>
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="B349" t="inlineStr">
         <is>
-          <t>ch6_path_a</t>
+          <t>ch6_path_a2</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t>송순의 목소리가 콧노래와 겹쳐지며 방 안 공기의 결이 미세하게 바뀐다. 처음으로 의식 한가운데 사람 체온이 끼어든다. 구해 내려는 이름 하나가 제단의 질서를 비틀기 시작한다.</t>
+          <t>송금의 노래가 잠깐 흔들린다. 살아 있는 사람의 목소리가 아니라, 아주 오래된 기억이 잠시 되돌아오는 것처럼. 그러나 돌아오는 건 사람 전체가 아니라, 아직 이름이 남아 있는 한 조각뿐이다.</t>
         </is>
       </c>
       <c r="O349" t="inlineStr">
@@ -28430,16 +28769,21 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t>송금의 노래가 잠깐 흔들린다. 살아 있는 사람의 목소리가 아니라, 아주 오래된 기억이 잠시 되돌아오는 것처럼. 그러나 돌아오는 건 사람 전체가 아니라, 아직 이름이 남아 있는 한 조각뿐이다.</t>
+          <t>송순이 끝내 손을 놓지 않았던 태도와, 무서운 소리를 헛것이라 치워 버리지 않았던 믿음이 마지막 실처럼 남아 의식을 흔든다.</t>
         </is>
       </c>
       <c r="O350" t="inlineStr">
         <is>
           <t>narration</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>CG_Threshold_TrustedSongsoon</t>
         </is>
       </c>
     </row>
@@ -28450,11 +28794,11 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t>송순이 끝내 손을 놓지 않았던 태도와, 무서운 소리를 헛것이라 치워 버리지 않았던 믿음이 마지막 실처럼 남아 의식을 흔든다.</t>
+          <t>붙들어 온 질문 셋 중 둘 이상이 이 순간에서 하나로 묶인다. 누구를 불렀는지, 누구를 밀어 넣었는지, 누가 판을 짰는지까지 알았기에 송순의 부름도 허공에 흩어지지 않는다.</t>
         </is>
       </c>
       <c r="O351" t="inlineStr">
@@ -28464,7 +28808,7 @@
       </c>
       <c r="P351" t="inlineStr">
         <is>
-          <t>CG_Threshold_TrustedSongsoon</t>
+          <t>CG_Branch_SolvedMid</t>
         </is>
       </c>
     </row>
@@ -28475,11 +28819,11 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t>문 앞에서부터 얽혀 든 콧노래의 결이 이 순간 송순의 목소리와 포개진다. 파멸에 더 가까이 다가섰기에, 되레 무엇을 붙들어야 하는지도 더 선명하게 보인다.</t>
+          <t>가면의 눈과 제단 문양이 어떻게 맞물렸는지까지 짚고 들어왔기에, 두 사람이 지금 끊어 낸 것이 막연한 공포가 아니라 짜여진 의식의 한 축이었다는 사실이 더 분명하게 남는다.</t>
         </is>
       </c>
       <c r="O352" t="inlineStr">
@@ -28489,57 +28833,67 @@
       </c>
       <c r="P352" t="inlineStr">
         <is>
-          <t>CG_Threshold_Resonance2</t>
+          <t>CG_Branch_MatchedPattern</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="B353" t="inlineStr">
         <is>
-          <t>ch6_path_a2</t>
+          <t>ch6_path_b</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t>붙들어 온 질문 셋 중 둘 이상이 이 순간에서 하나로 묶인다. 누구를 불렀는지, 누구를 밀어 넣었는지, 누가 판을 짰는지까지 알았기에 송순의 부름도 허공에 흩어지지 않는다.</t>
+          <t>이게 처음이 아니라는 걸 알았으니, 이번엔 기록보다 먼저 이 순서를 끊어야 한다.</t>
         </is>
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t>narration</t>
-        </is>
-      </c>
-      <c r="P353" t="inlineStr">
-        <is>
-          <t>CG_Branch_SolvedMid</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="B354" t="inlineStr">
         <is>
-          <t>ch6_path_a2</t>
+          <t>ch6_path_b</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>가면의 눈과 제단 문양이 어떻게 맞물렸는지까지 짚고 들어왔기에, 두 사람이 지금 끊어 낸 것이 막연한 공포가 아니라 짜여진 의식의 한 축이었다는 사실이 더 분명하게 남는다.</t>
+          <t>유웅룡은 이해심을 향해 달려간다. 제단의 순서가 한 사람을 더 삼키기 전에, 이번에는 몸으로 그 연결을 끊는다.</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
         <is>
           <t>narration</t>
-        </is>
-      </c>
-      <c r="P354" t="inlineStr">
-        <is>
-          <t>CG_Branch_MatchedPattern</t>
         </is>
       </c>
     </row>
@@ -28550,7 +28904,7 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -28559,7 +28913,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Tense</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -28574,12 +28928,17 @@
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t>이게 처음이 아니라는 걸 알고 물러서면, 나도 저 기사 밑줄 긋고 접어 둔 사람들과 다를 게 없지.</t>
+          <t>지금 막지 못하면, 다음 기록도 누군가의 사후 진술일 뿐이야.</t>
         </is>
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>thought</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>CG_Branch_FoundOldArticles</t>
         </is>
       </c>
     </row>
@@ -28590,16 +28949,41 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t>유웅룡은 이해심을 향해 달려가며, 지난 기사들에서 지워진 문장들을 머릿속으로 되짚는다. 덮인 문장이 많을수록, 이번엔 몸으로라도 그 빈칸을 메워야 한다고 느낀다. 기록자의 결단이 처음으로 육탄이 된다.</t>
+          <t>이판규를 미친놈 하나로 접어 두려던 판도 여기서 끝입니다. 불려간 자의 말이 헛소리가 아니었다면, 지금 저 안의 일 역시 우발이 아니라 누군가의 계산이겠지요.</t>
         </is>
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>thought</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>CG_Outcome_QMadness</t>
         </is>
       </c>
     </row>
@@ -28610,21 +28994,21 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Tense</t>
+          <t>Afraid</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
@@ -28634,107 +29018,62 @@
       </c>
       <c r="N357" t="inlineStr">
         <is>
-          <t>접힌 기록을 또 하나 만들 바엔, 차라리 여기서 같이 부서지는 편이 낫지.</t>
+          <t>언니가 달아난 게 아니라 붙들린 거라면, 여기서도 같은 말로 덮이게 둘 순 없어요. 사라진 사람이 먼저 도망쳤다고, 또 그렇게 몰아갈 테니까요.</t>
         </is>
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="P357" t="inlineStr">
         <is>
-          <t>CG_Branch_FoundOldArticles</t>
+          <t>CG_Outcome_QRunaway</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="B358" t="inlineStr">
         <is>
-          <t>ch6_path_b</t>
+          <t>ch6_path_b2</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>11</v>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E358" t="inlineStr">
-        <is>
-          <t>Tense</t>
-        </is>
-      </c>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t>이판규를 미친놈 하나로 접어 두려던 판도 여기서 끝입니다. 불려간 자의 말이 헛소리가 아니었다면, 지금 저 안의 일 역시 우발이 아니라 누군가의 계산이겠지요.</t>
+          <t>이 깊이까지는 아무도 끼어들지 못한다. 이 선택의 결과는 오롯이 두 사람과 의식의 중심에 남는다. 도움이 닿지 않는 자리의 대가이기도 하고, 방해받지 않고 끝까지 본 대가이기도 하다.</t>
         </is>
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t>thought</t>
-        </is>
-      </c>
-      <c r="P358" t="inlineStr">
-        <is>
-          <t>CG_Outcome_QMadness</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="B359" t="inlineStr">
         <is>
-          <t>ch6_path_b</t>
+          <t>ch6_path_b2</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>12</v>
-      </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>Songsoon</t>
-        </is>
-      </c>
-      <c r="E359" t="inlineStr">
-        <is>
-          <t>Afraid</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="N359" t="inlineStr">
         <is>
-          <t>언니가 달아난 게 아니라 붙들린 거라면, 여기서도 같은 말로 덮이게 둘 순 없어요. 사라진 사람이 먼저 도망쳤다고, 또 그렇게 몰아갈 테니까요.</t>
+          <t>유웅룡이 창고에서 끝까지 읽어 낸 악보와, 자료실에서 주워 온 낡은 기사 조각들이 여기서 하나의 문장으로 겹친다. 흩어져 있던 것들이 이제는 적어 남길 수 있는 증거가 된다.</t>
         </is>
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>narration</t>
         </is>
       </c>
       <c r="P359" t="inlineStr">
         <is>
-          <t>CG_Outcome_QRunaway</t>
+          <t>CG_Room4_ReadRitual</t>
         </is>
       </c>
     </row>
@@ -28745,16 +29084,21 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t>이 깊이까지는 아무도 끼어들지 못한다. 이 선택의 결과는 오롯이 두 사람과 의식의 중심에 남는다. 도움이 닿지 않는 자리의 대가이기도 하고, 방해받지 않고 끝까지 본 대가이기도 하다.</t>
+          <t>질문을 끝까지 밀고 와서야, 기록해야 할 문장의 순서도 달라진다. 이판규와 송금, 의식의 설계자까지 하나의 구조로 꿰어졌기에 이번 기록은 더는 단편 기사로 무너지지 않는다.</t>
         </is>
       </c>
       <c r="O360" t="inlineStr">
         <is>
           <t>narration</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>CG_Branch_SolvedMid</t>
         </is>
       </c>
     </row>
@@ -28765,11 +29109,11 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N361" t="inlineStr">
         <is>
-          <t>유웅룡이 창고에서 끝까지 읽어 낸 악보와, 자료실에서 주워 온 낡은 기사 조각들이 여기서 하나의 문장으로 겹친다. 흩어져 있던 것들이 이제는 적어 남길 수 있는 증거가 된다.</t>
+          <t>자료실에서 이어 붙인 문장과 제단 앞에서 들이민 반박까지 겹치자, 남길 기록은 추측보다 고발문에 가까워진다. 누가 어떤 거짓말로 사람을 밀어 넣었는지까지 적을 자리가 생긴다.</t>
         </is>
       </c>
       <c r="O361" t="inlineStr">
@@ -28779,7 +29123,7 @@
       </c>
       <c r="P361" t="inlineStr">
         <is>
-          <t>CG_Room4_ReadRitual</t>
+          <t>CG_Branch_ExposedArchivePattern</t>
         </is>
       </c>
     </row>
@@ -28790,11 +29134,11 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N362" t="inlineStr">
         <is>
-          <t>콧노래가 아직 귓가에서 가시지 않는다. 유웅룡은 자신 또한 저 문턱에서 아주 비켜 선 목격자만은 아니게 되었다는 사실을 안다. 그래서 더더욱, 본 자의 이름으로 적어 두어야 한다.</t>
+          <t>마지막 제단 앞에서 거짓말의 모양을 직접 들이민 탓에, 이제는 우발이었다는 말로도 이 밤을 봉합하기 어렵다. 남길 문장 자체가 한층 더 날카로워진다.</t>
         </is>
       </c>
       <c r="O362" t="inlineStr">
@@ -28804,82 +29148,92 @@
       </c>
       <c r="P362" t="inlineStr">
         <is>
-          <t>CG_Threshold_Resonance2</t>
+          <t>CG_Branch_ExposedTruthAtRitual</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="B363" t="inlineStr">
         <is>
-          <t>ch6_path_b2</t>
+          <t>ch6_path_record</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N363" t="inlineStr">
         <is>
-          <t>질문을 끝까지 밀고 와서야, 기록해야 할 문장의 순서도 달라진다. 이판규와 송금, 의식의 설계자까지 하나의 구조로 꿰어졌기에 이번 기록은 더는 단편 기사로 무너지지 않는다.</t>
+          <t>제단이 흔들리는 동안에도 유웅룡의 수첩에는 이름과 순번이 남는다. 누구도 완전히 구하지 못한 밤이지만, 다음 사람이 같은 거짓말로 사라지지 않게 할 증언은 만들어졌다.</t>
         </is>
       </c>
       <c r="O363" t="inlineStr">
         <is>
           <t>narration</t>
-        </is>
-      </c>
-      <c r="P363" t="inlineStr">
-        <is>
-          <t>CG_Branch_SolvedMid</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="B364" t="inlineStr">
         <is>
-          <t>ch6_path_b2</t>
+          <t>ch6_path_record</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="N364" t="inlineStr">
         <is>
-          <t>자료실에서 이어 붙인 문장과 제단 앞에서 들이민 반박까지 겹치자, 남길 기록은 추측보다 고발문에 가까워진다. 누가 어떤 거짓말로 사람을 밀어 넣었는지까지 적을 자리가 생긴다.</t>
+          <t>송순 씨, 언니 이름은 맨 위에 적었습니다. 나머지도 끝까지 적겠습니다.</t>
         </is>
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t>narration</t>
-        </is>
-      </c>
-      <c r="P364" t="inlineStr">
-        <is>
-          <t>CG_Branch_ExposedArchivePattern</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="B365" t="inlineStr">
         <is>
-          <t>ch6_path_b2</t>
+          <t>ch6_ritual_scene</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>assets/ev/hanbok.jpeg</t>
+        </is>
       </c>
       <c r="N365" t="inlineStr">
         <is>
-          <t>마지막 제단 앞에서 거짓말의 모양을 직접 들이민 탓에, 이제는 우발이었다는 말로도 이 밤을 봉합하기 어렵다. 남길 문장 자체가 한층 더 날카로워진다.</t>
+          <t>지하 의례실 깊숙이. 이해심이 제단 앞에 선다. 송금은 청색 한복 차림으로 노래하고 있다. 표정이 없다. 살기 위해 버틴 끝에 생기는 무표정이 아니라, 지나치게 오래 빌려 쓰여 자기 얼굴을 잃어버린 사람의 무표정이다.</t>
         </is>
       </c>
       <c r="O365" t="inlineStr">
         <is>
           <t>narration</t>
-        </is>
-      </c>
-      <c r="P365" t="inlineStr">
-        <is>
-          <t>CG_Branch_ExposedTruthAtRitual</t>
         </is>
       </c>
     </row>
@@ -28890,7 +29244,27 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Haesim</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Trance</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Center</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
@@ -28899,12 +29273,12 @@
       </c>
       <c r="N366" t="inlineStr">
         <is>
-          <t>지하 의례실 깊숙이. 이해심이 제단 앞에 선다. 송금은 청색 한복 차림으로 노래하고 있다. 표정이 없다. 살기 위해 버틴 끝에 생기는 무표정이 아니라, 지나치게 오래 빌려 쓰여 자기 얼굴을 잃어버린 사람의 무표정이다.</t>
+          <t>어리석은 자들이여. 문이 열리는 날, 경성은 비로소 속을 드러낼 것이다. 곪은 자리는 끝내 누군가 헤집어야 한다. 나는 이제 그 일을 두려워하지 않는다.</t>
         </is>
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -28915,41 +29289,21 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>2</v>
-      </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>Haesim</t>
-        </is>
-      </c>
-      <c r="E367" t="inlineStr">
-        <is>
-          <t>Trance</t>
-        </is>
-      </c>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>Center</t>
-        </is>
-      </c>
-      <c r="G367" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
-      <c r="L367" t="inlineStr">
-        <is>
-          <t>assets/ev/hanbok.jpeg</t>
+        <v>3</v>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Flicker</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
         <is>
-          <t>어리석은 자들이여. 문이 열리는 날, 경성은 비로소 속을 드러낼 것이다. 곪은 자리는 끝내 누군가 헤집어야 한다. 나는 이제 그 일을 두려워하지 않는다.</t>
+          <t>이해심의 뒤편 어둠 속엔 흰 천으로 얼굴을 가린 남자의 형체가 희미하게 선다. 가까이 있는데도 사람이라기보다 남의 신앙을 뒤에서 빨아먹는 그늘처럼 보인다. 향냄새 밑에 눌린 비린내가 그쪽에서 더 짙다.</t>
         </is>
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -28960,22 +29314,36 @@
         </is>
       </c>
       <c r="C368" t="n">
-        <v>3</v>
-      </c>
-      <c r="K368" t="inlineStr">
-        <is>
-          <t>Flicker</t>
-        </is>
-      </c>
-      <c r="L368" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Cheonyonghae</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
       <c r="N368" t="inlineStr">
         <is>
-          <t>이해심의 뒤편 어둠 속엔 흰 천으로 얼굴을 가린 남자의 형체가 희미하게 선다. 가까이 있는데도 사람이라기보다 남의 신앙을 뒤에서 빨아먹는 그늘처럼 보인다. 향냄새 밑에 눌린 비린내가 그쪽에서 더 짙다.</t>
+          <t>교주님, 문은 오래 기다렸습니다. 주저하는 자들 소리까지 들여놓을 까닭은 없지요.</t>
         </is>
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -28986,36 +29354,26 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>4</v>
-      </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>Cheonyonghae</t>
-        </is>
-      </c>
-      <c r="E369" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F369" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G369" t="inlineStr">
-        <is>
-          <t>Speaker</t>
+        <v>5</v>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>BlueTrace</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
         <is>
-          <t>교주님, 문은 오래 기다렸습니다. 주저하는 자들 소리까지 들여놓을 까닭은 없지요.</t>
+          <t>그 순간 유웅룡의 귓속에서 문 앞 콧노래가 다시 울린다. 방 안 노래와 어긋나지 않는다. 아까 문에 귀를 댄 뒤로, 이 공간은 이미 몸 안쪽까지 파고든 듯하다.</t>
         </is>
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>CG_RitualScene_Resonance2</t>
         </is>
       </c>
     </row>
@@ -29026,26 +29384,46 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Songgeum</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Trance</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Center</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t>BlueTrace</t>
+          <t>RitualGlow</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>assets/sfx/ritual_chant.mp3</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
         <is>
-          <t>그 순간 유웅룡의 귓속에서 문 앞 콧노래가 다시 울린다. 방 안 노래와 어긋나지 않는다. 아까 문에 귀를 댄 뒤로, 이 공간은 이미 몸 안쪽까지 파고든 듯하다.</t>
+          <t>(표정 없이, 노래를 흥얼거린다) …푸른… 옷을… 입고… 문 앞에… 서서…</t>
         </is>
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t>narration</t>
-        </is>
-      </c>
-      <c r="P370" t="inlineStr">
-        <is>
-          <t>CG_RitualScene_Resonance2</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -29056,21 +29434,21 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Songgeum</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Trance</t>
+          <t>Uneasy</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -29078,19 +29456,9 @@
           <t>Speaker</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr">
-        <is>
-          <t>RitualGlow</t>
-        </is>
-      </c>
-      <c r="M371" t="inlineStr">
-        <is>
-          <t>assets/sfx/ritual_chant.mp3</t>
-        </is>
-      </c>
       <c r="N371" t="inlineStr">
         <is>
-          <t>(표정 없이, 노래를 흥얼거린다) …푸른… 옷을… 입고… 문 앞에… 서서…</t>
+          <t>언니… 언니!</t>
         </is>
       </c>
       <c r="O371" t="inlineStr">
@@ -29106,36 +29474,26 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>7</v>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>Songsoon</t>
-        </is>
-      </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>Uneasy</t>
-        </is>
-      </c>
-      <c r="F372" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="G372" t="inlineStr">
-        <is>
-          <t>Speaker</t>
+        <v>8</v>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>FlashDark</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>assets/sfx/heartbeat_low.mp3</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
         <is>
-          <t>언니… 언니!</t>
+          <t>이해심의 안대 아래로 피가 번지기 시작한다. 하나는 불빛, 하나는 서릿발. 문이 열리고 있다. 방 안 촛불이 바깥바람 없이도 같은 방향으로 눕고, 벽면의 푸른 흔적이 젖은 살처럼 미세하게 꿈틀거린다.</t>
         </is>
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -29146,26 +29504,36 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>8</v>
-      </c>
-      <c r="K373" t="inlineStr">
-        <is>
-          <t>FlashDark</t>
-        </is>
-      </c>
-      <c r="M373" t="inlineStr">
-        <is>
-          <t>assets/sfx/heartbeat_low.mp3</t>
+        <v>9</v>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Haesim</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Trance</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Center</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
         <is>
-          <t>이해심의 안대 아래로 피가 번지기 시작한다. 하나는 불빛, 하나는 서릿발. 문이 열리고 있다. 방 안 촛불이 바깥바람 없이도 같은 방향으로 눕고, 벽면의 푸른 흔적이 젖은 살처럼 미세하게 꿈틀거린다.</t>
+          <t>너희는 늦었다. 법도, 기사도, 기도도 아무도 구하지 못했다. 나라를 위한다던 자도, 백성을 입에 올리던 자도 결국 하나도 건지지 못했지. 이제 남은 건 치료가 아니라 절단이다. 잘라내지 않으면 이 도시는 끝내 썩은 피를 제 몸이라 착각한 채 죽는다.</t>
         </is>
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -29176,21 +29544,21 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Haesim</t>
+          <t>Yuu</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Trance</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
@@ -29200,7 +29568,7 @@
       </c>
       <c r="N374" t="inlineStr">
         <is>
-          <t>너희는 늦었다. 법도, 기사도, 기도도 아무도 구하지 못했다. 나라를 위한다던 자도, 백성을 입에 올리던 자도 결국 하나도 건지지 못했지. 이제 남은 건 치료가 아니라 절단이다. 잘라내지 않으면 이 도시는 끝내 썩은 피를 제 몸이라 착각한 채 죽는다.</t>
+          <t>도시는 곪은 자리를 도려낸다는 말로 사람을 버려 왔습니다. 당신도 같은 말을 되풀이하며 사람을 의식의 몫으로 셈하고 있잖습니까.</t>
         </is>
       </c>
       <c r="O374" t="inlineStr">
@@ -29216,21 +29584,21 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Haesim</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Trance</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
@@ -29240,7 +29608,7 @@
       </c>
       <c r="N375" t="inlineStr">
         <is>
-          <t>그걸 정화라 부르지 마십시오. 사람을 셈하고 갈아 넣는 짓에 이름만 고상하게 붙인 학살이잖습니까.</t>
+          <t>학살? 우습구나. 이 도시는 애당초 누군가를 갈아 넣어 움직여 왔다. 빈민가 아이도, 여급도, 병든 여자도, 나라 잃은 백성도 다 써 먹히며 사라졌지. 나는 다만 그 화덕을 휘장 뒤에 숨기지 않을 뿐이야. 너희는 덮고, 나는 드러낸다.</t>
         </is>
       </c>
       <c r="O375" t="inlineStr">
@@ -29256,7 +29624,7 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -29280,7 +29648,7 @@
       </c>
       <c r="N376" t="inlineStr">
         <is>
-          <t>학살? 우습구나. 이 도시는 애당초 누군가를 갈아 넣어 움직여 왔다. 빈민가 아이도, 여급도, 병든 여자도, 나라 잃은 백성도 다 써 먹히며 사라졌지. 나는 다만 그 화덕을 휘장 뒤에 숨기지 않을 뿐이야. 너희는 덮고, 나는 드러낸다.</t>
+          <t>구원은 온전한 자에게 오지 않는다. 다 망가진 자에게만 문이 열린다. 나는 그걸 누구보다 먼저 배웠다. 황족의 피도, 독립의 꿈도, 여자의 몸도, 병든 폐도 끝내 나를 구하지 못했으니까.</t>
         </is>
       </c>
       <c r="O376" t="inlineStr">
@@ -29296,21 +29664,21 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Haesim</t>
+          <t>Yuu</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Trance</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
@@ -29320,7 +29688,7 @@
       </c>
       <c r="N377" t="inlineStr">
         <is>
-          <t>구원은 온전한 자에게 오지 않는다. 다 망가진 자에게만 문이 열린다. 나는 그걸 누구보다 먼저 배웠다. 황족의 피도, 독립의 꿈도, 여자의 몸도, 병든 폐도 끝내 나를 구하지 못했으니까.</t>
+          <t>당신 뒤에 선 작자가 누군진 이제 알겠습니다. 구원을 입에 올리며 사람 절망을 긁어 모으는 자들 말입니다. 이름만 청의교일 뿐, 속살은 늘 같은 장삿속이군요.</t>
         </is>
       </c>
       <c r="O377" t="inlineStr">
@@ -29336,11 +29704,11 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Cheonyonghae</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -29360,7 +29728,7 @@
       </c>
       <c r="N378" t="inlineStr">
         <is>
-          <t>당신 뒤에 선 작자가 누군진 이제 알겠습니다. 구원을 입에 올리며 사람 절망을 긁어 모으는 자들 말입니다. 이름만 청의교일 뿐, 속살은 늘 같은 장삿속이군요.</t>
+          <t>장사라…. 말은 곱게도 하는군. 세상은 늘 제 죄를 그런 말로 덮지. 저들은 다만 제 몫을 냈을 뿐이야.</t>
         </is>
       </c>
       <c r="O378" t="inlineStr">
@@ -29376,21 +29744,21 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Cheonyonghae</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Uneasy</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -29398,9 +29766,14 @@
           <t>Speaker</t>
         </is>
       </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>ScreenShake</t>
+        </is>
+      </c>
       <c r="N379" t="inlineStr">
         <is>
-          <t>장사라…. 말은 곱게도 하는군. 세상은 늘 제 죄를 그런 말로 덮지. 저들은 다만 제 몫을 냈을 뿐이야.</t>
+          <t>몫이라고 부르지 마. 언니도, 없어졌던 사람들도 누구한테 바칠 몫으로 태어난 적 없어.</t>
         </is>
       </c>
       <c r="O379" t="inlineStr">
@@ -29412,45 +29785,25 @@
     <row r="380">
       <c r="B380" t="inlineStr">
         <is>
-          <t>ch6_ritual_scene</t>
+          <t>ch6_threshold</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>15</v>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>Songsoon</t>
-        </is>
-      </c>
-      <c r="E380" t="inlineStr">
-        <is>
-          <t>Uneasy</t>
-        </is>
-      </c>
-      <c r="F380" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="G380" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t>ScreenShake</t>
+          <t>Flicker</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
         <is>
-          <t>몫이라고 부르지 마. 언니도, 없어졌던 사람들도 누구한테 바칠 몫으로 태어난 적 없어.</t>
+          <t>노랫소리를 따라 마지막 문턱을 넘기 직전, 두 사람은 동시에 걸음을 멈춘다. 이제부터는 보고도 모른 척할 수 없다.</t>
         </is>
       </c>
       <c r="O380" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -29461,21 +29814,46 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>1</v>
-      </c>
-      <c r="K381" t="inlineStr">
-        <is>
-          <t>Flicker</t>
+        <v>2</v>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>SlideRight</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>Tremble</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
         <is>
-          <t>노랫소리를 따라 마지막 문턱을 넘기 직전, 두 사람은 동시에 걸음을 멈춘다. 이제부터는 보고도 모른 척할 수 없다.</t>
+          <t>지금이라도 돌아가고 싶다면 말해요. 여기서부터는 기사도, 증언도, 정의도 우리를 지켜주지 못할 겁니다.</t>
         </is>
       </c>
       <c r="O381" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -29486,21 +29864,21 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Tense</t>
+          <t>Afraid</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
@@ -29510,7 +29888,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>SlideRight</t>
+          <t>FadeIn</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
@@ -29520,7 +29898,7 @@
       </c>
       <c r="N382" t="inlineStr">
         <is>
-          <t>지금이라도 돌아가고 싶다면 말해요. 여기서부터는 기사도, 증언도, 정의도 우리를 지켜주지 못할 겁니다.</t>
+          <t>무서워요. 그런데 돌아가면 더 무서울 것 같아요. 언니를 남겨두고 살아가는 쪽이요.</t>
         </is>
       </c>
       <c r="O382" t="inlineStr">
@@ -29536,21 +29914,21 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>Yuu</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Afraid</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
@@ -29558,19 +29936,9 @@
           <t>Speaker</t>
         </is>
       </c>
-      <c r="H383" t="inlineStr">
-        <is>
-          <t>FadeIn</t>
-        </is>
-      </c>
-      <c r="J383" t="inlineStr">
-        <is>
-          <t>Tremble</t>
-        </is>
-      </c>
       <c r="N383" t="inlineStr">
         <is>
-          <t>무서워요. 그런데 돌아가면 더 무서울 것 같아요. 언니를 남겨두고 살아가는 쪽이요.</t>
+          <t>그럼 갑시다. 이번엔 끝까지 갑니다.</t>
         </is>
       </c>
       <c r="O383" t="inlineStr">
@@ -29586,7 +29954,7 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -29610,12 +29978,17 @@
       </c>
       <c r="N384" t="inlineStr">
         <is>
-          <t>그럼 갑시다. 이번엔 끝까지 갑니다.</t>
+          <t>누가 덮으라 해도, 이번엔 못 접습니다. 자료실에서 본 그 기사도 결국 여기까지 이어져 있었으니까.</t>
         </is>
       </c>
       <c r="O384" t="inlineStr">
         <is>
           <t>normal</t>
+        </is>
+      </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>CG_Threshold_FoundOldArticles</t>
         </is>
       </c>
     </row>
@@ -29626,7 +29999,7 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -29635,7 +30008,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Tense</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
@@ -29650,17 +30023,17 @@
       </c>
       <c r="N385" t="inlineStr">
         <is>
-          <t>누가 덮으라 해도, 이번엔 못 접습니다. 자료실에서 본 그 기사도 결국 여기까지 이어져 있었으니까.</t>
+          <t>그리고… 문 앞에서 들은 소리가 아직 귓속에 남아 있습니다. 저 안이 우릴 먼저 듣고 있다는 걸 알면서도 들어가는 셈이지요.</t>
         </is>
       </c>
       <c r="O385" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>thought</t>
         </is>
       </c>
       <c r="P385" t="inlineStr">
         <is>
-          <t>CG_Threshold_FoundOldArticles</t>
+          <t>CG_Threshold_Resonance2</t>
         </is>
       </c>
     </row>
@@ -29671,21 +30044,21 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Yuu</t>
+          <t>Songsoon</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Tense</t>
+          <t>Uneasy</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
@@ -29695,17 +30068,17 @@
       </c>
       <c r="N386" t="inlineStr">
         <is>
-          <t>그리고… 문 앞에서 들은 소리가 아직 귓속에 남아 있습니다. 저 안이 우릴 먼저 듣고 있다는 걸 알면서도 들어가는 셈이지요.</t>
+          <t>기자님이 내 말을 먼저 믿어 줬으니, 저도 이번엔 망설이지 않을게요. 문이 열리면, 제가 먼저 언니를 부를게요.</t>
         </is>
       </c>
       <c r="O386" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="P386" t="inlineStr">
         <is>
-          <t>CG_Threshold_Resonance2</t>
+          <t>CG_Threshold_TrustedSongsoon</t>
         </is>
       </c>
     </row>
@@ -29716,21 +30089,21 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Songsoon</t>
+          <t>Yuu</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Uneasy</t>
+          <t>Tense</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
@@ -29740,17 +30113,17 @@
       </c>
       <c r="N387" t="inlineStr">
         <is>
-          <t>기자님이 내 말을 먼저 믿어 줬으니, 저도 이번엔 망설이지 않을게요. 문이 열리면, 제가 먼저 언니를 부를게요.</t>
+          <t>자료실에서 주운 기사도, 방 안에서 읽은 기록도 결국 여기까지 밀려왔군요. 이제 남은 건 외면하지 않는 일뿐입니다.</t>
         </is>
       </c>
       <c r="O387" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>thought</t>
         </is>
       </c>
       <c r="P387" t="inlineStr">
         <is>
-          <t>CG_Threshold_TrustedSongsoon</t>
+          <t>CG_Threshold_Investigation3</t>
         </is>
       </c>
     </row>
@@ -29761,41 +30134,21 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>8</v>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E388" t="inlineStr">
-        <is>
-          <t>Tense</t>
-        </is>
-      </c>
-      <c r="F388" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G388" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="N388" t="inlineStr">
         <is>
-          <t>자료실에서 주운 기사도, 방 안에서 읽은 기록도 결국 여기까지 밀려왔군요. 이제 남은 건 외면하지 않는 일뿐입니다.</t>
+          <t>누구에게도 연락하지 않기로 한 덕에, 두 사람은 도움받을 길도 핑계 댈 길도 없이 같은 공포를 정면으로 마주 선다.</t>
         </is>
       </c>
       <c r="O388" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>narration</t>
         </is>
       </c>
       <c r="P388" t="inlineStr">
         <is>
-          <t>CG_Threshold_Investigation3</t>
+          <t>CG_Threshold_CalledEditorFalse</t>
         </is>
       </c>
     </row>
@@ -29806,21 +30159,41 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="N389" t="inlineStr">
         <is>
-          <t>누구에게도 연락하지 않기로 한 덕에, 두 사람은 도움받을 길도 핑계 댈 길도 없이 같은 공포를 정면으로 마주 선다.</t>
+          <t>의례실 바닥에서 주운 종이까지 여기로 이어집니다. 남은 건 문장으로 증명하는 일이 아니라, 저 안에서 실제로 끊어내는 일입니다.</t>
         </is>
       </c>
       <c r="O389" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>thought</t>
         </is>
       </c>
       <c r="P389" t="inlineStr">
         <is>
-          <t>CG_Threshold_CalledEditorFalse</t>
+          <t>CG_Threshold_RitualNote</t>
         </is>
       </c>
     </row>
@@ -29831,66 +30204,41 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>10</v>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E390" t="inlineStr">
-        <is>
-          <t>Tense</t>
-        </is>
-      </c>
-      <c r="F390" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G390" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
+        <v>11</v>
       </c>
       <c r="N390" t="inlineStr">
         <is>
-          <t>의례실 바닥에서 주운 종이까지 여기로 이어집니다. 남은 건 문장으로 증명하는 일이 아니라, 저 안에서 실제로 끊어내는 일입니다.</t>
+          <t>병원, 폐공장, 자료실, 의례실에서 붙잡은 질문들이 이제야 한 줄로 선다. 끝내 다 푼 것은 아니어도, 무엇을 끊어야 하는지는 더 이상 흐리지 않다.</t>
         </is>
       </c>
       <c r="O390" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>narration</t>
         </is>
       </c>
       <c r="P390" t="inlineStr">
         <is>
-          <t>CG_Threshold_RitualNote</t>
+          <t>CG_Threshold_SolvedMid</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="B391" t="inlineStr">
         <is>
-          <t>ch6_threshold</t>
+          <t>scene_ending_erosion</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N391" t="inlineStr">
         <is>
-          <t>병원, 폐공장, 자료실, 의례실에서 붙잡은 질문들이 이제야 한 줄로 선다. 끝내 다 푼 것은 아니어도, 무엇을 끊어야 하는지는 더 이상 흐리지 않다.</t>
+          <t>낙원 안쪽 깊은 방에서 의식이 끝났다. 불꽃은 꺼졌지만 공기는 아직 뜨겁고, 유웅룡은 그 자리에 무릎을 꿇고 있었다.</t>
         </is>
       </c>
       <c r="O391" t="inlineStr">
         <is>
           <t>narration</t>
-        </is>
-      </c>
-      <c r="P391" t="inlineStr">
-        <is>
-          <t>CG_Threshold_SolvedMid</t>
         </is>
       </c>
     </row>
@@ -29901,16 +30249,36 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Tense</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="N392" t="inlineStr">
         <is>
-          <t>낙원 안쪽 깊은 방에서 의식이 끝났다. 불꽃은 꺼졌지만 공기는 아직 뜨겁고, 유웅룡은 그 자리에 무릎을 꿇고 있었다.</t>
+          <t>나는 더 이상 기록하지 않기로 한다. 이 사람들 곁에 남는 것이 내가 고른 길이다. 증거도, 기사도, 신용도 필요 없다.</t>
         </is>
       </c>
       <c r="O392" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>thought</t>
         </is>
       </c>
     </row>
@@ -29921,36 +30289,16 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>2</v>
-      </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E393" t="inlineStr">
-        <is>
-          <t>Tense</t>
-        </is>
-      </c>
-      <c r="F393" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G393" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="N393" t="inlineStr">
         <is>
-          <t>나는 더 이상 기록하지 않기로 한다. 이 사람들 곁에 남는 것이 내가 고른 길이다. 증거도, 기사도, 신용도 필요 없다.</t>
+          <t>기자 유웅룡은 그날 밤 사라졌다. 경성 어딘가에서 그를 봤다는 말이 돌았지만, 아무도 확인하지 않았다. 기사는 끝내 쓰이지 않았다.</t>
         </is>
       </c>
       <c r="O393" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
@@ -29961,11 +30309,11 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N394" t="inlineStr">
         <is>
-          <t>기자 유웅룡은 그날 밤 사라졌다. 경성 어딘가에서 그를 봤다는 말이 돌았지만, 아무도 확인하지 않았다. 기사는 끝내 쓰이지 않았다.</t>
+          <t>낙원은 여전히 그 자리에 있었다. 불빛도, 노래도, 사람들도.</t>
         </is>
       </c>
       <c r="O394" t="inlineStr">
@@ -29977,15 +30325,15 @@
     <row r="395">
       <c r="B395" t="inlineStr">
         <is>
-          <t>scene_ending_erosion</t>
+          <t>scene_gameover_credibility</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N395" t="inlineStr">
         <is>
-          <t>낙원은 여전히 그 자리에 있었다. 불빛도, 노래도, 사람들도.</t>
+          <t>기록은 남았지만 믿어 줄 사람은 없다. 기자로서의 발언권은 완전히 무너졌다.</t>
         </is>
       </c>
       <c r="O395" t="inlineStr">
@@ -30001,16 +30349,36 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Editor</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Angry</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
       </c>
       <c r="N396" t="inlineStr">
         <is>
-          <t>기록은 남았지만 믿어 줄 사람은 없다. 기자로서의 발언권은 완전히 무너졌다.</t>
+          <t>평판이 바닥이야. 네 기사는 더 이상 검토도 못 해. 아무도 이 신문에 실린 걸 믿지 않으니까.</t>
         </is>
       </c>
       <c r="O396" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -30021,21 +30389,21 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Editor</t>
+          <t>Yuu</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Tense</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
@@ -30045,12 +30413,12 @@
       </c>
       <c r="N397" t="inlineStr">
         <is>
-          <t>평판이 바닥이야. 네 기사는 더 이상 검토도 못 해. 아무도 이 신문에 실린 걸 믿지 않으니까.</t>
+          <t>이렇게 끝날 줄은 몰랐다. 증거보다 신뢰가 먼저라는 걸, 뒤늦게야 깨달았다.</t>
         </is>
       </c>
       <c r="O397" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>thought</t>
         </is>
       </c>
     </row>
@@ -30061,51 +30429,31 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>3</v>
-      </c>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E398" t="inlineStr">
-        <is>
-          <t>Tense</t>
-        </is>
-      </c>
-      <c r="F398" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="G398" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
+        <v>4</v>
       </c>
       <c r="N398" t="inlineStr">
         <is>
-          <t>이렇게 끝날 줄은 몰랐다. 증거보다 신뢰가 먼저라는 걸, 뒤늦게야 깨달았다.</t>
+          <t>유웅룡의 이름은 지면에서 사라졌다. 기사는 쓰이지 않았고, 사건은 묻혔다.</t>
         </is>
       </c>
       <c r="O398" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>narration</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="B399" t="inlineStr">
         <is>
-          <t>scene_gameover_credibility</t>
+          <t>scene_gameover_erosion</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N399" t="inlineStr">
         <is>
-          <t>유웅룡의 이름은 지면에서 사라졌다. 기사는 쓰이지 않았고, 사건은 묻혔다.</t>
+          <t>더는 기록과 현실의 경계를 붙들 수 없다. 의식은 끝내 사건 바깥으로 미끄러진다.</t>
         </is>
       </c>
       <c r="O399" t="inlineStr">
@@ -30121,16 +30469,31 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Yuu</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Shaken</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
       </c>
       <c r="N400" t="inlineStr">
         <is>
-          <t>더는 기록과 현실의 경계를 붙들 수 없다. 의식은 끝내 사건 바깥으로 미끄러진다.</t>
+          <t>적어야 할 것이 있었다. 분명히… 있었는데. 이름이 먼저였나, 날짜가 먼저였나.</t>
         </is>
       </c>
       <c r="O400" t="inlineStr">
         <is>
-          <t>narration</t>
+          <t>thought</t>
         </is>
       </c>
     </row>
@@ -30141,49 +30504,14 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>2</v>
-      </c>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>Yuu</t>
-        </is>
-      </c>
-      <c r="E401" t="inlineStr">
-        <is>
-          <t>Shaken</t>
-        </is>
-      </c>
-      <c r="F401" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="N401" t="inlineStr">
         <is>
-          <t>적어야 할 것이 있었다. 분명히… 있었는데. 이름이 먼저였나, 날짜가 먼저였나.</t>
+          <t>펜을 쥔 손은 그대로인데, 무엇을 적으려 했는지가 먼저 지워진다. 마지막까지 붙들던 이름 하나가, 젖은 잉크처럼 번져 사라진다.</t>
         </is>
       </c>
       <c r="O401" t="inlineStr">
-        <is>
-          <t>thought</t>
-        </is>
-      </c>
-    </row>
-    <row r="402">
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>scene_gameover_erosion</t>
-        </is>
-      </c>
-      <c r="C402" t="n">
-        <v>3</v>
-      </c>
-      <c r="N402" t="inlineStr">
-        <is>
-          <t>펜을 쥔 손은 그대로인데, 무엇을 적으려 했는지가 먼저 지워진다. 마지막까지 붙들던 이름 하나가, 젖은 잉크처럼 번져 사라진다.</t>
-        </is>
-      </c>
-      <c r="O402" t="inlineStr">
         <is>
           <t>narration</t>
         </is>
